--- a/qa/Feature-Tracker.xlsx
+++ b/qa/Feature-Tracker.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,7 +42,19 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="005A6774"/>
+      <color rgb="001E7F4F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00A06A14"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B3442E"/>
       <sz val="9"/>
     </font>
     <font>
@@ -60,7 +72,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +82,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F5FA8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F2EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7EEDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8E8E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -110,12 +137,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -603,12 +636,16 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Dropzone accept='.stl,.step,.stp,.iges,.igs'; drop fired POST /api/proxy/validate/cost + POST /api/proxy/validate?units=mm in parallel (&lt;3s apart, both 200). bad.txt -&gt; 'Unsupported file type' with zero validate requests; qty 'abc' -&gt; options panel opened with 'Fix the quantity list before submitting.' and no request. Routing-tab loading copy 'Analyzing across all manufacturing processes…' observed. Anonymous /analyze redirected to /login?next=%2Fanalyze.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -653,12 +690,16 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Five tabs (Decision|Routing &amp; DFM|Glass Box|Compare|History). /analyze lands on Routing &amp; DFM (mfg lens); switching to Cost eng landed on Glass Box and auto-opened the Inspector (default tab Sources); Sourcing landed on Compare. With no cost report (broken part) Glass Box showed 'No cost breakdown yet' and Compare 'Nothing to compare yet'. 'New part' reset to the cold-start dropzone.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -703,12 +744,16 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Selecting an OVERHANG issue row highlighted its faces ('shown in 3D' + 'Highlighting OVERHANG' note, severity-colored); clicking the DFM-matrix draft blocker selected/highlighted the injection-molding issue. Canvas face-click and the no-geometry-linked-faces toast were not deterministically exercisable on this part (every matrix blocker had geometry-linked issues); not observed to fail.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -753,12 +798,16 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/proxy/shops listed 2 profiles; picking 'Midwest Precision CNC' toasted 'Calibrating to Midwest Precision CNC…', re-ran POST /validate/cost and flipped the badge to 'Calibrated to'. Glass Box driver rate editor applied an override (toast 'Override … — re-costing', server re-cost, '1 override applied' chip); 'Reset overrides' re-cost + 'Cleared overrides' toast. 'Save as scenario' stored a session chip (shop · ovr · qty label); clicking the chip recalled options and re-cost. Scenarios cleared on reset.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -803,12 +852,16 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>qa-broken.stl: POST /validate/cost returned 400 GEOMETRY_INVALID; UI rendered the CostGeometryInvalidCard (repair reason + measured volume/watertight geometry) and a 'Geometry invalid' header badge — no generic error. Screenshot APP-005-geometry-invalid-card.png. Generic cost/DFM ErrorState retries and 429/5xx toasts could not be force-triggered in this environment (no fault injection); no deviation observed.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -853,12 +906,16 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Sub-plausible part (0.3mm cube) produced report.unit_warnings -&gt; persistent [data-testid=cad-unit-warning] banner ('Confirm CAD source units…' + IMPLAUSIBLE_VOLUME message). Setting units=inch and 'Re-cost with these inputs' re-ran BOTH /validate/cost and /validate; banner cleared. Inspector: Lineage/Governance/Sources/Audit tabs, defaults to Sources for cost role, collapsible; a driver override applied from the Inspector Sources tab triggered a real server re-cost.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -903,12 +960,16 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Empty state 'No history yet' with no report. With report: saved scenario chips recallable, 'Open cost history' navigated to /cost-decisions, 'Copy decision summary' wrote a plaintext make-by/crossover/DFM summary to the clipboard (verified content + 'Decision summary copied' toast). report.saved present -&gt; CostArtifactBar rendered ('Saved to cost history' with Open in history/PDF/JSON/CSV/RFQ ZIP/Share actions).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -953,12 +1014,16 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/proxy/analyses/{id} on mount; success rendered filename/STL/date header + full dashboard. Bogus ULID -&gt; 404 handled as 'Analysis not found' ErrorState with 'Back to history' link.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1003,12 +1068,16 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Share: POST /api/proxy/analyses/{id}/share -&gt; modal showing http://localhost:3000/s/&lt;token&gt;, 'Shared' badge + Copy link/Revoke. Revoke: DELETE same endpoint, returned to unshared 'Share' button.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1053,12 +1122,16 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/proxy/analyses/{id}/pdf downloaded 'qa-box-dfm-report.pdf' (valid %PDF, 29KB).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1103,12 +1176,16 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>'Attempt mesh repair' rendered on the NON_WATERTIGHT analysis (absent on clean ones); click opened a file picker, re-selecting qa-broken.stl POSTed /api/proxy/validate/repair; dashboard swapped for the RepairComparison ('Mesh repaired' Tier trimesh 10-&gt;12 faces, Original 'Not manufacturable' vs Repaired 'Issues found', download-repaired-file offer). Screenshot APP-011-repair-comparison.png.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1153,12 +1230,16 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>'Linked cost decisions' card listed the qa-box decisions (filename, mjf make-now, unreviewed) with 'Open decision' navigating to /cost-decisions/{id}; card absent on the broken analysis with no linked decision.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1203,12 +1284,16 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/proxy/analyses?limit=20; rows for all runs. Verdict select (All verdicts/Pass/Advisory/Required): choosing Required re-fetched with verdict=fail and showed only qa-broken.stl. Row click -&gt; /analyses/{ulid}. 'Load more'/500-cap counter and empty state not exercisable (4 rows, has_more=false); load-error retry not force-triggerable.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1253,12 +1338,16 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>QuotaDisplay rendered used/total progress bar from X-RateLimit headers with 'Resets in N min'.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1303,12 +1392,16 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>/cost (flag off) rendered the identical PartWorkspace cold-start dropzone; qa-part2.stl drop fired the same /validate/cost + /validate pair, landed on the Decision tab with 'Lens Design eng', 5 tabs, and persisted the decision (CostArtifactBar shown).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1353,12 +1446,16 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>NEXT_PUBLIC_STAGE_UI unset (default build): no DoorChooser rendered and no cv_door localStorage written — /cost behaves as APP-015, the documented flag-off expectation. Flag-on router not exercisable without a rebuild.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1403,12 +1500,16 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/proxy/cost-decisions?limit=20; columns File/Make now/Crossover/Quantities/Shared/Governance/When with Unreviewed badge and relative time; CostHonestyNote ('assumption-based, not yet validated') above the table; 'Compare decisions' routed to /cost-decisions/compare; row click -&gt; /cost-decisions/{id}; 'Shared' badge appeared for the shared decision. Pagination cap + empty state not exercisable (rows exist).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1453,12 +1554,16 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Detail GET on mount; header + 'Source SHA-256 · &lt;64-hex&gt;' mesh hash; exports: PDF 'qa-part2-cost-report.pdf' (54KB), JSON 'qa-part2-cost.json', CSV 'qa-part2-cost.csv'. Bogus id -&gt; 'Cost decision not found' ErrorState with 'Back to cost history'.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1503,12 +1608,16 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Approve with note POSTed /cost-decisions/{id}/approve: badge flipped to Approved with 'Signed off by user N on &lt;date&gt;' + approval-note card and 'Decision approved' toast; Reopen DELETEd the endpoint, badge back to Unreviewed. Stale warn card and read-only-role variant not exercisable (no stale data; analyst account).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1553,12 +1662,16 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>'Make outside' PUT /cost-decisions/{id}/disposition and rendered the recorded outcome + updated-by line; outcome note saved ('Outcome note saved' toast); changing outcome while approved reopened approval ('Outcome saved; prior approval reopened' toast, badge Unreviewed); withdraw cleared the outcome. 'Make in-house' enabled (route DFM clean on this part) — blocked/tooltip state and read-only variant not exercisable.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1603,12 +1716,16 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Share POST -&gt; modal with public URL http://localhost:3000/s/cost/&lt;token&gt;; DELETE revoked. 'RFQ ZIP' POSTed /rfq-packages with title 'RFQ package - qa-part2.stl', then downloaded /rfq-packages/{id}/download.zip as 'RFQ package - qa-part2-rfq.zip' (valid PK zip, 77KB) with 'RFQ package generated' toast.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1653,12 +1770,16 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>GET /cost-decisions?limit=100 filled both pickers; Compare disabled until two distinct ids; the id chosen on one side was disabled on the other; GET /cost-decisions/compare?ids=A,B rendered summary cards (make-now, crossover) and the per-quantity unit-cost table with cheaper side highlighted and signed Δ ($ and %). Fewer-than-2 empty state not exercisable (decisions exist). Screenshot APP-022-compare.png.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1703,12 +1824,16 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>bad.txt -&gt; toast 'Only .zip files are accepted' (no request). qa-batch.zip: staged upload copy observed ('Uploading ZIP directly…'), GET /uploads/capabilities + POST /api/proxy/batch fired, then auto-routed to /batch/{batch_id}. 5GB limit, CSV manifest, webhook, retry/failure-recovery states and double-submit lock not exercisable with a small local fixture (no deviation observed).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1753,12 +1878,16 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/proxy/batches?limit=20; row showed truncated ULID '01KZA3NDGYV1…', Completed badge, 2/2 items, created date; 'Download CSV' present only for the completed batch and fetched batch_&lt;ulid&gt;_results.csv (header filename,status,verdict,best_process,issue_count,duration_ms); row click -&gt; /batch/{ulid}. Cursor/empty/error states not exercisable.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1803,12 +1932,16 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Detail polled GET /api/proxy/batch/{id} (multiple polls, 5s interval) until 'completed'; items table (GET /batch/{id}/items) listed qa-box.stl/qa-part2.stl with statuses, verdicts, best process and 'View' links to created /analyses/{id}; 'Download CSV' appeared on completion and downloaded the results CSV.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1853,12 +1986,16 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Second batch (concurrency 1): 'Cancel batch' shown while non-terminal; AlertDialog 'Pending items will be skipped. This cannot be undone.'; confirm POSTed /batch/{id}/cancel, toasted 'Batch cancelled', items refreshed to Skipped (0/2, 2 skipped). Terminal Cancelled state hides the Cancel button and offers no CSV (verified on revisit; the in-page button clears on the next 5s poll). Screenshots APP-026-cancel-dialog.png / APP-026-cancelled-terminal.png.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1901,14 +2038,18 @@
           <t>UI+API</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Environment cannot produce a ready design: every generation fails in &lt;1s because the CAD kernel (gmsh) cannot load in this env - OSError libGLU.so.1 missing (confirmed by running src/designs/generator.py directly in the backend venv; arq worker uses the same venv). All reachable UI behavior verified and correct: template picker swaps fields (enclosure wall vs thickness, plate corner-hole options), POST /api/proxy/designs 200, list refresh while generating, failed generation renders the fail card with the engine error ('The CAD kernel could not generate this revision...') and 'Revise and retry' which enters revision mode. Viewer read-only card not tested (analyst account). Screenshots: app-027-created.png, app-027-fail-card.png</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1953,12 +2094,16 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Empty description shows 'Describe the starting shape and its dimensions first.'; 'Interpret safely' POSTed /api/proxy/designs/interpret 200 for '80 x 50 x 6 mm plate with four 6 mm corner holes' and prefilled the whole form (width=80, thickness=6, corner holes) with a green ready message + assumptions. No console errors.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2001,14 +2146,18 @@
           <t>UI+API</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Requires a ready revision (preview.stl, geometry hash, STEP download, verify link) but no revision can reach 'ready' in this env - design generation always fails because gmsh cannot load (libGLU.so.1 missing OS library). POST /designs/{id}/revisions itself works (revision rows are created and marked failed by the worker); preview/STEP/verify links are null on failed revisions as designed.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2053,12 +2202,16 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Trash icon opened window.confirm 'Archive “QA plate design”? Its audit evidence will be retained.' (typographic quotes); confirm fired DELETE /api/proxy/designs/{id} 200 and the card left the list. Screenshot app-030-archived.png</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2101,14 +2254,18 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>This build has dev tools ON (NEXT_PUBLIC_SHOW_DEV_TOOLS -&gt; DEV_TOOLS_ENV=true) and backend LABELING_ENABLED=1, so /label renders the labeling tool - the story's disabled EmptyState branch cannot render locally. Verified the enabled branch is honest (tool + corpus requests only, no errors).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2153,12 +2310,16 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Gate open locally. Page fired GET /api/proxy/corpus/parts?unlabeled_only=true&amp;limit=200&amp;labeler=... (200) and GET /api/proxy/corpus/progress?labeler=... (200). Corpus is empty in this env (no data/demo-parts seed dir), and the documented empty state 'No parts in the corpus queue' renders. Labeling interactions (mesh view, ontology hotkeys, POST /corpus/labels, skip/navigation) unreachable with zero parts - not exercised. Screenshot app-032-label-empty.png</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2203,12 +2364,16 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/proxy/reconstruct/capability 200 on mount; available:false (backend reconstruction backend 'none') renders 'Image-to-3D is not enabled' with the backend message, the assurance that no image was sent anywhere, and a 'Verify CAD instead' button. No console errors. Screenshot app-033-reconstruct.png</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2251,14 +2416,18 @@
           <t>UI+API</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Reconstruction capability is disabled locally (/health reports reconstruction.available=false, backend 'none'); the uploader/submit step is unreachable behind the honest disabled state verified in APP-033.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2301,14 +2470,18 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Same as APP-034: no reconstruction job can be created locally, so the mesh preview/confidence/hand-off step is unreachable.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2353,12 +2526,16 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>GET connectors + GET runs?limit=25 both 200 on load; connector cards show source system/kind, raw-stored and live-creds flags. Run disabled without a file. Dry-run of a 2-row SAP manifest CSV (columns from /api/proxy/manifest/import/template) POSTed multipart /api/proxy/integrations/runs 200, toasted 'Dry-run recorded', and prepended a row with status, 2/2 valid rows, dry_run mode, SHA-256 prefix and completion time. Screenshot app-036-integrations.png</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2403,12 +2580,16 @@
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Generated real notifications via API (governance change request -&gt; 'Governed change awaiting review', plus decision.created). Both GETs (dismissed=false/true) 200 populate Inbox/Dismissed; 'Mark all read' POSTed /notifications/read-all and stamped every row read; 'Open' POSTed /notifications/{id}/read then navigated to the mapped Verify destination (/verify?pane=calibration). Empty-inbox copy 'You're all caught up.' also observed pre-seed. Screenshot app-037-notifications-retest.png</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2453,12 +2634,16 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Dismiss POSTed /notifications/{id}/dismiss and moved the row to Dismissed with timestamp; Restore POSTed /notifications/{id}/restore and returned it to the inbox with its prior read state. Copy states dismissal changes only the user's inbox. No console errors. Screenshot app-038-dismiss-restore.png</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2503,12 +2688,16 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Loads GET /rfq-packages?limit=50 and GET /cost-decisions?limit=100 in parallel (both 200). Generate disabled at 0 selected; selecting an unapproved decision showed the amber 'package will preserve those warnings' banner; POST /rfq-packages 200 created 'QA RFQ Package' from the saved cost decision (created earlier via POST /api/proxy/validate/cost with qa-box.stl) and prepended it with a success toast. Screenshot app-039-rfq-create.png</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2553,12 +2742,16 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Row shows title/supplier ('supplier not specified'), 0/1 approved, amber warnings count (2), creation date; empty state 'No RFQ packages yet.' verified before first package. ZIP button fetched GET /rfq-packages/{id}/download.zip 200 application/zip; archive verified valid via direct authenticated download (package_manifest.json, line-items.csv, supplier-brief.pdf, per-decision folders). Screenshot app-040-rfq-list.png</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2603,12 +2796,16 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Title click -&gt; /rfq-packages/{id}; GET detail 200; stat cards (Approved 0/1, Stale, Unvalidated, Raw CAD), warnings card with code+message for the unapproved decision, items table with per-decision flags and a link to /cost-decisions/{id}; Download ZIP fetched the bundle (200). Bogus id renders 'RFQ package not found.' with Back. Screenshots app-041-rfq-detail.png, app-041-rfq-notfound.png</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2653,12 +2850,16 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>GET /onboarding returns 307 with Location http://localhost:3000/verify?welcome=1 (verified at HTTP level); browser lands on the Verify welcome flow (the verify client then consumes/strips the welcome param). No standalone UI rendered.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2703,12 +2904,16 @@
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Fresh account showed 'No API keys yet' with Create key. Create POST /api/proxy/keys 200 -&gt; table row with masked cv_live_&lt;prefix&gt;_… and Active badge; Rotate POST /keys/{id}/rotate 200 revealed a NEW secret; Revoke DELETE /keys/{id} 200 -&gt; 'Revoked' badge and action buttons removed. Success toasts observed; no console errors. Screenshot app-043-keys.png</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2753,12 +2958,16 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>RevealOnceModal opened after create and rotate showing the full cv_live_ token with Copy + 'I've saved it somewhere safe' acknowledge; cv_mint_once cookie was already scrubbed while the modal was open (document.cookie clean) and a page reload did not re-reveal. Page links to /api-reference and /scalar present.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2803,12 +3012,16 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>As org admin the full surface renders with the org switcher. Invited a second account as 'member', accepted the invite, and switched that account's active org to the inviting org via the switcher: page re-rendered with ONLY the switcher and the 'Admins only' EmptyState naming the actual role ("You're a member of qa-app2's Organization...") - no admin sections (screenshot app-045-member-gate2.png; an earlier text-race in my script produced a false mixed reading, screenshot is authoritative). Switch persisted (active org echoed in switcher).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2853,12 +3066,16 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>InviteForm POST created a pending invite and displayed the one-time accept link (email not configured locally); the invitee accepted via the link and appeared in the members table, invite badge flipped to accepted; admin removed the member successfully. A second invite was revoked via the confirm dialog (badge revoked). Last-admin protection surfaced verbatim on self-remove: 'Cannot remove the last admin - an org must keep at least one.'</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2903,12 +3120,16 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Mapping CRUD: add (groups/qa-admins/member) listed the row; duplicate add surfaced the backend error 'A SAML group mapping for this org, attribute, and value already exists.'; delete removed it. Read-only SSO panel shows honest states (SAML SP metadata: 'Not enabled in this deployment' in this deployment) plus exact ACS/metadata/login/OIDC callback/SCIM URLs with contextual hints.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2953,12 +3174,16 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Ops health card rendered from backend /health/deep: Postgres and Redis healthy, worker heartbeat ok, queue depth shown. Unreachable/degraded fail-card branch not exercised (backend healthy in this env). Screenshot app-045-048-org.png</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3003,12 +3228,16 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>AUTH_MODE defaults to password locally so the form renders. Client-side: sub-8-char input is stopped by the native minLength constraint before submit; 8+ chars without a digit shows 'Password must contain a digit.' and mismatch shows 'Passwords do not match.' - neither fires a network request. Valid submit POSTed /api/auth/password/initialize which returned 409 'A password is already configured for this account.' for this password-signup account, rendered verbatim as the inline error - honest handling (the only console entry is the browser's automatic 409 resource log).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3053,12 +3282,16 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Static showcase rendered (foundations, provenance chips, confidence, driver breakdowns, routing, DFM sections) with the interactive RoleLens ('Lens: Cost eng' etc.) and theme toggle (html theme attribute flips, page re-renders dark/light); zero /api/proxy data calls issued and no console/page errors. The 'object.stl' fixture name is not printed in the DOM verbatim - fixture data is hard-coded per evidence. Screenshot app-050-design-system.png</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3103,12 +3336,16 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Wrong password shows "Invalid email or password." under the password field; correct login navigates to /verify (default next).</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3153,12 +3390,16 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>MAGIC_LINK_UI_ENABLED and TURNSTILE_SITE_KEY are unset in the running frontend env; the magic-link section is correctly absent per the documented gating. Turnstile/submit-disable behavior not exercisable locally.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3203,12 +3444,16 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>SSO_LOGIN_PATH unset: SSO anchor and divider correctly absent; password enabled so footer correctly shows the "Create an account" signup link instead of the managed-access note.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3253,12 +3498,16 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Local gating correct (password signup form renders). Client validation (&gt;=8 chars, letter+digit) blocks the POST with the exact messages. Valid signup POSTs /api/auth/signup (200) and navigates to /onboarding, which server-redirects to /verify?welcome=1 (expected app behavior: onboarding is a redirect page).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3303,12 +3552,16 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="3" t="inlineStr"/>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Static confirmation page, no account enumeration.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3353,12 +3606,16 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>No token -&gt; "This sign-in link is missing or malformed." with Request-a-new-link -&gt; /login. #token= fragment is immediately scrubbed to /magic/verify (history.replaceState) and held in memory; clicking Continue POSTs /api/auth/magic/exchange and a bogus token renders the error alert.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3403,12 +3660,16 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Invite created via POST /api/proxy/orgs/invites as qa-tester (org admin, role viewer). Unauthenticated open shows the log-in-as-invited-account state with next-return login link; after logging in as the invitee the token redeems ("joined the organization as viewer") with Open ProofShape link; missing token shows "Invite token missing."</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3453,12 +3714,16 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>ZIP upload -&gt; 202 {batch_id,status,status_url:/api/v1/batch/{ulid}}; items extracted+processed by arq (batch completed, 2 items). No input -&gt; 400 BATCH_INPUT_REQUIRED; file+direct_upload_id -&gt; 400 BATCH_INPUT_CONFLICT. webhook_secret never echoed (response carries only batch_id/status/status_url).</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3503,12 +3768,16 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="3" t="inlineStr"/>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>s3_bucket present -&gt; 501 {code:S3_INPUT_UNSUPPORTED, doc_url}; no Batch row created (list unchanged).</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3553,12 +3822,16 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>job_type=weird -&gt; 422 INVALID_JOB_TYPE naming valid set. job_type=cost with bad manifest (quantities='abc') -&gt; 400 INVALID_COST_MANIFEST 'Row 2: invalid quantity'. BATCH_COST_ENABLED is on (default): valid cost batch accepted 202 and completed; the 501 BATCH_COST_NOT_ENABLED flag-off path not exercisable without env change (notes-only).</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3601,14 +3874,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>TESTED-FAIL</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Bad archive returns 500 instead of 400: POST /api/v1/batch with a non-ZIP payload named .zip (STL bytes, application/zip) -&gt; HTTP 500 'Internal Server Error' (reproduced twice). Cause: batch_service.extract_zip_path_to_items opens zipfile.ZipFile which raises zipfile.BadZipFile; batch_router.py only catches ValueError around extraction, so BadZipFile escapes as an unhandled 500. Expected 400 per story.</t>
+        </is>
+      </c>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Other guards pass: concurrency_limit=99 -&gt; 422 INVALID_BATCH_CONCURRENCY (min/max in body); webhook_url=169.254.169.254 -&gt; 400 webhook_url_rejected (SSRF); no orphaned batch left after the 500 (list shows only legit batches). Size caps (413 zip/manifest) verified in code only per briefing (declared Content-Length check exists at batch_router.py:230-247); not exercised with real GB uploads.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3651,14 +3932,18 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Direct upload requires S3 and is honestly disabled locally: GET /api/v1/uploads/capabilities -&gt; available:false, unavailable_code:DIRECT_UPLOAD_REQUIRES_S3. Unknown direct_upload_id -&gt; clean 404 DIRECT_UPLOAD_NOT_FOUND. Attach/idempotent-recovery/queue-outage (503 BATCH_ENQUEUE_FAILED) paths not exercisable in this environment.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3703,12 +3988,16 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="3" t="inlineStr"/>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Newest-first with per-batch completed/failed/skipped counts, next_cursor, has_more; other-org key sees empty list (no leak); limit=500 -&gt; 422 le=100 validation.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3753,12 +4042,16 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Progress returns durable counters (total/completed/failed/skipped/pending). Other-org and unknown batch both -&gt; 404 (never 403). Items return filename, status, analysis_id/url, verdict/best_process/issue_count, error_message, duration_ms; status=failed filter works; cursor fields present.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3803,12 +4096,16 @@
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Completed batch -&gt; 200 text/csv, Content-Disposition attachment filename=batch_{id}_results.csv with DFM columns. Pending batch -&gt; 400 'Batch not yet completed (status: pending)'. Other-org -&gt; 404.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3853,12 +4150,16 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="3" t="inlineStr"/>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Cancel pending batch -&gt; 200 {batch_id,status:cancelled}, completed_at stamped, both items terminalized to skipped (pending_items:0). Re-cancel -&gt; 409 'already in terminal state: cancelled'; cancel of completed batch -&gt; 409; other-org cancel -&gt; 404.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3903,12 +4204,16 @@
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="3" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>LABELING_ENABLED=1: routes exist and are deliberately unauthenticated. Corpus root empty -&gt; honest empty behavior: list {total:0, offset, limit, labeled:0, unlabeled:0, parts:[]}; unlabeled_only accepted; unknown part_id -&gt; 404 'part_id not in manifest'. Per-part label overlay/mesh_url untestable with an empty manifest (noted).</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3951,14 +4256,18 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="3" t="inlineStr"/>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>No manifest parts exist, so the positive FileResponse/ETag path cannot be exercised. Verified 404 for unknown part_id and for traversal attempt (..%2F..%2Fetc%2Fpasswd) -&gt; 404.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4001,14 +4310,18 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>Label POST needs a manifest part; corpus manifest is empty. Verified part_id-not-in-manifest -&gt; 404 (this check precedes label-ontology validation, so the 422 path is also unreachable without a part).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4053,12 +4366,16 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="3" t="inlineStr"/>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Progress returns total_parts/labeled/unlabeled, per_label_counts zero-filled across all 6 ontology keys, per_guess_counts, sorted labelers[]; ?labeler=alice accepted.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4103,12 +4420,16 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="3" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>List returns org-scoped (project, current revision) pairs; other-org key sees empty list and gets 404 on my design id; unknown design -&gt; 404.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4153,12 +4474,16 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="3" t="inlineStr"/>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>Valid plate plan -&gt; 202 with serialized design (status generating, revision queued), job_id, poll_url. Extra body field -&gt; 422 (extra='forbid'). NOTE (environmental, not app): generation later fails honestly with DESIGN_GENERATION_FAILED because gmsh cannot load (libGLU.so.1 missing in this container); failure copy/error code surfaced correctly on poll. 403 no-org path untestable (signup always creates an org).</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4203,12 +4528,16 @@
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>Prompt '60x40 mm plate 5mm thick with two 6mm holes' -&gt; 200 structured interpreter output (needs_input with kind=plate, prefill dims, missing hole_diameter_mm) with no DB write; empty prompt -&gt; 422.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4253,12 +4582,16 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>Revision create -&gt; 202 with new revision + job_id; POST while revision 1 still generating -&gt; 409 (verified on a fresh design). Revision list returns current_revision + all revisions with per-revision error objects; revisions/0 and /99 -&gt; 404.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4303,12 +4636,16 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="3" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>Archive while generating -&gt; 409 'A generating design cannot be archived'; after terminal revision -&gt; 204; unknown and other-org design -&gt; 404. Re-archiving an archived design returns 204 (idempotent) - not contradicted by the documented expected.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4351,14 +4688,18 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>Artifacts can never reach 'ready' in this environment: gmsh import fails (OSError libGLU.so.1 missing), so every revision ends failed - environmental, not an app bug. Verified: not-ready revision -&gt; 409 'Design artifact is not ready' for preview.stl and download.step; unknown design -&gt; 404. X-Geometry-SHA256/streaming/410 paths untestable.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4403,12 +4744,16 @@
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>Catalog returns 5 static connectors: 3 offline_csv (configured:true) + 2 sandbox_api (configured:false, live_credentials_required:true) with id/mode/boundary_label/description metadata; no org data.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4453,12 +4798,16 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>POST (secret as object) -&gt; 201 with serialized profile; raw secret never echoed - only secret_fingerprint (hmac_sha256). String secret -&gt; 422 validation. GET lists org profiles with connector_id filter.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4503,12 +4852,16 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>Detail 200 org-scoped; other-org key -&gt; 404. Probe -&gt; 200 probe object (read_only:true, mode sandbox_api, fingerprint; no live write). DELETE -&gt; 200 serialized profile with revoked_at set and configured:false.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4553,12 +4906,16 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="3" t="inlineStr"/>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>ground_truth_csv dry_run -&gt; run status passed, rows_valid=2, imported_count=0, raw_stored:false, file hashed+counted. mode=import -&gt; imported_count=2. mode=yolo -&gt; 400; unknown connector -&gt; 404; empty file -&gt; 400; non-UTF-8 -&gt; 400. 413 &gt;10MB cap notes-only (code-verified cap read via _import_cap_bytes).</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4603,12 +4960,16 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="3" t="inlineStr"/>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>List cursor-paginated with connector_id+status filters; status=bogus -&gt; 400 'invalid integration run status'; detail 200 own org, other-org run -&gt; 404.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4653,12 +5014,16 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="3" t="inlineStr"/>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>Created from one saved cost decision (POST /validate/cost on qa-box.stl -&gt; saved.id) -&gt; 201 package with items, honest warnings (decision_unapproved, confidence_unvalidated), raw_cad_included:false, live_supplier_send:false. Empty decision_ids -&gt; 400; unknown decision -&gt; 404; other-org decision -&gt; 404.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4703,12 +5068,16 @@
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>List returns org-scoped packages; detail 200 with items; other-org and unknown package -&gt; 404 'RFQ package not found.'</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4753,12 +5122,16 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="3" t="inlineStr"/>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>download.zip -&gt; 200 application/zip, Content-Disposition 'QA_RFQ_Package-{ulid}.zip' (sanitized title). Valid ZIP containing package_manifest.json, line-items.csv, supplier-brief.md/pdf, cost-decisions.json, per-decision evidence + raw-cad-unavailable.txt. Other-org -&gt; 404.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4803,12 +5176,16 @@
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>200 {available:false, can_submit:true (analyst), effective_backend:none, customer_data_egress:false, requires_egress_acknowledgement:false} with honest human message, accuracy_notice (estimate, not authoritative CAD), verify_path fallback.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4853,12 +5230,16 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="3" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>Submit with image + ULID Idempotency-Key -&gt; 501 RECONSTRUCTION_UNAVAILABLE with explicit copy about no local model and remote-egress opt-in flags (EXPECTED default). 428/400/409/503/202 paths require an enabled backend - untestable here.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4901,14 +5282,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr"/>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>TESTED-FAIL</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>Malformed job_id crashes with 500: GET /api/v1/reconstructions/01JUNKNOWNULIDAAAAAAAAAAAA/mesh.stl (26 chars but invalid Crockford ULID) -&gt; HTTP 500 'Internal Server Error'. Cause: reconstruction_service._validate_ulid raises ValueError which reconstruct_router.download_reconstruction_mesh does not catch. Expected 404 for any unknown job per story.</t>
+        </is>
+      </c>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="3" t="inlineStr"/>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>Well-formed unknown ULID -&gt; 404 'Mesh not found or job not complete' correctly. Success/ownership-positive path untestable (no reconstruction backend).</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4951,14 +5340,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
-        </is>
-      </c>
-      <c r="J89" s="3" t="inlineStr"/>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>TESTED-FAIL</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Invalid payload returns 422, documented expected is 400: POST /api/v1/ground-truth with actual_unit_cost_usd=-2 -&gt; 422 VALIDATION_ERROR (pydantic gt=0), and empty part_id -&gt; 422 (min_length). Story (and route docstring) promise 'a non-positive cost / empty part_id is a clean 400'; the service-level ValueError-&gt;400 path is unreachable for these named cases. Minor status-code deviation; no crash.</t>
+        </is>
+      </c>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="3" t="inlineStr"/>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>All other assertions pass: create 200 org-stamped; source_type=synthetic forced stand_in with source rewritten '[STAND-IN - not real]' even when stand_in:false sent; last-write-wins dedup on (part_id,process,quantity,shop) verified (new id, old id 404s, cost updated); reads viewer org-scoped; other-org detail -&gt; 404.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5003,12 +5400,16 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="3" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>With 3 real records: 422 honest refusal naming n_real:3, n_records:4 (stand-ins excluded), min_real:8, with clear copy that synthetic records never count. EXPECTED honest gate.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5053,12 +5454,16 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="3" t="inlineStr"/>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>Template -&gt; plain-text CSV header + example row. Import: multipart AND raw text/csv body both work; mixed file (1 good, 1 bad quantity) -&gt; 200 {imported:1, skipped:1, total:2, errors:[{line:3, reason:'quantity not an integer'}]} - honest partial success, no coercion; empty body -&gt; 400. 413 &gt;10MB streamed cap notes-only.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5103,12 +5508,16 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="3" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>GET /metrics unauthenticated -&gt; 200 text/plain; version=0.0.4 with HTTP counters/histograms, cadverify_jobs_current / batches_current / batch_items / webhook gauges, cadverify_async_worker_up. METRICS_ENABLED=0 and missing-prometheus-client paths not exercisable without env changes (notes-only).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5153,12 +5562,16 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>Labels are route templates (e.g. /api/v1/batch/{batch_id}/cancel) - scrape contains zero raw ULIDs after many ULID-addressed requests (grep '01KZA2' = 0). Unmatched requests collapse to __unmatched__; cost_decisions_total clamped to outcome=ok; status gauges bucketed to fixed sets with 'other' overflow bucket present.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5203,12 +5616,16 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="3" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>page_size=500 -&gt; 422 (cap&lt;=100: {"code":"VALIDATION_ERROR","message":"[{'type': 'less_than_equal', 'loc': ('quer); cross-org: other-org catalog empty verified</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5253,12 +5670,16 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>keyset keys=['next_cursor', 'rows']; cold_projection=None truncated=None nrows=2</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5303,12 +5724,16 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="3" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>portfolio keys=['rows', 'summary']</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5353,12 +5778,16 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="3" t="inlineStr"/>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>triage keys=['by_process', 'summary']; body={"summary": {"total": 2, "analyzed": 0, "makeable": 0, "needs_review": 0, "unknown": 2, "truncated": false}, "by_process": [{"process": "mjf", "label": "MJF 3D Printing", "count": 2}]}</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5403,12 +5832,16 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="3" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>makeability keys=['buckets', 'evaluation_note', 'summary']; body={"summary": {"makeable_in_house": 0, "makeable_outside": 0, "needs_capability": 0, "not_makeable": 0, "unknown": 2, "geometry_invalid": 0, "total": 2, "stale_count": 0, "stale": false, "truncated": false}, "buckets": ["makeable_in_house", "makeable_outside", "needs_capability", "not_makeable", "unknown", "geometry_invalid"], "evaluation_note": "No parts have been evaluated against a declared machine inventory \u2014 in-house makeability is 'unknown'. Declare machines and (re-)cost parts to popul; invalid-bucket detail: {"code": "BAD_REQUEST", "message": "invalid bucket: expected one of makeable_in_house, makeable_outside, needs_capability, not_makeable, unknown, geometry_invalid", "doc_url": "http://localhost:3000/d; could not find valid bucket name to drill (tried None, makeable_now, makeable, blocked)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5453,12 +5886,16 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="3" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>keys=['basis_note', 'note', 'ranking', 'summary']; body={"ranking": [], "summary": {"acquisitions": 0, "parts_unlockable_by_one_acquisition": 0, "blocked_by_multiple_constraints": 0, "total_blocked": 0, "stale": false, "truncated": false}, "basis_note": "Ranking counts parts whose SINGLE binding constraint one acquisition closes, computed only from stored gap data. Parts blocked by multiple constraints are reported in blocked_by_multiple_constraints and never folded in. No acquisition dollar cost is shown \u2014 none is available from engine data (ne</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5503,12 +5940,16 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="3" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>cross-org: foreign decision detail verified</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -5553,12 +5994,16 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="3" t="inlineStr"/>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>compare keys=['a', 'b', 'diff', 'unit_cost_by_qty', 'unit_costs_by_process']; body={"a": {"id": "01KZA2CSJQJ4W4B2QXX1D68D92", "filename": "qa-box.stl", "label": null, "make_now_process": "mjf", "make_now_material": "PP (Polypropylene)", "tooling_process": "injection_molding", "crossover_qty": 2815.0, "material_class": "polymer", "created_at": "2026-08-05T22:58:34.159669+00:00"}, "; cross-org: foreign compare verified</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5601,14 +6046,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr"/>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>TESTED-FAIL</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>note&gt;1000 chars: documented expected=400, actual=422 (router Field(max_length=1000) rejects with 422 before the service 400 at cost_decision_service.py:506-509 can fire)</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="3" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>invalid disposition -&gt; 422 (422 via Literal, documented); inhouse -&gt; 200; DFM-blocked 409 path not triggerable with clean fixture</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5653,12 +6106,16 @@
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>long approve note -&gt; 422 (validation reject; expected col makes no status claim)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5703,12 +6160,16 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="3" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>pdf 53591 bytes, disposition=attachment; filename="qa-box-cost-report.pdf"</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5753,7 +6214,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr"/>
@@ -5803,12 +6264,16 @@
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="3" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>share resp={"share_url": "/s/cost/XBQ5xzjPbb4C", "share_short_id": "XBQ5xzjPbb4C"}</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5853,7 +6318,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr"/>
@@ -5901,14 +6366,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I108" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
-        </is>
-      </c>
-      <c r="J108" s="3" t="inlineStr"/>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>TESTED-FAIL</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>Template example row is malformed: header is process,name,... but the example row is 'Haas VF-2 #1,cnc_3axis,...' (name/process swapped), and the capabilities JSON is not CSV-quoted (inner quotes not doubled) so csv parsing shatters the row. Importing the template endpoint output verbatim into POST /machine-inventory/import fails its own contract: 200 {imported:0, skipped:1, errors:[{line:2, reason: capabilities is not valid JSON}]} (machine_inventory_service._example_row)</t>
+        </is>
+      </c>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="3" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>Header itself is correct and complete (process + all 9 optional columns); catalog returns provenance=catalog_template entries and passed</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5953,12 +6426,16 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="3" t="inlineStr"/>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>initial={"ops": {}, "provenance": "user", "updated_at": null}</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6003,12 +6480,16 @@
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="3" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>summary={"imported": 1, "skipped": 1, "total": 2, "errors": [{"line": 3, "reason": "count not an integer ('abc')"}]}</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6053,12 +6534,16 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="3" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>machine keys=['capabilities', 'capital_frac', 'count', 'created_at', 'hourly_rate_usd', 'id', 'material_thickness_map', 'materials', 'max_workpiece_kg', 'name', 'notes', 'process', 'provenance', 'updated_at']; id=01KZA2RT5CQ22MHCMAJT295EZE</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6103,7 +6588,7 @@
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr"/>
@@ -6153,12 +6638,16 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="3" t="inlineStr"/>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>cross-org: foreign material version verified</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6203,12 +6692,16 @@
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="3" t="inlineStr"/>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>pre-publish effective={"flag_enabled": false, "using_governed": false, "source": "base_rate_table_material_prices", "provenance": "default", "validated": false, "payload": null}; post-publish effective: flag=False using_governed=False source=base_rate_table_material_prices</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6253,12 +6746,16 @@
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="3" t="inlineStr"/>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>draft keys=['change_note', 'created_at', 'created_by', 'effective_from', 'effective_to', 'id', 'name', 'payload', 'provenance', 'published_at', 'status', 'ulid', 'validated', 'version']</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6303,7 +6800,7 @@
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr"/>
@@ -6353,12 +6850,16 @@
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="3" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>published v1: status=published effective_from=2026-08-05T23:06:05.347371+00:00; decision stale_reason=material_library_published:v1 stale_at=2026-08-05T23:06:05.347371+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6403,12 +6904,16 @@
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="3" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>initial empty-versions list + flag_enabled verified in earlier run before drafts existed; post-publish: flag=True governed=True source=governed_rate_card</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6453,12 +6958,16 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="3" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>create-default-draft (200, payload seeded from default table), copy via from_version_id, and draft discard all verified in earlier run</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6503,12 +7012,16 @@
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="3" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>diff={"changed": [{"path": "global.labor_rate", "from": 70.0, "to": 35.0}], "added": [], "removed": []}; cross-org: foreign rate diff verified</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6553,12 +7066,16 @@
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="3" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>publish/409/400/timeline-close verified; fresh decision marked stale with reason=rate_library_published:v4; already-stale decisions keep first reason by design (stale_at IS NULL filter, cost_decision_service.py:593)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -6603,7 +7120,7 @@
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr"/>
@@ -6653,12 +7170,16 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr"/>
       <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="3" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>full lifecycle verified (draft/edit/400 invalid/publish/409s/archive rules); fresh decision marked stale with reason=shop_profile_published:qa-shop:v4; already-stale decisions keep first reason by design</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -6703,12 +7224,16 @@
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="3" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>cross-org: foreign part-context verified</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -6753,12 +7278,16 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="3" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>declare keys=['annual_volume', 'mesh_hash', 'parent_assembly', 'portfolio_delta', 'program', 'provenance', 'units_per_parent']; portfolio row match=True; portfolio context_note=Annualized $/year figures are derived from USER-DECLARED annual volumes (provenance: user); parts without a declared volume show null, never a fabricated demand quantity.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -6801,14 +7330,18 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="3" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>Core behavior (persist real STEP/IGES edge tree) not exercisable: server returns honest 501 NOT_IMPLEMENTED 'STEP/IGES parsing is unavailable on this server (gmsh not installed)' for any STEP upload (health also reports reconstruction unavailable). Pre-extraction guard verified: empty upload -&gt; 400 (expected 400). Auth/kill-switch/org gates shared with other BOM routes verified there.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -6853,12 +7386,16 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr"/>
       <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="3" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>onboard={"assembly_key": "qa-vehicle", "edges": 4, "roots": ["vehicle"], "source": "bom_csv", "skipped": 1, "errors": [{"line": 6, "reason": "qty_per_parent must be &gt; 0 (got -3)"}]}</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6903,12 +7440,16 @@
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="3" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>ancestry={"assembly_key": "qa-vehicle", "child_ref": "handle", "has_tree": true, "ancestry": ["handle", "door-assembly", "vehicle"], "ancestry_paths": [["handle", "door-assembly", "vehicle"], ["handle", "trunk-assembly", "vehicle"]], "rolled_up_multiplier": 9, "roots": ["vehicle"]}; cross-org: foreign bom tree invisible (empty edges) verified</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6953,12 +7494,16 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="3" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>summary={"imported": 2, "updated": 0, "skipped": 1, "total": 3, "errors": [{"line": 4, "reason": "missing part_id"}]}; re-import summary={"imported": 0, "updated": 1, "skipped": 0, "total": 1, "errors": []}</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7003,12 +7548,16 @@
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="3" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>with_geometry counts only /validate-uploaded analyses by normalized stem; verified 0 before upload, 1 after uploading qa-box.stl analysis; cross-org: other-org manifest empty verified</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7053,12 +7602,16 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>Verified: 401 no key, 403 viewer key, 200 with geometry summary (8v/12f, bbox 40x30x10, watertight), 21 ranked process_scores with standards citations, best_process + exact 'geometry-manufacturability; material not declared' basis label, priority_fixes/segments/features/universal_issues; ?include_thickness=true adds wall_thickness_map; ?units=inch scales bbox x25.4 exactly once (1016x762x254); 400s for unknown rule_pack (lists 4 packs), unknown units, bad magic (qa-fake.stl rejected as too-small STL), unsupported suffix .xyz, empty file; 501 NOT_IMPLEMENTED for STEP (gmsh not installed, honest). Persistence confirmed: rows appear in GET /api/v1/analyses. Untested (budget/env): 413 &gt;100MB, 504 timeout, mesh-hash dedup, usage_event row.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7103,12 +7656,16 @@
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="3" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>202 with analysis_id, job_id (ULID), poll_url /api/v1/jobs/{ulid}, and immediate synchronous result. Job later reachable and completed (status 'partial', sam3d heuristic_fallback). 503 SAM3D_ENQUEUE_FAILED path untestable (Redis healthy).</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7153,12 +7710,16 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="3" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>401/403 verified. STL: 200 model/gltf-binary ('glTF' magic) with X-Mesh-Original-Faces:12, X-Mesh-Preview-Faces:12, X-Mesh-Decimated:false, X-Mesh-Source:stl, Cache-Control:no-store. 400 bad file. STEP: honest 501 NOT_IMPLEMENTED (gmsh not installed) as documented. Untested: decimation &gt;50k faces, 120/hr;1000/day 429, 413, single-flight cache.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7203,12 +7764,16 @@
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="3" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>401 verified. 400 native CAD (.SLDASM) with specific export-to-STEP message; 400 non-STEP suffix (.stl) with allowed-suffix list; format=analysis validates material_class first (400 listing 5 classes) before parsing. STEP parse paths return honest 501 (gmsh not installed), so 200 json/glb/analysis outputs untestable in this environment. Nothing persisted (no new /analyses rows from these calls).</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7253,12 +7818,16 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="3" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>401/403 verified; 200 returns quick result {filename, verdict:pass, geometry, issues:[]} with no per-process scores; 400 bad file. 413 untested (budget).</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7303,12 +7872,16 @@
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="3" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>No auth needed. 200 with demo:true and same shape as /validate incl. wall_thickness_map via include_thickness. 400 bad magic. Verified 413 (not 400) FILE_TOO_LARGE for exact-length binary STL declaring 500,001 triangles ('exceeds DEMO_MAX_TRIANGLES limit of 500,000'). No-persistence and 10/hr 429 untested (kept to 4 demo calls); 504 untested.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -7353,12 +7926,16 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="3" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>401/403 verified. 200 decision dict with estimates (unit/fixed/variable/confidence bands), assumptions/drivers with DEFAULT provenance, identity block (org-corpus retrieval suggestion with honest caveats), saved:{id,url:/api/v1/cost-decisions/...} persisted (later visible as decision_link on analysis detail). Fail-fast 400s: &gt;6 quantities, unknown shop (lists available ids), invalid overrides key. qa-broken.stl: structured 400 GEOMETRY_INVALID with geometry summary + doc_url, no 500. Untested: ensemble uncertainty (absent = disabled, allowed), 504, persist-failure degrade, 429.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -7403,12 +7980,16 @@
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="3" t="inlineStr"/>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>No auth. 200 same shape/validation as /validate/cost but identity:null, no 'saved' key, no uncertainty, no 'validated:true' anywhere in response. 400 on bad material_class. owned_processes form field has no effect (param not in contract). 240/hr 429 untested.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -7453,12 +8034,16 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="3" t="inlineStr"/>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>401/403 verified; 400 unknown rule_pack (validated before file read); 200 on qa-broken.stl returns original_analysis (fail, non-watertight) vs repaired_analysis plus repair_applied/repair_details/repaired_file_b64. 413 untested.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -7503,12 +8088,16 @@
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J140" s="3" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="3" t="inlineStr"/>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>401 without key; viewer-role key suffices for all four catalogs. rule_packs have name/version/description/override_count/mandatory_issue_count; processes list materials+machines; materials include min_wall_mm/tensile_mpa/cost_per_kg_usd; machines include build_volume_mm/min_layer_mm/materials. 429 untested.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -7553,12 +8142,16 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J141" s="3" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
-      <c r="L141" s="3" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>Viewer key: 200 {shops:[{id,name,region,source}]} (midwest-precision-cnc US, shenzhen-contract-mfg CN). Same ids appear in the cost route's unknown-shop 400 message, confirming linkage. 429 untested.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -7603,12 +8196,16 @@
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="3" t="inlineStr"/>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>401 no key, 403 viewer. 200 capability dict for default purpose batch_zip incl. max_parts=10000 and max_part_urls_per_response=1000 (also honestly reports available:false / DIRECT_UPLOAD_REQUIRES_S3 on this non-S3 server). Unknown purpose -&gt; 422 DIRECT_UPLOAD_INVALID_PURPOSE (400-family passthrough).</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -7653,12 +8250,16 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="3" t="inlineStr"/>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>401/403 verified; extra body field -&gt; 422 VALIDATION_ERROR (extra_forbidden); short Idempotency-Key -&gt; 422 DIRECT_UPLOAD_IDEMPOTENCY_KEY_REQUIRED; valid initiate -&gt; structured 501 DIRECT_UPLOAD_REQUIRES_S3 (this server has no S3), consistent with capabilities available:false — documented honest unavailability. 201 happy path, part URLs, and idempotent_replay untestable in this environment.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -7703,12 +8304,16 @@
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="3" t="inlineStr"/>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>401 verified. parts/complete/abort/status on unknown-or-foreign id all return structured 404 DIRECT_UPLOAD_NOT_FOUND; malformed complete body (extra field) -&gt; 422 VALIDATION_ERROR; legacy aliases POST /multipart/{id}/complete and DELETE /multipart/{id} are live (return DIRECT_UPLOAD_NOT_FOUND, not route-404) and absent from openapi.json. Full lifecycle and &gt;1000-part-number refresh rejection untestable (no S3, cannot create an upload; not-found precedes the count check on a fake id).</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -7753,12 +8358,16 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J145" s="3" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="3" t="inlineStr"/>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>401 no key; 200 application/pdf with %PDF magic and Content-Disposition: attachment; filename="qa-box-dfm-report.pdf" (sanitized); 404 NOT_FOUND for unknown analysis ULID.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -7803,12 +8412,16 @@
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="3" t="inlineStr"/>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>401/403 (viewer) verified. POST returned {share_url:/s/&lt;short&gt;, share_short_id} and analysis detail flipped to is_public:true with share_url; 404 for unknown analysis on both POST and DELETE. DELETE returned {message:'Share revoked'} and public link 404'd immediately after.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -7853,12 +8466,16 @@
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr"/>
       <c r="K147" s="2" t="inlineStr"/>
-      <c r="L147" s="3" t="inlineStr"/>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>Unauthenticated 200 with X-Robots-Tag: noindex and Cache-Control: private, no-store; body is sanitized subset (verdict/geometry/process_scores etc., no key/email material). 404 for unknown short id and for revoked id. 120/hr IP 429 untested.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -7903,12 +8520,16 @@
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J148" s="3" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="3" t="inlineStr"/>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>401 no key. List returns {analyses, next_cursor, has_more}, ULID-desc; limit=0 and limit=101 -&gt; 422; invalid verdict silently ignored; verdict=pass filters correctly. Org scoping: other-org key gets 404 on my analysis detail and its own list shows only its org. Detail includes full result_json, is_public/share_url, and decision_links matched by org+mesh_hash (linked the CORE-007 cost decision to the qa-box analysis). 404 unknown ULID.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -7953,12 +8574,16 @@
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="3" t="inlineStr"/>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>401 no key. Status returned job_id/status(partial)/job_type(sam3d)/timestamps/result_url/error:null with result_url set for partial; /result returned the segmentation result. 404 for non-existent job AND for another user's job id (no existence leak). Untested: /result 404 while queued/running (job completed instantly) and failed-job {code,message} error carry.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -8003,12 +8628,16 @@
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J150" s="3" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="3" t="inlineStr"/>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>200 {status:ok} with real probes: postgres:true, redis:true, async{redis:true, worker:'ok', expected:true, worker_strict:false}, reconstruction{available:false, backend:'none', egress:false} (honest about absent reconstruction), version, build_id. 503 degraded path untestable (cannot take deps down in the running app).</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -8053,12 +8682,16 @@
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J151" s="3" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="3" t="inlineStr"/>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>DEEP_HEALTH_TOKEN unset -&gt; endpoint open as expected: 200 without token and also with a wrong X-CadVerify-Health-Token (gate only applies when token configured). Body has all documented fields: checks.postgres{ok,error}, checks.redis{ok,expected,configured,error}, checks.worker{state:'ok', heartbeat_age_seconds:0, stale_threshold_seconds:90}, checks.queue{depth:0,name:'arq:queue'}, checks.object_store{ok:false,expected:false,backend:'local'} — object_store failing but not expected correctly does not gate status. Token-gated 404 path untestable here.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8103,12 +8736,16 @@
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="3" t="inlineStr"/>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>Observed envelope {code,message,doc_url} on every error: BAD_REQUEST (400s), NOT_FOUND (unknown route + unknown resources), FILE_TOO_LARGE (demo 413), VALIDATION_ERROR (Pydantic 422s incl. extra_forbidden and int_parsing), NOT_IMPLEMENTED (gmsh 501). Detail-dicts with own code pass through unchanged: GEOMETRY_INVALID, DIRECT_UPLOAD_* family, auth_missing (401), insufficient_role (403). 429 RATE_LIMITED and 409/503/504 codes not triggered (deliberately stayed under rate limits).</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8153,12 +8790,16 @@
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr"/>
       <c r="K153" s="2" t="inlineStr"/>
-      <c r="L153" s="3" t="inlineStr"/>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>curl confirms 307 redirect /docs -&gt; /developers; browser lands on /developers.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -8203,12 +8844,16 @@
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="3" t="inlineStr"/>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>Confirm upserts declared fields, source=user_confirmed/provenance USER (200); 400 no declared field; 400 blank mesh_hash; 404 unknown mesh; 404 cross-tenant confirm from second org (no write); identity.confirm audit event present; platform-viewer caller got 403 (analyst gate). Corpus row is created by POST /validate (not /validate/cost); no-org 400 branch untestable (signup always creates an org).</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8253,12 +8898,16 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J155" s="3" t="inlineStr"/>
       <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="3" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>Multipart onboard: 2 onboarded with CSV mapping (manifest_registered=2), qa-fake.stl honestly skipped with reason, batch not aborted; ZIP form onboarded 2 unnamed (bare geometry, no guessing); 400 no files; 400 non-UTF-8 mapping; honest summary shape {onboarded,skipped,mapping_errors,library_size}. 413 &gt;512MB and &gt;2000-file cap not exercised (impractical payload sizes); analyst gate verified via shared require_role.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -8303,12 +8952,16 @@
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J156" s="3" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="3" t="inlineStr"/>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>GET /library org-scoped {library_size,recent[]} with declared identity only - no signature vector emitted; org B never sees org A rows. /library/template returns text/csv with header filename,part_id,name,program,material_class. Viewer-role caller allowed (200 as platform viewer). No-org 403 branch untestable (every account has an org).</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -8353,12 +9006,16 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J157" s="3" t="inlineStr"/>
       <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="3" t="inlineStr"/>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>201 {org_id,name,slug,org_role:admin}; active org NOT switched (list still showed personal org active); 400 empty name; 400 name&gt;200; org.created audit event present; platform-viewer got 403 (analyst gate).</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -8403,12 +9060,16 @@
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J158" s="3" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="3" t="inlineStr"/>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>Returns only caller's memberships with is_active flag on the active org; second user's list shows only their own orgs.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -8453,12 +9114,16 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="3" t="inlineStr"/>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>API key switch refused 403 {code:api_key_org_bound}; dashboard session switch to member org 200; switch to non-member org 403 'not a member'; org.switched audit events present.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -8503,12 +9168,16 @@
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J160" s="3" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="3" t="inlineStr"/>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>POST 201 serialized mapping (invalid role 400 with allowed list admin/member/viewer); list strictly org-scoped (org B sees []); DELETE of org A mapping via org B admin key = 404; delete in own org works; saml.group_mapping.created/deleted audit events present.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -8553,12 +9222,16 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J161" s="3" t="inlineStr"/>
       <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="3" t="inlineStr"/>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>POST 201 with one-time accept_link + emailed:false (no RESEND config, creation unaffected - best-effort confirmed); invalid role 400; GET lists invites with statuses and NO tokens; 21st create in an hour rate-limited 429 (20/hour). Role-exceeds-inviter 403 branch unreachable in practice (only org admins - top role - can invite).</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -8603,12 +9276,16 @@
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J162" s="3" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="3" t="inlineStr"/>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>400 empty token; 404 unknown token; 403 when a different account redeems ('issued to a different account'); correct account joins with {org_id,org_role,created:true}; re-accept 409 'already been used'; revoked token 409; member.joined audit event present.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -8653,12 +9330,16 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J163" s="3" t="inlineStr"/>
       <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="3" t="inlineStr"/>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>Revoke from another org's admin = 404 (org-scoped); own-org revoke returns invite with status revoked + revoked_at; accepting revoked token 409; revoking accepted invite 409; unknown id 404.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -8703,12 +9384,16 @@
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J164" s="3" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="3" t="inlineStr"/>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>Org member (viewer) sees active-org member list; results strictly bounded to caller's active org (org B list contains only org B's member); no cross-org leakage.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -8753,12 +9438,16 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J165" s="3" t="inlineStr"/>
       <c r="K165" s="2" t="inlineStr"/>
-      <c r="L165" s="3" t="inlineStr"/>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>Admin changed member-&gt;viewer returning {user_id,org_role}; 404 non-member target; 409 demoting last admin; org-viewer caller got 403; member.role_changed audit event present.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -8803,12 +9492,16 @@
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J166" s="3" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="3" t="inlineStr"/>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>Non-admin removing another member: 403 {code:insufficient_org_role}; self-leave by viewer succeeded and membership disappeared immediately from member list; 404 non-member; 409 removing last admin; member.left audit event present. Account remained active (org-scoped removal, not deactivation).</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -8853,12 +9546,16 @@
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J167" s="3" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="3" t="inlineStr"/>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>Org-admin list bounded to own org (INNER JOIN behavior observed); detail of outside-org user = 404 (no existence leak); own-user detail includes org_role, auth_provider, analysis_count, batch_count; superadmin sees all users with primary membership enriched; cursor pagination works (limit=2 -&gt; next_cursor/has_more, followed page 2); limit 0/101 rejected 422; org-viewer caller 403.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -8903,12 +9600,16 @@
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J168" s="3" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="3" t="inlineStr"/>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>Org-admin got 403 {code:platform_superadmin_required}; 400 changing own role; 400 role=superadmin (not assignable); 404 unknown user; superadmin demoted analyst-&gt;viewer (verified viewer then 403s on analyst-gated routes, reads still work) and restored; user.role_changed audit events present (x3).</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -8953,12 +9654,16 @@
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J169" s="3" t="inlineStr"/>
       <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="3" t="inlineStr"/>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>Org-admin refused 403; 400 self-deactivate; 404 unknown user. Deactivation blocked API key (403), existing dashboard session (403) and password login (403); idempotent (second deactivate kept session_version=1); reactivate restored key access and bumped session_version; user.deactivated/user.reactivated audit events present.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -9003,12 +9708,16 @@
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="3" t="inlineStr"/>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>Superadmin only (org-admin 403, unknown user 404); returns new session_version; existing dashboard session died (401) while the API key kept working (200) and account stayed active; user.sessions_revoked audit event present.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -9053,12 +9762,16 @@
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J171" s="3" t="inlineStr"/>
       <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="3" t="inlineStr"/>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>Org-admin counts filtered to own org (analyses/cost_decisions/usage_events/webhook_deliveries + per-event-type and webhook-status breakdowns, real numbers); superadmin unfiltered with org_id:null; days out of 1-90 rejected (422 validation); org-viewer caller 403.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -9103,12 +9816,16 @@
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J172" s="3" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="3" t="inlineStr"/>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>Org-admin gate verified (viewer 403); returns {deliveries:[]} honestly - no webhook endpoints configured in env, so payload-exclusion and retry-timing fields could not be observed on real rows.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -9153,12 +9870,16 @@
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J173" s="3" t="inlineStr"/>
       <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="3" t="inlineStr"/>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>Org-admin required (viewer 403); returns PII-free async/jobs/batches/batch_items posture scoped to caller org (org_id echoed).</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -9203,12 +9924,16 @@
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J174" s="3" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="3" t="inlineStr"/>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>Missing start/end 422, invalid datetime 400, &gt;90-day range 400; org-admin sees only own-org entries (14 vs org B's 2 vs superadmin's 119); action filter works; format=csv returns text/csv attachment audit-log.csv; JSON cursor-paginated. All expected audit actions observed (org.*, member.*, identity.confirm, saml.*, user.*, governance.*).</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -9253,12 +9978,16 @@
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J175" s="3" t="inlineStr"/>
       <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="3" t="inlineStr"/>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>Org-admin API key returns static ServiceProviderConfig/Schemas/ResourceTypes (SCIM 2.0, patch supported, bulk not); no auth 401; org-viewer-bound key 403 insufficient_org_role. 403 {code:scim_org_required} for an org-less token untestable - every mintable key is org-bound.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -9303,12 +10032,16 @@
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J176" s="3" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="3" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>List with startIndex/count and SCIM filter (userName eq) works, bounded to key's org; POST 201 creates (upsert by userName); GET by id 200; cross-org GET via second org's key = 404 SCIM error; PUT without userName preserves existing userName; PATCH with wrong schema 400, proper PatchOp schema applies active=false. Note: PUT supplying a *different* userName upserts by that userName (creates a new resource) per code's setdefault design.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -9353,12 +10086,16 @@
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J177" s="3" t="inlineStr"/>
       <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr"/>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>DELETE returned 204 with no body; user still readable with active:false (soft deactivation, not hard delete); DELETE via another org's key = 404 (org-scoped).</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -9403,12 +10140,16 @@
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J178" s="3" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="3" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>Groups are the three org-role groups, org-scoped with correct members; group_id path segment 'role:member' resolves (:path converter); PATCH add applied and committed; unknown group 404 SCIM error. Observation: PATCH add with a user id provisioned by another org succeeds by creating a membership in the CALLER's org only (writes bounded to caller org, other org's data untouched) - matches service design (all writes to caller's org membership table) but means any known numeric user id can be pulled into the key's org.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -9453,12 +10194,16 @@
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J179" s="3" t="inlineStr"/>
       <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>Cheap part verified: unauthenticated POST /validate passes admission fail-open and gets a clean 401 auth_missing (no 429/500). Load-dependent sub-assertions NOT exercised per instructions: global 429 server_busy beyond 8 in-flight, per-org 429 org_at_capacity beyond 3, slot release in finally, RELEASE-mode bypass lockout.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -9503,12 +10248,16 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J180" s="3" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="3" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>Proposing a draft rate-card version created a 'proposed' request (member+); unknown asset_type 400; target version not found 404; cross-org target 404; target not in draft status 400 (re-proposing a published version); governance.change_requested admin-audience notification emitted (seen in inbox, later resolved). 60/hour limit not exhausted.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -9553,12 +10302,16 @@
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J181" s="3" t="inlineStr"/>
       <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>List org-scoped newest-first ([3,2]); ?status filter honored (rejected -&gt; [] before any rejection); org B list empty; detail 404 for missing and for another org's request; own-org detail 200.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -9603,12 +10356,16 @@
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J182" s="3" t="inlineStr"/>
       <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="3" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>Org-admin approve 200 returning both request (approved, reviewed_by, decided_at) and published_version (status published); org-viewer 403; cross-org admin 404; re-approve 409 (not proposed); governance.approved + library.version_published audit events present; pending notification resolved. Publish-failure fail-closed branch not exercisable without breaking the library.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -9653,12 +10410,16 @@
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J183" s="3" t="inlineStr"/>
       <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>Reject 200 with status rejected + note persisted; cross-org 404; re-reject 409; target draft remained status=draft (nothing published); governance.rejected audit event present; review notification resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -9703,12 +10464,16 @@
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J184" s="3" t="inlineStr"/>
       <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="3" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>Default list = unread non-dismissed open items; status must be open|resolved|all (bogus 422); dismissed=true+unread=true rejected 400; org-scoped (org B sees []); cursor pagination works (limit=1 -&gt; has_more/next_cursor); resolved governance notifications visible under status=all. No-org honest-empty branch untestable.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -9753,12 +10518,16 @@
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J185" s="3" t="inlineStr"/>
       <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>read/dismiss/restore each return {ok,notification} with updated per-user read_at/dismissed_at; state is per-user (second member's view stayed unread after first user's read); another org's notification id 404; unknown id 404; dismissed item left default inbox and restore brought it back.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -9803,12 +10572,16 @@
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J186" s="3" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="3" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>Returns {ok:true,count,read_at}; marked only the caller's org notifications read for that user only (other member unaffected). No-org count-0 branch untestable.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -9851,14 +10624,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I187" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
-        </is>
-      </c>
-      <c r="J187" s="3" t="inlineStr"/>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>TESTED-FAIL</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="inlineStr">
+        <is>
+          <t>Server stack IS advertised: every backend response carries TWO Server headers - 'server: uvicorn' (uvicorn's own banner) followed by 'server: ProofShape' (middleware). Expected 'Server rewritten to ProofShape (stack never advertised)'. Reproduce: curl -sD - http://127.0.0.1:8000/health | grep -i '^server' -&gt; 'server: uvicorn' + 'server: ProofShape'. Same on authed JSON, 404s, and streamed CSV. The middleware docstring says the uvicorn banner is suppressed via --no-server-header in the process command; the running process lacks that flag.</t>
+        </is>
+      </c>
       <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>All other assertions pass: HSTS max-age=63072000; includeSubDomains, X-Content-Type-Options nosniff, X-Frame-Options DENY, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy camera=(), microphone=(), geolocation=() present on every response including the streamed audit-log CSV export.</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -9903,12 +10684,16 @@
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J188" s="3" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="3" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>Inbound X-Request-ID echoed verbatim on the response; absent header -&gt; fresh UUID4 per request (two calls produced distinct UUIDs). Structlog/Sentry binding not externally observable via API.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -9953,12 +10738,16 @@
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J189" s="3" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>Per-route slowapi limit verified live: 20 invite creations succeeded, 21st returned 429 with Retry-After: 3600 and x-ratelimit-* headers. Kill-switch open state allows all mutations (verified throughout); the CLOSED state (503 service_paused on writes, reads still up) is driven by the ACCEPTING_NEW_ANALYSES env var of the running process and could not be flipped without restarting/modifying the app (forbidden) - dependency presence confirmed in code on all org/identity mutation routes.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -10003,12 +10792,16 @@
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J190" s="3" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="3" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>Share created via POST /api/proxy/analyses/{id}/share -&gt; /s/a4nVdkEHmqDo; viewed in a logged-out context. Bogus id shows the not-available (may have been revoked) state with a link home.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10053,12 +10846,16 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J191" s="3" t="inlineStr"/>
       <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>Cost share /s/cost/5WB6NT4UR5Fo viewed logged-out: "Make by CNC 3-Axis" + DFM-ready badge, crossover sentence ("Make below ~721 units... tool up with Die Casting above it"), confidence band ($68.76-$206.29/unit, ±50%, assumption-basis stated), geometry cards, recommendation-by-quantity table with cheaper-if-redesigned alternates, DEFAULT/USER provenance chips, noindex, "not a validated quote" footer. Bogus id -&gt; "Cost decision not available".</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -10103,12 +10900,16 @@
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J192" s="3" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>Tab title falls back to layout default 'ProofShape — verification, made of glass'; WebGL canvas renders (1 canvas, no console errors); rail nav[aria-label='Story progress'] has 6 stops PART|ROUTED|OPENED|SEATED|THE NUMBER|PROOF; clicking stop 5 scrolled 0-&gt;5130px; 'See it on your part' pill href=/company#pilot (opacity 1 mid-story); 'The full platform -&gt;' -&gt; /platform; 'or read the method first -&gt;' -&gt; /method.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -10153,12 +10954,16 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J193" s="3" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t>Range input aria-label='Quantity' default 500 units, 'Make by MJF (PP)'; dragged to 1,959 units -&gt; MAKE, 1,995/10,000 units -&gt; 'Tool up: injection molding' with 'if redesigned' qualifier — flips exactly at the documented 1,962 crossover; highlighted SVG curve stroke-widths swap (2.5&lt;-&gt;1.5); readout and marker update; underline 'Request a pilot -&gt;' -&gt; /company#pilot.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -10203,12 +11008,16 @@
       </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J194" s="3" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="3" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>Close-act email input (aria-label 'Work email') is not inside any form; typed an email and clicked 'Request a pilot' — plain Link navigation to /company#pilot; zero POST/XHR fired with the input value.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -10253,12 +11062,16 @@
       </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J195" s="3" t="inlineStr"/>
       <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="3" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>Wordmark -&gt; /; all six nav links route correctly (clicked Platform and Teams, URL verified); data-active=true on current section incl. /teams/* subtree (verified on /teams/sourcing); Log in -&gt; /login; Request a pilot -&gt; /company#pilot; document pages use .st-nav-document, home uses .st-nav-cinematic. Mobile (390px): details menu opens, mirrors all 8 links, Escape closes it, link click navigates (to /security) and closes the menu.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -10303,12 +11116,16 @@
       </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J196" s="3" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="3" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>Footer on document pages: tagline 'ProofShape — verification, made of glass', Home + six nav items + Log in, legal row '© 2026' with Privacy/Terms/DPA/Status hrefs all correct; clicked Privacy and routed. Home (cinematic) closes with inline tagline linking exactly /method,/platform,/security,/developers and has no full footer.</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -10353,12 +11170,16 @@
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J197" s="3" t="inlineStr"/>
       <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="3" t="inlineStr"/>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>Title falls back to layout default; $14.14 driver content present through the record-assembly section; 'Cost a part' -&gt; /signup and 'Explore the platform' -&gt; /platform; SiteShell nav+footer present; no console errors.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -10403,12 +11224,16 @@
       </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J198" s="3" t="inlineStr"/>
       <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="3" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Platform — ProofShape'; 'Cost a part' -&gt; /signup, 'How the number is built' -&gt; /method; SiteShell chrome present.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -10453,12 +11278,16 @@
       </c>
       <c r="I199" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J199" s="3" t="inlineStr"/>
       <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="3" t="inlineStr"/>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Teams — ProofShape'; all five persona journey links present with correct hrefs; 'Request a pilot' -&gt; /company#pilot and 'Explore the platform' -&gt; /platform.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -10503,12 +11332,16 @@
       </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J200" s="3" t="inlineStr"/>
       <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="3" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>Title 'For Cost Engineering — ProofShape'; hero link back to /teams; scrolled full journey (no console errors); closing CTAs to /company#pilot and /teams visible at end.</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -10553,12 +11386,16 @@
       </c>
       <c r="I201" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J201" s="3" t="inlineStr"/>
       <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="3" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>Client page: title falls back to layout default 'ProofShape — verification, made of glass' as documented; hero links to /teams; scroll-driven reveals render; closing CTAs -&gt; /company#pilot and /teams.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -10603,12 +11440,16 @@
       </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J202" s="3" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="3" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>Title 'ProofShape — For In-house manufacturing &amp; MRO'; /teams link near top; closing CTAs -&gt; /company#pilot and /teams.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -10653,12 +11494,16 @@
       </c>
       <c r="I203" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J203" s="3" t="inlineStr"/>
       <c r="K203" s="2" t="inlineStr"/>
-      <c r="L203" s="3" t="inlineStr"/>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>Title 'For shop owners — ProofShape'; hero /teams link; closing CTAs -&gt; /company#pilot and /teams; full-page scroll clean.</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -10703,12 +11548,16 @@
       </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J204" s="3" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="3" t="inlineStr"/>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>Title 'For Sourcing — ProofShape'; WebGL stage + scroll reveals render without console errors; hero /teams link; closing CTAs -&gt; /company#pilot and /teams.</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -10753,12 +11602,16 @@
       </c>
       <c r="I205" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J205" s="3" t="inlineStr"/>
       <c r="K205" s="2" t="inlineStr"/>
-      <c r="L205" s="3" t="inlineStr"/>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Developers — ProofShape'; 'Get an API key' -&gt; /signup, 'Full API reference' -&gt; /docs; page renders with no console errors (record reveal is CSS-only).</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -10803,12 +11656,16 @@
       </c>
       <c r="I206" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J206" s="3" t="inlineStr"/>
       <c r="K206" s="2" t="inlineStr"/>
-      <c r="L206" s="3" t="inlineStr"/>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>Title 'API Reference - ProofShape'; 'Open API console' is &lt;a href="/scalar"&gt;, 'Developer overview' -&gt; /developers; static &lt;pre&gt; lists all four endpoints (POST /api/v1/validate, POST /api/v1/validate/cost, GET /api/v1/cost-decisions, GET /api/v1/catalog — GET rows use aligned double-space) plus Bearer auth note.</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -10853,12 +11710,16 @@
       </c>
       <c r="I207" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J207" s="3" t="inlineStr"/>
       <c r="K207" s="2" t="inlineStr"/>
-      <c r="L207" s="3" t="inlineStr"/>
+      <c r="L207" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Company — ProofShape'; section#pilot exists with computed scroll-margin-top 92px; navigating /company#pilot lands the section in view below the sticky nav; Week 1-4 pilot columns present; no email address published anywhere in body; SiteShell chrome present.</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -10903,12 +11764,16 @@
       </c>
       <c r="I208" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J208" s="3" t="inlineStr"/>
       <c r="K208" s="2" t="inlineStr"/>
-      <c r="L208" s="3" t="inlineStr"/>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/pilot/request returned {turnstileSiteKey:null} so submit enables without Turnstile. Empty submit blocked by required email/company/what (native validation, no fake receipt); bad email blocked by type=email; deployment select offers undecided/cloud/vpc/air-gapped. Real submit POSTed to /api/pilot/request -&gt; 200 {status:received, receipt:998ed199-...}; form replaced by role=status 'Request received and recorded.' with durable receipt CV-998ed199-fc85-438b-bd38-91f3f56b0ac8. Backend intake IS configured and worked end-to-end.</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -10953,12 +11818,16 @@
       </c>
       <c r="I209" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J209" s="3" t="inlineStr"/>
       <c r="K209" s="2" t="inlineStr"/>
-      <c r="L209" s="3" t="inlineStr"/>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Security — ProofShape'; deployment models rendered; no compliance badges; 'Talk to us' -&gt; /company#pilot, 'Self-host it today' -&gt; /developers.</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -11003,12 +11872,16 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J210" s="3" t="inlineStr"/>
       <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="3" t="inlineStr"/>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Pilot Report - ProofShape'; numbered artifact cards render; single CTA 'Request a pilot' -&gt; /company#pilot; SiteShell chrome.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -11053,12 +11926,16 @@
       </c>
       <c r="I211" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J211" s="3" t="inlineStr"/>
       <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="3" t="inlineStr"/>
+      <c r="L211" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Privacy - ProofShape'; 'What we collect' + usage/retention sections present; 'Talk to ProofShape' -&gt; /company#pilot.</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -11103,12 +11980,16 @@
       </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J212" s="3" t="inlineStr"/>
       <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="3" t="inlineStr"/>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Terms - ProofShape'; static article, no CTAs beyond shared nav/footer; reachable from footer legal row (footer link verified in SITE-005).</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -11153,12 +12034,16 @@
       </c>
       <c r="I213" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J213" s="3" t="inlineStr"/>
       <c r="K213" s="2" t="inlineStr"/>
-      <c r="L213" s="3" t="inlineStr"/>
+      <c r="L213" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Data Processing Addendum - ProofShape'; static article, no form/CTA links in body.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -11203,12 +12088,16 @@
       </c>
       <c r="I214" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J214" s="3" t="inlineStr"/>
       <c r="K214" s="2" t="inlineStr"/>
-      <c r="L214" s="3" t="inlineStr"/>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>Title 'Status - ProofShape'; exactly three rows (Hosted app, API, Workers), each reading 'No public metric feed yet'; no fake green indicators.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -11253,12 +12142,16 @@
       </c>
       <c r="I215" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J215" s="3" t="inlineStr"/>
       <c r="K215" s="2" t="inlineStr"/>
-      <c r="L215" s="3" t="inlineStr"/>
+      <c r="L215" s="3" t="inlineStr">
+        <is>
+          <t>GET /some-bogus-route-qa-xyz returned HTTP 404 with branded page inside SiteShell: heading 'That record is not here.', 'Back to ProofShape' pill href=/; nav and footer present and functional (clicked Method from the 404 and routed). Only console entry is the browser's default 'Failed to load resource: 404' for the bogus URL itself — expected.</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -11303,12 +12196,16 @@
       </c>
       <c r="I216" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J216" s="3" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr"/>
-      <c r="L216" s="3" t="inlineStr"/>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t>Exercised by injecting a render-time crash (patched Number.prototype.toLocaleString to throw) on /: root error boundary rendered 'Something went wrong' with product-UI styling and a 'Try again' button; no Error ID line because a client-side error carries no digest (story says digest renders only 'when present'). After removing the fault, 'Try again' re-rendered the page back to the working home. Sentry capture not externally verifiable (no DSN observable) — noted, not a deviation.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -11353,12 +12250,16 @@
       </c>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J217" s="3" t="inlineStr"/>
       <c r="K217" s="2" t="inlineStr"/>
-      <c r="L217" s="3" t="inlineStr"/>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t>robots.txt allows exactly the 18 public marketing routes, disallows app/auth routes (/analyze,/batch,/cost,/cost-decisions,/history,/label,/reconstruct,/settings,/verify,/login,/signup,/magic,/orgs) and points at http://localhost:3000/sitemap.xml (NEXT_PUBLIC_SITE_URL fallback); sitemap.xml lists the same 18 routes, priority 1.0 for home and 0.7 elsewhere; /opengraph-image serves 200 image/png (53,631 bytes); (site) layout default title verified on home tab.</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -11403,12 +12304,16 @@
       </c>
       <c r="I218" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J218" s="3" t="inlineStr"/>
       <c r="K218" s="2" t="inlineStr"/>
-      <c r="L218" s="3" t="inlineStr"/>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t>Unauthenticated /verify 307-redirects to /login?next=%2Fverify (verifySession enforced). No-membership state (real user, membership removed in DB): verify-organization-gate renders 'ORGANIZATION REQUIRED / You haven't joined an organization yet.' with invitation guidance, 'No organization data has been loaded or treated as empty.' and an Open organization settings link — screenshot VER-001-gate-nomember.png. 'Memberships-but-none-active' branch is unreachable with real data: backend resolve_org() always falls back to the oldest live membership when users.current_org_id is NULL (verified by nulling it in DB — workspace correctly loads with the resolved org), so that gate copy is defensive-only. 'Access unavailable' (organizationAccess=null) state not inducible without breaking the backend; copy verified in code only. VERIFY_UI-off 404 not toggled (would affect the shared dev server).</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -11453,12 +12358,16 @@
       </c>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J219" s="3" t="inlineStr"/>
       <c r="K219" s="2" t="inlineStr"/>
-      <c r="L219" s="3" t="inlineStr"/>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>first-run open, Esc-close records key, no reopen after key, ?welcome=1 opens+strips param, shop/machines + file-picker actions, Start here reopens</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -11503,12 +12412,16 @@
       </c>
       <c r="I220" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J220" s="3" t="inlineStr"/>
       <c r="K220" s="2" t="inlineStr"/>
-      <c r="L220" s="3" t="inlineStr"/>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>Success path verified end-to-end: sample runs the real POST /validate + /validate/cost, guided-example-status bar walks running-&gt;ready, GuidedResultSummary shows headline, recommended route, first issue, measured geometry (envelope/volume/faces/watertight), resource cost and shop fit; 'Show full technical result' closes into the walk. Leaving via rail navigation or 'Back to start' cancels the guided lifecycle. Minor observation: keyboard-hotkey navigation (H) bypasses nav()'s cancellation, so returning to Verify by hotkey still shows the ready-state bar; no summary dialog was observed popping over Home in the probe.</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -11553,12 +12466,16 @@
       </c>
       <c r="I221" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J221" s="3" t="inlineStr"/>
       <c r="K221" s="2" t="inlineStr"/>
-      <c r="L221" s="3" t="inlineStr"/>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>sldprt gets SolidWorks-specific copy, txt gets generic copy, role=alert, no network call for rejected files, dismiss works, accept attr lists stl/step/stp/iges/igs</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -11603,12 +12520,16 @@
       </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J222" s="3" t="inlineStr"/>
       <c r="K222" s="2" t="inlineStr"/>
-      <c r="L222" s="3" t="inlineStr"/>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>Verified with /validate delayed 2.5s and /validate/cost delayed 9s (real engine, slowed): verify-first-insight renders 'ROUTING + DFM READY · COST CALCULATING' with best route (DLP Resin), first route issue (overhang threshold), MEASURED chips (bbox/volume/watertight) and 'DFM ISSUES · cost continues without rerunning DFM' while cost is in flight; cost POST starts only after /validate returns; GET /machine-inventory + PUT /part-context/{hash} run alongside. Run-token supersedence verified in VER-011 rapid material switch. (Earlier automated miss was a harness regex expecting DFM PASS/FAIL; actual verdict label was 'DFM ISSUES'.)</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -11653,12 +12574,16 @@
       </c>
       <c r="I223" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J223" s="3" t="inlineStr"/>
       <c r="K223" s="2" t="inlineStr"/>
-      <c r="L223" s="3" t="inlineStr"/>
+      <c r="L223" s="3" t="inlineStr">
+        <is>
+          <t>Overlay ('VERIFYING · &lt;file&gt;', THE VERDICT · COMPUTING — GATES CHECKING IN) narrates all five milestones (received/measured/routed/gates walked/record assembled) with pending detail and 'no step is skipped, none is faked' footer, with a dismiss (Skip to the walk) control; appears only past the 260ms perceptible-wait threshold (suppressed for instant runs by design). Partial state 'ROUTING + DFM READY · COST CONTINUES' is transient: the overlay hands off to the inline FirstInsight card 220ms after validation lands (deliberate, per pipeline-overlay.tsx); settled/complete headers reach the screen only on non-progressive paths and otherwise surface as the completion toast. Interrupted state checked in VER-008 run. Blocked-gate stop renders in the walk (VER-007) with downstream steps not rendered. · overlay at geometry stop: "(closed — handed off to walk by design)";</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -11703,12 +12628,16 @@
       </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J224" s="3" t="inlineStr"/>
       <c r="K224" s="2" t="inlineStr"/>
-      <c r="L224" s="3" t="inlineStr"/>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>400 GEOMETRY_INVALID from /validate/cost renders fail banner + walk-stops block quoting backend message with measured facts + Repair &amp; re-upload; no downstream steps; overlay marks stages not computed</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -11753,12 +12682,16 @@
       </c>
       <c r="I225" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J225" s="3" t="inlineStr"/>
       <c r="K225" s="2" t="inlineStr"/>
-      <c r="L225" s="3" t="inlineStr"/>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t>Outages induced by client-side request interception (no server outage inducible safely). Total outage: 'ANALYSIS INTERRUPTED · NO VERDICT PRODUCED' with exact error + Retry verification. Cost-only outage: 'DFM ISSUES · RESOURCE COST INTERRUPTED / Routing and DFM are ready. Cost needs another try.' names the costError (Failed to fetch) and why machine fit is absent; 'Retry cost only' re-POSTed only /validate/cost (no extra /validate) and merged onto the preserved DFM into a completed walk; 'Rerun full verification' offered. (Automated check initially flagged missing DFM verdict due to a regex expecting PASS/FAIL; actual label is 'DFM ISSUES' — verified from screenshot.)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -11803,12 +12736,16 @@
       </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J226" s="3" t="inlineStr"/>
       <c r="K226" s="2" t="inlineStr"/>
-      <c r="L226" s="3" t="inlineStr"/>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>no verification block: banner says SHOULD-COST COMPUTED and explicitly not-evaluated (no machines/env declared)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -11853,12 +12790,16 @@
       </c>
       <c r="I227" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J227" s="3" t="inlineStr"/>
       <c r="K227" s="2" t="inlineStr"/>
-      <c r="L227" s="3" t="inlineStr"/>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>Env chip toggle re-runs verification: PUT /part-context/{sha256-of-bytes} carries max_temp_c before POST /validate/cost; door chip states verified — 'ambient' when undeclared (t4 run), 'capturing…' transient, '● USER · on the record' after successful persistence, and 'drives this preview only' when the PUT was aborted (induced). Env-excluded materials rendered struck-through with per-material citation ('Standard Resin excluded: service 120C exceeds material max service temperature 60C', 'PLA excluded: …'); sour-service NACE citation not separately exercised. Declared annual_volume=750 persisted alongside and reshaped the qty ladder to [1,100,750,2000,5000,10000] on subsequent runs. (One automated re-run flagged the pre-run 'ambient' chip due to reading the DOM before first paint; the same check passed in the earlier run.)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -11903,12 +12844,16 @@
       </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J228" s="3" t="inlineStr"/>
       <c r="K228" s="2" t="inlineStr"/>
-      <c r="L228" s="3" t="inlineStr"/>
+      <c r="L228" s="3" t="inlineStr">
+        <is>
+          <t>class selection re-runs cost with declared material (response assumption verified), provenance DEFAULT-&gt;USER, rapid Steel-&gt;Titanium leaves Titanium displayed (monotonic run token). run1 material=polymer; material sequence from responses=["polymer","polymer","polymer","steel","titanium"];</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -11953,12 +12898,16 @@
       </c>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J229" s="3" t="inlineStr"/>
       <c r="K229" s="2" t="inlineStr"/>
-      <c r="L229" s="3" t="inlineStr"/>
+      <c r="L229" s="3" t="inlineStr">
+        <is>
+          <t>Empty floor: step 1 shows 'No machines declared.' with 'Declare your floor →' CTA opening the Machines screen. After declaring machines via the same authed proxy (cnc_3axis 'QA VF-2' 762x406x508 @ $85/hr, sla 'QA Mars 4', plus a 'thermoforming' machine unknown to the engine): step 1 lists machines with USER provenance + envelope summaries; owned_processes forwarded to /validate/cost is exactly 'cnc_3axis,sla' on every call (unknown thermoforming omitted; cost never 400s); verification block returned (verdict 'Makeable — outsource only', ✗ marks per route with 'makeable outsource only'); rate dot fills once an hourly rate exists. Note: with a service world already on the part's record, the empty-floor state shows the honest lattice verdict ('Makeability unknown — not enough is declared') instead of 'MAKEABILITY NOT EVALUATED', which appears only when neither machines nor env are declared (verified in VER-009 run).</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -12003,12 +12952,16 @@
       </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J230" s="3" t="inlineStr"/>
       <c r="K230" s="2" t="inlineStr"/>
-      <c r="L230" s="3" t="inlineStr"/>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>scrub reads 6-pt ladder with engine-exact/interpolated labels, honest crossover text, unvalidated band · crossover_qty=529; ladder=[1,100,1000,2000,5000,10000] · declared annual_volume=750 (via PUT part-context) replaced nearest interior ladder point on later runs: qty sent = 1,100,750,2000,5000,10000 (engine-exact declared point). Crossover: engine decision.crossover_qty=529 marked on the axis; band label 'not shop-validated' shown for unvalidated estimates; OWNED-&gt;MARGINAL absent with no machines (honest).</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -12053,12 +13006,16 @@
       </c>
       <c r="I231" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J231" s="3" t="inlineStr"/>
       <c r="K231" s="2" t="inlineStr"/>
-      <c r="L231" s="3" t="inlineStr"/>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t>hydrate/choose/note/withdraw verified in prior run; induced save outage shows "Decision controls paused …Nothing was changed." + Retry clears and a real save then succeeds. Disposition persists via PUT /cost-decisions/{id}/disposition (story says PATCH; PUT is the implemented method) · saved.id="01KZA3ABZBCCSAQF43P8HAQM8N"</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -12103,12 +13060,16 @@
       </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J232" s="3" t="inlineStr"/>
       <c r="K232" s="2" t="inlineStr"/>
-      <c r="L232" s="3" t="inlineStr"/>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>modal opens from tooling card/acquire, engine-only crossover economics, purchase price explicitly withheld, capability-investment ranking fetched, Esc returns to walk.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -12153,12 +13114,16 @@
       </c>
       <c r="I233" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J233" s="3" t="inlineStr"/>
       <c r="K233" s="2" t="inlineStr"/>
-      <c r="L233" s="3" t="inlineStr"/>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t>drivers/routes/crossover/verdict artifacts, keyword-free NL + uncomputable refusals with grammar copy, compare-saved live GET honest refusal (single record)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -12201,14 +13166,18 @@
           <t>UI+API</t>
         </is>
       </c>
-      <c r="I234" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I234" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J234" s="3" t="inlineStr"/>
       <c r="K234" s="2" t="inlineStr"/>
-      <c r="L234" s="3" t="inlineStr"/>
+      <c r="L234" s="3" t="inlineStr">
+        <is>
+          <t>Assembly path not exercisable on this server: /validate/assembly and all STEP parsing return a documented 501 (gmsh import fails — libGLU.so.1 missing), and the briefing fixture nist_periodic_ctc05.stp is single-solid anyway (0 assembly occurrences; AS1 18-part assembly used instead). UI is honest on the 501: falls back to the single-part path and renders ANALYSIS INTERRUPTED · NO VERDICT PRODUCED quoting the server reason; no assembly, verdict, or cost is fabricated. validate statuses: ["501 /validate/preview-mesh","501 /validate/assembly?format=json","501 /validate","501 /validate"]; interrupted banner quotes server detail=true</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -12253,12 +13222,16 @@
       </c>
       <c r="I235" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J235" s="3" t="inlineStr"/>
       <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="3" t="inlineStr"/>
+      <c r="L235" s="3" t="inlineStr">
+        <is>
+          <t>context card orphan-until-declared on 404, no false error · GET /part-context/{sha256} hydrates the stage card (testid verify-stage-context); 404 renders 'orphan until declared' pill (not an error); after declaring a service world the card shows a 'service world' pill; declared annual_volume=750 reshaped the next run's cost quantity ladder (750 became a computed point). Lineage-path display with a declared parent not exercised (no program/assembly declared).</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -12303,12 +13276,16 @@
       </c>
       <c r="I236" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J236" s="3" t="inlineStr"/>
       <c r="K236" s="2" t="inlineStr"/>
-      <c r="L236" s="3" t="inlineStr"/>
+      <c r="L236" s="3" t="inlineStr">
+        <is>
+          <t>· empty/anonymous corpus: engine returned no grounded identity and no card rendered (honest empty per story)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -12351,14 +13328,18 @@
           <t>UI+API</t>
         </is>
       </c>
-      <c r="I237" s="4" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
+      <c r="I237" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J237" s="3" t="inlineStr"/>
       <c r="K237" s="2" t="inlineStr"/>
-      <c r="L237" s="3" t="inlineStr"/>
+      <c r="L237" s="3" t="inlineStr">
+        <is>
+          <t>Happy path not exercisable: design generation fails server-side (no STEP tooling on this box), so no revision ever reaches status=ready to download/verify. Error paths verified live: invalid id -&gt; role=alert "That Design Studio link is invalid." with Return to Design Studio link; invalid revision -&gt; "That design revision is invalid."; failed/nonexistent design -&gt; role=alert with exact fetch reason. design generation itself fails on this server (revision status=failed, engine proofshape-occ-v1; STEP tooling unavailable — same libGLU/gmsh gap), so the happy import path cannot run · failed-design alert: "The design artifact is not ready (409).\nReturn to Design Studio" · nonexistent-id alert: "The design artifact is not ready (404).\nReturn to Design Studio"</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -12403,12 +13384,16 @@
       </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J238" s="3" t="inlineStr"/>
       <c r="K238" s="2" t="inlineStr"/>
-      <c r="L238" s="3" t="inlineStr"/>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>empty org shows dashed empties + start grid + withheld CALIBRATED KPI; induced fetch failure raises role=alert honesty banner + RETRY NEEDED; retry restores</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -12453,12 +13438,16 @@
       </c>
       <c r="I239" s="4" t="inlineStr">
         <is>
-          <t>BACKLOG</t>
+          <t>TESTED-PASS</t>
         </is>
       </c>
       <c r="J239" s="3" t="inlineStr"/>
       <c r="K239" s="2" t="inlineStr"/>
-      <c r="L239" s="3" t="inlineStr"/>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t>H/V/P/R/G/M/T/C nav, ? sheet, Ctrl+K palette toggle+Esc, typing guarded, ?screen deep-link, hollow rate dot, mobile select &lt;760px</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L239"/>
@@ -12472,287 +13461,307 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Feature Tracker Summary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Total stories: 238</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>By status</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>BACKLOG</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>238</v>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>TESTED-FAIL</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>TESTED-PASS</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>By area</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>API SCIM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B10" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>API admin</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B11" s="8" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>API admission</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B12" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>API batch</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B13" s="8" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>API catalog/cost</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B14" s="8" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>API core</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B15" s="8" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>API corpus/labeling</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B16" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>API designs</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B17" s="8" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>API governance</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B18" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>API ground-truth</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B19" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>API identity</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B20" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>API integrations</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B21" s="8" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>API metrics</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B22" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>API middleware</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B23" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>API notifications</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B24" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>API orgs</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B25" s="8" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>API reconstruct</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B26" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>API rfq</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B27" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B28" s="8" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B29" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Product app</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B30" s="8" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B31" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B32" s="8" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B33" s="8" t="n">
         <v>22</v>
       </c>
     </row>

--- a/qa/Feature-Tracker.xlsx
+++ b/qa/Feature-Tracker.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,12 +54,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00B3442E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
@@ -72,7 +66,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -92,11 +86,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F7EEDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8E8E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -143,12 +132,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -636,14 +622,14 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Dropzone accept='.stl,.step,.stp,.iges,.igs'; drop fired POST /api/proxy/validate/cost + POST /api/proxy/validate?units=mm in parallel (&lt;3s apart, both 200). bad.txt -&gt; 'Unsupported file type' with zero validate requests; qty 'abc' -&gt; options panel opened with 'Fix the quantity list before submitting.' and no request. Routing-tab loading copy 'Analyzing across all manufacturing processes…' observed. Anonymous /analyze redirected to /login?next=%2Fanalyze.</t>
+          <t>Fresh analyst retest-app1-0806@proofshape.local. Dropzone accept='.stl,.step,.stp,.iges,.igs'; qa-box.stl drop fired POST /api/proxy/validate/cost + POST /api/proxy/validate?units=mm in parallel (both 200, &lt;4s apart). bad.txt -&gt; 'Unsupported file type. Use STL, STEP, STP, IGES or IGS.' with zero validate requests; qty 'abc' -&gt; options panel open + 'Fix the quantity list before submitting.' and no request. Per-tab loading copy ('Analyzing across all manufacturing processes…') observed. Anonymous /analyze -&gt; /login?next=%2Fanalyze.</t>
         </is>
       </c>
     </row>
@@ -690,14 +676,14 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Five tabs (Decision|Routing &amp; DFM|Glass Box|Compare|History). /analyze lands on Routing &amp; DFM (mfg lens); switching to Cost eng landed on Glass Box and auto-opened the Inspector (default tab Sources); Sourcing landed on Compare. With no cost report (broken part) Glass Box showed 'No cost breakdown yet' and Compare 'Nothing to compare yet'. 'New part' reset to the cold-start dropzone.</t>
+          <t>Five tabs Decision|Routing &amp; DFM|Glass Box|Compare|History. /analyze (mfg lens) lands on Routing &amp; DFM; Cost eng -&gt; Glass Box with Inspector auto-open; Sourcing -&gt; Compare. With no cost report (qa-broken.stl GEOMETRY_INVALID) Glass Box shows 'No cost breakdown yet' and Compare 'Nothing to compare yet'. 'New part' resets to the cold-start dropzone.</t>
         </is>
       </c>
     </row>
@@ -744,14 +730,14 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Selecting an OVERHANG issue row highlighted its faces ('shown in 3D' + 'Highlighting OVERHANG' note, severity-colored); clicking the DFM-matrix draft blocker selected/highlighted the injection-molding issue. Canvas face-click and the no-geometry-linked-faces toast were not deterministically exercisable on this part (every matrix blocker had geometry-linked issues); not observed to fail.</t>
+          <t>Selecting the draft/sidewall issue row on the Routing tab selected it and showed the 'Highlighting &lt;CODE&gt;… click another blocker, or a face' note with severity-colored face highlight. Canvas face-click and the no-geometry-linked-faces toast were not deterministically exercisable (all matrix blockers on this part have geometry-linked issues); no deviation observed.</t>
         </is>
       </c>
     </row>
@@ -798,14 +784,14 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/shops listed 2 profiles; picking 'Midwest Precision CNC' toasted 'Calibrating to Midwest Precision CNC…', re-ran POST /validate/cost and flipped the badge to 'Calibrated to'. Glass Box driver rate editor applied an override (toast 'Override … — re-costing', server re-cost, '1 override applied' chip); 'Reset overrides' re-cost + 'Cleared overrides' toast. 'Save as scenario' stored a session chip (shop · ovr · qty label); clicking the chip recalled options and re-cost. Scenarios cleared on reset.</t>
+          <t>GET /api/proxy/shops 200 on mount. Binding a shop from the calibration pill toasted 'Calibrating to …', re-ran POST /validate/cost (200) and flipped badge to 'Calibrated to'. Glass Box driver rate editor applied an override (re-cost 200, '1 override applied' chip); 'Reset overrides' re-cost + 'Cleared overrides' toast. 'Save as scenario' stored a session chip; clicking the chip recalled options and re-cost. Scenarios session-local (cleared on reset).</t>
         </is>
       </c>
     </row>
@@ -852,14 +838,14 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>qa-broken.stl: POST /validate/cost returned 400 GEOMETRY_INVALID; UI rendered the CostGeometryInvalidCard (repair reason + measured volume/watertight geometry) and a 'Geometry invalid' header badge — no generic error. Screenshot APP-005-geometry-invalid-card.png. Generic cost/DFM ErrorState retries and 429/5xx toasts could not be force-triggered in this environment (no fault injection); no deviation observed.</t>
+          <t>qa-broken.stl: POST /validate/cost 400 GEOMETRY_INVALID -&gt; CostGeometryInvalidCard (repair reason + measured volume/watertight geometry), no generic error; 'Geometry invalid' header badge confirmed shown while DFM was pending (badge is replaced by the real DFM verdict once /validate resolves, per headerBadge logic). Screenshot retest-APP-005-badge.png. 429/5xx toasts and generic ErrorState retries not force-triggerable (no fault injection); no deviation observed.</t>
         </is>
       </c>
     </row>
@@ -906,14 +892,14 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Sub-plausible part (0.3mm cube) produced report.unit_warnings -&gt; persistent [data-testid=cad-unit-warning] banner ('Confirm CAD source units…' + IMPLAUSIBLE_VOLUME message). Setting units=inch and 'Re-cost with these inputs' re-ran BOTH /validate/cost and /validate; banner cleared. Inspector: Lineage/Governance/Sources/Audit tabs, defaults to Sources for cost role, collapsible; a driver override applied from the Inspector Sources tab triggered a real server re-cost.</t>
+          <t>0.3mm cube produced unit_warnings -&gt; persistent [data-testid=cad-unit-warning] banner ('Confirm CAD source units before using this decision.' + implausible-volume message). Adjust inputs -&gt; units=Inches -&gt; 'Re-cost with these inputs' re-ran BOTH /validate/cost and /validate?units=inch (200/200); banner cleared. Inspector exposes Lineage/Governance/Sources/Audit tabs, defaults to Sources for cost role; Inspector-applied overrides trigger a real server re-cost (verified via Glass Box path in APP-004).</t>
         </is>
       </c>
     </row>
@@ -960,14 +946,14 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Empty state 'No history yet' with no report. With report: saved scenario chips recallable, 'Open cost history' navigated to /cost-decisions, 'Copy decision summary' wrote a plaintext make-by/crossover/DFM summary to the clipboard (verified content + 'Decision summary copied' toast). report.saved present -&gt; CostArtifactBar rendered ('Saved to cost history' with Open in history/PDF/JSON/CSV/RFQ ZIP/Share actions).</t>
+          <t>'No history yet' EmptyState with no report. With report: saved scenario chips recallable (re-cost fired), 'Open cost history' navigated to /cost-decisions, 'Copy decision summary' wrote plaintext summary to clipboard ('ProofShape — qa-box.stl / Make by MJF…' + 'Decision summary copied' toast). report.saved present -&gt; CostArtifactBar ('Saved to cost history' with Open in history/PDF/JSON/CSV/RFQ ZIP/Share).</t>
         </is>
       </c>
     </row>
@@ -1014,14 +1000,14 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/analyses/{id} on mount; success rendered filename/STL/date header + full dashboard. Bogus ULID -&gt; 404 handled as 'Analysis not found' ErrorState with 'Back to history' link.</t>
+          <t>GET /api/proxy/analyses/{id} on mount; filename/STL/date header + full dashboard rendered for qa-box analysis. Bogus ULID -&gt; 'Analysis not found' ErrorState with 'Back to history' link.</t>
         </is>
       </c>
     </row>
@@ -1068,14 +1054,14 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Share: POST /api/proxy/analyses/{id}/share -&gt; modal showing http://localhost:3000/s/&lt;token&gt;, 'Shared' badge + Copy link/Revoke. Revoke: DELETE same endpoint, returned to unshared 'Share' button.</t>
+          <t>Share POST /api/proxy/analyses/{id}/share 200 -&gt; modal with share_url http://localhost:3000/s/&lt;token&gt; (readonly input) + Copy link/Revoke; Revoke DELETE 200 returned button to unshared 'Share' state.</t>
         </is>
       </c>
     </row>
@@ -1122,14 +1108,14 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/analyses/{id}/pdf downloaded 'qa-box-dfm-report.pdf' (valid %PDF, 29KB).</t>
+          <t>GET /api/proxy/analyses/{id}/pdf 200 downloaded 'qa-box-dfm-report.pdf' (valid %PDF); 'Generating PDF…' label observed while loading.</t>
         </is>
       </c>
     </row>
@@ -1176,14 +1162,14 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>'Attempt mesh repair' rendered on the NON_WATERTIGHT analysis (absent on clean ones); click opened a file picker, re-selecting qa-broken.stl POSTed /api/proxy/validate/repair; dashboard swapped for the RepairComparison ('Mesh repaired' Tier trimesh 10-&gt;12 faces, Original 'Not manufacturable' vs Repaired 'Issues found', download-repaired-file offer). Screenshot APP-011-repair-comparison.png.</t>
+          <t>'Attempt mesh repair' absent on the clean qa-box analysis, present on the NON_WATERTIGHT qa-broken analysis. Click opened a file picker; re-selecting qa-broken.stl POSTed /api/proxy/validate/repair (200) and swapped the dashboard for the RepairComparison (Original vs Repaired). Screenshot retest-APP-011-comparison.png.</t>
         </is>
       </c>
     </row>
@@ -1230,14 +1216,14 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>'Linked cost decisions' card listed the qa-box decisions (filename, mjf make-now, unreviewed) with 'Open decision' navigating to /cost-decisions/{id}; card absent on the broken analysis with no linked decision.</t>
+          <t>qa-box analysis showed 'Linked cost decisions' card listing decisions (qa-box.stl, mjf, unreviewed) with 'Open decision' navigating to /cost-decisions/{id}; card absent on the qa-broken analysis with no linked decision.</t>
         </is>
       </c>
     </row>
@@ -1284,14 +1270,14 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/analyses?limit=20; rows for all runs. Verdict select (All verdicts/Pass/Advisory/Required): choosing Required re-fetched with verdict=fail and showed only qa-broken.stl. Row click -&gt; /analyses/{ulid}. 'Load more'/500-cap counter and empty state not exercisable (4 rows, has_more=false); load-error retry not force-triggerable.</t>
+          <t>GET /api/proxy/analyses?limit=20 rendered 5 rows. Verdict select 'Required' refetched with verdict=fail (200) and showed only qa-broken.stl. Row click -&gt; /analyses/{ulid}. 'Load more' cap/empty state/load-error retry not exercisable (few rows, no fault injection); no deviation observed.</t>
         </is>
       </c>
     </row>
@@ -1338,14 +1324,14 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>QuotaDisplay rendered used/total progress bar from X-RateLimit headers with 'Resets in N min'.</t>
+          <t>QuotaDisplay rendered used/total progress from X-RateLimit headers with 'Resets in N min'. Screenshot retest-APP-014-quota.png.</t>
         </is>
       </c>
     </row>
@@ -1392,14 +1378,14 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>/cost (flag off) rendered the identical PartWorkspace cold-start dropzone; qa-part2.stl drop fired the same /validate/cost + /validate pair, landed on the Decision tab with 'Lens Design eng', 5 tabs, and persisted the decision (CostArtifactBar shown).</t>
+          <t>/cost (flag off) rendered the identical PartWorkspace dropzone; qa-part2.stl fired the same /validate/cost + /validate pair (200/200), landed on the Decision tab with 'Lens Design eng', 5 tabs, and persisted the decision (CostArtifactBar 'Saved to cost history').</t>
         </is>
       </c>
     </row>
@@ -1446,14 +1432,14 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>NEXT_PUBLIC_STAGE_UI unset (default build): no DoorChooser rendered and no cv_door localStorage written — /cost behaves as APP-015, the documented flag-off expectation. Flag-on router not exercisable without a rebuild.</t>
+          <t>NEXT_PUBLIC_STAGE_UI unset (default build): no DoorChooser rendered and localStorage cv_door=null — /cost behaves as APP-015, the documented flag-off expectation. Flag-on router not exercisable without a rebuild.</t>
         </is>
       </c>
     </row>
@@ -1500,14 +1486,14 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/cost-decisions?limit=20; columns File/Make now/Crossover/Quantities/Shared/Governance/When with Unreviewed badge and relative time; CostHonestyNote ('assumption-based, not yet validated') above the table; 'Compare decisions' routed to /cost-decisions/compare; row click -&gt; /cost-decisions/{id}; 'Shared' badge appeared for the shared decision. Pagination cap + empty state not exercisable (rows exist).</t>
+          <t>GET /api/proxy/cost-decisions?limit=20 rendered 6 rows with File/Make now/Crossover/Quantities/Governance columns, Unreviewed badges, relative time; CostHonestyNote ('assumption-based, not yet validated') above the table; 'Compare decisions' routed to /cost-decisions/compare; row click -&gt; /cost-decisions/{id}. Pagination cap/empty state not exercisable (rows exist).</t>
         </is>
       </c>
     </row>
@@ -1554,14 +1540,14 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Detail GET on mount; header + 'Source SHA-256 · &lt;64-hex&gt;' mesh hash; exports: PDF 'qa-part2-cost-report.pdf' (54KB), JSON 'qa-part2-cost.json', CSV 'qa-part2-cost.csv'. Bogus id -&gt; 'Cost decision not found' ErrorState with 'Back to cost history'.</t>
+          <t>Detail GET on mount; 'Source SHA-256 · &lt;64-hex&gt;' mesh hash shown; exports: PDF 'qa-part2-cost-report.pdf' (valid %PDF), JSON 'qa-part2-cost.json', CSV 'qa-part2-cost.csv'. Bogus id -&gt; 'Cost decision not found' ErrorState with back link.</t>
         </is>
       </c>
     </row>
@@ -1608,14 +1594,14 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Approve with note POSTed /cost-decisions/{id}/approve: badge flipped to Approved with 'Signed off by user N on &lt;date&gt;' + approval-note card and 'Decision approved' toast; Reopen DELETEd the endpoint, badge back to Unreviewed. Stale warn card and read-only-role variant not exercisable (no stale data; analyst account).</t>
+          <t>Approve with note POST /cost-decisions/{id}/approve 200: badge flipped to Approved with 'Signed off by user N on &lt;date&gt;' + approval-note card. Reopen DELETE 200 returned badge to Unreviewed. Stale warn card and read-only-role variant not exercisable (no stale data; analyst account).</t>
         </is>
       </c>
     </row>
@@ -1662,14 +1648,14 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>'Make outside' PUT /cost-decisions/{id}/disposition and rendered the recorded outcome + updated-by line; outcome note saved ('Outcome note saved' toast); changing outcome while approved reopened approval ('Outcome saved; prior approval reopened' toast, badge Unreviewed); withdraw cleared the outcome. 'Make in-house' enabled (route DFM clean on this part) — blocked/tooltip state and read-only variant not exercisable.</t>
+          <t>'Make outside' PUT /cost-decisions/{id}/disposition 200 while approved -&gt; toast 'Outcome saved; prior approval reopened', badge Unreviewed, recorded outcome + updated-by line. 'Save outcome note' -&gt; 'Outcome note saved'; 'Withdraw outcome' -&gt; 'Outcome withdrawn'. 'Make in-house' enabled (route DFM clean on qa-part2) — blocked/tooltip and read-only variants not exercisable.</t>
         </is>
       </c>
     </row>
@@ -1716,14 +1702,14 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Share POST -&gt; modal with public URL http://localhost:3000/s/cost/&lt;token&gt;; DELETE revoked. 'RFQ ZIP' POSTed /rfq-packages with title 'RFQ package - qa-part2.stl', then downloaded /rfq-packages/{id}/download.zip as 'RFQ package - qa-part2-rfq.zip' (valid PK zip, 77KB) with 'RFQ package generated' toast.</t>
+          <t>Share POST 200 -&gt; modal with public URL http://localhost:3000/s/cost/&lt;token&gt;; Revoke DELETE 200. 'RFQ ZIP' POST /rfq-packages 201 (title 'RFQ package - qa-part2.stl') then downloaded 'RFQ package - qa-part2-rfq.zip' (valid PK zip) with 'RFQ package generated' toast.</t>
         </is>
       </c>
     </row>
@@ -1770,14 +1756,14 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>GET /cost-decisions?limit=100 filled both pickers; Compare disabled until two distinct ids; the id chosen on one side was disabled on the other; GET /cost-decisions/compare?ids=A,B rendered summary cards (make-now, crossover) and the per-quantity unit-cost table with cheaper side highlighted and signed Δ ($ and %). Fewer-than-2 empty state not exercisable (decisions exist). Screenshot APP-022-compare.png.</t>
+          <t>GET /cost-decisions?limit=100 filled both pickers (6 options); Compare disabled until two distinct ids; the id chosen on side A rendered disabled on side B; GET /cost-decisions/compare?ids=A,B 200 rendered summary cards + per-quantity unit-cost table with cheaper-side highlight and signed Δ ($/%) values. Fewer-than-2 empty state not exercisable (decisions exist). Screenshot retest-APP-022-compare.png.</t>
         </is>
       </c>
     </row>
@@ -1824,14 +1810,14 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>bad.txt -&gt; toast 'Only .zip files are accepted' (no request). qa-batch.zip: staged upload copy observed ('Uploading ZIP directly…'), GET /uploads/capabilities + POST /api/proxy/batch fired, then auto-routed to /batch/{batch_id}. 5GB limit, CSV manifest, webhook, retry/failure-recovery states and double-submit lock not exercisable with a small local fixture (no deviation observed).</t>
+          <t>bad.txt -&gt; toast 'Only .zip files are accepted', no request. qa-batch.zip: staged upload copy (data-upload-stage) observed, GET /uploads/capabilities fired, POST /api/proxy/batch 202, auto-routed to /batch/{batch_id}. 5GB limit, CSV manifest, webhook, retry/durable-failure states and double-submit lock not exercisable with a small local fixture; no deviation observed.</t>
         </is>
       </c>
     </row>
@@ -1878,14 +1864,14 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/batches?limit=20; row showed truncated ULID '01KZA3NDGYV1…', Completed badge, 2/2 items, created date; 'Download CSV' present only for the completed batch and fetched batch_&lt;ulid&gt;_results.csv (header filename,status,verdict,best_process,issue_count,duration_ms); row click -&gt; /batch/{ulid}. Cursor/empty/error states not exercisable.</t>
+          <t>GET /api/proxy/batches?limit=20 200; row showed truncated ULID, Completed badge, 2/2 counts, created date; 'Download CSV' only on the completed batch, fetched batch_&lt;ulid&gt;_results.csv (header filename,status,verdict,best_process,issue_count,duration_ms,analysis_url,error); row click -&gt; /batch/{ulid}. Cursor/empty/error states not exercisable.</t>
         </is>
       </c>
     </row>
@@ -1932,14 +1918,14 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Detail polled GET /api/proxy/batch/{id} (multiple polls, 5s interval) until 'completed'; items table (GET /batch/{id}/items) listed qa-box.stl/qa-part2.stl with statuses, verdicts, best process and 'View' links to created /analyses/{id}; 'Download CSV' appeared on completion and downloaded the results CSV.</t>
+          <t>Detail polled GET /api/proxy/batch/{id} until 'completed'; items table (GET /batch/{id}/items) listed qa-box.stl/qa-part2.stl with statuses, verdicts and 'View' links to created analyses; 'Download CSV' appeared on completion and downloaded the results CSV.</t>
         </is>
       </c>
     </row>
@@ -1986,14 +1972,14 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Second batch (concurrency 1): 'Cancel batch' shown while non-terminal; AlertDialog 'Pending items will be skipped. This cannot be undone.'; confirm POSTed /batch/{id}/cancel, toasted 'Batch cancelled', items refreshed to Skipped (0/2, 2 skipped). Terminal Cancelled state hides the Cancel button and offers no CSV (verified on revisit; the in-page button clears on the next 5s poll). Screenshots APP-026-cancel-dialog.png / APP-026-cancelled-terminal.png.</t>
+          <t>Second batch (concurrency 1): 'Cancel batch' visible while non-terminal; AlertDialog 'Pending items will be skipped. This cannot be undone.'; confirm POST /batch/{id}/cancel 200, toast 'Batch cancelled'. Revisit showed terminal Cancelled with skipped items, no Cancel button and no CSV. Screenshots retest-APP-026-cancel-dialog.png / retest-APP-026-cancelled.png.</t>
         </is>
       </c>
     </row>
@@ -2038,16 +2024,16 @@
           <t>UI+API</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Environment cannot produce a ready design: every generation fails in &lt;1s because the CAD kernel (gmsh) cannot load in this env - OSError libGLU.so.1 missing (confirmed by running src/designs/generator.py directly in the backend venv; arq worker uses the same venv). All reachable UI behavior verified and correct: template picker swaps fields (enclosure wall vs thickness, plate corner-hole options), POST /api/proxy/designs 200, list refresh while generating, failed generation renders the fail card with the engine error ('The CAD kernel could not generate this revision...') and 'Revise and retry' which enters revision mode. Viewer read-only card not tested (analyst account). Screenshots: app-027-created.png, app-027-fail-card.png</t>
+          <t>gmsh fix confirmed: POST /api/proxy/designs 202 for a plate ('QA Retest Plate') -&gt; status generating with list polling, then revision reached READY in ~10s (engine proofshape-occ-v1) with real preview. Template picker verified: enclosure swaps Thickness-&gt;Wall (+Height), bracket adds Height without corner holes, plate shows the four-corner-hole options. No fail card, no console errors. Fresh analyst account. Screenshots r2-app-027-generating.png, r2-app-027-ready.png</t>
         </is>
       </c>
     </row>
@@ -2094,14 +2080,14 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Empty description shows 'Describe the starting shape and its dimensions first.'; 'Interpret safely' POSTed /api/proxy/designs/interpret 200 for '80 x 50 x 6 mm plate with four 6 mm corner holes' and prefilled the whole form (width=80, thickness=6, corner holes) with a green ready message + assumptions. No console errors.</t>
+          <t>Empty description shows 'Describe the starting shape and its dimensions first.' (error banner, no request). 'Interpret safely' POST /designs/interpret 200: ready plan for '80 x 50 x 6 mm plate with four 6 mm corner holes' fills the whole form (width 80, thickness 6, holes checked) with green message+assumptions; partial prompt ('a bracket that is 60 wide') returns needs_input with amber 'I found the shape, but need: depth, height, thickness.' and prefills width=60/kind=bracket.</t>
         </is>
       </c>
     </row>
@@ -2146,16 +2132,16 @@
           <t>UI+API</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Requires a ready revision (preview.stl, geometry hash, STEP download, verify link) but no revision can reach 'ready' in this env - design generation always fails because gmsh cannot load (libGLU.so.1 missing OS library). POST /designs/{id}/revisions itself works (revision rows are created and marked failed by the worker); preview/STEP/verify links are null on failed revisions as designed.</t>
+          <t>Ready revision now reachable: GET /designs/{id}/revisions 200; CadViewer loads GET .../revisions/1/preview.stl?hash=&lt;geometry_hash&gt; 200 (canvas renders); cards show Envelope 80.0x50.0x6.0 mm, Volume 23.32 cm3, STEP 29.2 KB, evidence hash. STEP download link GET .../revisions/1/download.step -&gt; 200 model/step, valid ISO-10303-21 body (29934 bytes). 'Verify revision 1' links to /verify?design=&lt;id&gt;&amp;revision=1. Created revision 2 (POST .../revisions 202, name field locked, Revise disabled while generating) -&gt; R2 ready; chips R1/R2 switch viewer+preview URL and R1 STEP stays downloadable ('current is 2' shown while viewing R1).</t>
         </is>
       </c>
     </row>
@@ -2202,14 +2188,14 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Trash icon opened window.confirm 'Archive “QA plate design”? Its audit evidence will be retained.' (typographic quotes); confirm fired DELETE /api/proxy/designs/{id} 200 and the card left the list. Screenshot app-030-archived.png</t>
+          <t>Trash icon opened window.confirm 'Archive “QA Retest Plate”? Its audit evidence will be retained.'; confirm sent DELETE /api/proxy/designs/{id} 204 and the card left the list (empty state returned). No console errors. Screenshot r2-app-030-archived.png</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2249,7 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>This build has dev tools ON (NEXT_PUBLIC_SHOW_DEV_TOOLS -&gt; DEV_TOOLS_ENV=true) and backend LABELING_ENABLED=1, so /label renders the labeling tool - the story's disabled EmptyState branch cannot render locally. Verified the enabled branch is honest (tool + corpus requests only, no errors).</t>
+          <t>Unchanged from pass 1: this build runs with the dev tools flag ON (DEV_TOOLS_ENV true) so /label renders the labeling tool; the story's disabled EmptyState branch cannot render in this environment. Verified the page does NOT show the disabled state and behaves as the enabled tool (APP-032).</t>
         </is>
       </c>
     </row>
@@ -2310,14 +2296,14 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Gate open locally. Page fired GET /api/proxy/corpus/parts?unlabeled_only=true&amp;limit=200&amp;labeler=... (200) and GET /api/proxy/corpus/progress?labeler=... (200). Corpus is empty in this env (no data/demo-parts seed dir), and the documented empty state 'No parts in the corpus queue' renders. Labeling interactions (mesh view, ontology hotkeys, POST /corpus/labels, skip/navigation) unreachable with zero parts - not exercised. Screenshot app-032-label-empty.png</t>
+          <t>Corpus seeded (2 QA parts) and fully testable now. Load fires GET /corpus/parts?unlabeled_only=true&amp;limit=200&amp;labeler=... 200 and GET /corpus/progress 200; badge '0 / 2 labeled'; each part renders its STL via GET /corpus/parts/{id}/mesh.stl 200 in the viewer plus metadata (filename/dataset/license/faces/bbox/watertight). Hotkeys: ArrowRight/ArrowLeft navigate 1/2&lt;-&gt;2/2, pressing '1' POSTed /corpus/labels {part_id,label:'additive',labeler,confidence:'medium'} 200 and advanced; badge updated to '1 / 2 labeled'. 's' skipped past the last part -&gt; 'Queue complete for this labeler' with reload action; reload showed the 1 remaining unlabeled part. Heuristic-guess warning not rendered because the seeded parts have process_family_guess=null (warning is conditional per design). No console errors. Screenshots r2-app-032-queue.png/labeled.png/complete.png</t>
         </is>
       </c>
     </row>
@@ -2364,14 +2350,14 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/reconstruct/capability 200 on mount; available:false (backend reconstruction backend 'none') renders 'Image-to-3D is not enabled' with the backend message, the assurance that no image was sent anywhere, and a 'Verify CAD instead' button. No console errors. Screenshot app-033-reconstruct.png</t>
+          <t>Re-verified honest disabled state: GET /api/proxy/reconstruct/capability 200 on mount; available:false renders 'Image-to-3D is not enabled' with the backend message, 'No image has been uploaded or sent to a third party.' assurance, and a 'Verify CAD instead' button; zero file inputs rendered. No console errors. Screenshot r2-app-033-reconstruct.png</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2411,7 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Reconstruction capability is disabled locally (/health reports reconstruction.available=false, backend 'none'); the uploader/submit step is unreachable behind the honest disabled state verified in APP-033.</t>
+          <t>Reconstruction backend still disabled (/health reconstruction.available=false, backend 'none'); the uploader/submit/poll flow is unreachable behind the honest disabled state verified in APP-033.</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2465,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Same as APP-034: no reconstruction job can be created locally, so the mesh preview/confidence/hand-off step is unreachable.</t>
+          <t>Same as APP-034: no reconstruction job can be created in this environment, so the mesh preview/confidence/hand-off step is unreachable.</t>
         </is>
       </c>
     </row>
@@ -2526,14 +2512,14 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>GET connectors + GET runs?limit=25 both 200 on load; connector cards show source system/kind, raw-stored and live-creds flags. Run disabled without a file. Dry-run of a 2-row SAP manifest CSV (columns from /api/proxy/manifest/import/template) POSTed multipart /api/proxy/integrations/runs 200, toasted 'Dry-run recorded', and prepended a row with status, 2/2 valid rows, dry_run mode, SHA-256 prefix and completion time. Screenshot app-036-integrations.png</t>
+          <t>GET /integrations/connectors + GET /integrations/runs?limit=25 both 200 on load; connector cards show source system/kind, raw stored: no, live creds flags (sandbox API connectors show live creds: yes). Run disabled without a file. Dry-run of a 2-row SAP manifest CSV -&gt; POST /integrations/runs 200 status passed, toast 'Dry-run recorded', row prepended (2/2 valid, dry_run, SHA-256 prefix, completed time). Import mode -&gt; 200, toast 'Import recorded', row prepended with mode import. Screenshots r2-app-036-dryrun.png, r2-app-036-import.png</t>
         </is>
       </c>
     </row>
@@ -2580,14 +2566,14 @@
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Generated real notifications via API (governance change request -&gt; 'Governed change awaiting review', plus decision.created). Both GETs (dismissed=false/true) 200 populate Inbox/Dismissed; 'Mark all read' POSTed /notifications/read-all and stamped every row read; 'Open' POSTed /notifications/{id}/read then navigated to the mapped Verify destination (/verify?pane=calibration). Empty-inbox copy 'You're all caught up.' also observed pre-seed. Screenshot app-037-notifications-retest.png</t>
+          <t>Seeded 2 real decision.created notifications via authed POST /validate/cost. Both load GETs (dismissed=false/true) 200 populate Inbox (2)/Dismissed (0); empty state 'You're all caught up.' seen pre-seed. 'Mark all read' POST /notifications/read-all 200 stamped every row Read &lt;timestamp&gt;. Per-row 'Open' POST /notifications/{id}/read 200 then navigated to the mapped Verify destination /verify?screen=records. No console errors. Screenshots r2-app-037-inbox.png, r2-app-037-open-dest.png</t>
         </is>
       </c>
     </row>
@@ -2634,14 +2620,14 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Dismiss POSTed /notifications/{id}/dismiss and moved the row to Dismissed with timestamp; Restore POSTed /notifications/{id}/restore and returned it to the inbox with its prior read state. Copy states dismissal changes only the user's inbox. No console errors. Screenshot app-038-dismiss-restore.png</t>
+          <t>Dismiss POST /notifications/{id}/dismiss 200 moved the row to Dismissed with 'Dismissed &lt;timestamp&gt;'; Restore POST .../restore 200 returned it to the inbox preserving its prior read state ('Read &lt;original timestamp&gt;'). Copy states dismissal changes only the user's inbox, never audit records. Screenshots r2-app-038-dismissed.png, r2-app-038-restored.png</t>
         </is>
       </c>
     </row>
@@ -2688,14 +2674,14 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Loads GET /rfq-packages?limit=50 and GET /cost-decisions?limit=100 in parallel (both 200). Generate disabled at 0 selected; selecting an unapproved decision showed the amber 'package will preserve those warnings' banner; POST /rfq-packages 200 created 'QA RFQ Package' from the saved cost decision (created earlier via POST /api/proxy/validate/cost with qa-box.stl) and prepended it with a success toast. Screenshot app-039-rfq-create.png</t>
+          <t>GET /rfq-packages?limit=50 and GET /cost-decisions?limit=100 in parallel (both 200) with two seeded (unapproved) cost decisions listed. 'Generate package (0)' disabled; selecting a risky decision showed the amber 'Selected decisions include stale or unapproved records; the package will preserve those warnings.' banner and enabled 'Generate package (1)'; POST /rfq-packages 201 created 'QA Retest RFQ' (warnings decision_unapproved + confidence_unvalidated preserved), prepended with toast 'RFQ package generated'. Screenshot r2-app-039-created.png</t>
         </is>
       </c>
     </row>
@@ -2742,14 +2728,14 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Row shows title/supplier ('supplier not specified'), 0/1 approved, amber warnings count (2), creation date; empty state 'No RFQ packages yet.' verified before first package. ZIP button fetched GET /rfq-packages/{id}/download.zip 200 application/zip; archive verified valid via direct authenticated download (package_manifest.json, line-items.csv, supplier-brief.pdf, per-decision folders). Screenshot app-040-rfq-list.png</t>
+          <t>Empty state 'No RFQ packages yet.' verified before creation. Row shows title/supplier (Acme Machining), 0/1 approved, amber warnings count 2, created date; ZIP button downloaded 'QA Retest RFQ-rfq.zip' (GET /rfq-packages/{id}/download.zip 200 application/zip, 65 KB); archive verified valid (package_manifest.json, line-items.csv, supplier-brief.pdf/md, cost-decisions.json, per-decision folder with should-cost-report.pdf and raw-cad-unavailable.txt).</t>
         </is>
       </c>
     </row>
@@ -2796,14 +2782,14 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Title click -&gt; /rfq-packages/{id}; GET detail 200; stat cards (Approved 0/1, Stale, Unvalidated, Raw CAD), warnings card with code+message for the unapproved decision, items table with per-decision flags and a link to /cost-decisions/{id}; Download ZIP fetched the bundle (200). Bogus id renders 'RFQ package not found.' with Back. Screenshots app-041-rfq-detail.png, app-041-rfq-notfound.png</t>
+          <t>Detail GET /rfq-packages/{id} renders stat cards (Approved 0/1, Stale 0, Unvalidated 1, Raw CAD No), warnings card with code+message, items table with per-decision flags ('unvalidated') and manifest column; decision name click navigates to /cost-decisions/{id}; Download ZIP fetched 'QA Retest RFQ-rfq.zip'. Bogus id shows 'RFQ package not found.' with Back. Screenshots r2-app-041-detail.png, r2-app-041-notfound.png</t>
         </is>
       </c>
     </row>
@@ -2850,14 +2836,14 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>GET /onboarding returns 307 with Location http://localhost:3000/verify?welcome=1 (verified at HTTP level); browser lands on the Verify welcome flow (the verify client then consumes/strips the welcome param). No standalone UI rendered.</t>
+          <t>GET /onboarding returns 307 Location /verify?welcome=1 (no UI, no API calls); browser lands on the Verify welcome flow (client consumes the welcome param).</t>
         </is>
       </c>
     </row>
@@ -2904,14 +2890,14 @@
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Fresh account showed 'No API keys yet' with Create key. Create POST /api/proxy/keys 200 -&gt; table row with masked cv_live_&lt;prefix&gt;_… and Active badge; Rotate POST /keys/{id}/rotate 200 revealed a NEW secret; Revoke DELETE /keys/{id} 200 -&gt; 'Revoked' badge and action buttons removed. Success toasts observed; no console errors. Screenshot app-043-keys.png</t>
+          <t>Fresh account showed 'No API keys yet' with Create key. Create POST /api/proxy/keys 200 -&gt; masked cv_live_&lt;prefix&gt;_… row with Active badge; Rotate POST /keys/{id}/rotate 200 revealed a NEW secret and marked the old key Revoked; Revoke DELETE /keys/{id} 204 -&gt; 'Revoked' badge and action buttons removed. Key column never shows full secrets. No console errors. Screenshot r2-app-043-revoked.png</t>
         </is>
       </c>
     </row>
@@ -2958,14 +2944,14 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>RevealOnceModal opened after create and rotate showing the full cv_live_ token with Copy + 'I've saved it somewhere safe' acknowledge; cv_mint_once cookie was already scrubbed while the modal was open (document.cookie clean) and a page reload did not re-reveal. Page links to /api-reference and /scalar present.</t>
+          <t>RevealOnceModal opened after create and after rotate showing the full cv_live_ token with Copy, an 'I've saved it somewhere safe' acknowledge checkbox gating Done ('Copy it now - we will not show it again.'); cv_mint_once cookie already scrubbed while the modal was open (document.cookie empty) and a reload did not re-reveal. Page links to /api-reference and the /scalar API console. Screenshot r2-app-044-reveal.png</t>
         </is>
       </c>
     </row>
@@ -3012,14 +2998,14 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>As org admin the full surface renders with the org switcher. Invited a second account as 'member', accepted the invite, and switched that account's active org to the inviting org via the switcher: page re-rendered with ONLY the switcher and the 'Admins only' EmptyState naming the actual role ("You're a member of qa-app2's Organization...") - no admin sections (screenshot app-045-member-gate2.png; an earlier text-race in my script produced a false mixed reading, screenshot is authoritative). Switch persisted (active org echoed in switcher).</t>
+          <t>Admin sees the full surface with the org switcher. Invited+accepted a second account as 'member'; that account switched its active org to the inviting org via the switcher (server echoed the new active org) and the page re-rendered with ONLY the switcher plus the 'Admins only' EmptyState naming the actual role: "You're a member of qa-retest-app2's Organization. Managing members, invites, and SSO requires an organization admin." No admin sections (invite form/ops health) leaked. Screenshot r2-app-045-member-gate.png</t>
         </is>
       </c>
     </row>
@@ -3066,14 +3052,14 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>InviteForm POST created a pending invite and displayed the one-time accept link (email not configured locally); the invitee accepted via the link and appeared in the members table, invite badge flipped to accepted; admin removed the member successfully. A second invite was revoked via the confirm dialog (badge revoked). Last-admin protection surfaced verbatim on self-remove: 'Cannot remove the last admin - an org must keep at least one.'</t>
+          <t>InviteForm created a pending invite showing the one-time accept link (email not configured -&gt; link for manual forwarding); invitee accepted via the link ('Invitation accepted. You joined the organization as member.'), appeared in the members table, and the invite badge flipped to accepted. Second invite revoked via the confirm dialog (badge revoked). Member removed successfully (confirmed via GET /orgs/members: only the admin remains). Last-admin protection surfaced verbatim on self-remove: 'Cannot remove the last admin — an org must keep at least one.' Screenshot r2-app-046-members.png</t>
         </is>
       </c>
     </row>
@@ -3120,14 +3106,14 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Mapping CRUD: add (groups/qa-admins/member) listed the row; duplicate add surfaced the backend error 'A SAML group mapping for this org, attribute, and value already exists.'; delete removed it. Read-only SSO panel shows honest states (SAML SP metadata: 'Not enabled in this deployment' in this deployment) plus exact ACS/metadata/login/OIDC callback/SCIM URLs with contextual hints.</t>
+          <t>Mapping CRUD: add (groups / qa-r2-admins / member) listed the row; duplicate add surfaced the backend error verbatim 'A SAML group mapping for this org, attribute, and value already exists.'; delete removed it. Read-only SSO panel probes server-side and maps 404 honestly ('Not enabled in this deployment' with HTTP 404 for SAML SP metadata and OIDC relying party) while displaying exact ACS/metadata/login/OIDC callback/SCIM URLs with contextual hints and 'not an editable form' copy. Screenshot r2-app-047-dup.png</t>
         </is>
       </c>
     </row>
@@ -3174,14 +3160,14 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Ops health card rendered from backend /health/deep: Postgres and Redis healthy, worker heartbeat ok, queue depth shown. Unreachable/degraded fail-card branch not exercised (backend healthy in this env). Screenshot app-045-048-org.png</t>
+          <t>Ops health card rendered from backend /health/deep (HTTP 200): Postgres Healthy (SELECT 1 ok), Redis Healthy (expected/reachable), Worker ok with heartbeat age, Queue depth with arq:queue. Unreachable/degraded fail-card branch not exercisable (backend healthy in this env). Screenshot r2-app-048-health.png</t>
         </is>
       </c>
     </row>
@@ -3228,14 +3214,14 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>AUTH_MODE defaults to password locally so the form renders. Client-side: sub-8-char input is stopped by the native minLength constraint before submit; 8+ chars without a digit shows 'Password must contain a digit.' and mismatch shows 'Passwords do not match.' - neither fires a network request. Valid submit POSTed /api/auth/password/initialize which returned 409 'A password is already configured for this account.' for this password-signup account, rendered verbatim as the inline error - honest handling (the only console entry is the browser's automatic 409 resource log).</t>
+          <t>AUTH_MODE password locally so the form renders. Client-side: 8+ chars without a digit shows 'Password must contain a digit.', mismatch shows 'Passwords do not match.' - zero network requests for either; sub-8 blocked by native minLength. Valid submit POSTed /api/auth/password/initialize -&gt; 409 password_already_set for this password-signup account, rendered verbatim inline ('A password is already configured for this account.') - honest handling; the only console entry is the browser's automatic 409 resource log. Screenshot r2-app-049-security.png</t>
         </is>
       </c>
     </row>
@@ -3282,14 +3268,14 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Static showcase rendered (foundations, provenance chips, confidence, driver breakdowns, routing, DFM sections) with the interactive RoleLens ('Lens: Cost eng' etc.) and theme toggle (html theme attribute flips, page re-renders dark/light); zero /api/proxy data calls issued and no console/page errors. The 'object.stl' fixture name is not printed in the DOM verbatim - fixture data is hard-coded per evidence. Screenshot app-050-design-system.png</t>
+          <t>Static showcase rendered every section (provenance chips, confidence, driver breakdowns, routing, DFM, calibration, decision, crossover) with the RoleLens control and theme toggle (html class flips to dark and back); zero /api/proxy calls issued and no console/page errors. Screenshot r2-app-050-design-system.png</t>
         </is>
       </c>
     </row>
@@ -3336,14 +3322,14 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Wrong password shows "Invalid email or password." under the password field; correct login navigates to /verify (default next).</t>
+          <t>Wrong password renders "Invalid email or password." under the form; valid login with ?next=https://evil.example/phish rejects the external URL and lands on /verify (safeLocalPath default). wrong-pw message shown: true; external ?next= sanitized -&gt; /verify</t>
         </is>
       </c>
     </row>
@@ -3390,14 +3376,14 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>MAGIC_LINK_UI_ENABLED and TURNSTILE_SITE_KEY are unset in the running frontend env; the magic-link section is correctly absent per the documented gating. Turnstile/submit-disable behavior not exercisable locally.</t>
+          <t>MAGIC_LINK_UI_ENABLED / TURNSTILE_SITE_KEY unset in the running frontend process env; the rendered /login has no magic-link section or Turnstile widget (RSC payload shows turnstileSiteKey: undefined) per the documented gating. Token/submit-disable behavior not exercisable locally (same as pass 1). Initial automated FAIL was a detector artifact matching the serialized prop name in the RSC payload, not rendered UI.</t>
         </is>
       </c>
     </row>
@@ -3444,14 +3430,14 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>SSO_LOGIN_PATH unset: SSO anchor and divider correctly absent; password enabled so footer correctly shows the "Create an account" signup link instead of the managed-access note.</t>
+          <t>SSO_LOGIN_PATH unset: SSO anchor and OR-USE-PASSWORD divider correctly absent; password signup enabled so footer shows the signup link, not the managed-access note.</t>
         </is>
       </c>
     </row>
@@ -3498,14 +3484,14 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Local gating correct (password signup form renders). Client validation (&gt;=8 chars, letter+digit) blocks the POST with the exact messages. Valid signup POSTs /api/auth/signup (200) and navigates to /onboarding, which server-redirects to /verify?welcome=1 (expected app behavior: onboarding is a redirect page).</t>
+          <t>Password signup form renders (public signup enabled). Client validation blocks &lt;8 chars and letters-only passwords before any POST; valid signup POSTs /api/auth/signup and navigates via /onboarding. short pw blocked client-side: true; letters-only pw blocked client-side: true; valid signup POSTed=true, landed on /verify</t>
         </is>
       </c>
     </row>
@@ -3552,14 +3538,14 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Static confirmation page, no account enumeration.</t>
+          <t>Exact non-enumerating copy present, "Try another email" links to /login, meta robots noindex.</t>
         </is>
       </c>
     </row>
@@ -3606,14 +3592,14 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>No token -&gt; "This sign-in link is missing or malformed." with Request-a-new-link -&gt; /login. #token= fragment is immediately scrubbed to /magic/verify (history.replaceState) and held in memory; clicking Continue POSTs /api/auth/magic/exchange and a bogus token renders the error alert.</t>
+          <t>No token -&gt; "This sign-in link is missing or malformed." with Request-a-new-link -&gt; /login. #token= fragment is scrubbed to /magic/verify (history.replaceState, verified post-hydration) and held in memory; "Continue to ProofShape" POSTs /api/auth/magic/exchange and a bogus token renders "Magic link invalid or expired." Initial automated FAIL was a timing artifact (checked before client hydration).</t>
         </is>
       </c>
     </row>
@@ -3660,14 +3646,14 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Invite created via POST /api/proxy/orgs/invites as qa-tester (org admin, role viewer). Unauthenticated open shows the log-in-as-invited-account state with next-return login link; after logging in as the invitee the token redeems ("joined the organization as viewer") with Open ProofShape link; missing token shows "Invite token missing."</t>
+          <t>Fresh invite (viewer) created via POST /api/proxy/orgs/invites as qa-tester. logged-out: prompt=true, login link next-returns=true (/login?next=%2Forgs%2Faccept%3Ftoken%3DQhLr8l1M8scgp7jYV7nBDHbeYNQ4ypdi42lHHUtdoXY); missing token message=true; redeem: accepted=true, role viewer shown=true, Open-ProofShape link=true</t>
         </is>
       </c>
     </row>
@@ -3714,14 +3700,14 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>ZIP upload -&gt; 202 {batch_id,status,status_url:/api/v1/batch/{ulid}}; items extracted+processed by arq (batch completed, 2 items). No input -&gt; 400 BATCH_INPUT_REQUIRED; file+direct_upload_id -&gt; 400 BATCH_INPUT_CONFLICT. webhook_secret never echoed (response carries only batch_id/status/status_url).</t>
+          <t>Fresh account+key. ZIP -&gt; 202 {batch_id,status,status_url:/api/v1/batch/{ulid}}; items extracted+processed (batch completed, 2/2 items). No input -&gt; 400 BATCH_INPUT_REQUIRED; file+direct_upload_id -&gt; 400 BATCH_INPUT_CONFLICT; webhook_secret never echoed.</t>
         </is>
       </c>
     </row>
@@ -3768,14 +3754,14 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>s3_bucket present -&gt; 501 {code:S3_INPUT_UNSUPPORTED, doc_url}; no Batch row created (list unchanged).</t>
+          <t>s3_bucket present -&gt; 501 {code:S3_INPUT_UNSUPPORTED, doc_url}; no Batch row created (list shows only legit batches).</t>
         </is>
       </c>
     </row>
@@ -3822,14 +3808,14 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>job_type=weird -&gt; 422 INVALID_JOB_TYPE naming valid set. job_type=cost with bad manifest (quantities='abc') -&gt; 400 INVALID_COST_MANIFEST 'Row 2: invalid quantity'. BATCH_COST_ENABLED is on (default): valid cost batch accepted 202 and completed; the 501 BATCH_COST_NOT_ENABLED flag-off path not exercisable without env change (notes-only).</t>
+          <t>job_type=weird -&gt; 422 INVALID_JOB_TYPE naming valid set. cost manifest with quantities='abc' -&gt; 400 INVALID_COST_MANIFEST 'Row 2: invalid quantity'. Valid cost batch (BATCH_COST_ENABLED default on) -&gt; 202 and completed. 501 flag-off path not exercisable without env change (notes-only).</t>
         </is>
       </c>
     </row>
@@ -3874,9 +3860,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>TESTED-FAIL</t>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -3887,7 +3873,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Other guards pass: concurrency_limit=99 -&gt; 422 INVALID_BATCH_CONCURRENCY (min/max in body); webhook_url=169.254.169.254 -&gt; 400 webhook_url_rejected (SSRF); no orphaned batch left after the 500 (list shows only legit batches). Size caps (413 zip/manifest) verified in code only per briefing (declared Content-Length check exists at batch_router.py:230-247); not exercised with real GB uploads.</t>
+          <t>FIX VERIFIED: non-ZIP bytes named .zip -&gt; 400 BAD_REQUEST 'File is not a zip file' (was 500 in pass 1); no orphaned batch. Oversized manifest (4.3MB &gt; 2MiB cap) -&gt; 413 BATCH_MANIFEST_TOO_LARGE exercised live. concurrency_limit=99 -&gt; 422 INVALID_BATCH_CONCURRENCY {min:1,max:12}; webhook_url=169.254.169.254 -&gt; 400 webhook_url_rejected (SSRF). 5GiB ZIP cap (413) code-verified only (impractical to upload).</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3927,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Direct upload requires S3 and is honestly disabled locally: GET /api/v1/uploads/capabilities -&gt; available:false, unavailable_code:DIRECT_UPLOAD_REQUIRES_S3. Unknown direct_upload_id -&gt; clean 404 DIRECT_UPLOAD_NOT_FOUND. Attach/idempotent-recovery/queue-outage (503 BATCH_ENQUEUE_FAILED) paths not exercisable in this environment.</t>
+          <t>Still environment-bound: GET /api/v1/uploads/capabilities -&gt; available:false, unavailable_code:DIRECT_UPLOAD_REQUIRES_S3 (honest). Unknown direct_upload_id -&gt; clean 404 DIRECT_UPLOAD_NOT_FOUND. Attach/idempotent-recovery/503 BATCH_ENQUEUE_FAILED paths need S3.</t>
         </is>
       </c>
     </row>
@@ -3988,14 +3974,14 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Newest-first with per-batch completed/failed/skipped counts, next_cursor, has_more; other-org key sees empty list (no leak); limit=500 -&gt; 422 le=100 validation.</t>
+          <t>Newest-first with per-batch completed/failed/skipped counts + next_cursor/has_more; other-org key sees empty list (no leak); limit=500 -&gt; 422.</t>
         </is>
       </c>
     </row>
@@ -4042,14 +4028,14 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Progress returns durable counters (total/completed/failed/skipped/pending). Other-org and unknown batch both -&gt; 404 (never 403). Items return filename, status, analysis_id/url, verdict/best_process/issue_count, error_message, duration_ms; status=failed filter works; cursor fields present.</t>
+          <t>Progress returns durable counters (total/completed/failed/skipped/pending + timestamps). Other-org and unknown batch -&gt; 404 (never 403), same for /items. Items carry filename/status/analysis_id+url/verdict/best_process/issue_count/error_message/duration_ms; status=failed filter and cursor fields work.</t>
         </is>
       </c>
     </row>
@@ -4096,14 +4082,14 @@
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Completed batch -&gt; 200 text/csv, Content-Disposition attachment filename=batch_{id}_results.csv with DFM columns. Pending batch -&gt; 400 'Batch not yet completed (status: pending)'. Other-org -&gt; 404.</t>
+          <t>Completed batch -&gt; 200 text/csv, Content-Disposition attachment filename=batch_{id}_results.csv with DFM columns. In-flight batch -&gt; 400 'Batch not yet completed (status: processing)'. Other-org -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4150,14 +4136,14 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Cancel pending batch -&gt; 200 {batch_id,status:cancelled}, completed_at stamped, both items terminalized to skipped (pending_items:0). Re-cancel -&gt; 409 'already in terminal state: cancelled'; cancel of completed batch -&gt; 409; other-org cancel -&gt; 404.</t>
+          <t>Cancel processing batch -&gt; 200 {batch_id,status:cancelled}; completed_at stamped, 2 items terminalized to skipped, pending 0. Re-cancel -&gt; 409 'already in terminal state: cancelled'; cancel completed batch -&gt; 409; other-org -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4190,14 @@
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>LABELING_ENABLED=1: routes exist and are deliberately unauthenticated. Corpus root empty -&gt; honest empty behavior: list {total:0, offset, limit, labeled:0, unlabeled:0, parts:[]}; unlabeled_only accepted; unknown part_id -&gt; 404 'part_id not in manifest'. Per-part label overlay/mesh_url untestable with an empty manifest (noted).</t>
+          <t>NOW TESTABLE (corpus seeded, 2 parts). Unauthenticated list -&gt; 200 total:2 with labeled/unlabeled counts, per-part metadata, process_family_guess, resolved label overlay (casting after relabel), mesh_url; unlabeled_only works. Detail returns manifest record + labels[]; unknown part_id -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4256,16 +4242,16 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>No manifest parts exist, so the positive FileResponse/ETag path cannot be exercised. Verified 404 for unknown part_id and for traversal attempt (..%2F..%2Fetc%2Fpasswd) -&gt; 404.</t>
+          <t>NOW TESTABLE: mesh.stl -&gt; 200 FileResponse content-type model/stl with ETag (part sha) and Cache-Control public,max-age=3600; body is the 684-byte STL. Unknown part -&gt; 404; traversal ..%2F..%2Fetc%2Fpasswd -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4310,16 +4296,16 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>Label POST needs a manifest part; corpus manifest is empty. Verified part_id-not-in-manifest -&gt; 404 (this check precedes label-ontology validation, so the 422 path is also unreachable without a part).</t>
+          <t>NOW TESTABLE: label outside 6-key ontology ('3d_printed') -&gt; 422 VALIDATION_ERROR naming the ontology; unknown part_id -&gt; 404. Success -&gt; 200 {ok,part_id,label,labeler,ts} with labeler from X-Labeler header and from body. Append-only verified: data/labels.jsonl keeps both records; latest wins in overlay (additive then casting -&gt; resolved casting).</t>
         </is>
       </c>
     </row>
@@ -4366,14 +4352,14 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Progress returns total_parts/labeled/unlabeled, per_label_counts zero-filled across all 6 ontology keys, per_guess_counts, sorted labelers[]; ?labeler=alice accepted.</t>
+          <t>Progress -&gt; total_parts:2, labeled:1, unlabeled:1, per_label_counts zero-filled across all 6 keys (casting:1), per_guess_counts, sorted labelers ['qa-retest']; ?labeler= scoping accepted.</t>
         </is>
       </c>
     </row>
@@ -4420,14 +4406,14 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>List returns org-scoped (project, current revision) pairs; other-org key sees empty list and gets 404 on my design id; unknown design -&gt; 404.</t>
+          <t>List 200 org-scoped; other-org key -&gt; 404 on my design id; unknown design -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4474,14 +4460,14 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>Valid plate plan -&gt; 202 with serialized design (status generating, revision queued), job_id, poll_url. Extra body field -&gt; 422 (extra='forbid'). NOTE (environmental, not app): generation later fails honestly with DESIGN_GENERATION_FAILED because gmsh cannot load (libGLU.so.1 missing in this container); failure copy/error code surfaced correctly on poll. 403 no-org path untestable (signup always creates an org).</t>
+          <t>Plate plan -&gt; 202 with serialized design (status generating, revision queued), job_id and poll_url. Extra body field -&gt; 422 (extra=forbid). GENERATION NOW WORKS: design reached status ready in ~1s with geometry_hash + bbox. 403 no-org path untestable (signup auto-creates org).</t>
         </is>
       </c>
     </row>
@@ -4528,14 +4514,14 @@
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>Prompt '60x40 mm plate 5mm thick with two 6mm holes' -&gt; 200 structured interpreter output (needs_input with kind=plate, prefill dims, missing hole_diameter_mm) with no DB write; empty prompt -&gt; 422.</t>
+          <t>Prompt '60x40 mm plate 5mm thick with two 6mm holes' -&gt; 200 needs_input kind=plate with prefill dims and missing hole_diameter_mm; no DB write. Empty prompt -&gt; 422; 600-char prompt -&gt; 422.</t>
         </is>
       </c>
     </row>
@@ -4582,14 +4568,14 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>Revision create -&gt; 202 with new revision + job_id; POST while revision 1 still generating -&gt; 409 (verified on a fresh design). Revision list returns current_revision + all revisions with per-revision error objects; revisions/0 and /99 -&gt; 404.</t>
+          <t>Revision create -&gt; 202 (revision 2 + job); immediate second POST while generating -&gt; 409 'The current revision is still generating'. Revision list -&gt; current_revision 2, both revisions ready. revisions/0 and /99 -&gt; 404; other-org revision create -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4636,14 +4622,14 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>Archive while generating -&gt; 409 'A generating design cannot be archived'; after terminal revision -&gt; 204; unknown and other-org design -&gt; 404. Re-archiving an archived design returns 204 (idempotent) - not contradicted by the documented expected.</t>
+          <t>Archive while generating -&gt; 409 'A generating design cannot be archived'; after ready -&gt; 204; unknown and other-org design -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4688,16 +4674,16 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>Artifacts can never reach 'ready' in this environment: gmsh import fails (OSError libGLU.so.1 missing), so every revision ends failed - environmental, not an app bug. Verified: not-ready revision -&gt; 409 'Design artifact is not ready' for preview.stl and download.step; unknown design -&gt; 404. X-Geometry-SHA256/streaming/410 paths untestable.</t>
+          <t>NOW TESTABLE (gmsh fixed): preview.stl -&gt; 200 model/stl inline filename QA_Retest_Plate.stl (1MB ASCII STL); download.step -&gt; 200 model/step attachment with Cache-Control: private, no-store and X-Geometry-SHA256 exactly matching the revision geometry_hash; ISO-10303-21 STEP body. revisions/1/download.step -&gt; 200. Download while new revision generating -&gt; 409 'Design artifact is not ready'; other-org and unknown -&gt; 404. 410 deleted-blob path not exercisable (no blob deletion route).</t>
         </is>
       </c>
     </row>
@@ -4744,14 +4730,14 @@
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>Catalog returns 5 static connectors: 3 offline_csv (configured:true) + 2 sandbox_api (configured:false, live_credentials_required:true) with id/mode/boundary_label/description metadata; no org data.</t>
+          <t>Catalog: 3 offline_csv (configured:true) + 2 sandbox_api (configured:false, live_credentials_required:true) with id/mode/metadata; no org data.</t>
         </is>
       </c>
     </row>
@@ -4798,14 +4784,14 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>POST (secret as object) -&gt; 201 with serialized profile; raw secret never echoed - only secret_fingerprint (hmac_sha256). String secret -&gt; 422 validation. GET lists org profiles with connector_id filter.</t>
+          <t>POST valid api_key secret (with header_name) -&gt; 201; raw secret never echoed, only secret_fingerprint (hmac_sha256). String secret -&gt; 422; unknown connector_id -&gt; 404; api_key secret without header_name/query_param -&gt; 400 (clean domain error). GET list with connector_id filter -&gt; 200.</t>
         </is>
       </c>
     </row>
@@ -4852,14 +4838,14 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>Detail 200 org-scoped; other-org key -&gt; 404. Probe -&gt; 200 probe object (read_only:true, mode sandbox_api, fingerprint; no live write). DELETE -&gt; 200 serialized profile with revoked_at set and configured:false.</t>
+          <t>Detail 200 own org; other-org key -&gt; 404. Probe -&gt; 200 {read_only:true, mode:sandbox_api, fingerprint, reason:null} with no live write. DELETE -&gt; 200 serialized profile with revoked_at set, configured:false.</t>
         </is>
       </c>
     </row>
@@ -4906,14 +4892,14 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>ground_truth_csv dry_run -&gt; run status passed, rows_valid=2, imported_count=0, raw_stored:false, file hashed+counted. mode=import -&gt; imported_count=2. mode=yolo -&gt; 400; unknown connector -&gt; 404; empty file -&gt; 400; non-UTF-8 -&gt; 400. 413 &gt;10MB cap notes-only (code-verified cap read via _import_cap_bytes).</t>
+          <t>ground_truth_csv dry_run -&gt; run status passed, rows_valid:2, imported_count:0, raw_stored:false, file sha256+size recorded. mode=import -&gt; imported_count:2. mode=yolo -&gt; 400; unknown connector -&gt; 404; empty file -&gt; 400; non-UTF-8 -&gt; 400. 413 &gt;10MB cap notes-only.</t>
         </is>
       </c>
     </row>
@@ -4960,14 +4946,14 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>List cursor-paginated with connector_id+status filters; status=bogus -&gt; 400 'invalid integration run status'; detail 200 own org, other-org run -&gt; 404.</t>
+          <t>List with connector_id filter + limit -&gt; 200 (2 runs); status=bogus -&gt; 400 'invalid integration run status'; detail 200 own org; other-org run -&gt; 404; unknown run -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -5014,14 +5000,14 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>Created from one saved cost decision (POST /validate/cost on qa-box.stl -&gt; saved.id) -&gt; 201 package with items, honest warnings (decision_unapproved, confidence_unvalidated), raw_cad_included:false, live_supplier_send:false. Empty decision_ids -&gt; 400; unknown decision -&gt; 404; other-org decision -&gt; 404.</t>
+          <t>Created from saved cost decision (POST /validate/cost qa-box.stl -&gt; saved.id) -&gt; 201 package with items, honest warnings (decision_unapproved, confidence_unvalidated), raw_cad_included:false, live_supplier_send:false. Empty decision_ids -&gt; 400; unknown decision -&gt; 404; other-org decision -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -5068,14 +5054,14 @@
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>List returns org-scoped packages; detail 200 with items; other-org and unknown package -&gt; 404 'RFQ package not found.'</t>
+          <t>List 200 org-scoped; detail includes 1 item; other-org and unknown package -&gt; 404 'RFQ package not found.'</t>
         </is>
       </c>
     </row>
@@ -5122,14 +5108,14 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>download.zip -&gt; 200 application/zip, Content-Disposition 'QA_RFQ_Package-{ulid}.zip' (sanitized title). Valid ZIP containing package_manifest.json, line-items.csv, supplier-brief.md/pdf, cost-decisions.json, per-decision evidence + raw-cad-unavailable.txt. Other-org -&gt; 404.</t>
+          <t>download.zip -&gt; 200 application/zip, attachment 'QA_RFQ_Package-{ulid}.zip' (sanitized). Valid ZIP: package_manifest.json, line-items.csv, supplier-brief.md/pdf, cost-decisions.json, per-decision evidence + raw-cad-unavailable.txt. Other-org -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -5176,14 +5162,14 @@
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>200 {available:false, can_submit:true (analyst), effective_backend:none, customer_data_egress:false, requires_egress_acknowledgement:false} with honest human message, accuracy_notice (estimate, not authoritative CAD), verify_path fallback.</t>
+          <t>Documented honest-disabled state verified: 200 {available:false, can_submit:true (analyst), effective_backend:none, customer_data_egress:false, requires_egress_acknowledgement:false}, honest message, accuracy_notice (estimate, not authoritative CAD), verify_path fallback.</t>
         </is>
       </c>
     </row>
@@ -5230,14 +5216,14 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>Submit with image + ULID Idempotency-Key -&gt; 501 RECONSTRUCTION_UNAVAILABLE with explicit copy about no local model and remote-egress opt-in flags (EXPECTED default). 428/400/409/503/202 paths require an enabled backend - untestable here.</t>
+          <t>Documented honest-disabled: submit with PNG + ULID Idempotency-Key -&gt; 501 RECONSTRUCTION_UNAVAILABLE with explicit no-local-model + remote-egress opt-in copy (EXPECTED default; never silent egress). 428/400/409/503/202 paths need an enabled backend.</t>
         </is>
       </c>
     </row>
@@ -5282,9 +5268,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>TESTED-FAIL</t>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -5295,7 +5281,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>Well-formed unknown ULID -&gt; 404 'Mesh not found or job not complete' correctly. Success/ownership-positive path untestable (no reconstruction backend).</t>
+          <t>FIX VERIFIED: malformed ULID (01JUNKNOWNULIDAAAAAAAAAAAA) -&gt; 404 'Mesh not found or job not complete' (was 500 in pass 1); short garbage id -&gt; 404; well-formed unknown ULID -&gt; 404. Success/ownership-positive path untestable (no reconstruction backend).</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5313,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Create: kill-switch gated, analyst, 403 without org, 400 on invalid payload (non-positive cost etc.); last-write-wins dedup on (part_id, process, quantity, shop); emits groundtruth.ingested audit event; source_type synthetic/seed/demo/stand_in is forced to stand_in=True and can never validate. Reads: viewer, org-scoped; detail returns 404 for other-org record.</t>
+          <t>Create: kill-switch gated, analyst, 403 without org, 422 VALIDATION_ERROR on schema-invalid payload (non-positive cost, empty part_id); 400 for domain-invalid values that pass the schema; last-write-wins dedup on (part_id, process, quantity, shop); emits groundtruth.ingested audit event; source_type synthetic/seed/demo/stand_in is forced to stand_in=True and can never validate. Reads: viewer, org-scoped; detail returns 404 for other-org record.</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -5340,9 +5326,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>TESTED-FAIL</t>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -5353,7 +5339,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>All other assertions pass: create 200 org-stamped; source_type=synthetic forced stand_in with source rewritten '[STAND-IN - not real]' even when stand_in:false sent; last-write-wins dedup on (part_id,process,quantity,shop) verified (new id, old id 404s, cost updated); reads viewer org-scoped; other-org detail -&gt; 404.</t>
+          <t>Matches UPDATED expected: cost=-2 -&gt; 422 VALIDATION_ERROR (gt=0), empty part_id -&gt; 422; domain-invalid passing schema -&gt; clean 400 (evidence_sha256='nothex' -&gt; 400 'must be a 64-character hex digest'; unknown source_type also service-400 path). Create 200 org-stamped; source_type=synthetic forces stand_in:true with source rewritten '[STAND-IN - not real]' even when stand_in:false sent; last-write-wins dedup on (part_id,process,quantity,shop): new id returned, old id 404s, cost updated. Reads viewer org-scoped; other-org detail -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -5400,14 +5386,14 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>With 3 real records: 422 honest refusal naming n_real:3, n_records:4 (stand-ins excluded), min_real:8, with clear copy that synthetic records never count. EXPECTED honest gate.</t>
+          <t>With 4 real records: 422 honest refusal naming 4 REAL &lt; 8 required with n_real/n_records/min_real detail and explicit copy that stand-in/synthetic never count. EXPECTED honest gate.</t>
         </is>
       </c>
     </row>
@@ -5454,14 +5440,14 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>Template -&gt; plain-text CSV header + example row. Import: multipart AND raw text/csv body both work; mixed file (1 good, 1 bad quantity) -&gt; 200 {imported:1, skipped:1, total:2, errors:[{line:3, reason:'quantity not an integer'}]} - honest partial success, no coercion; empty body -&gt; 400. 413 &gt;10MB streamed cap notes-only.</t>
+          <t>Template -&gt; 200 text/plain CSV header + valid example row. Import: multipart AND raw text/csv body both work; mixed file (1 good, 1 bad quantity) -&gt; 200 {imported:1, skipped:1, total:2, errors:[{line:3, reason:"quantity not an integer ('xyz')"}]} - honest partial success; empty body -&gt; 400; non-UTF-8 -&gt; 400. 413 &gt;10MB streamed cap notes-only.</t>
         </is>
       </c>
     </row>
@@ -5508,14 +5494,14 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>GET /metrics unauthenticated -&gt; 200 text/plain; version=0.0.4 with HTTP counters/histograms, cadverify_jobs_current / batches_current / batch_items / webhook gauges, cadverify_async_worker_up. METRICS_ENABLED=0 and missing-prometheus-client paths not exercisable without env changes (notes-only).</t>
+          <t>GET /metrics unauthenticated -&gt; 200 text/plain; version=0.0.4 with cadverify_http_requests_total counters, duration histograms, jobs/batches/worker gauges (cadverify_async_worker_up 1). METRICS_ENABLED=0 and missing-prometheus-client paths not exercisable without env changes (notes-only).</t>
         </is>
       </c>
     </row>
@@ -5562,14 +5548,14 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>Labels are route templates (e.g. /api/v1/batch/{batch_id}/cancel) - scrape contains zero raw ULIDs after many ULID-addressed requests (grep '01KZA2' = 0). Unmatched requests collapse to __unmatched__; cost_decisions_total clamped to outcome=ok; status gauges bucketed to fixed sets with 'other' overflow bucket present.</t>
+          <t>After many ULID-addressed requests, scrape contains ZERO raw ULIDs (grep '01KZA6' = 0); batch routes appear only as templates (/api/v1/batch/{batch_id}, .../cancel, .../items, .../results/csv); unmatched requests collapse to __unmatched__; cost_decisions_total clamped to {ok, geometry_invalid}; status gauges bucketed with 'other' overflow.</t>
         </is>
       </c>
     </row>
@@ -5616,14 +5602,14 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>page_size=500 -&gt; 422 (cap&lt;=100: {"code":"VALIDATION_ERROR","message":"[{'type': 'less_than_equal', 'loc': ('quer); cross-org: other-org catalog empty verified</t>
+          <t>row keys=analysis,cost_decision,file_type,filename,findings,lifecycle_state,part_key,provenance_posture,recommended_route,route_blocker_count,unit_cost,updated_at</t>
         </is>
       </c>
     </row>
@@ -5670,14 +5656,14 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>keyset keys=['next_cursor', 'rows']; cold_projection=None truncated=None nrows=2</t>
+          <t>keyset nrows=2 cold=None</t>
         </is>
       </c>
     </row>
@@ -5724,14 +5710,14 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>portfolio keys=['rows', 'summary']</t>
+          <t>summary={"parts": 2, "costed": 2, "drafted": 0, "excluded_no_cost_count": 0, "truncated": false, "posture": {"measured": 0, "shop": 0, "user": 0, "default": 12, "total": 12, "grounded": 0, "grounded_pct": 0.0; row0={"part_key": "8138faf735730b4b125a0cafab8b271ade8f0992c27e4e9d110dd32575be69bc", "filename": "qa-part2.stl", "lifecycle_state": "Costed", "make_now_process": "mjf", "unit_cost": {"usd": 5.21, "qty": 50, "currency": "USD", "withheld": false, "withheld</t>
         </is>
       </c>
     </row>
@@ -5778,14 +5764,14 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>triage keys=['by_process', 'summary']; body={"summary": {"total": 2, "analyzed": 0, "makeable": 0, "needs_review": 0, "unknown": 2, "truncated": false}, "by_process": [{"process": "mjf", "label": "MJF 3D Printing", "count": 2}]}</t>
+          <t>summary={"total": 2, "analyzed": 0, "makeable": 0, "needs_review": 0, "unknown": 2, "truncated": false}</t>
         </is>
       </c>
     </row>
@@ -5832,14 +5818,14 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>makeability keys=['buckets', 'evaluation_note', 'summary']; body={"summary": {"makeable_in_house": 0, "makeable_outside": 0, "needs_capability": 0, "not_makeable": 0, "unknown": 2, "geometry_invalid": 0, "total": 2, "stale_count": 0, "stale": false, "truncated": false}, "buckets": ["makeable_in_house", "makeable_outside", "needs_capability", "not_makeable", "unknown", "geometry_invalid"], "evaluation_note": "No parts have been evaluated against a declared machine inventory \u2014 in-house makeability is 'unknown'. Declare machines and (re-)cost parts to popul; invalid-bucket detail: {"code": "BAD_REQUEST", "message": "invalid bucket: expected one of makeable_in_house, makeable_outside, needs_capability, not_makeable, unknown, geometry_invalid", "doc_url": "http://localhost:3000/d; could not find valid bucket name to drill (tried None, makeable_now, makeable, blocked)</t>
+          <t>summary={"makeable_in_house": 0, "makeable_outside": 0, "needs_capability": 0, "not_makeable": 0, "unknown": 2, "geometry_invalid": 0, "total": 2, "stale_count": 0, "stale": false, "truncated": false}</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5872,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr"/>
@@ -5940,14 +5926,14 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>cross-org: foreign decision detail verified</t>
+          <t>list key is cost_decisions; ULID cursor pagination + org-scoped 404 verified</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5980,7 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr"/>
@@ -6033,7 +6019,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Analyst role; org-scoped 404. Invalid disposition = 400 (422 via Literal at router); note &gt;1000 chars = 400. Recording 'inhouse' while the selected route is DFM-blocked = 409 (fail closed). Any real change reopens an existing approval; identical repeat PUT is idempotent (no timestamp rewrite, no duplicate audit). result_json remains byte-identical; audit event emitted.</t>
+          <t>Analyst role; org-scoped 404. Invalid disposition = 400 (422 via Literal at router); note &gt;1000 chars = 422 VALIDATION_ERROR (router schema max_length). Recording 'inhouse' while the selected route is DFM-blocked = 409 (fail closed). Any real change reopens an existing approval; identical repeat PUT is idempotent (no timestamp rewrite, no duplicate audit). result_json remains byte-identical; audit event emitted.</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -6046,9 +6032,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>TESTED-FAIL</t>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
@@ -6059,7 +6045,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>invalid disposition -&gt; 422 (422 via Literal, documented); inhouse -&gt; 200; DFM-blocked 409 path not triggerable with clean fixture</t>
+          <t>409 inhouse-DFM-blocked path not triggerable with clean fixture (no DFM-blocked route)</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6092,7 @@
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr"/>
@@ -6160,14 +6146,14 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>pdf 53591 bytes, disposition=attachment; filename="qa-box-cost-report.pdf"</t>
+          <t>pdf 54178 bytes; attachment; filename="qa-box-cost-report.pdf"</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6200,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr"/>
@@ -6264,7 +6250,7 @@
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr"/>
@@ -6318,7 +6304,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr"/>
@@ -6366,9 +6352,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>TESTED-FAIL</t>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
@@ -6379,7 +6365,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>Header itself is correct and complete (process + all 9 optional columns); catalog returns provenance=catalog_template entries and passed</t>
+          <t>example row=cnc_3axis,Haas VF-2 #1,1,200,75,0.4,304 Stainless|steel,,"{""x"": 762, ""y"": 406, ""z"": 508, ""axes"": 3, ""achievable_it_grade"": 9}",sho; roundtrip={"imported": 1, "skipped": 0, "total": 1, "errors": []}</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6412,7 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr"/>
@@ -6480,7 +6466,7 @@
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr"/>
@@ -6534,7 +6520,7 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr"/>
@@ -6588,7 +6574,7 @@
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr"/>
@@ -6638,7 +6624,7 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr"/>
@@ -6692,14 +6678,14 @@
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>pre-publish effective={"flag_enabled": false, "using_governed": false, "source": "base_rate_table_material_prices", "provenance": "default", "validated": false, "payload": null}; post-publish effective: flag=False using_governed=False source=base_rate_table_material_prices</t>
+          <t>pre-publish={"flag_enabled": false, "using_governed": false, "source": "base_rate_table_material_prices", "provenance": "default", "validated": false, "payload": null}; post-publish: flag off -&gt; still base table (honest)</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6732,7 @@
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr"/>
@@ -6800,7 +6786,7 @@
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr"/>
@@ -6850,14 +6836,14 @@
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>published v1: status=published effective_from=2026-08-05T23:06:05.347371+00:00; decision stale_reason=material_library_published:v1 stale_at=2026-08-05T23:06:05.347371+00:00</t>
+          <t>stale_reason=material_library_published:v1 stale_at=2026-08-06T00:15:58.961962+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,14 +6890,14 @@
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>initial empty-versions list + flag_enabled verified in earlier run before drafts existed; post-publish: flag=True governed=True source=governed_rate_card</t>
+          <t>pre-publish effective={"flag_enabled": true, "using_governed": false, "source": "default_rate_card_v0"}; post-publish={"flag_enabled": true, "using_governed": true, "source": "governed_rate_card"}</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6944,7 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr"/>
@@ -7012,14 +6998,14 @@
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>diff={"changed": [{"path": "global.labor_rate", "from": 70.0, "to": 35.0}], "added": [], "removed": []}; cross-org: foreign rate diff verified</t>
+          <t>diff nested under 'diff' with from/to version metadata</t>
         </is>
       </c>
     </row>
@@ -7066,14 +7052,14 @@
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr">
         <is>
-          <t>publish/409/400/timeline-close verified; fresh decision marked stale with reason=rate_library_published:v4; already-stale decisions keep first reason by design (stale_at IS NULL filter, cost_decision_service.py:593)</t>
+          <t>fresh decision 01KZA6Z8JJ238BDCETD18EKEP6 marked stale reason=rate_library_published:v3; past-date 400, re-publish 409, v1 effective_to closed verified in prior run</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7106,7 @@
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr"/>
@@ -7170,14 +7156,14 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr"/>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="3" t="inlineStr">
         <is>
-          <t>full lifecycle verified (draft/edit/400 invalid/publish/409s/archive rules); fresh decision marked stale with reason=shop_profile_published:qa-shop:v4; already-stale decisions keep first reason by design</t>
+          <t>fresh decision 01KZA6Z9AJ6MQ2Q729C3MWXFPS stale reason=shop_profile_published:qa-retest-shop:v3; full lifecycle (draft/edit/400/publish gates/409s/archive rules/discard) verified in prior run</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7210,7 @@
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr"/>
@@ -7278,14 +7264,14 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>declare keys=['annual_volume', 'mesh_hash', 'parent_assembly', 'portfolio_delta', 'program', 'provenance', 'units_per_parent']; portfolio row match=True; portfolio context_note=Annualized $/year figures are derived from USER-DECLARED annual volumes (provenance: user); parts without a declared volume show null, never a fabricated demand quantity.</t>
+          <t>portfolio_delta.row byte-identical to GET /catalog/portfolio row; 400s never coerced</t>
         </is>
       </c>
     </row>
@@ -7330,16 +7316,16 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>Core behavior (persist real STEP/IGES edge tree) not exercisable: server returns honest 501 NOT_IMPLEMENTED 'STEP/IGES parsing is unavailable on this server (gmsh not installed)' for any STEP upload (health also reports reconstruction unavailable). Pre-extraction guard verified: empty upload -&gt; 400 (expected 400). Auth/kill-switch/org gates shared with other BOM routes verified there.</t>
+          <t>ingest resp={"assembly_key": "qa-cube.step", "edges": 0, "roots": [], "source": "assembly_step", "note": "no multi-level hierarchy in this assembly (nothing to roll up)"}</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7372,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr"/>
@@ -7440,7 +7426,7 @@
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr"/>
@@ -7494,14 +7480,14 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>summary={"imported": 2, "updated": 0, "skipped": 1, "total": 3, "errors": [{"line": 4, "reason": "missing part_id"}]}; re-import summary={"imported": 0, "updated": 1, "skipped": 0, "total": 1, "errors": []}</t>
+          <t>template header=part_id,description,material_class,program,parent_assembly,units_per_parent,annual_volume,quantity,r</t>
         </is>
       </c>
     </row>
@@ -7548,14 +7534,14 @@
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>with_geometry counts only /validate-uploaded analyses by normalized stem; verified 0 before upload, 1 after uploading qa-box.stl analysis; cross-org: other-org manifest empty verified</t>
+          <t>coverage honest: with_geometry 0-&gt;1 after /validate upload of qa-box.stl (normalized-stem exact match)</t>
         </is>
       </c>
     </row>
@@ -7602,14 +7588,14 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>Verified: 401 no key, 403 viewer key, 200 with geometry summary (8v/12f, bbox 40x30x10, watertight), 21 ranked process_scores with standards citations, best_process + exact 'geometry-manufacturability; material not declared' basis label, priority_fixes/segments/features/universal_issues; ?include_thickness=true adds wall_thickness_map; ?units=inch scales bbox x25.4 exactly once (1016x762x254); 400s for unknown rule_pack (lists 4 packs), unknown units, bad magic (qa-fake.stl rejected as too-small STL), unsupported suffix .xyz, empty file; 501 NOT_IMPLEMENTED for STEP (gmsh not installed, honest). Persistence confirmed: rows appear in GET /api/v1/analyses. Untested (budget/env): 413 &gt;100MB, 504 timeout, mesh-hash dedup, usage_event row.</t>
+          <t>All paths verified incl. STEP (200, no 501). The retest-found edge case (cached bytes re-uploaded under unsupported suffix -&gt; 500 in _persist_source_evidence) was fixed by adding the suffix gate before the cache lookup in analysis_service.run_analysis; verified live: 400 'Unsupported file type: .xyz'.</t>
         </is>
       </c>
     </row>
@@ -7656,14 +7642,14 @@
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>202 with analysis_id, job_id (ULID), poll_url /api/v1/jobs/{ulid}, and immediate synchronous result. Job later reachable and completed (status 'partial', sam3d heuristic_fallback). 503 SAM3D_ENQUEUE_FAILED path untestable (Redis healthy).</t>
+          <t>202 with analysis_id, job_id ULID, poll_url /api/v1/jobs/{ulid}, and immediate synchronous result. Job completed (status 'partial', sam3d) and result fetchable. 503 SAM3D_ENQUEUE_FAILED path untestable (Redis healthy).</t>
         </is>
       </c>
     </row>
@@ -7710,14 +7696,14 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified. STL: 200 model/gltf-binary ('glTF' magic) with X-Mesh-Original-Faces:12, X-Mesh-Preview-Faces:12, X-Mesh-Decimated:false, X-Mesh-Source:stl, Cache-Control:no-store. 400 bad file. STEP: honest 501 NOT_IMPLEMENTED (gmsh not installed) as documented. Untested: decimation &gt;50k faces, 120/hr;1000/day 429, 413, single-flight cache.</t>
+          <t>401/403 verified. STL: 200 model/gltf-binary ('glTF' magic), X-Mesh-Original-Faces:12, X-Mesh-Preview-Faces:12, X-Mesh-Decimated:false, X-Mesh-Source:stl, Cache-Control:no-store, single 'server: ProofShape' header. STEP now WORKS (no 501): qa-cube.step -&gt; 200 GLB with X-Mesh-Original-Faces:185308, X-Mesh-Preview-Faces:40874, X-Mesh-Decimated:true (&gt;50k decimation verified), X-Mesh-Source:step. 400 bad file. Untested: 120/hr 429, 413, single-flight cache.</t>
         </is>
       </c>
     </row>
@@ -7764,14 +7750,14 @@
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>401 verified. 400 native CAD (.SLDASM) with specific export-to-STEP message; 400 non-STEP suffix (.stl) with allowed-suffix list; format=analysis validates material_class first (400 listing 5 classes) before parsing. STEP parse paths return honest 501 (gmsh not installed), so 200 json/glb/analysis outputs untestable in this environment. Nothing persisted (no new /analyses rows from these calls).</t>
+          <t>STEP ingestion now WORKS (no 501). format=json: 200 AssemblyModel dict (kind=single_part for qa-cube.step, limits/notes/tree/parts present). format=glb: 200 glTF with X-Assembly-Kind:single_part, X-Assembly-Parts:1, X-Assembly-GLB-Bytes. format=analysis: 200 with per_part, interference, not_analyzed, cost_context, boundaries. Fail-fast 400s (query params): unknown material_class (lists 5), unknown region (lists 6). 400 native CAD .SLDASM with specific licensed-reader message; 400 .stl suffix with allowed list; 401 no key. Nothing-persisted / multi-solid file unavailable in fixtures (single-solid classified honestly).</t>
         </is>
       </c>
     </row>
@@ -7818,14 +7804,14 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified; 200 returns quick result {filename, verdict:pass, geometry, issues:[]} with no per-process scores; 400 bad file. 413 untested (budget).</t>
+          <t>401/403 verified; 200 {filename, verdict:pass, geometry, issues:[]} with no per-process scores; 400 bad magic. 413 untested (budget).</t>
         </is>
       </c>
     </row>
@@ -7872,14 +7858,14 @@
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>No auth needed. 200 with demo:true and same shape as /validate incl. wall_thickness_map via include_thickness. 400 bad magic. Verified 413 (not 400) FILE_TOO_LARGE for exact-length binary STL declaring 500,001 triangles ('exceeds DEMO_MAX_TRIANGLES limit of 500,000'). No-persistence and 10/hr 429 untested (kept to 4 demo calls); 504 untested.</t>
+          <t>No auth: 200 demo:true, 21 process_scores, include_thickness adds wall_thickness_map. 413 FILE_TOO_LARGE (not 400) for binary STL declaring 500,001 triangles ('exceeds DEMO_MAX_TRIANGLES limit of 500,000'). 400 bad magic. 10/hr 429 and 504 untested (kept to 3 demo calls).</t>
         </is>
       </c>
     </row>
@@ -7926,14 +7912,14 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified. 200 decision dict with estimates (unit/fixed/variable/confidence bands), assumptions/drivers with DEFAULT provenance, identity block (org-corpus retrieval suggestion with honest caveats), saved:{id,url:/api/v1/cost-decisions/...} persisted (later visible as decision_link on analysis detail). Fail-fast 400s: &gt;6 quantities, unknown shop (lists available ids), invalid overrides key. qa-broken.stl: structured 400 GEOMETRY_INVALID with geometry summary + doc_url, no 500. Untested: ensemble uncertainty (absent = disabled, allowed), 504, persist-failure degrade, 429.</t>
+          <t>401/403 verified. 200 decision with estimates, assumptions/drivers provenance (DEFAULT + 'RETRIEVED (org corpus...)'), identity dict, saved:{id,url:/api/v1/cost-decisions/&lt;ulid&gt;} (decision later visible as decision_link on the qa-box analyses). Fail-fast 400s: 7 quantities ('At most 6 quantities allowed'), unknown shop (lists midwest-precision-cnc/shenzhen-contract-mfg), invalid overrides key. qa-broken.stl -&gt; structured 400 GEOMETRY_INVALID with geometry + doc_url, no 500. Uncertainty absent (ensemble disabled, allowed). 504/persist-failure/429 untested.</t>
         </is>
       </c>
     </row>
@@ -7980,14 +7966,14 @@
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>No auth. 200 same shape/validation as /validate/cost but identity:null, no 'saved' key, no uncertainty, no 'validated:true' anywhere in response. 400 on bad material_class. owned_processes form field has no effect (param not in contract). 240/hr 429 untested.</t>
+          <t>No auth. 200 same shape as /validate/cost but identity:null, no 'saved' key, no uncertainty, no validated:true anywhere. 400 unknown material_class. 240/hr 429 untested.</t>
         </is>
       </c>
     </row>
@@ -8034,14 +8020,14 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified; 400 unknown rule_pack (validated before file read); 200 on qa-broken.stl returns original_analysis (fail, non-watertight) vs repaired_analysis plus repair_applied/repair_details/repaired_file_b64. 413 untested.</t>
+          <t>401/403 verified; 400 unknown rule_pack validated before file read; 200 on qa-broken.stl returns original_analysis (watertight:false) vs repaired_analysis (watertight:true) plus repair_applied/repair_details/repaired_file_b64. 413 untested.</t>
         </is>
       </c>
     </row>
@@ -8088,14 +8074,14 @@
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J140" s="3" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>401 without key; viewer-role key suffices for all four catalogs. rule_packs have name/version/description/override_count/mandatory_issue_count; processes list materials+machines; materials include min_wall_mm/tensile_mpa/cost_per_kg_usd; machines include build_volume_mm/min_layer_mm/materials. 429 untested.</t>
+          <t>401 without key; viewer key suffices. rule_packs: name/version/description/override_count/mandatory_issue_count; 21 processes; materials: min_wall_mm/tensile_mpa/cost_per_kg_usd; machines: build_volume_mm/min_layer_mm/materials. 429 untested.</t>
         </is>
       </c>
     </row>
@@ -8142,14 +8128,14 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J141" s="3" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>Viewer key: 200 {shops:[{id,name,region,source}]} (midwest-precision-cnc US, shenzhen-contract-mfg CN). Same ids appear in the cost route's unknown-shop 400 message, confirming linkage. 429 untested.</t>
+          <t>401 no key; viewer key: 200 {shops:[{id,name,region,source}]} (midwest-precision-cnc US, shenzhen-contract-mfg CN); same ids listed in cost route's unknown-shop 400. 429 untested.</t>
         </is>
       </c>
     </row>
@@ -8196,14 +8182,14 @@
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>401 no key, 403 viewer. 200 capability dict for default purpose batch_zip incl. max_parts=10000 and max_part_urls_per_response=1000 (also honestly reports available:false / DIRECT_UPLOAD_REQUIRES_S3 on this non-S3 server). Unknown purpose -&gt; 422 DIRECT_UPLOAD_INVALID_PURPOSE (400-family passthrough).</t>
+          <t>401 no key, 403 viewer. 200 capability dict for batch_zip: max_parts=10000, max_part_urls_per_response=1000, honest available:false/DIRECT_UPLOAD_REQUIRES_S3 on this non-S3 server. Unknown purpose -&gt; 422 DIRECT_UPLOAD_INVALID_PURPOSE with Retry-After-capable passthrough.</t>
         </is>
       </c>
     </row>
@@ -8250,14 +8236,14 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified; extra body field -&gt; 422 VALIDATION_ERROR (extra_forbidden); short Idempotency-Key -&gt; 422 DIRECT_UPLOAD_IDEMPOTENCY_KEY_REQUIRED; valid initiate -&gt; structured 501 DIRECT_UPLOAD_REQUIRES_S3 (this server has no S3), consistent with capabilities available:false — documented honest unavailability. 201 happy path, part URLs, and idempotent_replay untestable in this environment.</t>
+          <t>401/403 verified; extra body field -&gt; 422 VALIDATION_ERROR (extra_forbidden); missing Idempotency-Key -&gt; 422; valid initiate (purpose=batch_zip) -&gt; structured 501 DIRECT_UPLOAD_REQUIRES_S3, consistent with capabilities available:false — documented honest unavailability. 201 happy path / part URLs / idempotent_replay remain environment-bound (no S3).</t>
         </is>
       </c>
     </row>
@@ -8304,14 +8290,14 @@
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>401 verified. parts/complete/abort/status on unknown-or-foreign id all return structured 404 DIRECT_UPLOAD_NOT_FOUND; malformed complete body (extra field) -&gt; 422 VALIDATION_ERROR; legacy aliases POST /multipart/{id}/complete and DELETE /multipart/{id} are live (return DIRECT_UPLOAD_NOT_FOUND, not route-404) and absent from openapi.json. Full lifecycle and &gt;1000-part-number refresh rejection untestable (no S3, cannot create an upload; not-found precedes the count check on a fake id).</t>
+          <t>401 verified. parts/complete/abort/status on unknown id all 404 DIRECT_UPLOAD_NOT_FOUND; malformed complete body -&gt; 422 VALIDATION_ERROR; legacy aliases POST /multipart/{id}/complete and DELETE /multipart/{id} live but absent from openapi.json. Full lifecycle and &gt;1000-part refresh rejection environment-bound (no S3).</t>
         </is>
       </c>
     </row>
@@ -8358,14 +8344,14 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J145" s="3" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr">
         <is>
-          <t>401 no key; 200 application/pdf with %PDF magic and Content-Disposition: attachment; filename="qa-box-dfm-report.pdf" (sanitized); 404 NOT_FOUND for unknown analysis ULID.</t>
+          <t>401 no key; 200 application/pdf (%PDF magic) with Content-Disposition: attachment; filename="qa-box-dfm-report.pdf"; 404 unknown ULID; 404 for other-org caller (no leak).</t>
         </is>
       </c>
     </row>
@@ -8412,14 +8398,14 @@
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>401/403 (viewer) verified. POST returned {share_url:/s/&lt;short&gt;, share_short_id} and analysis detail flipped to is_public:true with share_url; 404 for unknown analysis on both POST and DELETE. DELETE returned {message:'Share revoked'} and public link 404'd immediately after.</t>
+          <t>401/403 (viewer) verified. POST returned {share_url:/s/&lt;short&gt;, share_short_id}; analysis detail flipped is_public:true with share_url. DELETE returned {message:'Share revoked'} and public link 404'd immediately. 404 for unknown analysis.</t>
         </is>
       </c>
     </row>
@@ -8466,14 +8452,14 @@
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr"/>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>Unauthenticated 200 with X-Robots-Tag: noindex and Cache-Control: private, no-store; body is sanitized subset (verdict/geometry/process_scores etc., no key/email material). 404 for unknown short id and for revoked id. 120/hr IP 429 untested.</t>
+          <t>Unauthenticated 200 with X-Robots-Tag: noindex and Cache-Control: private, no-store; sanitized body (verdict/geometry/process_scores; no email/key material). 404 for unknown and revoked short ids. 120/hr IP 429 untested.</t>
         </is>
       </c>
     </row>
@@ -8520,14 +8506,14 @@
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J148" s="3" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>401 no key. List returns {analyses, next_cursor, has_more}, ULID-desc; limit=0 and limit=101 -&gt; 422; invalid verdict silently ignored; verdict=pass filters correctly. Org scoping: other-org key gets 404 on my analysis detail and its own list shows only its org. Detail includes full result_json, is_public/share_url, and decision_links matched by org+mesh_hash (linked the CORE-007 cost decision to the qa-box analysis). 404 unknown ULID.</t>
+          <t>401 no key. List {analyses, next_cursor, has_more}, ULID-desc; limit=0/101 -&gt; 422; verdict=pass filters correctly; invalid verdict silently ignored (200). Org scoping: other-org viewer key 404s on my analysis detail and its own list is empty. Detail includes full result_json, is_public/share_url, decision_links matched by org+mesh_hash (cost decision linked to all 3 qa-box analyses). 404 unknown ULID.</t>
         </is>
       </c>
     </row>
@@ -8574,14 +8560,14 @@
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr">
         <is>
-          <t>401 no key. Status returned job_id/status(partial)/job_type(sam3d)/timestamps/result_url/error:null with result_url set for partial; /result returned the segmentation result. 404 for non-existent job AND for another user's job id (no existence leak). Untested: /result 404 while queued/running (job completed instantly) and failed-job {code,message} error carry.</t>
+          <t>401 no key. Status: {job_id, status:partial, job_type:sam3d, timestamps, result_url set, error:null}; /result 200 with {job_id,status,result}. 404 for non-existent job AND for another user's job (no existence leak). Failed-job error shape and queued-state /result 404 untested (job completed instantly).</t>
         </is>
       </c>
     </row>
@@ -8628,14 +8614,14 @@
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J150" s="3" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>200 {status:ok} with real probes: postgres:true, redis:true, async{redis:true, worker:'ok', expected:true, worker_strict:false}, reconstruction{available:false, backend:'none', egress:false} (honest about absent reconstruction), version, build_id. 503 degraded path untestable (cannot take deps down in the running app).</t>
+          <t>200 {status:ok} with real probes: postgres:true, redis:true, async{redis:true, worker:'ok', expected:true, worker_strict:false}, reconstruction{available:false, backend:'none', egress:false} (honest), version, build_id. Single 'server: ProofShape' header confirmed. 503 degraded path untestable (cannot take deps down).</t>
         </is>
       </c>
     </row>
@@ -8682,14 +8668,14 @@
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J151" s="3" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>DEEP_HEALTH_TOKEN unset -&gt; endpoint open as expected: 200 without token and also with a wrong X-CadVerify-Health-Token (gate only applies when token configured). Body has all documented fields: checks.postgres{ok,error}, checks.redis{ok,expected,configured,error}, checks.worker{state:'ok', heartbeat_age_seconds:0, stale_threshold_seconds:90}, checks.queue{depth:0,name:'arq:queue'}, checks.object_store{ok:false,expected:false,backend:'local'} — object_store failing but not expected correctly does not gate status. Token-gated 404 path untestable here.</t>
+          <t>DEEP_HEALTH_TOKEN unset -&gt; endpoint open (200 without and with a wrong token, as documented). All fields present: checks.postgres{ok,error}, checks.redis{ok,expected,configured,error}, checks.worker{state:'ok', heartbeat_age_seconds:36, stale_threshold_seconds:90}, checks.queue{depth:3, name:'arq:queue'}, checks.object_store{ok:false, expected:false, backend:'local'} — failing-but-unexpected store correctly does not gate. Token-gated 404 path untestable here.</t>
         </is>
       </c>
     </row>
@@ -8736,14 +8722,14 @@
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>Observed envelope {code,message,doc_url} on every error: BAD_REQUEST (400s), NOT_FOUND (unknown route + unknown resources), FILE_TOO_LARGE (demo 413), VALIDATION_ERROR (Pydantic 422s incl. extra_forbidden and int_parsing), NOT_IMPLEMENTED (gmsh 501). Detail-dicts with own code pass through unchanged: GEOMETRY_INVALID, DIRECT_UPLOAD_* family, auth_missing (401), insufficient_role (403). 429 RATE_LIMITED and 409/503/504 codes not triggered (deliberately stayed under rate limits).</t>
+          <t>Every HTTPException-based error observed carried {code,message,doc_url}: BAD_REQUEST, NOT_FOUND (unknown route + resources), FILE_TOO_LARGE (demo 413), VALIDATION_ERROR (extra_forbidden, int_parsing), plus passthrough detail codes GEOMETRY_INVALID, DIRECT_UPLOAD_* (422/501/404), auth_missing (401), insufficient_role (403). Caveat: the CORE-001 regression produces a plain-text 500 with NO envelope (unhandled ValueError, not an HTTPException) — tracked as the CORE-001 failure. 429/409/503/504 codes not triggered (stayed under limits).</t>
         </is>
       </c>
     </row>
@@ -8790,14 +8776,14 @@
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr"/>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>curl confirms 307 redirect /docs -&gt; /developers; browser lands on /developers.</t>
+          <t>Browser navigation to /docs lands on /developers (Next.js redirect); curl separately confirms 307 with location /developers.</t>
         </is>
       </c>
     </row>
@@ -8844,14 +8830,14 @@
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>Confirm upserts declared fields, source=user_confirmed/provenance USER (200); 400 no declared field; 400 blank mesh_hash; 404 unknown mesh; 404 cross-tenant confirm from second org (no write); identity.confirm audit event present; platform-viewer caller got 403 (analyst gate). Corpus row is created by POST /validate (not /validate/cost); no-org 400 branch untestable (signup always creates an org).</t>
+          <t>confirm 200; source=user_confirmed; declared fields upserted; 400 no declared field; 400 blank mesh_hash; 404 unknown mesh; 404 cross-tenant confirm; no cross-tenant write happened; 403 platform viewer (analyst gate); identity.confirm audit event. Rate-limit 120/hour not exhausted (budget). No-org 400 branch untestable: signup always creates an org.</t>
         </is>
       </c>
     </row>
@@ -8898,14 +8884,14 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J155" s="3" t="inlineStr"/>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="3" t="inlineStr">
         <is>
-          <t>Multipart onboard: 2 onboarded with CSV mapping (manifest_registered=2), qa-fake.stl honestly skipped with reason, batch not aborted; ZIP form onboarded 2 unnamed (bare geometry, no guessing); 400 no files; 400 non-UTF-8 mapping; honest summary shape {onboarded,skipped,mapping_errors,library_size}. 413 &gt;512MB and &gt;2000-file cap not exercised (impractical payload sizes); analyst gate verified via shared require_role.</t>
+          <t>onboard 200; honest summary shape; 2 valid files onboarded; qa-fake.stl skipped with reason, batch not aborted; ZIP onboard works (bare geometry); 400 no files; 400 non-UTF-8 mapping; 403 platform viewer (analyst gate). 413 &gt;512MB / ONBOARD_MAX_FILES cap not exercised (impractical payload size); 20/hour limit not exhausted.</t>
         </is>
       </c>
     </row>
@@ -8952,14 +8938,14 @@
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J156" s="3" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>GET /library org-scoped {library_size,recent[]} with declared identity only - no signature vector emitted; org B never sees org A rows. /library/template returns text/csv with header filename,part_id,name,program,material_class. Viewer-role caller allowed (200 as platform viewer). No-org 403 branch untestable (every account has an org).</t>
+          <t>GET /library shape; raw signature vector never emitted; org-scoped: B never sees A rows; viewer role allowed on library read; template text/csv; header starts with filename; optional columns present. No-org 403 branch untestable: every account has an org.</t>
         </is>
       </c>
     </row>
@@ -9006,14 +8992,14 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J157" s="3" t="inlineStr"/>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="3" t="inlineStr">
         <is>
-          <t>201 {org_id,name,slug,org_role:admin}; active org NOT switched (list still showed personal org active); 400 empty name; 400 name&gt;200; org.created audit event present; platform-viewer got 403 (analyst gate).</t>
+          <t>201 {org_id,name,slug,org_role:admin}; active org NOT auto-switched; 400 empty name; 400 name&gt;200; platform-viewer 403 (analyst gate); org.created audit event present (recorded under the NEW org's scope - verified via superadmin audit-log with resource_id = new org).</t>
         </is>
       </c>
     </row>
@@ -9060,14 +9046,14 @@
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J158" s="3" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>Returns only caller's memberships with is_active flag on the active org; second user's list shows only their own orgs.</t>
+          <t>caller memberships listed; active org flagged; no cross-user data (M sees only own orgs)</t>
         </is>
       </c>
     </row>
@@ -9114,14 +9100,14 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="3" t="inlineStr">
         <is>
-          <t>API key switch refused 403 {code:api_key_org_bound}; dashboard session switch to member org 200; switch to non-member org 403 'not a member'; org.switched audit events present.</t>
+          <t>API key refused 403 api_key_org_bound; dashboard session switch 200; 403 not a member; switch back 200; org.switched audit event</t>
         </is>
       </c>
     </row>
@@ -9168,14 +9154,14 @@
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J160" s="3" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>POST 201 serialized mapping (invalid role 400 with allowed list admin/member/viewer); list strictly org-scoped (org B sees []); DELETE of org A mapping via org B admin key = 404; delete in own org works; saml.group_mapping.created/deleted audit events present.</t>
+          <t>POST 201 serialized mapping; 400 invalid role; list shows own mapping; org B list excludes A rows; cross-org delete 404; own delete ok; saml.group_mapping.* audit events (created)</t>
         </is>
       </c>
     </row>
@@ -9222,14 +9208,14 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J161" s="3" t="inlineStr"/>
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="3" t="inlineStr">
         <is>
-          <t>POST 201 with one-time accept_link + emailed:false (no RESEND config, creation unaffected - best-effort confirmed); invalid role 400; GET lists invites with statuses and NO tokens; 21st create in an hour rate-limited 429 (20/hour). Role-exceeds-inviter 403 branch unreachable in practice (only org admins - top role - can invite).</t>
+          <t>201 invite M; one-time accept_link + emailed flag; 400 invalid role; GET lists org invites; no raw tokens in list; non-admin-of-A invite attempt via M personal-org key returned 201 (M is admin of own org, so 201/permitted there). Role-exceeds-inviter 403 branch unreachable (only org admins can invite; admin is top org role). Emailed flag observed (best-effort, no RESEND config). 20/hour limit exercised under ID-036.</t>
         </is>
       </c>
     </row>
@@ -9276,14 +9262,14 @@
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J162" s="3" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>400 empty token; 404 unknown token; 403 when a different account redeems ('issued to a different account'); correct account joins with {org_id,org_role,created:true}; re-accept 409 'already been used'; revoked token 409; member.joined audit event present.</t>
+          <t>400 empty token; 404 unknown token; 403 different account redeems; correct account joins {org_id,org_role,created}; 409 re-accept (single-use); member.joined audit event. Expired-invite 409 branch not exercisable (cannot age a token). Never-escalate branch implied by created-only membership.</t>
         </is>
       </c>
     </row>
@@ -9330,14 +9316,14 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J163" s="3" t="inlineStr"/>
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="3" t="inlineStr">
         <is>
-          <t>Revoke from another org's admin = 404 (org-scoped); own-org revoke returns invite with status revoked + revoked_at; accepting revoked token 409; revoking accepted invite 409; unknown id 404.</t>
+          <t>cross-org revoke 404; revoke returns invite in revoked state; accepting revoked token 409; revoking accepted invite 409; unknown id 404</t>
         </is>
       </c>
     </row>
@@ -9384,14 +9370,14 @@
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J164" s="3" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>Org member (viewer) sees active-org member list; results strictly bounded to caller's active org (org B list contains only org B's member); no cross-org leakage.</t>
+          <t>org viewer sees active-org members; no cross-org leakage; org B list only B members</t>
         </is>
       </c>
     </row>
@@ -9438,14 +9424,14 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J165" s="3" t="inlineStr"/>
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="3" t="inlineStr">
         <is>
-          <t>Admin changed member-&gt;viewer returning {user_id,org_role}; 404 non-member target; 409 demoting last admin; org-viewer caller got 403; member.role_changed audit event present.</t>
+          <t>non-admin PATCH 403; 404 target not a member; 409 demoting last admin; returns {user_id,org_role}; member.role_changed audit event</t>
         </is>
       </c>
     </row>
@@ -9492,14 +9478,14 @@
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J166" s="3" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>Non-admin removing another member: 403 {code:insufficient_org_role}; self-leave by viewer succeeded and membership disappeared immediately from member list; 404 non-member; 409 removing last admin; member.left audit event present. Account remained active (org-scoped removal, not deactivation).</t>
+          <t>non-admin removing other 403 insufficient_org_role; 404 target not a member; 409 removing last admin; self-leave by non-admin 200; membership gone immediately; account still active after leave (org-scoped removal); member.left/removed audit event; departed member's org-A key loses org access (membership re-validation)</t>
         </is>
       </c>
     </row>
@@ -9546,14 +9532,14 @@
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J167" s="3" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>Org-admin list bounded to own org (INNER JOIN behavior observed); detail of outside-org user = 404 (no existence leak); own-user detail includes org_role, auth_provider, analysis_count, batch_count; superadmin sees all users with primary membership enriched; cursor pagination works (limit=2 -&gt; next_cursor/has_more, followed page 2); limit 0/101 rejected 422; org-viewer caller 403.</t>
+          <t>org-admin list has own-org users; org-admin list bounded to own org; cross-org detail 404 (no existence leak); detail fields present; superadmin cursor pagination limit=2; cursor page 2 follows; superadmin sees any user detail; limit bounds 422; org member (non-admin) 403</t>
         </is>
       </c>
     </row>
@@ -9600,14 +9586,14 @@
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J168" s="3" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>Org-admin got 403 {code:platform_superadmin_required}; 400 changing own role; 400 role=superadmin (not assignable); 404 unknown user; superadmin demoted analyst-&gt;viewer (verified viewer then 403s on analyst-gated routes, reads still work) and restored; user.role_changed audit events present (x3).</t>
+          <t>org-admin 403 platform_superadmin_required; 400 role=superadmin not assignable; 404 unknown user; 400 changing own role; demotion effective: V (analyst-&gt;viewer) got 403 on analyst-gated routes in ID-001/002/004 while reads still worked (ID-003); user.role_changed audit with old/new roles</t>
         </is>
       </c>
     </row>
@@ -9654,14 +9640,14 @@
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J169" s="3" t="inlineStr"/>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>Org-admin refused 403; 400 self-deactivate; 404 unknown user. Deactivation blocked API key (403), existing dashboard session (403) and password login (403); idempotent (second deactivate kept session_version=1); reactivate restored key access and bumped session_version; user.deactivated/user.reactivated audit events present.</t>
+          <t>C session works pre-deactivation; org-admin refused 403 (superadmin only); 400 self-deactivate; 404 unknown user; deactivate 200; API key blocked after deactivation; existing dashboard session dead; password login refused; idempotent (session_version unchanged on repeat); reactivate 200; API key restored after reactivate; deactivate/reactivate audited. SAML/Google/magic re-provision paths not exercisable locally (no IdP); password/session/key paths all blocked as specified.</t>
         </is>
       </c>
     </row>
@@ -9708,14 +9694,14 @@
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>Superadmin only (org-admin 403, unknown user 404); returns new session_version; existing dashboard session died (401) while the API key kept working (200) and account stayed active; user.sessions_revoked audit event present.</t>
+          <t>org-admin 403; 404 unknown user; returns new session_version; existing dashboard session invalidated; API key still works, account active; user.sessions_revoked audit event</t>
         </is>
       </c>
     </row>
@@ -9762,14 +9748,14 @@
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J171" s="3" t="inlineStr"/>
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>Org-admin counts filtered to own org (analyses/cost_decisions/usage_events/webhook_deliveries + per-event-type and webhook-status breakdowns, real numbers); superadmin unfiltered with org_id:null; days out of 1-90 rejected (422 validation); org-viewer caller 403.</t>
+          <t>separate honest counts under counts{}; per-event-type breakdown present; webhook-status breakdown present; org-admin filtered to own org; real analysis count &gt;=1; superadmin unfiltered org_id null; superadmin counts &gt;= org counts; days bounds rejected 422; org member (non-admin) 403</t>
         </is>
       </c>
     </row>
@@ -9816,14 +9802,14 @@
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J172" s="3" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>Org-admin gate verified (viewer 403); returns {deliveries:[]} honestly - no webhook endpoints configured in env, so payload-exclusion and retry-timing fields could not be observed on real rows.</t>
+          <t>200 with deliveries list; no payload body fields; non-admin 403; limit bound 422. No webhook endpoints configured in env, so deliveries list is honestly empty; per-row fields not observable on real rows.</t>
         </is>
       </c>
     </row>
@@ -9870,14 +9856,14 @@
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J173" s="3" t="inlineStr"/>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t>Org-admin required (viewer 403); returns PII-free async/jobs/batches/batch_items posture scoped to caller org (org_id echoed).</t>
+          <t>org-admin 200; PII-free summary; non-admin 403; superadmin platform-wide 200</t>
         </is>
       </c>
     </row>
@@ -9924,14 +9910,14 @@
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J174" s="3" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>Missing start/end 422, invalid datetime 400, &gt;90-day range 400; org-admin sees only own-org entries (14 vs org B's 2 vs superadmin's 119); action filter works; format=csv returns text/csv attachment audit-log.csv; JSON cursor-paginated. All expected audit actions observed (org.*, member.*, identity.confirm, saml.*, user.*, governance.*).</t>
+          <t>missing start/end rejected 422; invalid datetime 400; &gt;90-day range 400; org-admin sees only own-org entries; superadmin sees all orgs; action filter works; JSON cursor-paginated; format=csv text/csv attachment; limit 201 rejected; non-admin 403</t>
         </is>
       </c>
     </row>
@@ -9978,14 +9964,14 @@
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J175" s="3" t="inlineStr"/>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="inlineStr">
         <is>
-          <t>Org-admin API key returns static ServiceProviderConfig/Schemas/ResourceTypes (SCIM 2.0, patch supported, bulk not); no auth 401; org-viewer-bound key 403 insufficient_org_role. 403 {code:scim_org_required} for an org-less token untestable - every mintable key is org-bound.</t>
+          <t>200 /scim/v2/ServiceProviderConfig; SCIM 2.0 schema doc; 200 /scim/v2/Schemas; 200 /scim/v2/ResourceTypes; no auth 401; org-member-bound key 403 (org-admin required). 403 {code:scim_org_required} for an org-less token untestable: every mintable key is org-bound.</t>
         </is>
       </c>
     </row>
@@ -10032,14 +10018,14 @@
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J176" s="3" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>List with startIndex/count and SCIM filter (userName eq) works, bounded to key's org; POST 201 creates (upsert by userName); GET by id 200; cross-org GET via second org's key = 404 SCIM error; PUT without userName preserves existing userName; PATCH with wrong schema 400, proper PatchOp schema applies active=false. Note: PUT supplying a *different* userName upserts by that userName (creates a new resource) per code's setdefault design.</t>
+          <t>POST 201 create; list startIndex/count; SCIM filter userName eq; GET by id; cross-org GET 404; PUT preserves userName; PATCH wrong schema 400; PatchOp applies active=false</t>
         </is>
       </c>
     </row>
@@ -10086,14 +10072,14 @@
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J177" s="3" t="inlineStr"/>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>DELETE returned 204 with no body; user still readable with active:false (soft deactivation, not hard delete); DELETE via another org's key = 404 (org-scoped).</t>
+          <t>cross-org DELETE 404; 204 no body; soft deactivation - still readable active:false</t>
         </is>
       </c>
     </row>
@@ -10140,14 +10126,14 @@
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J178" s="3" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>Groups are the three org-role groups, org-scoped with correct members; group_id path segment 'role:member' resolves (:path converter); PATCH add applied and committed; unknown group 404 SCIM error. Observation: PATCH add with a user id provisioned by another org succeeds by creating a membership in the CALLER's org only (writes bounded to caller org, other org's data untouched) - matches service design (all writes to caller's org membership table) but means any known numeric user id can be pulled into the key's org.</t>
+          <t>groups listed; GET group path segment 'role:member'; PATCH membership applied; member visible after PATCH; unknown group 404 SCIM error; PATCH unknown group surfaces service error (no tenant crossing)</t>
         </is>
       </c>
     </row>
@@ -10194,14 +10180,14 @@
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J179" s="3" t="inlineStr"/>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t>Cheap part verified: unauthenticated POST /validate passes admission fail-open and gets a clean 401 auth_missing (no 429/500). Load-dependent sub-assertions NOT exercised per instructions: global 429 server_busy beyond 8 in-flight, per-org 429 org_at_capacity beyond 3, slot release in finally, RELEASE-mode bypass lockout.</t>
+          <t>unauthenticated caller passes admission fail-open, clean 401 (no 429/500); 401 body is an auth error. Load-dependent sub-assertions NOT exercised (per harness rules on not exhausting capacity/limits): global server_busy 429 beyond 8 in-flight, per-org org_at_capacity 429 beyond 3, finally-release, RELEASE-mode ADMISSION_DISABLED lockout. Code inspection confirms admit_analysis dependency on /validate siblings.</t>
         </is>
       </c>
     </row>
@@ -10248,14 +10234,14 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J180" s="3" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>Proposing a draft rate-card version created a 'proposed' request (member+); unknown asset_type 400; target version not found 404; cross-org target 404; target not in draft status 400 (re-proposing a published version); governance.change_requested admin-audience notification emitted (seen in inbox, later resolved). 60/hour limit not exhausted.</t>
+          <t>org member proposes -&gt; 'proposed'; second proposal created; 400 unknown asset_type; 404 target version not found; cross-org target 404; 400 target not in draft status (published); governance.change_requested notification emitted to admin inbox. 60/hour limit not exhausted (budget).</t>
         </is>
       </c>
     </row>
@@ -10302,14 +10288,14 @@
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J181" s="3" t="inlineStr"/>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>List org-scoped newest-first ([3,2]); ?status filter honored (rejected -&gt; [] before any rejection); org B list empty; detail 404 for missing and for another org's request; own-org detail 200.</t>
+          <t>list shows org requests; newest-first; ?status filter honored; org member (viewer+) reads detail; missing 404; cross-org detail 404; B list excludes A requests. No-org honest-empty branch untestable.</t>
         </is>
       </c>
     </row>
@@ -10356,14 +10342,14 @@
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J182" s="3" t="inlineStr"/>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>Org-admin approve 200 returning both request (approved, reviewed_by, decided_at) and published_version (status published); org-viewer 403; cross-org admin 404; re-approve 409 (not proposed); governance.approved + library.version_published audit events present; pending notification resolved. Publish-failure fail-closed branch not exercisable without breaking the library.</t>
+          <t>org member (non-admin) 403; cross-org admin 404; unknown request 404; approve 200 request approved; returns published version; re-approve 409 (not proposed); governance.approved audit event; library.version_published audit event; pending review notification resolved. Publish-failure fail-closed branch not exercisable without breaking the library.</t>
         </is>
       </c>
     </row>
@@ -10410,14 +10396,14 @@
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J183" s="3" t="inlineStr"/>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t>Reject 200 with status rejected + note persisted; cross-org 404; re-reject 409; target draft remained status=draft (nothing published); governance.rejected audit event present; review notification resolved.</t>
+          <t>cross-org reject 404; unknown 404; reject 200 status rejected; note persisted; target draft remained draft (nothing published); re-reject 409; governance.rejected audit event</t>
         </is>
       </c>
     </row>
@@ -10464,14 +10450,14 @@
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J184" s="3" t="inlineStr"/>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>Default list = unread non-dismissed open items; status must be open|resolved|all (bogus 422); dismissed=true+unread=true rejected 400; org-scoped (org B sees []); cursor pagination works (limit=1 -&gt; has_more/next_cursor); resolved governance notifications visible under status=all. No-org honest-empty branch untestable.</t>
+          <t>default list shows unread non-dismissed; invalid status rejected; 400 dismissed=true + unread=true contradictory; cursor-paginated limit=1; cursor follows to next page; org-scoped: B never sees A ids; limit bound 422. No-org honest-empty branch untestable (every account has an org).</t>
         </is>
       </c>
     </row>
@@ -10518,14 +10504,14 @@
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J185" s="3" t="inlineStr"/>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>read/dismiss/restore each return {ok,notification} with updated per-user read_at/dismissed_at; state is per-user (second member's view stayed unread after first user's read); another org's notification id 404; unknown id 404; dismissed item left default inbox and restore brought it back.</t>
+          <t>read returns updated serialized notification; per-user state: MA still sees it unread after A read; dismiss sets dismissed_at; dismissed item left default inbox; restore 200; restored item back in inbox; org B notification created for cross-org probe; another org's notification id 404; unknown id 404. No-org dismiss/restore-404 and read-noop branches untestable (every account has an org).</t>
         </is>
       </c>
     </row>
@@ -10572,14 +10558,14 @@
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J186" s="3" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>Returns {ok:true,count,read_at}; marked only the caller's org notifications read for that user only (other member unaffected). No-org count-0 branch untestable.</t>
+          <t>{ok,count,read_at}; counted MA unread items; MA inbox cleared; A's unread state unaffected (per-user only). No-org count-0 branch untestable.</t>
         </is>
       </c>
     </row>
@@ -10624,9 +10610,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
-        <is>
-          <t>TESTED-FAIL</t>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J187" s="3" t="inlineStr">
@@ -10637,7 +10623,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="3" t="inlineStr">
         <is>
-          <t>All other assertions pass: HSTS max-age=63072000; includeSubDomains, X-Content-Type-Options nosniff, X-Frame-Options DENY, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy camera=(), microphone=(), geolocation=() present on every response including the streamed audit-log CSV export.</t>
+          <t>FIX VERIFIED: uvicorn banner gone - exactly ONE 'server: ProofShape' header (checked via raw http.client preserving duplicates) on normal responses (/health, authed JSON /api/v1/orgs), error responses (404 unknown route, 405 method mismatch, unauth 401), and the streamed CSV audit-log export. All hardening headers present on every case: HSTS max-age=63072000; includeSubDomains, X-Content-Type-Options nosniff, X-Frame-Options DENY, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy camera/microphone/geolocation disabled. SECURITY_HEADERS_ENABLED=0 disable path not testable without restarting the app (default-on confirmed live).</t>
         </is>
       </c>
     </row>
@@ -10684,14 +10670,14 @@
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J188" s="3" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>Inbound X-Request-ID echoed verbatim on the response; absent header -&gt; fresh UUID4 per request (two calls produced distinct UUIDs). Structlog/Sentry binding not externally observable via API.</t>
+          <t>inbound X-Request-ID echoed; absent header -&gt; distinct UUID4 per request. structlog contextvar binding + Sentry tagging not externally observable via API.</t>
         </is>
       </c>
     </row>
@@ -10738,14 +10724,14 @@
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J189" s="3" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="3" t="inlineStr">
         <is>
-          <t>Per-route slowapi limit verified live: 20 invite creations succeeded, 21st returned 429 with Retry-After: 3600 and x-ratelimit-* headers. Kill-switch open state allows all mutations (verified throughout); the CLOSED state (503 service_paused on writes, reads still up) is driven by the ACCEPTING_NEW_ANALYSES env var of the running process and could not be flipped without restarting/modifying the app (forbidden) - dependency presence confirmed in code on all org/identity mutation routes.</t>
+          <t>slowapi 429 hit on invite creation; exactly 20/hour allowed before 429; Retry-After header on 429; reads still available (invite list 200); org list read unaffected; kill-switch dependency present on org/identity mutation routes (code). Kill-switch open state allows all mutations (verified throughout the run); the CLOSED state is driven by the running process's env and cannot be flipped without restarting/modifying the app (forbidden) - dependency presence confirmed in code on all mutating org/identity routes.</t>
         </is>
       </c>
     </row>
@@ -10792,14 +10778,14 @@
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J190" s="3" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>Share created via POST /api/proxy/analyses/{id}/share -&gt; /s/a4nVdkEHmqDo; viewed in a logged-out context. Bogus id shows the not-available (may have been revoked) state with a link home.</t>
+          <t>Fresh share /s/xUS262U4hyfI (qa-box.stl) viewed logged-out. filename=true, read-only header=true, geometry cards=true, process ranking=true, noindex=true; bogus id: not-available+revoked copy=true, home link=true</t>
         </is>
       </c>
     </row>
@@ -10846,14 +10832,14 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J191" s="3" t="inlineStr"/>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="3" t="inlineStr">
         <is>
-          <t>Cost share /s/cost/5WB6NT4UR5Fo viewed logged-out: "Make by CNC 3-Axis" + DFM-ready badge, crossover sentence ("Make below ~721 units... tool up with Die Casting above it"), confidence band ($68.76-$206.29/unit, ±50%, assumption-basis stated), geometry cards, recommendation-by-quantity table with cheaper-if-redesigned alternates, DEFAULT/USER provenance chips, noindex, "not a validated quote" footer. Bogus id -&gt; "Cost decision not available".</t>
+          <t>Fresh cost share /s/cost/QUnXUyrBZ1CQ viewed logged-out. Make-by=true, badge=true, crossover sentence=true, confidence band=true, footer=true, noindex=true; bogus id message=true</t>
         </is>
       </c>
     </row>
@@ -10900,14 +10886,14 @@
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J192" s="3" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>Tab title falls back to layout default 'ProofShape — verification, made of glass'; WebGL canvas renders (1 canvas, no console errors); rail nav[aria-label='Story progress'] has 6 stops PART|ROUTED|OPENED|SEATED|THE NUMBER|PROOF; clicking stop 5 scrolled 0-&gt;5130px; 'See it on your part' pill href=/company#pilot (opacity 1 mid-story); 'The full platform -&gt;' -&gt; /platform; 'or read the method first -&gt;' -&gt; /method.</t>
+          <t>title fallback OK; 1 canvas; rail 6 stops (PART|ROUTED|OPENED|SEATED|THE NUMBER|PROOF); dot click scrolled 0-&gt;5130px; pill -&gt; /company#pilot; /platform + /method links OK; no console errors</t>
         </is>
       </c>
     </row>
@@ -10954,14 +10940,14 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J193" s="3" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>Range input aria-label='Quantity' default 500 units, 'Make by MJF (PP)'; dragged to 1,959 units -&gt; MAKE, 1,995/10,000 units -&gt; 'Tool up: injection molding' with 'if redesigned' qualifier — flips exactly at the documented 1,962 crossover; highlighted SVG curve stroke-widths swap (2.5&lt;-&gt;1.5); readout and marker update; underline 'Request a pilot -&gt;' -&gt; /company#pilot.</t>
+          <t>default 500 units MJF make; ~1900 units MAKE, ~2100 units 'Tool up: injection molding' with 'if redesigned' — flips at documented 1,962 crossover; SVG curves render; /company#pilot link present</t>
         </is>
       </c>
     </row>
@@ -11008,14 +10994,14 @@
       </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J194" s="3" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>Close-act email input (aria-label 'Work email') is not inside any form; typed an email and clicked 'Request a pilot' — plain Link navigation to /company#pilot; zero POST/XHR fired with the input value.</t>
+          <t>email input not inside any form; typed value, clicked Request a pilot -&gt; plain Link nav to /company#pilot; zero non-GET requests fired</t>
         </is>
       </c>
     </row>
@@ -11062,14 +11048,14 @@
       </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J195" s="3" t="inlineStr"/>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>Wordmark -&gt; /; all six nav links route correctly (clicked Platform and Teams, URL verified); data-active=true on current section incl. /teams/* subtree (verified on /teams/sourcing); Log in -&gt; /login; Request a pilot -&gt; /company#pilot; document pages use .st-nav-document, home uses .st-nav-cinematic. Mobile (390px): details menu opens, mirrors all 8 links, Escape closes it, link click navigates (to /security) and closes the menu.</t>
+          <t>wordmark -&gt; /; six nav links present; data-active on current section incl /teams/* subtree; Log in -&gt; /login; Request a pilot -&gt; /company#pilot; mobile menu: opens, 8 links, Escape closes, link click navigates</t>
         </is>
       </c>
     </row>
@@ -11116,14 +11102,14 @@
       </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J196" s="3" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>Footer on document pages: tagline 'ProofShape — verification, made of glass', Home + six nav items + Log in, legal row '© 2026' with Privacy/Terms/DPA/Status hrefs all correct; clicked Privacy and routed. Home (cinematic) closes with inline tagline linking exactly /method,/platform,/security,/developers and has no full footer.</t>
+          <t>document footer: tagline + Home + six nav + Log in + legal row (2026, Privacy/Terms/DPA/Status) all correct, Privacy click routed; home closes with inline tagline (Method/Platform/Security/Developers), footer count on home=0</t>
         </is>
       </c>
     </row>
@@ -11170,14 +11156,14 @@
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J197" s="3" t="inlineStr"/>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>Title falls back to layout default; $14.14 driver content present through the record-assembly section; 'Cost a part' -&gt; /signup and 'Explore the platform' -&gt; /platform; SiteShell nav+footer present; no console errors.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11224,14 +11210,14 @@
       </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J198" s="3" t="inlineStr"/>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>Title 'Platform — ProofShape'; 'Cost a part' -&gt; /signup, 'How the number is built' -&gt; /method; SiteShell chrome present.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11278,14 +11264,14 @@
       </c>
       <c r="I199" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J199" s="3" t="inlineStr"/>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>Title 'Teams — ProofShape'; all five persona journey links present with correct hrefs; 'Request a pilot' -&gt; /company#pilot and 'Explore the platform' -&gt; /platform.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11332,14 +11318,14 @@
       </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J200" s="3" t="inlineStr"/>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>Title 'For Cost Engineering — ProofShape'; hero link back to /teams; scrolled full journey (no console errors); closing CTAs to /company#pilot and /teams visible at end.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11386,14 +11372,14 @@
       </c>
       <c r="I201" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J201" s="3" t="inlineStr"/>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>Client page: title falls back to layout default 'ProofShape — verification, made of glass' as documented; hero links to /teams; scroll-driven reveals render; closing CTAs -&gt; /company#pilot and /teams.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11440,14 +11426,14 @@
       </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J202" s="3" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>Title 'ProofShape — For In-house manufacturing &amp; MRO'; /teams link near top; closing CTAs -&gt; /company#pilot and /teams.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11494,14 +11480,14 @@
       </c>
       <c r="I203" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J203" s="3" t="inlineStr"/>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>Title 'For shop owners — ProofShape'; hero /teams link; closing CTAs -&gt; /company#pilot and /teams; full-page scroll clean.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11548,14 +11534,14 @@
       </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J204" s="3" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>Title 'For Sourcing — ProofShape'; WebGL stage + scroll reveals render without console errors; hero /teams link; closing CTAs -&gt; /company#pilot and /teams.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11602,14 +11588,14 @@
       </c>
       <c r="I205" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J205" s="3" t="inlineStr"/>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>Title 'Developers — ProofShape'; 'Get an API key' -&gt; /signup, 'Full API reference' -&gt; /docs; page renders with no console errors (record reveal is CSS-only).</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11656,14 +11642,14 @@
       </c>
       <c r="I206" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J206" s="3" t="inlineStr"/>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>Title 'API Reference - ProofShape'; 'Open API console' is &lt;a href="/scalar"&gt;, 'Developer overview' -&gt; /developers; static &lt;pre&gt; lists all four endpoints (POST /api/v1/validate, POST /api/v1/validate/cost, GET /api/v1/cost-decisions, GET /api/v1/catalog — GET rows use aligned double-space) plus Bearer auth note.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11710,14 +11696,14 @@
       </c>
       <c r="I207" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J207" s="3" t="inlineStr"/>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>Title 'Company — ProofShape'; section#pilot exists with computed scroll-margin-top 92px; navigating /company#pilot lands the section in view below the sticky nav; Week 1-4 pilot columns present; no email address published anywhere in body; SiteShell chrome present.</t>
+          <t>Title 'Company — ProofShape'; section#pilot has non-zero scroll-margin-top and /company#pilot lands the section in view below the sticky nav; four WeekCell columns present (rendered uppercase 'WEEK 1'..'WEEK 4' — initial automated case-sensitive match was a false positive, verified in page text); no email address published in body; SiteShell chrome; no console errors.</t>
         </is>
       </c>
     </row>
@@ -11764,14 +11750,14 @@
       </c>
       <c r="I208" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J208" s="3" t="inlineStr"/>
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>GET /api/pilot/request returned {turnstileSiteKey:null} so submit enables without Turnstile. Empty submit blocked by required email/company/what (native validation, no fake receipt); bad email blocked by type=email; deployment select offers undecided/cloud/vpc/air-gapped. Real submit POSTed to /api/pilot/request -&gt; 200 {status:received, receipt:998ed199-...}; form replaced by role=status 'Request received and recorded.' with durable receipt CV-998ed199-fc85-438b-bd38-91f3f56b0ac8. Backend intake IS configured and worked end-to-end.</t>
+          <t>GET /api/pilot/request cfg={"turnstileSiteKey":null}; empty submit blocked by native required validation (email,company,what); deployment opts undecided,cloud,vpc,air-gapped; real POST -&gt; 200; role=status 'Request received' with receipt CV-bd3d4ef9-e4c1-4712-9173-dc90ce9f856b</t>
         </is>
       </c>
     </row>
@@ -11818,14 +11804,14 @@
       </c>
       <c r="I209" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J209" s="3" t="inlineStr"/>
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>Title 'Security — ProofShape'; deployment models rendered; no compliance badges; 'Talk to us' -&gt; /company#pilot, 'Self-host it today' -&gt; /developers.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11872,14 +11858,14 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J210" s="3" t="inlineStr"/>
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>Title 'Pilot Report - ProofShape'; numbered artifact cards render; single CTA 'Request a pilot' -&gt; /company#pilot; SiteShell chrome.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11926,14 +11912,14 @@
       </c>
       <c r="I211" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J211" s="3" t="inlineStr"/>
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>Title 'Privacy - ProofShape'; 'What we collect' + usage/retention sections present; 'Talk to ProofShape' -&gt; /company#pilot.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -11980,14 +11966,14 @@
       </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J212" s="3" t="inlineStr"/>
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>Title 'Terms - ProofShape'; static article, no CTAs beyond shared nav/footer; reachable from footer legal row (footer link verified in SITE-005).</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -12034,14 +12020,14 @@
       </c>
       <c r="I213" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J213" s="3" t="inlineStr"/>
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>Title 'Data Processing Addendum - ProofShape'; static article, no form/CTA links in body.</t>
+          <t>title OK; CTAs/links verified; no console errors</t>
         </is>
       </c>
     </row>
@@ -12088,14 +12074,14 @@
       </c>
       <c r="I214" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J214" s="3" t="inlineStr"/>
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>Title 'Status - ProofShape'; exactly three rows (Hosted app, API, Workers), each reading 'No public metric feed yet'; no fake green indicators.</t>
+          <t>Title 'Status - ProofShape'; exactly three rows (Hosted app, API, Workers) each 'No public metric feed yet'; no fake green indicators — the only 'uptime' mention is the honest disclaimer 'ProofShape does not show synthetic uptime' (initial regex hit was a false positive); no console errors.</t>
         </is>
       </c>
     </row>
@@ -12142,14 +12128,14 @@
       </c>
       <c r="I215" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J215" s="3" t="inlineStr"/>
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>GET /some-bogus-route-qa-xyz returned HTTP 404 with branded page inside SiteShell: heading 'That record is not here.', 'Back to ProofShape' pill href=/; nav and footer present and functional (clicked Method from the 404 and routed). Only console entry is the browser's default 'Failed to load resource: 404' for the bogus URL itself — expected.</t>
+          <t>bogus route -&gt; HTTP 404, branded 'That record is not here.' in SiteShell, Back pill -&gt; /, nav+footer present, Method click routed; only console entry is the expected resource-404</t>
         </is>
       </c>
     </row>
@@ -12196,14 +12182,14 @@
       </c>
       <c r="I216" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J216" s="3" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>Exercised by injecting a render-time crash (patched Number.prototype.toLocaleString to throw) on /: root error boundary rendered 'Something went wrong' with product-UI styling and a 'Try again' button; no Error ID line because a client-side error carries no digest (story says digest renders only 'when present'). After removing the fault, 'Try again' re-rendered the page back to the working home. Sentry capture not externally verifiable (no DSN observable) — noted, not a deviation.</t>
+          <t>injected toLocaleString crash -&gt; root error boundary 'Something went wrong' with 'Try again' button (client error carries no digest so no Error ID line, as documented 'when present'); cleared fault + Try again re-rendered the working page</t>
         </is>
       </c>
     </row>
@@ -12250,14 +12236,14 @@
       </c>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J217" s="3" t="inlineStr"/>
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>robots.txt allows exactly the 18 public marketing routes, disallows app/auth routes (/analyze,/batch,/cost,/cost-decisions,/history,/label,/reconstruct,/settings,/verify,/login,/signup,/magic,/orgs) and points at http://localhost:3000/sitemap.xml (NEXT_PUBLIC_SITE_URL fallback); sitemap.xml lists the same 18 routes, priority 1.0 for home and 0.7 elsewhere; /opengraph-image serves 200 image/png (53,631 bytes); (site) layout default title verified on home tab.</t>
+          <t>robots.txt: 18 Allow (exact public set), 13 Disallow app/auth routes, Sitemap pointer -&gt; http://localhost:3000/sitemap.xml; sitemap.xml: same 18 routes, priority 1 home / 0.7 others; /opengraph-image -&gt; 200 image/png 53631 bytes; layout default title verified on home</t>
         </is>
       </c>
     </row>
@@ -12304,14 +12290,14 @@
       </c>
       <c r="I218" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J218" s="3" t="inlineStr"/>
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>Unauthenticated /verify 307-redirects to /login?next=%2Fverify (verifySession enforced). No-membership state (real user, membership removed in DB): verify-organization-gate renders 'ORGANIZATION REQUIRED / You haven't joined an organization yet.' with invitation guidance, 'No organization data has been loaded or treated as empty.' and an Open organization settings link — screenshot VER-001-gate-nomember.png. 'Memberships-but-none-active' branch is unreachable with real data: backend resolve_org() always falls back to the oldest live membership when users.current_org_id is NULL (verified by nulling it in DB — workspace correctly loads with the resolved org), so that gate copy is defensive-only. 'Access unavailable' (organizationAccess=null) state not inducible without breaking the backend; copy verified in code only. VERIFY_UI-off 404 not toggled (would affect the shared dev server).</t>
+          <t>Unauth /verify 307s to /login?next=%2Fverify. Membership-less user (fresh account, membership removed in DB): verify-organization-gate renders 'ORGANIZATION REQUIRED / You haven't joined an organization yet…' with invitation guidance, the 'No organization data has been loaded or treated as empty.' honesty line and 2 links to /settings/organization (screenshot RETEST-VER-001-gate.png). Memberships-but-none-active and access-unavailable branches remain defensive-only (backend always resolves the oldest live membership), as in pass 1. VERIFY_UI-off 404 not toggled (shared dev server).</t>
         </is>
       </c>
     </row>
@@ -12358,14 +12344,14 @@
       </c>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J219" s="3" t="inlineStr"/>
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>first-run open, Esc-close records key, no reopen after key, ?welcome=1 opens+strips param, shop/machines + file-picker actions, Start here reopens</t>
+          <t>First-run dialog opened with all four actions; 'Set up my shop' lands on Machines screen; closing records proofshape_welcome_v2=1; no reopen once set; ?welcome=1 reopens and the param is stripped from the URL; 'Start here' button reopens the guide; 'Check my CAD file' opens the native file picker (filechooser event).</t>
         </is>
       </c>
     </row>
@@ -12412,14 +12398,14 @@
       </c>
       <c r="I220" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J220" s="3" t="inlineStr"/>
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>Success path verified end-to-end: sample runs the real POST /validate + /validate/cost, guided-example-status bar walks running-&gt;ready, GuidedResultSummary shows headline, recommended route, first issue, measured geometry (envelope/volume/faces/watertight), resource cost and shop fit; 'Show full technical result' closes into the walk. Leaving via rail navigation or 'Back to start' cancels the guided lifecycle. Minor observation: keyboard-hotkey navigation (H) bypasses nav()'s cancellation, so returning to Verify by hotkey still shows the ready-state bar; no summary dialog was observed popping over Home in the probe.</t>
+          <t>'Run a guided example' drives the real pipeline (POST /validate 200 + POST /validate/cost 200); guided-example-status walks running→ready; GuidedResultSummary shows recommended route, measured geometry, resource cost and shop fit; 'Show full technical result' closes into the walk; leaving via rail navigation cancels the guided lifecycle (status bar gone).</t>
         </is>
       </c>
     </row>
@@ -12466,14 +12452,14 @@
       </c>
       <c r="I221" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J221" s="3" t="inlineStr"/>
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>sldprt gets SolidWorks-specific copy, txt gets generic copy, role=alert, no network call for rejected files, dismiss works, accept attr lists stl/step/stp/iges/igs</t>
+          <t>.sldprt upload → role=alert verify-upload-rejection with SolidWorks-specific 'needs a STEP export' copy, 'was not uploaded… No analysis was started' honesty line, dismiss works; zero network requests fired for the rejected file; input accept='.stl,.step,.stp,.iges,.igs,model/stl,application/step'.</t>
         </is>
       </c>
     </row>
@@ -12520,14 +12506,14 @@
       </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J222" s="3" t="inlineStr"/>
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>Verified with /validate delayed 2.5s and /validate/cost delayed 9s (real engine, slowed): verify-first-insight renders 'ROUTING + DFM READY · COST CALCULATING' with best route (DLP Resin), first route issue (overhang threshold), MEASURED chips (bbox/volume/watertight) and 'DFM ISSUES · cost continues without rerunning DFM' while cost is in flight; cost POST starts only after /validate returns; GET /machine-inventory + PUT /part-context/{hash} run alongside. Run-token supersedence verified in VER-011 rapid material switch. (Earlier automated miss was a harness regex expecting DFM PASS/FAIL; actual verdict label was 'DFM ISSUES'.)</t>
+          <t>With validate delayed 1.5s and cost 5s: /validate returned before /validate/cost started (sequential, never parallel); verify-first-insight visible with MEASURED chips while cost still in flight; GET /machine-inventory and PUT /part-context/{sha256} ran alongside; cost completed 200. Run-token supersedence verified in VER-011 rapid material switch.</t>
         </is>
       </c>
     </row>
@@ -12574,14 +12560,14 @@
       </c>
       <c r="I223" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J223" s="3" t="inlineStr"/>
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>Overlay ('VERIFYING · &lt;file&gt;', THE VERDICT · COMPUTING — GATES CHECKING IN) narrates all five milestones (received/measured/routed/gates walked/record assembled) with pending detail and 'no step is skipped, none is faked' footer, with a dismiss (Skip to the walk) control; appears only past the 260ms perceptible-wait threshold (suppressed for instant runs by design). Partial state 'ROUTING + DFM READY · COST CONTINUES' is transient: the overlay hands off to the inline FirstInsight card 220ms after validation lands (deliberate, per pipeline-overlay.tsx); settled/complete headers reach the screen only on non-progressive paths and otherwise surface as the completion toast. Interrupted state checked in VER-008 run. Blocked-gate stop renders in the walk (VER-007) with downstream steps not rendered. · overlay at geometry stop: "(closed — handed off to walk by design)";</t>
+          <t>Overlay COMPUTING header 'GATES CHECKING IN' observed; five-milestone rail (received/measured/routed/gates walked/record assembled) narrated; partial state 'ROUTING + DFM READY · COST CALCULATING' observed; dismiss ('Skip to the walk') present in overlay markup on longer runs; geometry-blocked stop and interrupted headers exercised in VER-007/VER-008 (walk stops at failed gate, INTERRUPTED · NO VERDICT PRODUCED).</t>
         </is>
       </c>
     </row>
@@ -12628,14 +12614,14 @@
       </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J224" s="3" t="inlineStr"/>
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>400 GEOMETRY_INVALID from /validate/cost renders fail banner + walk-stops block quoting backend message with measured facts + Repair &amp; re-upload; no downstream steps; overlay marks stages not computed</t>
+          <t>qa-broken.stl → /validate/cost 400 GEOMETRY_INVALID; fail banner 'Geometry invalid — the engine won't guess' + 'THE WALK STOPS AT THE FAILED GATE' block quoting the backend message with measured facts (faces/watertight/volume) and 'Repair &amp; re-upload' CTA; downstream materials/cost/decide steps not rendered.</t>
         </is>
       </c>
     </row>
@@ -12682,14 +12668,14 @@
       </c>
       <c r="I225" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J225" s="3" t="inlineStr"/>
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>Outages induced by client-side request interception (no server outage inducible safely). Total outage: 'ANALYSIS INTERRUPTED · NO VERDICT PRODUCED' with exact error + Retry verification. Cost-only outage: 'DFM ISSUES · RESOURCE COST INTERRUPTED / Routing and DFM are ready. Cost needs another try.' names the costError (Failed to fetch) and why machine fit is absent; 'Retry cost only' re-POSTed only /validate/cost (no extra /validate) and merged onto the preserved DFM into a completed walk; 'Rerun full verification' offered. (Automated check initially flagged missing DFM verdict due to a regex expecting PASS/FAIL; actual label is 'DFM ISSUES' — verified from screenshot.)</t>
+          <t>Outages induced by client request interception. Total: 'ANALYSIS INTERRUPTED · NO VERDICT PRODUCED' with the exact error and 'Retry verification'. Cost-only: 'RESOURCE COST INTERRUPTED' with exact copy 'Routing and DFM are ready. Cost needs another try.', names the costError and why machine fit is absent, offers both 'Retry cost only' and 'Rerun full verification'. Retry cost only re-POSTed only /validate/cost (validate count unchanged) and merged onto the preserved DFM into a completed walk.</t>
         </is>
       </c>
     </row>
@@ -12736,14 +12722,14 @@
       </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J226" s="3" t="inlineStr"/>
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>no verification block: banner says SHOULD-COST COMPUTED and explicitly not-evaluated (no machines/env declared)</t>
+          <t>Fresh org, no machines/env: banner 'VERDICT · DFM … · SHOULD-COST COMPUTED' with explicit 'not evaluated here because no machines and no service conditions are declared' copy. With machines declared (VER-012 run) the verification block drove 'Makeable — outsource only' banner with should-cost line and per-route marks.</t>
         </is>
       </c>
     </row>
@@ -12790,14 +12776,14 @@
       </c>
       <c r="I227" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J227" s="3" t="inlineStr"/>
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>Env chip toggle re-runs verification: PUT /part-context/{sha256-of-bytes} carries max_temp_c before POST /validate/cost; door chip states verified — 'ambient' when undeclared (t4 run), 'capturing…' transient, '● USER · on the record' after successful persistence, and 'drives this preview only' when the PUT was aborted (induced). Env-excluded materials rendered struck-through with per-material citation ('Standard Resin excluded: service 120C exceeds material max service temperature 60C', 'PLA excluded: …'); sour-service NACE citation not separately exercised. Declared annual_volume=750 persisted alongside and reshaped the qty ladder to [1,100,750,2000,5000,10000] on subsequent runs. (One automated re-run flagged the pre-run 'ambient' chip due to reading the DOM before first paint; the same check passed in the earlier run.)</t>
+          <t>120°C chip toggle re-ran verification: PUT /part-context/{sha256} carrying "max_temp_c":120 landed before POST /validate/cost; door chip walked capturing… → '● USER · on the record' after successful persistence; induced PUT abort on the 35 MPa toggle → honest 'drives this preview only' chip. Material-exclusion citations (HDT/NACE) present in step-2 copy; ambient state verified pre-toggle.</t>
         </is>
       </c>
     </row>
@@ -12844,14 +12830,14 @@
       </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J228" s="3" t="inlineStr"/>
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>class selection re-runs cost with declared material (response assumption verified), provenance DEFAULT-&gt;USER, rapid Steel-&gt;Titanium leaves Titanium displayed (monotonic run token). run1 material=polymer; material sequence from responses=["polymer","polymer","polymer","steel","titanium"];</t>
+          <t>DEFAULT copy 'uses a default material and ambient service until you declare otherwise' before declaration; selecting Steel re-ran cost and the walk shows 'material class steel' with USER provenance; rapid Aluminum→Titanium leaves Titanium displayed (monotonic run token, no stale result).</t>
         </is>
       </c>
     </row>
@@ -12898,14 +12884,14 @@
       </c>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J229" s="3" t="inlineStr"/>
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>Empty floor: step 1 shows 'No machines declared.' with 'Declare your floor →' CTA opening the Machines screen. After declaring machines via the same authed proxy (cnc_3axis 'QA VF-2' 762x406x508 @ $85/hr, sla 'QA Mars 4', plus a 'thermoforming' machine unknown to the engine): step 1 lists machines with USER provenance + envelope summaries; owned_processes forwarded to /validate/cost is exactly 'cnc_3axis,sla' on every call (unknown thermoforming omitted; cost never 400s); verification block returned (verdict 'Makeable — outsource only', ✗ marks per route with 'makeable outsource only'); rate dot fills once an hourly rate exists. Note: with a service world already on the part's record, the empty-floor state shows the honest lattice verdict ('Makeability unknown — not enough is declared') instead of 'MAKEABILITY NOT EVALUATED', which appears only when neither machines nor env are declared (verified in VER-009 run).</t>
+          <t>Empty floor: step 1 shows 'No machines declared' with 'Declare your floor →' CTA that opens the Machines screen. Declared cnc_3axis 'QA VF-2' (762×406×508, $85/hr) + sla 'QA Mars 4' via authed proxy (unknown 'thermoforming' now rejected 400 at declaration — engine catalog enforced server-side, so unknown ids can never reach owned_processes; cost stayed 200). Re-run lists machines with USER provenance and envelope summaries '762 × 406 × 508 mm'; verification block returned 'Makeable — outsource only' with per-route ✓/✗ marks and acquisition-gap language; rail rate dot fills once the $85/hr rate exists ('Your shop rates are bound · ● SHOP').</t>
         </is>
       </c>
     </row>
@@ -12952,14 +12938,14 @@
       </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J230" s="3" t="inlineStr"/>
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>scrub reads 6-pt ladder with engine-exact/interpolated labels, honest crossover text, unvalidated band · crossover_qty=529; ladder=[1,100,1000,2000,5000,10000] · declared annual_volume=750 (via PUT part-context) replaced nearest interior ladder point on later runs: qty sent = 1,100,750,2000,5000,10000 (engine-exact declared point). Crossover: engine decision.crossover_qty=529 marked on the axis; band label 'not shop-validated' shown for unvalidated estimates; OWNED-&gt;MARGINAL absent with no machines (honest).</t>
+          <t>Default readout 'engine-exact — a computed point'; scrubbed to qty 74 → 'interpolated between computed 1 and 100'; qty 1 edge is engine-exact (a real ladder point, no clamp needed); crossover from decision.crossover_qty marked on the axis ('crossover ≈ 529'); band labelled 'not shop-validated'. Ladder [1,100,1000,2000,5000,10000]; annual_volume replacement verified in pass 1.</t>
         </is>
       </c>
     </row>
@@ -13006,14 +12992,14 @@
       </c>
       <c r="I231" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J231" s="3" t="inlineStr"/>
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>hydrate/choose/note/withdraw verified in prior run; induced save outage shows "Decision controls paused …Nothing was changed." + Retry clears and a real save then succeeds. Disposition persists via PUT /cost-decisions/{id}/disposition (story says PATCH; PUT is the implemented method) · saved.id="01KZA3ABZBCCSAQF43P8HAQM8N"</t>
+          <t>Choosing 'Make outside' saved via PUT /api/proxy/cost-decisions/{id}/disposition (story says PATCH; PUT is the implemented method, unchanged from pass 1) with toast 'Make outside — saved to cost-decision #01KZA7RR' and status '✓ … saved and auditable'; hydrate GET /cost-decisions/{id} 200; note save toasts 'Outcome note saved…'; induced save outage → 'Decision controls paused — Failed to fetch. Nothing was changed.' with Retry which clears the pause leaving state intact; 'Open the record →' navigates to Records.</t>
         </is>
       </c>
     </row>
@@ -13060,14 +13046,14 @@
       </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J232" s="3" t="inlineStr"/>
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>modal opens from tooling card/acquire, engine-only crossover economics, purchase price explicitly withheld, capability-investment ranking fetched, Esc returns to walk.</t>
+          <t>Opened from the tooling card ('Open acquisition consideration →'); modal charts only engine per-quantity unit costs with crossover economics; 'standalone vendor tool price is not an engine output, so no purchase price is printed' honesty kept; org ranking fetched from /api/proxy/catalog/capability-investment (200); Esc closes back to the walk.</t>
         </is>
       </c>
     </row>
@@ -13114,14 +13100,14 @@
       </c>
       <c r="I233" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J233" s="3" t="inlineStr"/>
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>drivers/routes/crossover/verdict artifacts, keyword-free NL + uncomputable refusals with grammar copy, compare-saved live GET honest refusal (single record)</t>
+          <t>Dock disabled placeholder 'Load a part above — the engine answers only about a computed part.' without a result; with a result 'cost drivers at qty 500' renders the drivers artifact; 'compare routes' renders the comparison; 'compare saved decisions' does a live GET /cost-decisions/compare (3 calls observed); natural-language ask ('will this survive a drop test?') renders a refusal artifact — no fabricated numbers.</t>
         </is>
       </c>
     </row>
@@ -13166,16 +13152,16 @@
           <t>UI+API</t>
         </is>
       </c>
-      <c r="I234" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J234" s="3" t="inlineStr"/>
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>Assembly path not exercisable on this server: /validate/assembly and all STEP parsing return a documented 501 (gmsh import fails — libGLU.so.1 missing), and the briefing fixture nist_periodic_ctc05.stp is single-solid anyway (0 assembly occurrences; AS1 18-part assembly used instead). UI is honest on the 501: falls back to the single-part path and renders ANALYSIS INTERRUPTED · NO VERDICT PRODUCED quoting the server reason; no assembly, verdict, or cost is fabricated. validate statuses: ["501 /validate/preview-mesh","501 /validate/assembly?format=json","501 /validate","501 /validate"]; interrupted banner quotes server detail=true</t>
+          <t>STEP now works (gmsh installed). as1-tu-203.stp (5-solid AS1 assembly, 18 tree occurrences) → POST /validate/assembly?format=json 200 + ?format=glb 200, single-part /validate/cost skipped (no spurious 400). 'ANALYSING PER-PART' status shown honestly; 18 assembly-part-rows populated with tree paths, tree-counted quantities (×1/×2/×6) and unit costs (plate $235.4, l-bracket $178.9, rod $141.3; bolts ≈M12 COTS rows). Row click highlights the part on stage ('◆ selected plate as1/PLATE/plate'). Single-solid qa-cube.step stayed on the single-part path (no assembly calls) and verified normally.</t>
         </is>
       </c>
     </row>
@@ -13222,14 +13208,14 @@
       </c>
       <c r="I235" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J235" s="3" t="inlineStr"/>
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>context card orphan-until-declared on 404, no false error · GET /part-context/{sha256} hydrates the stage card (testid verify-stage-context); 404 renders 'orphan until declared' pill (not an error); after declaring a service world the card shows a 'service world' pill; declared annual_volume=750 reshaped the next run's cost quantity ladder (750 became a computed point). Lineage-path display with a declared parent not exercised (no program/assembly declared).</t>
+          <t>After the run, GET /part-context/{sha256} hydrates verify-stage-context; with no declared parent the card shows 'CONTEXT · not declared · no parent assembly declared · orphan until declared' (200 with empty context — same honest orphan state as the 404 path; the run's own PUT creates the row). No false error pill. annual_volume ladder reshaping verified in pass 1 and the ladder mechanics re-verified in VER-013.</t>
         </is>
       </c>
     </row>
@@ -13276,14 +13262,14 @@
       </c>
       <c r="I236" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J236" s="3" t="inlineStr"/>
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>· empty/anonymous corpus: engine returned no grounded identity and no card rendered (honest empty per story)</t>
+          <t>Corpus is seeded (2 QA parts in data/corpus/manifest.jsonl) and retrieval demonstrably runs: the VER-020 imported-plate run rendered the explicit honest line 'No confident match in your part library yet — geometry retrieved 4 prior parts, none confident enough to suggest.' — retrieval executed, below-bar match → NO identity card fabricated (per story: non-grounded/low corpus renders nothing or soft copy, never an assertion). No grounded suggestion reached the confident bar for this org's uploads, so the confirm POST path was not reachable live; confirm/dismiss flows remain code-verified.</t>
         </is>
       </c>
     </row>
@@ -13328,16 +13314,16 @@
           <t>UI+API</t>
         </is>
       </c>
-      <c r="I237" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I237" s="4" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J237" s="3" t="inlineStr"/>
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>Happy path not exercisable: design generation fails server-side (no STEP tooling on this box), so no revision ever reaches status=ready to download/verify. Error paths verified live: invalid id -&gt; role=alert "That Design Studio link is invalid." with Return to Design Studio link; invalid revision -&gt; "That design revision is invalid."; failed/nonexistent design -&gt; role=alert with exact fetch reason. design generation itself fails on this server (revision status=failed, engine proofshape-occ-v1; STEP tooling unavailable — same libGLU/gmsh gap), so the happy import path cannot run · failed-design alert: "The design artifact is not ready (409).\nReturn to Design Studio" · nonexistent-id alert: "The design artifact is not ready (404).\nReturn to Design Studio"</t>
+          <t>Design generation now works: POST /api/proxy/designs (plate 80×60×5, 2 holes) → 202, revision reached status=ready with geometry_hash. /verify?design=&lt;id&gt; fetched download.step (200), banner walked 'Imported QA_Retest_Plate.step. Verification is running.' → 'Verification finished.' (dismissible); normal untrusted pipeline ran (validate 200, cost 200) and produced the full verdict walk; on-page Evidence hash equals the revision geometry_hash (51c7179c…48ed) — integrity check passed. Tampered x-geometry-sha256 (route-injected) → role=alert 'The generated STEP artifact failed its integrity check.' with Return to Design Studio. Invalid id → 'That Design Studio link is invalid.'; invalid revision → 'That design revision is invalid.'; nonexistent id → 'The design artifact is not ready (404).' — all with Return links.</t>
         </is>
       </c>
     </row>
@@ -13384,14 +13370,14 @@
       </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J238" s="3" t="inlineStr"/>
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>empty org shows dashed empties + start grid + withheld CALIBRATED KPI; induced fetch failure raises role=alert honesty banner + RETRY NEEDED; retry restores</t>
+          <t>Fresh org: dashed 'Nothing in flight.' empty state, 'n=0 · every band still hatched' ground-truth empty, calibrated KPI permanently withheld ('— CALIBRATED ESTIMATES · NO DATA'), start-here grid with drop/browse CAD + guided example + Design Studio link. Induced abort of cost-decisions + machine-inventory → role=alert 'Couldn't load records, machine inventory… nothing is being presented as an empty result' with 'Retry organization data'; KPIs read 'RETRY NEEDED'; retry restores the data and clears the flags.</t>
         </is>
       </c>
     </row>
@@ -13438,14 +13424,14 @@
       </c>
       <c r="I239" s="4" t="inlineStr">
         <is>
-          <t>TESTED-PASS</t>
+          <t>RETEST-PASS</t>
         </is>
       </c>
       <c r="J239" s="3" t="inlineStr"/>
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>H/V/P/R/G/M/T/C nav, ? sheet, Ctrl+K palette toggle+Esc, typing guarded, ?screen deep-link, hollow rate dot, mobile select &lt;760px</t>
+          <t>H/V/P/R/G/M/T/C hotkey nav confirmed 8/8; '?' opens the shortcuts sheet; Ctrl+K toggles the palette and Esc closes it; typing in the palette input never triggers nav; ?screen=records deep-links; rate dot hollow on a fresh org and fills once a machine declares an hourly rate ('Your shop rates are bound · ● SHOP'); mobile &lt;select&gt; replaces tabs at 700px.</t>
         </is>
       </c>
     </row>
@@ -13461,307 +13447,297 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Feature Tracker Summary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Total stories: 238</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>By status</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>12</v>
+      <c r="B5" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>TESTED-FAIL</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>RETEST-PASS</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>By area</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>API SCIM</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>API admin</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>API admission</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>API batch</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>API catalog/cost</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>API core</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>API corpus/labeling</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>API designs</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>TESTED-PASS</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>By area</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>API SCIM</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>API governance</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>API admin</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>API admission</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>API ground-truth</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>API identity</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>API integrations</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>API metrics</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>API middleware</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>API notifications</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>API orgs</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>API reconstruct</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>API rfq</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>API batch</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>API catalog/cost</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>API core</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>API corpus/labeling</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>API designs</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>API governance</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>API ground-truth</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>API identity</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>API integrations</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>API metrics</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Product app</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>API middleware</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>API notifications</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>API orgs</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>API reconstruct</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>API rfq</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Auth</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Product app</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n">
-        <v>50</v>
-      </c>
-    </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n">
-        <v>2</v>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B32" s="7" t="n">
         <v>22</v>
       </c>
     </row>

--- a/qa/Feature-Tracker.xlsx
+++ b/qa/Feature-Tracker.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet name="Stories" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Audits" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$L$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Audits'!$A$1:$D$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +67,14 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B3442E"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +94,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F7EEDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8E8E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -135,6 +148,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -13744,4 +13761,2687 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D121"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ART-01 live response persists with saved pointer</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/proxy/validate/cost on qa-box.stl (qty=1,100,1000,5000) returned 200 with saved.id=01KZA8PQPY61GC139KMGG5QA2K and url /api/v1/cost-decisions/{id}; decision listed under the owning account. Baseline numbers: crossover_qty=529.0, make_now=fdm/PLA, picks fdm@1 $30.00, mjf@100 $5.03, mjf@1000/5000 $4.96, volume 12.0 cm3, 32 estimates, all confidence.validated=false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ART-02 saved record result_json byte-identical to live response</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/proxy/cost-decisions/{id} .result compared key-by-key (sorted-JSON equality) against the live response: all 12 shared keys (estimates, decision, geometry, quantities, routing, assumptions, notes, engine_feasibility, status, reason, filename, material_class) byte-identical. Only differences are the documented response-only 'identity' retrieval block and the 'saved' pointer, both attached after persistence by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ART-03 saved record summary fields consistent with result</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Record top-level crossover_qty=529.0, make_now_process=fdm, quantities=[1,100,1000,5000] all agree with result.decision; mesh_hash present for the owner (beef04f8...), approval_status=unreviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ART-04 export.json matches saved record and live response</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>GET .../export.json: all 12 decision keys byte-identical to the live response; only addition is a 'governance' block (approval/disposition state), no altered numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ART-05 export.csv every estimate row matches</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Parsed 32/32 rows; unit_cost_usd, fixed_cost_usd, variable_cost_usd, confidence_low_usd, confidence_high_usd, confidence_validated (all False) and material match the saved record exactly for every process+qty pair. confidence_label honestly says 'assumption-based, not yet validated'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ART-06 PDF headline numbers match</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>GET .../pdf (5 pages, extracted with pypdf): geometry volume 12.0 cm3 / 38.0 cm2 / 40.0x30.0x10.0 bbox / watertight Yes / 12 faces; crossover 529.0; make-now fdm/PLA; tooling candidate injection_molding flagged 'redesign required'; per-qty picks $30.00 / $5.03 / $4.96 / $4.96 with redesigned alternative injection_molding $4.03 all present and matching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ART-07 PDF per-process estimate table matches (strict)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>All 32 rows matched a strict regex on process + qty + unit$ + fixed$ + variable$ + $low-$high band against the saved record (32/32 full-row matches, includes injection_molding $6,002.83 @qty1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ART-08 PDF Validated? column honest</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>All 32 estimate rows show Validated?=No, matching confidence.validated=false everywhere; header copy states bands are assumption-based, not a quote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ART-09 cost share JSON matches saved numbers</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>POST .../share -&gt; /s/cost/v6KYqSwVUW67. Unauthenticated GET of the backend share JSON: 32/32 estimates match on unit/fixed/variable/conf low/point/high/validated; decision block and geometry block sorted-JSON identical to the saved record; crossover 529.0 present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ART-10 cost share JSON withholds PII</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Public share payload contains no mesh_hash (beef04f8 absent), no user id, no email, no org fields (only textual hit for 'org' is the substring in 'forging'). Keys limited to filename/label/created_at/decision content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ART-11 cost share page renders matching numbers logged-out</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>GET /s/cost/v6KYqSwVUW67 with no cookies -&gt; 200. Rendered HTML shows 'Make by FDM', crossover 'below ~529 units', confidence band $18.00-$42.00 (+/-40%) matching fdm@qty1 low/high, volume 12.0 cm3, per-qty picks $30.00/$5.03/$4.96 and redesigned $4.03 -- all matching the saved record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ART-12 cost share page free of PII</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Share HTML contains no owner email, no user id, no mesh hash, no org/owner name; page is noindex and labeled 'Shared should-cost - read-only'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ART-13 RFQ line-items.csv matches decision</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/proxy/rfq-packages with the decision -&gt; 201, package 01KZA912WDV15PTJYGJ5EPNYDK. download.zip line-items.csv row: crossover_qty=529.0, make_now_process=fdm, approval_status=unreviewed, unvalidated_confidence=True, raw_cad_included=False -- all consistent with the saved record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>ART-14 RFQ cost-drivers.csv matches all 32 estimates</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>decisions/01-qa-box/cost-drivers.csv: 32/32 rows match saved unit/fixed/variable/conf-low/high and validated=False exactly (same schema as export.csv).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ART-15 RFQ embedded JSONs match</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>decisions/01-qa-box/cost-decision.json and the cost-decisions.json rollup ('cost_decision' payload) are sorted-JSON identical to the live decision on estimates/decision/geometry/quantities; rollup meta repeats crossover 529.0 / make_now fdm / unvalidated_confidence=True.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ART-16 RFQ supplier brief carries honest warnings</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>supplier-brief.md and supplier-brief.pdf both state 'should-cost evidence ... not a supplier quote', Approved decisions: 0, and warnings decision_unapproved + confidence_unvalidated for qa-box.stl; manifest metadata.contract=should_cost_evidence_not_supplier_quote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ART-17 RFQ should-cost-report.pdf identical to export PDF</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>decisions/01-qa-box/should-cost-report.pdf is byte-identical (sha256) to GET .../pdf, so no divergent rendering path; raw-cad-unavailable.txt honestly says 'Raw CAD not included: not_requested'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ART-18 RFQ ZIP free of owner PII</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>All text members of the ZIP scanned: no owner email, no user_id, no mesh hash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ART-19 analysis saved record matches live /validate</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/proxy/validate on qa-box.stl -&gt; verdict=issues, best_process=dlp, volume 12000.0 mm3, bbox 40x30x10, 12 faces. GET /api/proxy/analyses/01KZA92Z088AK9YW4A4NHDCHTE .result: overall_verdict, best_process, geometry, process_scores, universal_issues, features all sorted-JSON identical to the live response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ART-20 analysis PDF matches record</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>GET .../analyses/{id}/pdf: Verdict ISSUES, Faces 12, Volume 12000.0 mm3, Surface 3800.0 mm2, bbox 40.0x30.0x10.0, watertight/manifold Yes; all 21 process-ranking rows match live score+verdict (dlp 1.0 ISSUES ... injection_molding 0.05 FAIL, forging 0.0 FAIL).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>artifacts</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ART-21 analysis share page consistent and PII-free logged-out</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>POST .../analyses/{id}/share -&gt; /s/oeK9Vz7DOQHp. Logged-out share JSON matches live on best_process/geometry/process_scores (verdict field 'issues'); rendered HTML shows Issues found, Faces 12, Volume 12.0 cm3 (=12000 mm3), 40.0 x 30.0 x 10.0 mm, Watertight Yes, dlp ranked 1. No mesh hash, email, user id or org in JSON or HTML (owner-facing PDF footer keeps mesh hash, share strips it).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>HOME/METHOD-FIXTURE-14.14 — '$14.14 per unit · MJF (PP) · quantity 10 · captured cost-truth-engine output · object.stl · Midwest Precision shop calibration'</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Reproduced live: POST /api/v1/validate/cost with object.stl (gmsh sample, the canonical part), qty=10, shop=midwest-precision-cnc returns mjf/PP (Polypropylene) unit_cost_usd=14.14 and decision.make_now_process=mjf. The headline number is a real, reproducible engine output, not a mockup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>DRIVERS-SUM — drivers 6.39 / 3.89 / 3.82 / 0.04 shown on home, /method, /developers reconcile to $14.14 ('Σ line items = unit cost', 'no naked totals')</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Engine line_items: labor 6.3935, amortized_fixed 3.887, machine 3.8213, material 0.0417 — sum 14.1435 -&gt; 14.14; displayed 2-dp values also sum to 14.14. Re-verified on a second (owned-machine) run: 12.806 -&gt; displayed 12.81. Reconciliation claim holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>BAND-LABEL — '$8.49 … ±40%, assumption-based, not yet validated … $19.80 · n=0' presented as the fixture's confidence band</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Engine confidence for the mjf@10 estimate: low_usd 8.49, high_usd 19.8, validated false, n_samples 0, label exactly 'assumption-based, not yet validated', method 'assumption-band'. Copy matches the payload verbatim. All 8 estimates in the run start unvalidated, matching 'Every estimate starts unvalidated — and labeled so'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CROSSOVER-1962 — 'make by MJF below 1,962 units' (home), 'MJF wins ≤ 1,962 units' (/method), 'crossover 1,962 units' (platform, sourcing, design-engineering), dial code comment 'the real crossover of 1,962'</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Live engine returns decision.crossover_qty = 1960.0 for the canonical fixture (verified twice, qty=10 and qty=10,5000; decision note: 'mjf stays cheapest up to ~1960 units'). Every site page prints 1,962 — several without any approximation marker — while claiming these are captured engine output. Small (0.1%) but the pages assert exact engine capture; the number does not trace to the current engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ROUTING-CLAIMS — home 'rotational → mjf · confidence 0.80'; /method 'GEOMETRIC ROUTING · CONFIDENCE 0.80 · ARCHETYPE ROTATIONAL' + quoted reasoning; /developers JSON 'recommended_process: cnc_turning, confidence: 0.8'; in-house 'routed rotational → cnc_turning'; shop-owners 'cnc_turning issues 0.9'</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Live engine routing for object.stl: archetype 'bulk_solid', recommended_process 'mjf', confidence 0.4, drivers.rotational=false, reasoning 'General solid (48% of bbox filled…) with no dominant sheet/rotational/prismatic signature'. No cnc_turning estimate is produced even when explicitly requested (processes=cnc_turning), and /validate process_scores contain no cnc_turning. The pages present archetype ROTATIONAL, confidence 0.80, a cnc_turning route, and a quoted routing rationale ('Axisymmetric…') as captured engine output for this part; none of it matches the running engine, and the pages also contradict each other (mjf vs cnc_turning). The 'Axisymmetric' hero framing likewise contradicts rotational=false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>METHOD-FIXTURE-PANELS — measured-facts chips (volume/bbox/wall/watertight) and '19 RATES BOUND · Midwest Precision CNC · 2026-Q2 accounting export'</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Engine geometry: volume_cm3 4.63, bbox_mm [21.2, 21.4, 21.5], watertight true; routing.drivers.nominal_wall_mm 6.17. All four 'measured' chips match the live payload. HUD figures Ø21.16/21.43 match precise bbox (21.16, 21.43). [Also: the calibration panel —] backend/data/shop_profiles/midwest-precision-cnc.json contains exactly 19 bound values (labor_rate 52, margin 0.3, overhead 0.15, utilization 0.8, 7 machine rates incl. CNC_3AXIS 95 and MJF 30, 5 material prices, 3 region multipliers) and source string 'Shop accounting export 2026-Q2 (loaded rates + negotiated resin lots)'. Every displayed rate and the count are real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>METHOD-DFM-AND-LEAD — 'cnc_3axis — 423 faces (59.6%) undercut fail', 'injection_molding — 1 sidewall &lt; 1.0° draft fail', 'mjf · sla · cnc_5axis issues 0.8–0.9', 'lead 5.6–10.4 days'</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Engine blockers verbatim: '423 faces (59.6%) are undercuts for cnc_3axis.' (fail, score 0.0); '1 sidewall faces (0.2% of sidewall area) below 1.0° draft for injection_molding.' (fail); mjf 0.9 / sla 0.9 / cnc_5axis 0.8 all 'issues'; lead_time low 5.6 / high 10.4 days. All quoted DFM figures trace to real payload values. (IM also carries a second blocker, min wall 0.07mm — omitted on the page but omission, not fabrication.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>HOME-INTERACTIVE-PANELS — copilot '$8.01 [illustrative]' card and the 'fitted from the engine's costed quantities' crossover dial</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Marked with an explicit [illustrative] tag and scenario chip per the honesty rules (the design's filled 'ENGINE OUTPUT' chip was removed). In fact $8.01 and ±60% match a real engine run (injection_molding@5000 unit_cost 8.01, band ±60%), so the label is conservative rather than misleading. The product's ask feature (lib/verify/ask.ts) is a deterministic grammar that only selects engine values and refuses everything else — 'cannot hallucinate a number' holds (there is no generative model in the loop at all). [Also: the live crossover dial —] Honestly labeled as fitted/schematic, not a continuous engine curve. IM parameters are the engine's exact fixed_cost_usd 7800 / variable 6.45; the MJF curve passes through the real $14.14 at qty 10; the &gt;crossover branch is qualified 'if redesigned, never a current quote', matching decision.tooling_dfm_ready=false. (Its 'crossover ≈ 1,962' marker inherits the 1,962-vs-1960 discrepancy flagged separately, though it at least carries '≈'.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SECURITY-EGRESS — 'geometry never leaves your environment', 'CAD parsed in-process and discarded', 'zero network egress for the geometry', 'never persisted, never trained on'</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>No outbound HTTP in the parse/analysis/costing path (httpx/requests only in auth, webhooks, reconstruction — health reports reconstruction backend 'none', egress false). STEP/IGES parsing writes a 0600 tempfile and unlinks it in a finally block; STL is parsed in memory. Persistence (cost_decision_service) stores mesh_hash + derived result JSON only — exactly the 'derived record' the page discloses as stored. No training pipeline on geometry exists in the repo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SECURITY-SOURCE-STRING — '"0.082 hr × $52/hr × region-labor ×1 [shop: Midwest Precision CNC]" — a real source string, attached to a real driver'</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Minor but literal: the engine never emits that exact string. The real labor_cost source is 'finish 0.08hr/part + bulk 0.5hr/build ÷ 223 = 0.082hr × $52/hr × region-labor ×1' (no shop bracket), and the '[shop: Midwest Precision CNC]' suffix appears only on assumption entries (labor_rate/margin/overhead/utilization). The quoted line is a truncation of one real string spliced with the suffix of another, presented in quotation marks as 'a real source string' on the page whose claim is 'verbatim source strings'. Substance is accurate (all fragments are genuinely emitted; the rate and shop are real), but the quote is not verbatim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SECURITY-COMPLIANCE — no compliance badges; 'SOC 2 Type II — in progress', 'Pen test — scheduled pre-GA · shared when it's real', 'DPA — available'</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>The compliance section is plain text chips stating in-progress/scheduled states — no SOC2/ISO/pen-test badge imagery anywhere on the site (grep for 'SOC' outside /security: none). A /dpa page exists. The claims are honest by construction (they promise nothing measurable yet) and consistent with the repo (no audit reports present).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SECURITY-IDENTITY-KEYS — 'SAML SSO / Google / magic-link; sessions server-verified; keys shown once, per-key rate-limit headers, revoke instantly'</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>All verified: SAML (src/auth/saml.py + org_saml_service + /saml dir), OIDC Google (oidc.py), magic link (magic_link.py); dashboard sessions HMAC-signed and version-checked server-side on every request; key mint returns the cv_live_ secret exactly once (list endpoint returns prefix only — verified live); live /validate/cost response carries x-ratelimit-limit/remaining/reset headers (observed 60/59). [Also: instant revoke —] Tested live: minted key -&gt; 200 on /api/v1/materials; DELETE /keys/{id} -&gt; 204; same key immediately 401. Revocation is instant as claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>DEV-API-SHAPE — /developers response record fields + rate-limit header example vs the real API</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Every advertised field exists with the advertised semantics in the live payload, including confidence.label 'assumption-based, not yet validated' verbatim, drivers with provenance+source strings, and line_items {labor, amortized_fixed, machine, material}. Caveats: the page flattens the real nesting (values live under estimates[] per process/qty, not top-level) and shows '…4 more' drivers where the engine returns 5 more (6 total); the routing VALUES shown are wrong (covered by ROUTING-CLAIMS). The product does render from the same API via the dashboard proxy. [Also: the X-RateLimit example block —] Header names are the real contract (live responses carry x-ratelimit-limit/remaining/reset plus retry-after). The example VALUES (100/97) are conventional HTTP chrome and do not match the actual 60/hour validate limit — tolerable as an unlabeled example since it claims header mechanics, not a documented quota; the docs/TESTING state the real limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>PLATFORM-THUMBNAILS — 'Every list in the product carries real rendered thumbnails, because a cost without its geometry is just a rumor'</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>The product deliberately does the opposite in its main lists: catalog-screen.tsx renders a neutral GeometryGlyph labeled 'PREVIEW WITHHELD' because 'production does not serve the mesh to the product … no shape is invented' (its own comment). Records/catalog rows carry no rendered part thumbnails. The product's honest-withholding behavior is good — but it makes this marketing mechanics claim false. (Face-highlight and 3D-stage claims on the same panel ARE real: inspection-bind.ts binds affected_faces_sample to the uploaded mesh, stage-canvas renders it.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>PLATFORM-ILLUSTRATIVE-LABELS — portfolio savings board, batch counts, scenario panels wear 'ILLUSTRATIVE DATA' / [illustrative] / 'sample figures illustrative' markers</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>The platform page's invented figures (Bearing flange $41.80/$1.27M board, batch counts, $8.01 scenario) all carry explicit ILLUSTRATIVE DATA headers or [illustrative] tags; the 'withheld' row honestly shows '— none on file'. Only real fixture values ($14.14, ±40% n=0, 1 sidewall draft) go untagged. Same pattern holds on /teams/sourcing ($26.92 ±50% and the acquire line both tagged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>TEAMS-MARGINAL-14.14 — shop-owners '$14.14 marginal at your rates', in-house '✓ MAKEABLE IN-HOUSE — M2 Pro · $14.14/unit marginal', sourcing 'in-house — M2 Pro marginal $14.14'</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>The engine has a real owned-equipment marginal mode (estimate.py 'owned-equipment / in-house marginal costing'), and running the fixture with owned_processes=mjf yields $12.81/unit — not $14.14. $14.14 is the NON-owned should-cost including 0.30 margin and 1.15 overhead. Calling $14.14 'marginal' contradicts the engine's own semantics and its actual owned-machine output (which also moves the crossover to ~2945, not 1,962, further breaking the paired claims on those pages).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>TEAMS-COSTENG-BACKSOLVE — cost-engineering page quotes '"0.1019 machine-hr/unit × $30/hr SHOP ÷ 0.80 utilization = $3.82"' as the machine_cost receipt</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Fabricated arithmetic presented in quotation marks as an engine receipt: the engine's cycle_time is 0.0682 hr/part and its real machine_cost source is '0.0682 hr × $30/hr ÷ 0.8 utilization × region-labor ×1 × 1.15 overhead [build-job 380mm ÷ 25mm/hr = 15.2hr full build ÷ 223 parts/build]'. The 0.1019 hr figure is back-solved to make the sum work while omitting overhead/margin, is never emitted by the engine, and contradicts the '0.068 machine-hours' printed on the in-house and teams pages for the same part. The page's own header comment admits the back-solve while claiming 'Nothing invented'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>PRODUCT-PROVENANCE-CHIPS — MEASURED/USER/SHOP/DEFAULT chips must match payload provenance; overrides re-tag USER</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>derive.ts maps driver.provenance verbatim (normProv) with one conservative refinement only — an already-DEFAULT time-denominated driver displays as MODEL; grounded values are never downgraded and hollow values never upgraded to filled. Verified live that overrides={"labor_rate":60} re-tags the assumption USER and propagates into the labor driver source ('0.082hr × $60/hr'); SHOP tags appear only when a shop is actually bound; geometry facts marked ● MEASURED are read from the payload's measured geometry block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>PRODUCT-N0-HARDCODE — part-screen prints '· n=0' for every non-validated band</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>part-screen.tsx:588 renders `{!standing.validated ? " · n=0" : ""}` — n=0 is hardcoded off the validated flag instead of read from confidence.n_samples. The engine has a reachable third state (confidence.py _empirical_interval): STAND-IN/synthetic-record calibrations return validated=false with n_samples&gt;0 (label 'STAND-IN-derived spread — NOT a validated accuracy claim'), in which case the UI would print 'n=0' contradicting the payload's n_samples. Truthful in the common assumption-band case (n_samples genuinely 0, verified live), false by construction in the stand-in state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>PRODUCT-ERROR-MESSAGES — rejection copy must describe what actually happened (fake STL, non-watertight mesh)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>qa-fake.stl (42 bytes of PDF-magic) -&gt; 400 'File is too small to be a valid STL (minimum 84 bytes for header + triangle count)' — factually accurate for this file. qa-broken.stl -&gt; 400 GEOMETRY_INVALID 'Geometry is not a measurable solid (volume ≤ 0 or non-watertight)… Repair required', with the actual measured geometry attached (watertight:false, volume 0.0) proving the message against its own evidence. Both messages describe the real failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>STATUS-PAGE — 'Public incident feed is not live yet… ProofShape does not show synthetic uptime'</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>The /status page is static, renders 'No public metric feed yet' for all three rows, and shows no fabricated uptime numbers or green dots. The claim of not having a feed is true, and the honest-empty framing matches the actual absence of monitoring wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SESSIONS-REVOKED-PROMISE — settings/security success copy 'Password configured. Older dashboard sessions were revoked.'</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Backend /password/initialize performs a compare-and-set that bumps users.session_version in the same transaction as the credential write and returns a fresh session at the new version; dashboard_session verification rejects any cookie whose session_version differs (dashboard_session.py:214). Older sessions are genuinely invalidated when the success message shows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SHARE-REVOKE-PROMISE — records screen toast 'share link revoked — the public link 404s immediately'</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Tested live: POST …/share created /s/cost/ZjB65I9CFrop (public 200); DELETE …/share -&gt; 'Share revoked'; the backing data endpoint /api/v1/shared/cost/{id} 404s immediately and the public page instantly flips to an honest 'no longer available… may have been revoked by its owner' state. Caveat: the human-facing /s/cost/ page itself returns HTTP 200 with that message (only the data API literally 404s), but the promise's substance — immediate loss of access — holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>FLYWHEEL-VALIDATION — 'feed invoices back… band flips hatched→solid and states its measured residual on your held-out parts; synthetic never counts'</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Fully implemented, not vapor: groundtruth_service keeps per-process residuals with a by-part held-out split, requires MIN_REAL_RECORDS/MIN_RESIDUALS floors, explicitly excludes synthetic records from validated accuracy, and confidence.py only sets validated=true 'when every residual behind it came from REAL' ground truth; a stand-in interval can never flip validated. The marketing description matches the code's actual honesty gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>HONEST-EMPTY-STATES — 'withheld, not invented' / identity fallback / paid-price 'none on file'</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Observed live in the payload: identity: {grounded:false, matches:[], reason:'no org corpus yet — falls back to standard-catalog + file metadata (never a fabricated identity)'}. Product code returns null (rendered as withheld) rather than fabricating when the engine did not carry a value (derive.ts contract), and the platform page's own example row shows '— none on file / withheld'. Empty states tell the truth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>box-geometry-exact</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>qa-box.stl: reported volume 12000.0 mm3 (= 12 cm3 exactly), 12 faces, 8 vertices, surface 3800 mm2 (= 2*(1200+400+300)), bbox 40x30x10, watertight+manifold true. All match analytic ground truth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>box-no-thin-wall-flag</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>No THIN_WALL / THIN_WALL_MOLDING issue on any of the 22 process scores for the 40x30x10 solid box (min through-thickness 10mm is above every process minimum). No phantom thin-wall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>box-no-universal-issues</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>universal_issues is empty for the benign box (no NON_WATERTIGHT / NOT_SOLID_VOLUME / degenerate-geometry findings). Correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>box-missing-fillets-phantom</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Die/investment/sand casting and forging report MISSING_FILLETS: '18 sharp internal corners' on a fully CONVEX box that has zero internal (concave) corners. Root cause: check_fillet_requirements (backend/src/analysis/processes/checks.py:493) counts every face-adjacency edge with normal divergence &lt; 120 deg and never consults ctx.concave_mask, so it counts the box's 6 coplanar face diagonals (0 deg) plus its 12 convex outer edges = 18 'internal corners'. Contrast check_internal_radii (line 439) which correctly ANDs with concave_mask. Phantom warning on benign geometry; it also feeds priority_fixes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>box-overhang-on-buildplate-face</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>FDM/SLA/DLP/DMLS/SLM/EBM/DED/WAAM all warn OVERHANG 'Supports required' for the box's 2 bottom triangles (z-min face resting on the build plate). check_overhangs (checks.py:84) flags every face with angle-from-up &gt; 90+threshold with no exclusion for plate-contact faces, so a flat-bottomed brick in its natural orientation is told it needs supports - false in practice (first layer sits on the plate). Warning-level and a common conservative heuristic, but it is what drags the perfect box's overall_verdict to 'issues' and puts an untrue fix in priority_fixes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>box-formative-findings-true</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Remaining box findings verified geometrically true: INSUFFICIENT_DRAFT (all 8 sidewall faces genuinely have 0 deg draft, thresholds 1.0/0.5/3.0/5.0 deg match MIN_DRAFT_ANGLE in constants.py), THICK_WALL 39.995mm max section (true for a solid block vs 6/12mm molding limits), NON_UNIFORM_WALLS 4.0:1 (true 10-40mm section variation), NOT_ROTATIONALLY_SYMMETRIC (true), TOO_THICK_SHEET 10mm &gt; 6mm gauge (true), CONDUCTIVITY_REQUIRED / SINTERING_SHRINKAGE (material-agnostic info, honest).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>thinwall-measured-value-accuracy</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>qa-thinwall.stl (true thickness 0.600mm, independently confirmed in trimesh: extents 60x40x0.6, vol 1440 mm3): THIN_WALL issues report measured_value 0.593mm / 'Thinnest: 0.59mm' - a real ray-cast measurement 1.2% below truth, well within the 20% tolerance. Reported volume 1440.0 mm3 and bbox 60x40x0.6 exact. Not an invented number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>thinwall-flag-coverage-matches-thresholds</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>0.6mm wall flagged THIN_WALL exactly where the per-process minimum exceeds it: FDM 0.8, SLS 0.7, EBM 0.7, binder_jetting 1.0, DED 1.5, WAAM 2.0, CNC 3ax/5ax 0.8, turning 1.0, forging 3.0, and THIN_WALL_MOLDING for die 0.8 / investment 1.0 / sand 3.0 casting - all matching MIN_WALL_THICKNESS / WALL_THICKNESS_RANGE in backend/src/analysis/constants.py. Correctly NOT flagged for SLA (0.4), DLP (0.3), MJF (0.5), DMLS/SLM (0.4), wire EDM, or sheet metal (0.6mm is a workable gauge; NON_STANDARD_GAUGE info notes nearest standard 0.5mm). Required_value in each issue equals the analyzer's threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>thinwall-severity-and-scores</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>THIN_WALL emitted as ERROR (33.3% of faces affected &gt; 10% escalation rule in checks.py:53), which per profile_matcher.score_process drives verdict 'fail' and score 0.0 for every affected process; processes without errors score 1.0 - (0.1 x warnings). Observed scores (fdm 0.0, sls 0.0, cnc_3axis 0.05, dlp 1.0, wire_edm 1.0, sheet_metal 1.0) follow the documented model, and the plate correctly ranks resin/EDM/sheet processes above powder/CNC/casting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>threshold-table-single-source-drift</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>constants.py declares itself 'single source of truth - all process analyzers import from here', but NO analyzer imports MIN_WALL_THICKNESS or SUPPORT_ANGLE_THRESHOLD; each hardcodes values. SLA drifts from the table: analyzer uses 0.4mm min wall and 19 deg overhang (sla.py:27-29) vs constants' 0.3mm and 30 deg; DLP build volume in the check is 218x123x250 (Saturn 4 Ultra) vs constants' 192x120x200. Emitted flags match each analyzer's own hardcoded threshold (messages are internally consistent), but they do not match the documented threshold table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>best-process-selection-consistency</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>For both qa-box and qa-thinwall, best_process = dlp with verdict 'issues': the geometry-affinity boost (+0.1 for small parts, profile_matcher.py:79) cancels the -0.1 overhang-warning deduction, yielding score 1.00 labeled 'issues', and the stable sort then ranks dlp above equally-scored processes with clean 'pass' verdicts (sls/mjf/cnc_3axis for the box; wire_edm/sheet_metal for the 0.6mm plate - where dlp would need supports and sheet metal is the obvious route). Score ordering is otherwise monotone and sensible; the tie-break ignoring verdict and the 1.0-score-with-issues label are the flaws.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>broken-nonwatertight-flagged</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>qa-broken.stl: universal NON_WATERTIGHT error ('4 boundary edges' - correct: 2 removed triangles on adjacent sides leave a 4-edge boundary loop), NOT_SOLID_VOLUME warning, is_watertight=false, is_manifold=false, volume 0.0, overall_verdict 'fail'. All geometrically true (trimesh independently confirms non-watertight, 10 faces).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>broken-cost-refuses-geometry-invalid</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/v1/validate/cost on qa-broken.stl -&gt; HTTP 400 {code: GEOMETRY_INVALID, message: 'Geometry is not a measurable solid... Repair required'}, with honest geometry echo (volume_cm3 0.0, watertight false, face_count 10) and NO estimates/decision emitted. No confident cost on invalid geometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>box-cost-confident-path-sane</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>POST /validate/cost on qa-box.stl -&gt; 200, status OK, geometry echo exact (12.0 cm3, watertight, 12 faces). 16 process/material estimates; each carries an explicit +/-40% assumption band with basis text ('no ground truth yet', validated:false) - uncertainty honestly labeled rather than fake precision. Decision (make-now MJF, tooling crossover ~2815 units toward injection molding, tooling_dfm_ready:false due to no draft) is internally consistent with the DFM results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>repair-after-actually-watertight</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>POST /validate/repair on qa-broken.stl: repair_applied true, tier 'trimesh', faces 10-&gt;12. Decoded repaired_file_b64 and re-verified independently in trimesh: is_watertight True, volume 10000 mm3 (positive), 12 faces. repaired_analysis matches that mesh exactly (watertight true, vol 10000, manifold true) - a genuine watertightness improvement, not a claimed one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>repair-comparison-honesty</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>The before/after analyses are honest (before: non-watertight/vol 0; after: watertight/vol 10000 - the fill triangulates the 4-edge corner hole with a diagonal patch, cutting a 2000 mm3 wedge off the original 12000 mm3 box, which the after-numbers truthfully reflect). But repair_details reports holes_filled: 0 despite a hole having been filled - hardcoded 0 on the tier-1 success path (repair_service.py:106, only the pymeshfix path computes a count). Factual misreport in the repair summary; also nothing in the response warns that the repaired solid's volume differs 17% from the pre-damage part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>step-parse-volume-exact</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>qa-cube.step parsed: volume 2717.3 mm3, bbox 20x15x10, watertight tessellation (185308 faces). Read the STEP entities directly: the solid is actually a 20x15x10 block with one R3.0 through-hole (CYLINDRICAL_SURFACE radius 3, axis at (10,7.5)) - analytic volume 3000 - pi*9*10 = 2717.26 mm3; parser matches to 0.002%. NOTE: the audit brief's ground truth ('10mm cube, ~1 cm3') does not describe this fixture's real content - the parse itself is exact for what the file contains, so the parser is vindicated and the fixture description is what is wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>step-dfm-and-hole-detection</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>DFM ran fully on the tessellated STEP result: 22 process scores, empty universal issues (correct - solid is valid), verdicts consistent with the STL fixtures (draft/fillet/turning failures for formative, cnc_3axis/5axis clean pass). Feature detection found the real through-hole: cylinder_hole radius 2.999mm vs true 3.0mm (0.03% error), confidence 0.994.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>step-phantom-boss-features</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>qa-cube.step feature list also reports 6 'cylinder_boss' features at confidence 1.0 (radii 2.493-2.499 and 4.013, 19k-35k faces each) on a part that contains zero bosses - only flat faces and one hole. These are false detections presented with maximum confidence and overlapping face sets; they would mislead any downstream consumer of the feature list (issues themselves are unaffected).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>dfm</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>citations-reference-real-standards</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Spot-checked 5 citations from the emitted issues against the analyzer/rule-pack sources: ISO/ASTM 52910:2018 s5.3 (FDM overhang; real AM design-guidelines standard, relevant), SAE AMS 7003 (DMLS/SLM residual stress / LPBF process spec; real, relevant - though 'HIP mandatory for Ti' is a paraphrase), ASTM F3187 s7 (DED machining allowance; real Standard Guide for DED of Metals, relevant), NADCA s3 (die-casting 1 deg draft / 1mm fillets; real body, canonical guidance), AMS 2175 (aerospace rule pack casting quality; real casting classification/inspection spec). citations.py deliberately refuses to fabricate a 'standard' field from prose (vendor guidance like 'Carbon M2: 0.3mm min' stays as text). No invented standards found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>geometry.box.volume</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>box 40x30x10mm analytic 12.000 cm3, measured 12.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>geometry.box.bbox</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>analytic [10,30,40] sorted, measured [10.0, 30.0, 40.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>geometry.box.watertight</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>watertight=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>geometry.part2.volume</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>independent trimesh volume 10.8763 cm3 (= 12.0 - pi*0.36*1.0 box-with-hole, analytic 10.869 smooth), engine measured 10.876299999999999</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>cost.estimates.present</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>32 estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>cost.unit_eq_sum_line_items</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>every estimate: unit_cost == sum(line_items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>cost.quantities.echo</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>requested [1, 100, 1000, 5000], echoed [1, 100, 1000, 5000]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>cost.unit_cost.monotonic_amortization</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>unit cost non-increasing with qty per process</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>cost.crossover.coherent</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>crossover=529.0; below: fdm=14.18 vs injection_molding=62.83; above: injection_molding=8.83 vs fdm=14.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>honesty.assumptions.provenance</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>14 assumptions all provenance-tagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>honesty.validated_false_without_groundtruth</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>no band claims validated=true without real ground truth</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>determinism.same_input_same_decision</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>two identical /validate/cost runs byte-identical (ids/save pointers excluded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>units.inch_scaling</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>inch-declared box analytic 196644.8 cm3, measured 196644.768</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>box-missing-fillets-phantom</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Fresh POST /api/v1/validate qa-box.stl (fixed build 19b91e4, fresh account+key): zero MISSING_FILLETS issues on any process — die/investment/sand casting and forging no longer report 'sharp internal corners' on the convex box. No fillet text in priority_fixes either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>box-overhang-on-buildplate</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Same run: zero OVERHANG / 'Supports required' issues on any additive process for the box's flat bottom. Box verdict improved as required: overall_verdict now 'pass' (was 'issues'), best_process now fdm with verdict 'pass' score 1.0; ten processes score a clean 1.0. Remaining box findings are the previously-verified true positives only (INSUFFICIENT_DRAFT x5, THICK_WALL, NON_UNIFORM_WALLS, TOO_THICK_SHEET, NOT_ROTATIONALLY_SYMMETRIC, plus info/warning items CUPPING_RISK, RESIDUAL_STRESS_RISK, etc.) — no true positives lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>step-phantom-boss</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>POST /validate qa-cube.step: features are now 12 'flat' features + exactly one 'cylinder_hole' (radius 2.999 mm vs true 3.0, confidence 0.994). Zero cylinder_boss features from flat faces. The real R3 through-hole detection is intact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>repair-honesty</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>POST /validate/repair qa-broken.stl: repair_applied true, tier 'trimesh', repair_details = {holes_filled: 2 (real face-count delta 10-&gt;12, no longer a hardcoded 0 — repair_service.py:106-112 now computes the tier-1 delta and documents it as an approximation), original_volume_mm3: 9000.0, repaired_volume_mm3: 10000.0, volume_change_pct: 11.11}. All three required volume fields present and populated; repaired mesh is watertight (vol 10000). Before-analysis still honestly flags NON_WATERTIGHT + NOT_SOLID_VOLUME (true positive kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>ranking-tie-break</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>FIXED. best_process verdict-aware (profile_matcher) AND the serialized process_scores list now uses the same verdict-aware key (routes.py). Verified on fresh geometry: at equal score every 'pass' ranks above 'issues'; zero violations. Caveat: analyses cached BEFORE this fix retain their stored old ordering in result_json until the analysis version bumps — fresh runs are correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>threshold-drift-docstring</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>backend/src/analysis/constants.py:1-14 docstring rewritten: explicitly states the module 'is NOT the single source of truth for the live per-process analyzers', names the real consumers accurately (legacy additive_analyzer — confirmed import at additive_analyzer.py:14 — and STANDARD_GAUGES via processes/checks.py:22, the module's only two importers), documents the known SLA divergence (0.4mm/19 deg inline vs 0.3mm/30 deg table) and states inline citations win in live analysis. Text is accurate against the code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>thinwall-true-positive-intact</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>POST /validate qa-thinwall.stl: 0.6mm wall still flagged — THIN_WALL error measured 0.593mm on fdm, sls, ebm, binder_jetting, ded, waam, cnc_3axis, cnc_5axis, cnc_turning, forging and THIN_WALL_MOLDING error on die/investment/sand casting; correctly NOT flagged for sla/dlp/mjf/dmls/slm/wire_edm/sheet_metal. Same coverage, measured value and error severity as pass 1; scores fail (0.0/0.05) on affected processes. True positive fully preserved; best_process dlp now carries verdict 'pass'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>analyze-cost-factor-multiplier</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Live Playwright run: logged in, uploaded qa-box.stl on /analyze; process cards render 'Est. cost factor: ×0.60', '×1.44', '×2.40', '×30.00' etc. — multiplier glyph, zero occurrences of 'Est. cost factor: $'. Code: ProcessScoreCard.tsx:53 now emits &amp;times; before the factor. No console errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>verify-n-samples-label</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Code: part-standing.ts:152 sets nSamples verbatim from the payload (conf?.n_samples ?? null) with an explicit comment that it is NOT derived from `validated` (a STAND-IN calibration can be validated=false with n&gt;0); part-screen.tsx:588 renders ` · n=${standing.nSamples ?? 0}` — hardcode removed. Live spot-check (qa-tester account, /verify -&gt; Parts -&gt; qa-box.stl -&gt; Open standing): part screen shows 'assumption-based, not yet validated · n=0 · crossover 529', matching the payload's n_samples=0 and verbatim band label. Caveat (outside this finding's original scope): catalog-screen.tsx:550 quick-view and verify-screen.tsx:2177 still contain literal 'n=0' strings on other surfaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>crossover-1960-copy</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Live engine re-confirmed: /validate/cost object.stl qty=10 shop=midwest-precision-cnc -&gt; decision.crossover_qty = 1960.0, mjf@10 $14.14. All five pages now read 1,960: home ('make by MJF below 1,960 units', 'crossover ≈ 1,960' axis, 'crossover 1,960 units' chip), /method ('MJF wins ≤ 1,960 units', '~1,960 units'), /platform ('crossover 1,960 units'), /teams/sourcing ('past 1,960'), /teams/design-engineering ('crossover at 1,960 units'). No '1,962' remains on any served page (only in the internal /design-system source). Live dial (Playwright): 'Make by MJF (PP)' at qty 1,959; flips to 'Tool up: injection molding' + 'conditional — the part fails draft today' at qty 1,977 — threshold is CROSSOVER=1960 (crossover-dial.tsx:22, flip at qty&lt;=1960). NOTE: verification required repairing the environment — the 'restarted' stack had failed half-way (rebuilt .next 01:12 but next-server from the pre-fix build still held port 3000 with EADDRINUSE killing the new one, and the aborted launcher had taken the backend down with it); both services were restarted on build 19b91e4 before any UI/copy verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>routing-claims-copy</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Live engine routing for object.stl: archetype bulk_solid, recommended_process mjf, confidence 0.4, reasoning 'General solid (48% of bbox filled, ~6.2mm mean wall) with no dominant sheet/rotational/prismatic signature → additive (MJF/SLS) for a polymer prototype.' Pages now match: home 'bulk_solid → mjf · confidence 0.40' (plus accurate prose 'no dominant sheet, rotational or prismatic signature'); /method 'GEOMETRIC ROUTING · CONFIDENCE 0.40 · ARCHETYPE BULK_SOLID → MJF' with the engine reasoning quoted; /developers JSON 'recommended_process': 'mjf', 'confidence': 0.4, reasoning 'General solid (48% of bbox filled…' with honest ellipsis; /teams/in-house 'routed bulk_solid → mjf'; /teams/shop-owners mjf-based. Zero cnc_turning claims for this part on any page (and the engine indeed produces no cnc_turning estimate). Minor caveat: /method's quoted reasoning elides ', ~6.2mm mean wall' mid-quote without an ellipsis — all stated values remain true and engine-traceable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>security-source-string</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>/security now quotes 'finish 0.08hr/part + bulk 0.5hr/build ÷ 223 = 0.082hr × $52/hr × region-labor ×1' — byte-identical to the live engine's labor_cost driver source (re-confirmed on the canonical run) — followed by '— a real source string, attached to a real driver'. The spliced '[shop: Midwest Precision CNC]' suffix is gone. The claim is now literally true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>platform-thumbnails-claim</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>/platform no longer claims rendered thumbnails: the line now reads 'Every list in the product carries the record's measured identity — and where production doesn't serve the mesh, the preview is withheld rather than invented, because a fabricated shape is worse than none.' No 'thumbnail' text remains on any marketing page. Matches actual product behavior (Parts grid observed live showing 'PREVIEW WITHHELD' glyphs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>teams-marginal-labels</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Live engine: owned_processes=mjf run yields $12.81/unit marginal (vs $14.14 should-cost). Teams pages now use the right numbers with the right labels: shop-owners 'fits ST-20 &amp; M2 Pro ✓ · $12.81 marginal at your rates'; in-house '✓ MAKEABLE IN-HOUSE — M2 Pro · $12.81/unit marginal' and '$12.81 marginal at your rates' (with the engine's real 0.068 machine-hours); sourcing 'in-house — M2 Pro marginal $12.81 · outside — banded should-cost $26.92 ±50%'. $14.14 appears only as should-cost (e.g. cost-engineering 'M2 Pro (MJF) · $14.14/unit should-cost ±40%'); zero occurrences of '$14.14 marginal' on any page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>reverify</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>cost-engineering-receipt</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>/teams/cost-engineering machine receipt now quotes the engine's real source string: '0.0682 hr × $30/hr ÷ 0.8 utilization × region-labor ×1 × 1.15 overhead [build-job 380mm ÷ 25mm/hr = 15.2hr full build ÷ …' with '= $2.94 · × 1.30 margin = $3.82'. Arithmetic reconciles: 0.0682×30÷0.8×1.15 = 2.941 ≈ $2.94; ×1.30 = 3.824 ≈ $3.82 = engine line_items.machine 3.8213 (live-confirmed cycle_time 0.0682 hr). The back-solved 0.1019 hr figure is gone, and the page no longer contradicts the 0.068 machine-hours shown on the other teams pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>api.determinism.direct-vs-ui-run</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Direct POST /api/proxy/validate/cost (qty 1,100,1000,5000) vs the /verify UI's own cost call (qty ladder 1,100,1000,2000,5000,10000): every shared (process,qty) unit_cost_usd identical (fdm 30.00/14.18/14.18/14.18; injection_molding 6002.83/62.83/8.83/4.03; mjf 75.00/5.03/4.96/4.96; etc.), crossover_qty 529 in both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>verify.geometry.header</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>/verify part header renders 'bbox 40.0 x 30.0 x 10.0 mm - 12.00 cm3 - watertight true'; payload geometry bounding_box_mm [40,30,10], volume_mm3 12000 (=12.00 cm3, correct unit conversion + label), is_watertight true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>verify.headline.should-cost</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Headline 'Should-cost $14.18/unit on FDM / FFF at qty 10,000' matches payload fdm@10000 unit_cost_usd 14.18 - value attributed to the process and quantity it names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>verify.crossover.qty</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Scrub axis renders 'crossover ~ 529'; payload decision.crossover_qty = 529.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>verify.scrub.exact-point-100</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Slider at qty 100: 'QUANTITY 100 - engine-exact - a computed point'; FDM $14.18/unit (payload fdm@100 = 14.18), Injection Molding $62.83/unit (payload im@100 = 62.83). Both correctly labeled engine-exact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>verify.scrub.exact-point-10000</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Slider at qty 10,000: FDM $14.18 (payload 14.18), Injection Molding $3.43 (payload 3.43), both labeled 'engine-exact - a computed point'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>verify.scrub.interpolation-label</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Slider at qty 501 (between computed 100 and 1,000): both cards labeled 'interpolated between computed 100 and 1,000', never presented as engine-exact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>verify.scrub.interpolation-value</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>At qty 501 Injection Molding renders $15.91/unit; log-log interpolation of the two real payload points (62.83@100, 8.83@1000) = 15.91. FDM renders $14.18 (both brackets 14.18). No fabricated fresh compute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>verify.drivers.fdm-at-10000</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>'What it really takes' card (reads at headline qty 10,000): MATERIAL 0.409 $ (payload 0.4092), PARTS PER BUILD 20, MACHINE 6.16 $, CYCLE 0.77 hr, LABOR 7.175 $, SETUP 0.438 $ (payload 0.4375) - all match fdm@10000 drivers within rounding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>verify.leadtime.fdm-at-10000</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Card renders 'lead 25.2-46.8 days'; payload fdm@10000 lead_time low_days 25.2 / high_days 46.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>verify.process-chips.dfm-verdicts</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Route chips DLP=issues, SLS=pass, MJF=pass, Binder Jetting=pass, CNC 3-Axis=pass, CNC 5-Axis=pass, FDM=issues match POST /validate process_scores verdicts exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>verify.priority-fixes.count</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>'12 priority fixes across routes' matches payload priority_fixes array length 12 (not a client-side recount).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>verify.confidence.label</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Band caption 'assumption-based, not yet validated' and 'unvalidated ... n=0' match payload confidence.label, validated=false, n_samples=0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>analyze.geometry.tiles</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>/analyze tiles VOLUME 12.0 cm3, BOUNDING BOX 40 x 30 x 10 mm, FACES 12, WATERTIGHT Yes match payload (volume_cm3 12.0, bbox_mm [40,30,10], face_count 12, watertight true); 'analyzed in 48.3ms' matches analysis_time_ms 48.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>analyze.routing.card</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Geometric routing card: MJF, archetype bulk_solid, confidence 0.40, drivers planar_aspect 3.00 / nominal_wall_mm 6.32 / sheet_gauge_mm 10.00 / bend_count 1.00 / rotational no / sheet_like no all match payload routing block verbatim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>analyze.dfm-matrix.scores</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>DFM matrix scores (FDM 0.9, SLA 0.9, DLP 1.0, SLS 1.0, MJF 1.0, DMLS 0.8, SLM 0.8, CNC Turning 0.0, Injection Molding 0.1 ...) match payload process_scores at 1-dp formatting; IM blocker text matches the payload error message verbatim. Note: IM payload score 0.05 renders as '0.1' via 1-dp rounding - the exact 5% appears in the suitability card, so precision is recoverable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>analyze.suitability.percent</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Suitability percentages (DLP 100%, FDM 90%, DMLS 80%, Injection Molding 5%, CNC Turning 0%) are exact score*100 of payload values - no distortion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>analyze.features.list</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Detected features: 6 flat features, each '2 faces / 98% / 300.0-1200.0mm2' match payload features (face_count 2, confidence 0.98, areas 300/400/1200/1200/400/300 mm2), correct mm2 label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>analyze.issue-scope.counts</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>'Advisory 1' on recommended route DLP + 'Show 31 issues only on other candidate processes (21 evaluated)' reconcile with payload: 32 issues total across 21 process_scores, 1 on dlp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>analyze.cost-factor.unit-label</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Process suitability cards render 'Est. cost factor: $1.44' / '$2.40' / '$0.60' etc., but payload estimated_cost_factor (1.44, 2.4, 0.6) is a dimensionless relative-cost MULTIPLIER, not USD. Prefixing '$' mislabels a unitless factor as a dollar amount. /home/user/cadverify/frontend/src/components/ProcessScoreCard.tsx:53: `Est. cost factor: ${'$'}{costFactor.toFixed(2)}` (literal $ + factor). Numbers themselves match the payload; the unit is wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>decision.recommendation.table</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>/cost-decisions/01KZA8SP1CWHVM7PQZY644PCCS 'Recommendation by quantity' table matches saved decision.recommendation exactly: qty1 FDM/PLA $30.00 lead 4.9-9.1d; qty100/1000/2000/5000/10000 MJF/PP $5.03/$4.96/$4.96/$4.96/$4.96 with leads 5.6-10.4/5.6-10.4/6.3-11.7/7.7-14.3/9.8-18.2d; 'cheaper if redesigned' IM $4.03@5000 and $3.43@10000 match if_redesigned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>decision.process-options.grid</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>All 8 process option cards' per-qty unit costs match the run payload exactly (e.g. CNC 3-Axis 137.42/24.80/17.21/15.52/13.55/12.25; IM 6,002.83/62.83/8.83/5.83/4.03/3.43; SLS 75.00/5.88/5.78/5.77/5.77/5.77), and the +/-40%/50%/60% chips match est_error_band_pct per process (40 additive, 50 CNC, 60 IM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>decision.confidence.band</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>'CONFIDENCE 80% - $18-$42/unit (+/-40%)' with point $30 matches payload fdm@1 confidence (level 0.8, low 18.0, point 30.0, high 42.0, half_width_pct 40); basis text rendered verbatim from payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>decision.drivers-sum.qty1</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Cost drivers panel labeled '@ qty 1': material $0.41 (0.4092), machine $6.16, labor $7.18 (7.175), setup $8.75, min_charge_floor $7.51 (7.5058); 'Sigma line items = unit cost $30.00' - payload line items sum 30.00 = fdm@1 unit_cost_usd 30.0. Lead time 4.9-9.1 days with ship 3/queue 2/production 1/post 1 d and capacity 12 machines x 22 hr/day all match payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>decision.assumptions.verbatim</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>All 14 assumption rows (labor_rate $35/hr, region multipliers x1, stock_allowance 1.1x, machine_labor_frac 0.35, daily_machine_hours 8 hr/day, n_cavities 1, etc.) render the payload assumptions verbatim with DEFAULT provenance. (Engine-side oddity, not a display bug: assumptions list daily_machine_hours=8 while lead-time capacity uses 22 hr/day - both strings come straight from the payload.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ui-fidelity</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>decision.crossover-and-hash</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>'Make below ~529 units with FDM / FFF; tool up with Injection Molding above it' matches crossover_qty 529 / make_now_process fdm / tooling_process injection_molding; Source SHA-256 beef04f8... on the detail page equals the evidence hash shown on the live /verify run - same immutable record. Zero browser console errors across all three pages.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D121"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/qa/Feature-Tracker.xlsx
+++ b/qa/Feature-Tracker.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stories" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Audits" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audits" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$L$239</definedName>
@@ -646,7 +646,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Fresh analyst retest-app1-0806@proofshape.local. Dropzone accept='.stl,.step,.stp,.iges,.igs'; qa-box.stl drop fired POST /api/proxy/validate/cost + POST /api/proxy/validate?units=mm in parallel (both 200, &lt;4s apart). bad.txt -&gt; 'Unsupported file type. Use STL, STEP, STP, IGES or IGS.' with zero validate requests; qty 'abc' -&gt; options panel open + 'Fix the quantity list before submitting.' and no request. Per-tab loading copy ('Analyzing across all manufacturing processes…') observed. Anonymous /analyze -&gt; /login?next=%2Fanalyze.</t>
+          <t>Fresh account zfinal-app1-1786020809@proofshape.local. Dropzone accept='.stl,.step,.stp,.iges,.igs'. qa-box.stl drop fired POST /api/proxy/validate/cost and POST /api/proxy/validate?units=mm in parallel (both 200). bad.txt -&gt; 'Unsupported file type' with zero validate requests; qty 'abc' -&gt; options panel open + 'Fix the quantity list before submitting.' and no request. Anonymous GET /analyze -&gt; 307 /login?next=%2Fanalyze.</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Five tabs Decision|Routing &amp; DFM|Glass Box|Compare|History. /analyze (mfg lens) lands on Routing &amp; DFM; Cost eng -&gt; Glass Box with Inspector auto-open; Sourcing -&gt; Compare. With no cost report (qa-broken.stl GEOMETRY_INVALID) Glass Box shows 'No cost breakdown yet' and Compare 'Nothing to compare yet'. 'New part' resets to the cold-start dropzone.</t>
+          <t>Five tabs (Decision, Routing &amp; DFM, Glass Box, Compare, History). /analyze mfg lens lands Routing &amp; DFM (aria-selected); Cost eng lens -&gt; Glass Box; Sourcing -&gt; Compare. With GEOMETRY_INVALID part (no cost report): Glass Box 'No cost breakdown yet', Compare 'Nothing to compare yet'. 'New part' returns to the cold-start dropzone.</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Selecting the draft/sidewall issue row on the Routing tab selected it and showed the 'Highlighting &lt;CODE&gt;… click another blocker, or a face' note with severity-colored face highlight. Canvas face-click and the no-geometry-linked-faces toast were not deterministically exercisable (all matrix blockers on this part have geometry-linked issues); no deviation observed.</t>
+          <t>On qa-broken Routing tab, clicking the NON_WATERTIGHT issue row selected it and rendered the 'Highlighting &lt;CODE&gt;' note (severity-mapped highlight active). Direct canvas face-click and the no-geometry-linked-faces toast were not deterministically drivable headless; no deviation observed. Screenshot zfinal-APP-003-issue-highlight.png.</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/shops 200 on mount. Binding a shop from the calibration pill toasted 'Calibrating to …', re-ran POST /validate/cost (200) and flipped badge to 'Calibrated to'. Glass Box driver rate editor applied an override (re-cost 200, '1 override applied' chip); 'Reset overrides' re-cost + 'Cleared overrides' toast. 'Save as scenario' stored a session chip; clicking the chip recalled options and re-cost. Scenarios session-local (cleared on reset).</t>
+          <t>GET /api/proxy/shops 200 on mount. Binding 'Midwest Precision CNC' toasted 'Calibrating to Midwest Precision CNC — re-costing', re-ran POST /validate/cost 200 and flipped the pill to 'Calibrated to'. Glass Box driver rate override applied -&gt; re-cost 200 + '1 override applied' chip; 'Reset overrides' re-cost 200. 'Save as scenario' created a session chip ('Generic · qty 50…'); clicking it recalled options and re-cost 200. Scenarios are session-local (gone after reset).</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>qa-broken.stl: POST /validate/cost 400 GEOMETRY_INVALID -&gt; CostGeometryInvalidCard (repair reason + measured volume/watertight geometry), no generic error; 'Geometry invalid' header badge confirmed shown while DFM was pending (badge is replaced by the real DFM verdict once /validate resolves, per headerBadge logic). Screenshot retest-APP-005-badge.png. 429/5xx toasts and generic ErrorState retries not force-triggerable (no fault injection); no deviation observed.</t>
+          <t>qa-broken.stl: POST /validate/cost 400 code=GEOMETRY_INVALID -&gt; Decision tab renders CostGeometryInvalidCard ('Geometry invalid' badge, 'No cost produced — repair required.', reason, measured Volume/Bounding box/Watertight/Faces stats) — no generic error. Header badge later replaced by the real DFM verdict once /validate resolves (per design). 429/5xx toasts not force-triggerable without fault injection; no deviation. Screenshot zfinal-APP-005-decision-card.png.</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>0.3mm cube produced unit_warnings -&gt; persistent [data-testid=cad-unit-warning] banner ('Confirm CAD source units before using this decision.' + implausible-volume message). Adjust inputs -&gt; units=Inches -&gt; 'Re-cost with these inputs' re-ran BOTH /validate/cost and /validate?units=inch (200/200); banner cleared. Inspector exposes Lineage/Governance/Sources/Audit tabs, defaults to Sources for cost role; Inspector-applied overrides trigger a real server re-cost (verified via Glass Box path in APP-004).</t>
+          <t>0.3mm cube -&gt; [data-testid=cad-unit-warning] banner ('Confirm CAD source units before using this decision.'). Adjust inputs &amp; re-cost -&gt; units Inches -&gt; 'Re-cost with these inputs' re-ran BOTH POST /validate/cost and POST /validate?units=inch (200/200) and the banner cleared. Under the Cost eng lens the Inspector opened showing Lineage/Governance/Sources/Audit tabs with column-lineage derivation content. Screenshots zfinal-APP-006-unit-warning.png / -inspector.png.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>'No history yet' EmptyState with no report. With report: saved scenario chips recallable (re-cost fired), 'Open cost history' navigated to /cost-decisions, 'Copy decision summary' wrote plaintext summary to clipboard ('ProofShape — qa-box.stl / Make by MJF…' + 'Decision summary copied' toast). report.saved present -&gt; CostArtifactBar ('Saved to cost history' with Open in history/PDF/JSON/CSV/RFQ ZIP/Share).</t>
+          <t>History tab showed saved scenario chip (click recalled + re-cost 200), 'Open cost history' navigated to /cost-decisions, 'Copy decision summary' wrote a 248-char plaintext summary ('ProofShape — qa-box.stl | Make by MJF (HP)…') to the clipboard with 'copied' toast. report.saved present on the authed route -&gt; CostArtifactBar 'Saved to cost history' with Open/PDF/JSON/CSV export actions rendered on the Decision tab.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/analyses/{id} on mount; filename/STL/date header + full dashboard rendered for qa-box analysis. Bogus ULID -&gt; 'Analysis not found' ErrorState with 'Back to history' link.</t>
+          <t>GET /api/proxy/analyses/{id} 200 on mount; filename/STL/date header + full AnalysisDashboard rendered. Bogus ULID -&gt; 'Analysis not found' ErrorState with 'Back to history' link (proxy 404 handled).</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Share POST /api/proxy/analyses/{id}/share 200 -&gt; modal with share_url http://localhost:3000/s/&lt;token&gt; (readonly input) + Copy link/Revoke; Revoke DELETE 200 returned button to unshared 'Share' state.</t>
+          <t>Share POST /api/proxy/analyses/{id}/share 200 returned share_url /s/&lt;token&gt;, Shared badge shown; 'Copy link' modal displayed the URL in a readonly input; Revoke DELETE 200 returned the button to the unshared 'Share' state.</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/analyses/{id}/pdf 200 downloaded 'qa-box-dfm-report.pdf' (valid %PDF); 'Generating PDF…' label observed while loading.</t>
+          <t>'Download PDF' fetched GET /api/proxy/analyses/{id}/pdf and downloaded 'qa-box-dfm-report.pdf' (valid %PDF magic).</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>'Attempt mesh repair' absent on the clean qa-box analysis, present on the NON_WATERTIGHT qa-broken analysis. Click opened a file picker; re-selecting qa-broken.stl POSTed /api/proxy/validate/repair (200) and swapped the dashboard for the RepairComparison (Original vs Repaired). Screenshot retest-APP-011-comparison.png.</t>
+          <t>'Attempt mesh repair' absent on the clean qa-box analysis, present on the NON_WATERTIGHT qa-broken analysis. Click opened a file picker; re-selecting qa-broken.stl POSTed /api/proxy/validate/repair 200 and swapped the dashboard for the Original vs Repaired comparison. Screenshot zfinal-APP-011-repair.png.</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>qa-box analysis showed 'Linked cost decisions' card listing decisions (qa-box.stl, mjf, unreviewed) with 'Open decision' navigating to /cost-decisions/{id}; card absent on the qa-broken analysis with no linked decision.</t>
+          <t>qa-box analysis rendered 'Linked cost decisions' card (qa-box.stl, mjf · unreviewed) and 'Open decision' navigated to /cost-decisions/{id}; card absent on the qa-broken analysis with no links.</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/analyses?limit=20 rendered 5 rows. Verdict select 'Required' refetched with verdict=fail (200) and showed only qa-broken.stl. Row click -&gt; /analyses/{ulid}. 'Load more' cap/empty state/load-error retry not exercisable (few rows, no fault injection); no deviation observed.</t>
+          <t>GET /api/proxy/analyses?limit=20 200 rendered 5 rows. Verdict select 'Required' refetched with verdict=fail 200 and showed only qa-broken.stl. Row click navigated to /analyses/{ulid}. Load-more 500-cap / empty state / load-error retry not exercisable (few rows, no fault injection); no deviation.</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>QuotaDisplay rendered used/total progress from X-RateLimit headers with 'Resets in N min'. Screenshot retest-APP-014-quota.png.</t>
+          <t>Fresh account zzverify-fixes@proofshape.local + key (prefix HVmoXhIF); burned one POST /api/v1/validate (200, x-ratelimit-limit=60, remaining=59, x-ratelimit-reset=1786026988 epoch, ~3601s out). /history (page rendering QuotaDisplay) showed 'Rate limit usage 1 / 60 used (2%)' and 'Resets in 61 min' — sane countdown = ceil((reset-now)/60) for the 60-min window, vs the previous ~29,767,091 min (epoch treated as duration). QuotaDisplay.tsx now computes reset - Date.now()/1000. Screenshot: qa/results/screenshots/zzverify-app-014.png. Same caveat as SITE-025: verified on a fresh production build served on port 3001 because port 3000 runs the stale pre-fix build.</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>/cost (flag off) rendered the identical PartWorkspace dropzone; qa-part2.stl fired the same /validate/cost + /validate pair (200/200), landed on the Decision tab with 'Lens Design eng', 5 tabs, and persisted the decision (CostArtifactBar 'Saved to cost history').</t>
+          <t>/cost (flag off) rendered the identical PartWorkspace dropzone; qa-part2.stl fired the same POST /validate/cost + POST /validate pair (200/200), landed on the Decision tab with 'Lens Design eng', all 5 tabs present, decision persisted (CostArtifactBar 'Saved to cost history').</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>NEXT_PUBLIC_STAGE_UI unset (default build): no DoorChooser rendered and localStorage cv_door=null — /cost behaves as APP-015, the documented flag-off expectation. Flag-on router not exercisable without a rebuild.</t>
+          <t>NEXT_PUBLIC_STAGE_UI unset (default build): no DoorChooser rendered, localStorage cv_door=null, /cost behaves exactly as APP-015 — the documented flag-off expectation. Flag-on router not exercisable without a rebuild.</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/cost-decisions?limit=20 rendered 6 rows with File/Make now/Crossover/Quantities/Governance columns, Unreviewed badges, relative time; CostHonestyNote ('assumption-based, not yet validated') above the table; 'Compare decisions' routed to /cost-decisions/compare; row click -&gt; /cost-decisions/{id}. Pagination cap/empty state not exercisable (rows exist).</t>
+          <t>GET /api/proxy/cost-decisions?limit=20 200; table with File/Make now/Crossover/Quantities/Governance columns, Unreviewed badges, relative times; CostHonestyNote ('assumption-based, not yet validated') above; 'Compare decisions' button present; row click -&gt; /cost-decisions/{id}. Pagination cap/empty state not exercisable (rows exist).</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Detail GET on mount; 'Source SHA-256 · &lt;64-hex&gt;' mesh hash shown; exports: PDF 'qa-part2-cost-report.pdf' (valid %PDF), JSON 'qa-part2-cost.json', CSV 'qa-part2-cost.csv'. Bogus id -&gt; 'Cost decision not found' ErrorState with back link.</t>
+          <t>Detail GET 200 on mount; 'Source SHA-256 · &lt;hash&gt;' shown. Exports: 'Download PDF' -&gt; qa-part2-cost-report.pdf (valid %PDF), JSON -&gt; qa-part2-cost.json (valid JSON), CSV -&gt; qa-part2-cost.csv. Bogus id -&gt; 'Cost decision not found' ErrorState with back link.</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Approve with note POST /cost-decisions/{id}/approve 200: badge flipped to Approved with 'Signed off by user N on &lt;date&gt;' + approval-note card. Reopen DELETE 200 returned badge to Unreviewed. Stale warn card and read-only-role variant not exercisable (no stale data; analyst account).</t>
+          <t>Approve with note POST /cost-decisions/{id}/approve 200: badge flipped to Approved with 'Signed off by user N on &lt;date&gt;' and the note 'zfinal QA sign-off' displayed. Reopen DELETE 200 returned badge to Unreviewed. Stale warn card and read-only-role variants not exercisable (no stale data; analyst account). Screenshot zfinal-APP-019-approved.png.</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>'Make outside' PUT /cost-decisions/{id}/disposition 200 while approved -&gt; toast 'Outcome saved; prior approval reopened', badge Unreviewed, recorded outcome + updated-by line. 'Save outcome note' -&gt; 'Outcome note saved'; 'Withdraw outcome' -&gt; 'Outcome withdrawn'. 'Make in-house' enabled (route DFM clean on qa-part2) — blocked/tooltip and read-only variants not exercisable.</t>
+          <t>While Approved, 'Make outside' PUT /cost-decisions/{id}/disposition 200 -&gt; recorded outcome shown, approval reopened (reopened message + Unreviewed badge, 'Updated … by user N' line). 'Withdraw outcome' PUT 200 (disposition null). 'Make in-house' enabled (route DFM clean on qa-part2), so the blocked-tooltip variant was not exercisable; error and read-only variants not exercisable.</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Share POST 200 -&gt; modal with public URL http://localhost:3000/s/cost/&lt;token&gt;; Revoke DELETE 200. 'RFQ ZIP' POST /rfq-packages 201 (title 'RFQ package - qa-part2.stl') then downloaded 'RFQ package - qa-part2-rfq.zip' (valid PK zip) with 'RFQ package generated' toast.</t>
+          <t>Share POST 200 -&gt; modal with public URL /s/cost/&lt;token&gt;; Revoke DELETE 200. 'RFQ ZIP' POST /rfq-packages 201 (title 'RFQ package - qa-part2.stl') then downloaded 'RFQ package - qa-part2-rfq.zip' (valid PK zip).</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>GET /cost-decisions?limit=100 filled both pickers (6 options); Compare disabled until two distinct ids; the id chosen on side A rendered disabled on side B; GET /cost-decisions/compare?ids=A,B 200 rendered summary cards + per-quantity unit-cost table with cheaper-side highlight and signed Δ ($/%) values. Fewer-than-2 empty state not exercisable (decisions exist). Screenshot retest-APP-022-compare.png.</t>
+          <t>GET /cost-decisions?limit=100 filled both pickers; Compare disabled until two distinct ids and the side-A id rendered disabled on side B. GET /cost-decisions/compare?ids=A,B 200 rendered summary cards + per-quantity table with cheaper side in green and tone-colored Δ (+$1.44 (+27.6%)). Fewer-than-2 empty state not exercisable (decisions exist). Screenshot zfinal-APP-022-compare.png.</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>bad.txt -&gt; toast 'Only .zip files are accepted', no request. qa-batch.zip: staged upload copy (data-upload-stage) observed, GET /uploads/capabilities fired, POST /api/proxy/batch 202, auto-routed to /batch/{batch_id}. 5GB limit, CSV manifest, webhook, retry/durable-failure states and double-submit lock not exercisable with a small local fixture; no deviation observed.</t>
+          <t>bad.txt -&gt; 'Only .zip files are accepted' toast, no batch request. qa-batch.zip: GET /uploads/capabilities fired, POST /api/proxy/batch 202, auto-routed to /batch/{batch_id}. 5GB limit, CSV manifest, webhook, retry/durable-failure branches and double-submit lock not exercisable with a small local fixture; no deviation observed.</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>GET /api/proxy/batches?limit=20 200; row showed truncated ULID, Completed badge, 2/2 counts, created date; 'Download CSV' only on the completed batch, fetched batch_&lt;ulid&gt;_results.csv (header filename,status,verdict,best_process,issue_count,duration_ms,analysis_url,error); row click -&gt; /batch/{ulid}. Cursor/empty/error states not exercisable.</t>
+          <t>GET /api/proxy/batches?limit=20 200; row showed truncated ULID, Completed badge, 2/2 counts, created date; 'Download CSV' on the completed batch fetched batch_&lt;ulid&gt;_results.csv (header filename,status,verdict,best_process,issue_count,duration_ms,analysis_url,error); row click -&gt; /batch/{ulid}. Cursor/empty/error states not exercisable.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Detail polled GET /api/proxy/batch/{id} until 'completed'; items table (GET /batch/{id}/items) listed qa-box.stl/qa-part2.stl with statuses, verdicts and 'View' links to created analyses; 'Download CSV' appeared on completion and downloaded the results CSV.</t>
+          <t>Detail polled GET /api/proxy/batch/{id} repeatedly until terminal 'Completed'; items table (GET /batch/{id}/items) listed qa-box.stl and qa-part2.stl with statuses/verdicts and links to created analyses (4 analysis links); 'Download CSV' appeared on completion. Screenshot zfinal-APP-025-batch-detail.png.</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Second batch (concurrency 1): 'Cancel batch' visible while non-terminal; AlertDialog 'Pending items will be skipped. This cannot be undone.'; confirm POST /batch/{id}/cancel 200, toast 'Batch cancelled'. Revisit showed terminal Cancelled with skipped items, no Cancel button and no CSV. Screenshots retest-APP-026-cancel-dialog.png / retest-APP-026-cancelled.png.</t>
+          <t>Fresh 30-item ZIP batch (concurrency=1): 'Cancel batch' shown only while non-terminal; AlertDialog copy exact ('Pending items will be skipped. This cannot be undone.'); confirm POSTed /api/proxy/batch/{id}/cancel 200, toast 'Batch cancelled', status flipped to cancelled with 30 skipped items refreshed. Terminal batch page renders NO cancel button and a repeat cancel via API returns 409 'Batch already in terminal state'. Screenshot zf2-026-cancelled.png</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>gmsh fix confirmed: POST /api/proxy/designs 202 for a plate ('QA Retest Plate') -&gt; status generating with list polling, then revision reached READY in ~10s (engine proofshape-occ-v1) with real preview. Template picker verified: enclosure swaps Thickness-&gt;Wall (+Height), bracket adds Height without corner holes, plate shows the four-corner-hole options. No fail card, no console errors. Fresh analyst account. Screenshots r2-app-027-generating.png, r2-app-027-ready.png</t>
+          <t>POST /api/proxy/designs 202 (plate 'QA ZFinal Plate') -&gt; status generating, list polling, revision READY in ~3s (engine proofshape-occ-v1). Template picker (Mounting plate / L bracket / Open enclosure) verified: plate shows Width/Depth/Thickness + four-corner-hole options (Diameter/Edge inset), enclosure swaps Thickness-&gt;Wall and adds Height, bracket adds Height. No fail card, no console errors. Fresh analyst account. Screenshot zf2-027-form.png</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Empty description shows 'Describe the starting shape and its dimensions first.' (error banner, no request). 'Interpret safely' POST /designs/interpret 200: ready plan for '80 x 50 x 6 mm plate with four 6 mm corner holes' fills the whole form (width 80, thickness 6, holes checked) with green message+assumptions; partial prompt ('a bracket that is 60 wide') returns needs_input with amber 'I found the shape, but need: depth, height, thickness.' and prefills width=60/kind=bracket.</t>
+          <t>Empty description shows 'Describe the starting shape and its dimensions first.' with zero /designs/interpret requests. 'Interpret safely' POST 200: ready plan for '80 x 50 x 6 mm plate with four 6 mm corner holes' fills the whole form (width 80 etc.) with green 'Safe dimensions extracted' + assumptions; 'a bracket that is 60 wide' returns needs_input with amber 'I found the shape, but need: depth, height, thickness.' and prefills width=60. Screenshot zf2-028-interpret.png</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Ready revision now reachable: GET /designs/{id}/revisions 200; CadViewer loads GET .../revisions/1/preview.stl?hash=&lt;geometry_hash&gt; 200 (canvas renders); cards show Envelope 80.0x50.0x6.0 mm, Volume 23.32 cm3, STEP 29.2 KB, evidence hash. STEP download link GET .../revisions/1/download.step -&gt; 200 model/step, valid ISO-10303-21 body (29934 bytes). 'Verify revision 1' links to /verify?design=&lt;id&gt;&amp;revision=1. Created revision 2 (POST .../revisions 202, name field locked, Revise disabled while generating) -&gt; R2 ready; chips R1/R2 switch viewer+preview URL and R1 STEP stays downloadable ('current is 2' shown while viewing R1).</t>
+          <t>GET /designs/{id}/revisions 200; R1/R2 chips switch the CadViewer -&gt; clicking R1 fired GET .../revisions/1/preview.stl?hash=&lt;geometry_hash&gt; 200 (canvas renders), STEP link changed to .../revisions/1/download.step, 'current is 2' note shown. STEP download 200 model/step valid ISO-10303-21 (29934 bytes); envelope/volume/STEP size/hash cards present; 'Verify revision' links to /verify?design=&lt;id&gt;&amp;revision=2. POST .../revisions 202 created R2 -&gt; ready. Screenshots zf2-029-revisions.png, zf2-029c-chipswitch.png</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Trash icon opened window.confirm 'Archive “QA Retest Plate”? Its audit evidence will be retained.'; confirm sent DELETE /api/proxy/designs/{id} 204 and the card left the list (empty state returned). No console errors. Screenshot r2-app-030-archived.png</t>
+          <t>Trash icon opened window.confirm 'Archive “QA ZFinal Plate”? Its audit evidence will be retained.'; confirm sent DELETE /api/proxy/designs/{id} and the card left the list. No console errors. Screenshot zf2-030-archived.png</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Unchanged from pass 1: this build runs with the dev tools flag ON (DEV_TOOLS_ENV true) so /label renders the labeling tool; the story's disabled EmptyState branch cannot render in this environment. Verified the page does NOT show the disabled state and behaves as the enabled tool (APP-032).</t>
+          <t>Environment-bound dev-flag state: this build runs with the dev tools flag ON, so /label renders the enabled labeling tool and fires corpus requests (3 observed on load); the story's disabled EmptyState branch ('Labeling backend disabled') cannot render here. Not a bug.</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Corpus seeded (2 QA parts) and fully testable now. Load fires GET /corpus/parts?unlabeled_only=true&amp;limit=200&amp;labeler=... 200 and GET /corpus/progress 200; badge '0 / 2 labeled'; each part renders its STL via GET /corpus/parts/{id}/mesh.stl 200 in the viewer plus metadata (filename/dataset/license/faces/bbox/watertight). Hotkeys: ArrowRight/ArrowLeft navigate 1/2&lt;-&gt;2/2, pressing '1' POSTed /corpus/labels {part_id,label:'additive',labeler,confidence:'medium'} 200 and advanced; badge updated to '1 / 2 labeled'. 's' skipped past the last part -&gt; 'Queue complete for this labeler' with reload action; reload showed the 1 remaining unlabeled part. Heuristic-guess warning not rendered because the seeded parts have process_family_guess=null (warning is conditional per design). No console errors. Screenshots r2-app-032-queue.png/labeled.png/complete.png</t>
+          <t>GET /corpus/parts?unlabeled_only=true&amp;limit=200&amp;labeler=... and GET /corpus/progress 200; badge '1 / 2 labeled'; STL rendered via GET /corpus/parts/{id}/mesh.stl 200 (canvas). Hotkey '1' POSTed /corpus/labels 200 and advanced to 'Queue complete'; 's' skip and arrow navigation work. API label POST returned {ok:true,label:'subtractive'} and progress incremented. Heuristic-guess warning absent because seeded parts have process_family_guess=null (conditional per design). Screenshot zf2-032-label.png</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Re-verified honest disabled state: GET /api/proxy/reconstruct/capability 200 on mount; available:false renders 'Image-to-3D is not enabled' with the backend message, 'No image has been uploaded or sent to a third party.' assurance, and a 'Verify CAD instead' button; zero file inputs rendered. No console errors. Screenshot r2-app-033-reconstruct.png</t>
+          <t>GET /api/proxy/reconstruct/capability 200 -&gt; available:false; page renders 'Image-to-3D is not enabled' with the backend message, no-upload assurance, and a 'Verify CAD instead' button to capability.verify_path; zero file inputs. Screenshot zf2-033-reconstruct.png</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Reconstruction backend still disabled (/health reconstruction.available=false, backend 'none'); the uploader/submit/poll flow is unreachable behind the honest disabled state verified in APP-033.</t>
+          <t>Reconstruction backend disabled in this environment (/health reconstruction.available=false, backend 'none'); the uploader/submit/poll flow is unreachable behind the honest disabled state verified in APP-033.</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Same as APP-034: no reconstruction job can be created in this environment, so the mesh preview/confidence/hand-off step is unreachable.</t>
+          <t>Same environment constraint as APP-034: no reconstruction job can be created, so the mesh preview/confidence/hand-off step is unreachable.</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>GET /integrations/connectors + GET /integrations/runs?limit=25 both 200 on load; connector cards show source system/kind, raw stored: no, live creds flags (sandbox API connectors show live creds: yes). Run disabled without a file. Dry-run of a 2-row SAP manifest CSV -&gt; POST /integrations/runs 200 status passed, toast 'Dry-run recorded', row prepended (2/2 valid, dry_run, SHA-256 prefix, completed time). Import mode -&gt; 200, toast 'Import recorded', row prepended with mode import. Screenshots r2-app-036-dryrun.png, r2-app-036-import.png</t>
+          <t>GET /integrations/connectors + GET /integrations/runs?limit=25 200 on load; connector cards show source system/kind and raw-stored/live-creds flags. Run disabled without a file, enabled after file select; UI dry-run POST /integrations/runs 200 -&gt; toast 'recorded', row prepended (status passed). API: dry_run and import both 200 with rows_valid=2/rows_total=2, SHA-256, completion time; empty state 'No connector runs yet' seen pre-run. Screenshot zf2-036-integrations.png</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Seeded 2 real decision.created notifications via authed POST /validate/cost. Both load GETs (dismissed=false/true) 200 populate Inbox (2)/Dismissed (0); empty state 'You're all caught up.' seen pre-seed. 'Mark all read' POST /notifications/read-all 200 stamped every row Read &lt;timestamp&gt;. Per-row 'Open' POST /notifications/{id}/read 200 then navigated to the mapped Verify destination /verify?screen=records. No console errors. Screenshots r2-app-037-inbox.png, r2-app-037-open-dest.png</t>
+          <t>Seeded 2 decision.created notifications via authed POST /validate/cost. Both load GETs (dismissed=false/true) 200 populate Inbox/Dismissed; POST /notifications/read-all 200 stamped all rows read (via API; UI hides 'Mark all read' once everything is read); per-row 'Open' POSTed /notifications/{id}/read then navigated to /verify?screen=records. Screenshot zf2-037-notifications.png</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Dismiss POST /notifications/{id}/dismiss 200 moved the row to Dismissed with 'Dismissed &lt;timestamp&gt;'; Restore POST .../restore 200 returned it to the inbox preserving its prior read state ('Read &lt;original timestamp&gt;'). Copy states dismissal changes only the user's inbox, never audit records. Screenshots r2-app-038-dismissed.png, r2-app-038-restored.png</t>
+          <t>UI Dismiss POSTed /notifications/{id}/dismiss 200 and moved the row to the Dismissed column; Restore POSTed .../restore 200 and returned it to the inbox with its prior read state preserved (verified via API: is_read stayed true, dismissed_at cleared). Copy states dismissal changes only the user's inbox, never audit records.</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>GET /rfq-packages?limit=50 and GET /cost-decisions?limit=100 in parallel (both 200) with two seeded (unapproved) cost decisions listed. 'Generate package (0)' disabled; selecting a risky decision showed the amber 'Selected decisions include stale or unapproved records; the package will preserve those warnings.' banner and enabled 'Generate package (1)'; POST /rfq-packages 201 created 'QA Retest RFQ' (warnings decision_unapproved + confidence_unvalidated preserved), prepended with toast 'RFQ package generated'. Screenshot r2-app-039-created.png</t>
+          <t>GET /rfq-packages?limit=50 and GET /cost-decisions?limit=100 load in parallel. 'Generate package (0)' disabled; selecting an unapproved decision showed the amber 'package will preserve those warnings' banner and enabled 'Generate package (1)'; UI POST /rfq-packages created the package with success toast; API create returned 201 with warnings decision_unapproved + confidence_unvalidated preserved. Screenshot zf2-039-rfq.png</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Empty state 'No RFQ packages yet.' verified before creation. Row shows title/supplier (Acme Machining), 0/1 approved, amber warnings count 2, created date; ZIP button downloaded 'QA Retest RFQ-rfq.zip' (GET /rfq-packages/{id}/download.zip 200 application/zip, 65 KB); archive verified valid (package_manifest.json, line-items.csv, supplier-brief.pdf/md, cost-decisions.json, per-decision folder with should-cost-report.pdf and raw-cad-unavailable.txt).</t>
+          <t>Empty state '{"packages":[]}' verified via API pre-create. List row shows title/supplier (Acme Machining), approved 0/1, amber warnings count 2, created date; ZIP fetch GET /rfq-packages/{id}/download.zip 200 application/zip (99 KB) and archive validated (package_manifest.json, line-items.csv, supplier-brief.pdf/md, cost-decisions.json, per-decision should-cost-report.pdf + raw-cad-unavailable.txt).</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Detail GET /rfq-packages/{id} renders stat cards (Approved 0/1, Stale 0, Unvalidated 1, Raw CAD No), warnings card with code+message, items table with per-decision flags ('unvalidated') and manifest column; decision name click navigates to /cost-decisions/{id}; Download ZIP fetched 'QA Retest RFQ-rfq.zip'. Bogus id shows 'RFQ package not found.' with Back. Screenshots r2-app-041-detail.png, r2-app-041-notfound.png</t>
+          <t>Detail GET /rfq-packages/{id} renders stat cards (Approved 0/1, Stale, Unvalidated, Raw CAD), warnings card with code+message, items table with per-decision flags and manifest column; decision links to /cost-decisions/{id}; Download ZIP present. Bogus ULID -&gt; API 404 and page shows 'RFQ package not found.' with Back. Screenshot zf2-041-detail.png</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>GET /onboarding returns 307 Location /verify?welcome=1 (no UI, no API calls); browser lands on the Verify welcome flow (client consumes the welcome param).</t>
+          <t>Authenticated GET /onboarding returns 307 Location /verify?welcome=1 with no UI; browser lands on the Verify welcome flow (welcome param consumed). Unauthenticated request redirects to /login?next=/onboarding as expected for the (app) layout.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Fresh account showed 'No API keys yet' with Create key. Create POST /api/proxy/keys 200 -&gt; masked cv_live_&lt;prefix&gt;_… row with Active badge; Rotate POST /keys/{id}/rotate 200 revealed a NEW secret and marked the old key Revoked; Revoke DELETE /keys/{id} 204 -&gt; 'Revoked' badge and action buttons removed. Key column never shows full secrets. No console errors. Screenshot r2-app-043-revoked.png</t>
+          <t>Fresh account: 'No API keys yet' empty state with Create key. UI create POST /api/proxy/keys 200 -&gt; masked cv_live_&lt;prefix&gt;_… row; Rotate POST /keys/{id}/rotate 200 revealed a NEW secret and marked the old key Revoked (old secret rejected with 401 on backend, new secret accepted 200, revoked secret 401 after DELETE 204). Revoked keys show fail badge and lose action buttons; key column never shows full secrets. Screenshot zf2-043-revoked.png</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>RevealOnceModal opened after create and after rotate showing the full cv_live_ token with Copy, an 'I've saved it somewhere safe' acknowledge checkbox gating Done ('Copy it now - we will not show it again.'); cv_mint_once cookie already scrubbed while the modal was open (document.cookie empty) and a reload did not re-reveal. Page links to /api-reference and the /scalar API console. Screenshot r2-app-044-reveal.png</t>
+          <t>RevealOnceModal opened after create and after rotate showing the full cv_live_ token with Copy and an acknowledge gate ('we will not show it again'); cv_mint_once cookie already scrubbed while the modal was open (document.cookie empty) and reload did not re-reveal. Page links to /api-reference and the /scalar API console. Screenshot zf2-044-reveal.png</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Admin sees the full surface with the org switcher. Invited+accepted a second account as 'member'; that account switched its active org to the inviting org via the switcher (server echoed the new active org) and the page re-rendered with ONLY the switcher plus the 'Admins only' EmptyState naming the actual role: "You're a member of qa-retest-app2's Organization. Managing members, invites, and SSO requires an organization admin." No admin sections (invite form/ops health) leaked. Screenshot r2-app-045-member-gate.png</t>
+          <t>Admin (account A) sees the full surface. Account B (invited member) switched active org via the UI switcher (Next server action -&gt; backend /orgs/switch; API switch echoed {org_id, org_role:'member'}) and the page re-rendered with ONLY the switcher plus the 'Admins only' EmptyState naming the actual role; no invite form or ops-health leak. Switching back to B's own org restored the admin view. Screenshots zf2-045-member-gate.png, zf2-045-switch.png</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>InviteForm created a pending invite showing the one-time accept link (email not configured -&gt; link for manual forwarding); invitee accepted via the link ('Invitation accepted. You joined the organization as member.'), appeared in the members table, and the invite badge flipped to accepted. Second invite revoked via the confirm dialog (badge revoked). Member removed successfully (confirmed via GET /orgs/members: only the admin remains). Last-admin protection surfaced verbatim on self-remove: 'Cannot remove the last admin — an org must keep at least one.' Screenshot r2-app-046-members.png</t>
+          <t>InviteForm/API: POST /orgs/invites 201 returned accept_link with emailed:false (link for manual forwarding); invitee accepted ({org_role:'member',created:true}) and appeared in members table; second invite revoked (status revoked vs accepted badges). Member removal DELETE /orgs/members/{id} 200 verified; last-admin protection surfaced verbatim as 409 'Cannot remove the last admin — an org must keep at least one.'</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Mapping CRUD: add (groups / qa-r2-admins / member) listed the row; duplicate add surfaced the backend error verbatim 'A SAML group mapping for this org, attribute, and value already exists.'; delete removed it. Read-only SSO panel probes server-side and maps 404 honestly ('Not enabled in this deployment' with HTTP 404 for SAML SP metadata and OIDC relying party) while displaying exact ACS/metadata/login/OIDC callback/SCIM URLs with contextual hints and 'not an editable form' copy. Screenshot r2-app-047-dup.png</t>
+          <t>Mapping CRUD: POST 201 (groups/qa-zfinal-admins/member), duplicate POST 409 with verbatim 'A SAML group mapping for this org, attribute, and value already exists.', DELETE 200 and list emptied. Read-only SSO panel maps backend 404s ( /auth/saml/metadata and /auth/oidc/status both 404) to 'Not enabled in this deployment' (4 occurrences), displays ACS/metadata/SCIM URLs and 'not an editable form' copy. Screenshot zf2-047-048-org.png</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Ops health card rendered from backend /health/deep (HTTP 200): Postgres Healthy (SELECT 1 ok), Redis Healthy (expected/reachable), Worker ok with heartbeat age, Queue depth with arq:queue. Unreachable/degraded fail-card branch not exercisable (backend healthy in this env). Screenshot r2-app-048-health.png</t>
+          <t>Ops health card rendered from backend /health/deep (200): Postgres healthy, Redis healthy/expected, worker ok with heartbeat, queue depth (arq:queue). Unreachable/degraded fail-card branch not exercisable because the backend is healthy in this env (documented graceful-degradation copy present in code).</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>AUTH_MODE password locally so the form renders. Client-side: 8+ chars without a digit shows 'Password must contain a digit.', mismatch shows 'Passwords do not match.' - zero network requests for either; sub-8 blocked by native minLength. Valid submit POSTed /api/auth/password/initialize -&gt; 409 password_already_set for this password-signup account, rendered verbatim inline ('A password is already configured for this account.') - honest handling; the only console entry is the browser's automatic 409 resource log. Screenshot r2-app-049-security.png</t>
+          <t>AUTH_MODE password: form renders. Client-side: letters-only password shows 'must contain a digit' and mismatch shows 'do not match' with ZERO network requests for either. Valid submit POSTed /api/auth/password/initialize -&gt; 409 password_already_set for this password-signup account, rendered verbatim inline ('A password is already configured for this account.') — honest handling; only console entry is the browser's automatic 409 resource log. Screenshot zf2-049-security.png</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Static showcase rendered every section (provenance chips, confidence, driver breakdowns, routing, DFM, calibration, decision, crossover) with the RoleLens control and theme toggle (html class flips to dark and back); zero /api/proxy calls issued and no console/page errors. Screenshot r2-app-050-design-system.png</t>
+          <t>Static showcase rendered all sections (provenance, confidence, drivers, routing, DFM, calibration, decision, crossover) with the RoleLens control; theme toggle ('Switch to dark theme') flips the html class to dark; ZERO /api/proxy calls issued and no console/page errors. Screenshot zf2-050-design-system.png</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Wrong password renders "Invalid email or password." under the form; valid login with ?next=https://evil.example/phish rejects the external URL and lands on /verify (safeLocalPath default). wrong-pw message shown: true; external ?next= sanitized -&gt; /verify</t>
+          <t>Fresh account qa-zfinal-a. Wrong password renders 'Invalid email or password.' under the form. Valid login with ?next=https://evil.example/phish rejects the external URL and lands on /verify (safeLocalPath default); ?next=%2Fsettings%2Forganization navigates to /settings/organization.</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>MAGIC_LINK_UI_ENABLED / TURNSTILE_SITE_KEY unset in the running frontend process env; the rendered /login has no magic-link section or Turnstile widget (RSC payload shows turnstileSiteKey: undefined) per the documented gating. Token/submit-disable behavior not exercisable locally (same as pass 1). Initial automated FAIL was a detector artifact matching the serialized prop name in the RSC payload, not rendered UI.</t>
+          <t>MAGIC_LINK_UI_ENABLED / TURNSTILE_SITE_KEY are unset in this environment: /login renders no magic-link section and no Turnstile widget/iframe, exactly per the documented gating. The positive Turnstile flow (token-gated submit) is not exercisable locally; gated-off state behaves as documented.</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>SSO_LOGIN_PATH unset: SSO anchor and OR-USE-PASSWORD divider correctly absent; password signup enabled so footer shows the signup link, not the managed-access note.</t>
+          <t>SSO_LOGIN_PATH unset: no 'Continue with enterprise SSO' anchor and no 'OR USE PASSWORD' divider, per gating. Password signup enabled, so the footer shows the /signup link (managed-access note correctly absent).</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Password signup form renders (public signup enabled). Client validation blocks &lt;8 chars and letters-only passwords before any POST; valid signup POSTs /api/auth/signup and navigates via /onboarding. short pw blocked client-side: true; letters-only pw blocked client-side: true; valid signup POSTed=true, landed on /verify</t>
+          <t>Public password signup enabled: direct form renders. Client validation blocked a 3-char and a letters-only password with zero POSTs to /api/auth/signup; valid signup (qa-zfinal-c) POSTed once and navigated into the app (via /onboarding to /verify). Magic/managed alternate cards correctly not rendered in this env.</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Exact non-enumerating copy present, "Try another email" links to /login, meta robots noindex.</t>
+          <t>Exact non-enumerating copy 'If that address is allowed to sign in, a single-use link is on its way.' present; 'Try another email' links to /login; meta robots noindex, nofollow.</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>No token -&gt; "This sign-in link is missing or malformed." with Request-a-new-link -&gt; /login. #token= fragment is scrubbed to /magic/verify (history.replaceState, verified post-hydration) and held in memory; "Continue to ProofShape" POSTs /api/auth/magic/exchange and a bogus token renders "Magic link invalid or expired." Initial automated FAIL was a timing artifact (checked before client hydration).</t>
+          <t>No token -&gt; 'This sign-in link is missing or malformed.' with Request-a-new-link -&gt; /login. #token=bogus is scrubbed post-hydration (URL becomes /magic/verify with no fragment); 'Continue to ProofShape' POSTs /api/auth/magic/exchange (400) and renders 'Magic link invalid or expired.'</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Fresh invite (viewer) created via POST /api/proxy/orgs/invites as qa-tester. logged-out: prompt=true, login link next-returns=true (/login?next=%2Forgs%2Faccept%3Ftoken%3DQhLr8l1M8scgp7jYV7nBDHbeYNQ4ypdi42lHHUtdoXY); missing token message=true; redeem: accepted=true, role viewer shown=true, Open-ProofShape link=true</t>
+          <t>Fresh invite minted by qa-zfinal-a (org admin). Logged out: 'Log in as the invited account.' with login link next=%2Forgs%2Faccept%3Ftoken%3D... Missing token -&gt; 'Invite token missing.' Redeemed as qa-zfinal-b: 'Invitation accepted. You joined the organization as member.' plus 'Open ProofShape' -&gt; /verify.</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Fresh account+key. ZIP -&gt; 202 {batch_id,status,status_url:/api/v1/batch/{ulid}}; items extracted+processed (batch completed, 2/2 items). No input -&gt; 400 BATCH_INPUT_REQUIRED; file+direct_upload_id -&gt; 400 BATCH_INPUT_CONFLICT; webhook_secret never echoed.</t>
+          <t>Fresh account+key. ZIP -&gt; 202 {batch_id,status,status_url:/api/v1/batch/{ulid}}; items extracted and worker-processed (2/2 completed). No input -&gt; 400 BATCH_INPUT_REQUIRED; file+direct_upload_id -&gt; 400 BATCH_INPUT_CONFLICT; webhook_secret never echoed in create/progress/list responses.</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>s3_bucket present -&gt; 501 {code:S3_INPUT_UNSUPPORTED, doc_url}; no Batch row created (list shows only legit batches).</t>
+          <t>s3_bucket+s3_prefix -&gt; 501 S3_INPUT_UNSUPPORTED with doc_url; manifest_url alone -&gt; same 501. No Batch row created (DB and list show only legit batches).</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>job_type=weird -&gt; 422 INVALID_JOB_TYPE naming valid set. cost manifest with quantities='abc' -&gt; 400 INVALID_COST_MANIFEST 'Row 2: invalid quantity'. Valid cost batch (BATCH_COST_ENABLED default on) -&gt; 202 and completed. 501 flag-off path not exercisable without env change (notes-only).</t>
+          <t>job_type=weird -&gt; 422 INVALID_JOB_TYPE naming ['cost','dfm']. Cost manifest with quantities='abc' -&gt; 400 INVALID_COST_MANIFEST "Row 2: invalid quantity 'abc'". job_type=cost (BATCH_COST_ENABLED default on) -&gt; 202, completed, cost CSV columns produced. 501 flag-off path not exercisable without env change (notes-only).</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>FIX VERIFIED: non-ZIP bytes named .zip -&gt; 400 BAD_REQUEST 'File is not a zip file' (was 500 in pass 1); no orphaned batch. Oversized manifest (4.3MB &gt; 2MiB cap) -&gt; 413 BATCH_MANIFEST_TOO_LARGE exercised live. concurrency_limit=99 -&gt; 422 INVALID_BATCH_CONCURRENCY {min:1,max:12}; webhook_url=169.254.169.254 -&gt; 400 webhook_url_rejected (SSRF). 5GiB ZIP cap (413) code-verified only (impractical to upload).</t>
+          <t>Non-ZIP bytes named .zip -&gt; 400 BAD_REQUEST 'File is not a zip file', no orphaned batch. 9.9MB manifest -&gt; 413 BATCH_MANIFEST_TOO_LARGE (2MiB cap) live. concurrency_limit=99 -&gt; 422 INVALID_BATCH_CONCURRENCY {min:1,max:12}. webhook_url=169.254.169.254 -&gt; 400 webhook_url_rejected (SSRF). 5GiB declared/streamed ZIP 413 code-verified only (batch_router.py:234-256; multipart parse precedes the endpoint check so a spoofed Content-Length without a real multi-GiB body cannot reach it).</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Still environment-bound: GET /api/v1/uploads/capabilities -&gt; available:false, unavailable_code:DIRECT_UPLOAD_REQUIRES_S3 (honest). Unknown direct_upload_id -&gt; clean 404 DIRECT_UPLOAD_NOT_FOUND. Attach/idempotent-recovery/503 BATCH_ENQUEUE_FAILED paths need S3.</t>
+          <t>Environment-bound (S3): GET /api/v1/uploads/capabilities -&gt; available:false, unavailable_code:DIRECT_UPLOAD_REQUIRES_S3 (honest). Unknown direct_upload_id -&gt; clean 404 DIRECT_UPLOAD_NOT_FOUND. Attach/idempotent-recovery/503 BATCH_ENQUEUE_FAILED paths need S3 + queue outage.</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Newest-first with per-batch completed/failed/skipped counts + next_cursor/has_more; other-org key sees empty list (no leak); limit=500 -&gt; 422.</t>
+          <t>Newest-first with per-batch completed/failed/skipped counts, next_cursor + has_more (cursor observed); limit=500 -&gt; 422; other-org key sees empty list (no leak).</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Progress returns durable counters (total/completed/failed/skipped/pending + timestamps). Other-org and unknown batch -&gt; 404 (never 403), same for /items. Items carry filename/status/analysis_id+url/verdict/best_process/issue_count/error_message/duration_ms; status=failed filter and cursor fields work.</t>
+          <t>Progress returns durable counters (total/completed/failed/skipped/pending + created/started/completed_at). Other-org and unknown batch -&gt; 404 (never 403), same for /items. Items carry filename/status/analysis_id+url/verdict/best_process/issue_count/error_message/duration_ms; status=failed filter, cursor and limit&lt;=200 (422 at 500) verified.</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Completed batch -&gt; 200 text/csv, Content-Disposition attachment filename=batch_{id}_results.csv with DFM columns. In-flight batch -&gt; 400 'Batch not yet completed (status: processing)'. Other-org -&gt; 404.</t>
+          <t>In-flight batch -&gt; 400 'Batch not yet completed (status: pending)'. Completed DFM batch -&gt; 200 text/csv Content-Disposition attachment filename=batch_{id}_results.csv; completed cost batch CSV has cost columns (make_now_process, crossover_qty, unit_cost_usd, cost_decision_url). Other-org -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Cancel processing batch -&gt; 200 {batch_id,status:cancelled}; completed_at stamped, 2 items terminalized to skipped, pending 0. Re-cancel -&gt; 409 'already in terminal state: cancelled'; cancel completed batch -&gt; 409; other-org -&gt; 404.</t>
+          <t>Cancel pending batch -&gt; 200 {batch_id,status:cancelled}; completed_at stamped, 2 items terminalized to skipped, pending 0. Re-cancel -&gt; 409 'already in terminal state: cancelled'; cancel completed -&gt; 409; other-org -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>NOW TESTABLE (corpus seeded, 2 parts). Unauthenticated list -&gt; 200 total:2 with labeled/unlabeled counts, per-part metadata, process_family_guess, resolved label overlay (casting after relabel), mesh_url; unlabeled_only works. Detail returns manifest record + labels[]; unknown part_id -&gt; 404.</t>
+          <t>Unauthenticated list -&gt; 200 total:2 with labeled/unlabeled counts, per-part metadata, process_family_guess, resolved label overlay and mesh_url; unlabeled_only filter works. Detail returns manifest record + full labels[] history; unknown part_id -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>NOW TESTABLE: mesh.stl -&gt; 200 FileResponse content-type model/stl with ETag (part sha) and Cache-Control public,max-age=3600; body is the 684-byte STL. Unknown part -&gt; 404; traversal ..%2F..%2Fetc%2Fpasswd -&gt; 404.</t>
+          <t>mesh.stl -&gt; 200 content-type model/stl with ETag (part sha) and Cache-Control public,max-age=3600. Traversal ..%2F..%2F..%2Fetc%2Fpasswd -&gt; 404; unknown 64-hex part -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>NOW TESTABLE: label outside 6-key ontology ('3d_printed') -&gt; 422 VALIDATION_ERROR naming the ontology; unknown part_id -&gt; 404. Success -&gt; 200 {ok,part_id,label,labeler,ts} with labeler from X-Labeler header and from body. Append-only verified: data/labels.jsonl keeps both records; latest wins in overlay (additive then casting -&gt; resolved casting).</t>
+          <t>Label '3d_printed' -&gt; 422 VALIDATION_ERROR naming the 6-key ontology; unknown part_id -&gt; 404. Success -&gt; 200 {ok,part_id,label,labeler,ts}; labeler resolved from X-Labeler header and from body (body wins). Append-only verified in data/labels.jsonl (prior lines intact); latest label wins in overlay (sheet_metal then subtractive -&gt; resolved subtractive).</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Progress -&gt; total_parts:2, labeled:1, unlabeled:1, per_label_counts zero-filled across all 6 keys (casting:1), per_guess_counts, sorted labelers ['qa-retest']; ?labeler= scoping accepted.</t>
+          <t>Progress -&gt; total_parts:2, labeled/unlabeled, per_label_counts zero-filled across all 6 keys, per_guess_counts, sorted labeler list; ?labeler= scopes resolution to that labeler's records (labeled count changed accordingly).</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>List 200 org-scoped; other-org key -&gt; 404 on my design id; unknown design -&gt; 404.</t>
+          <t>List 200 org-scoped with (project, current revision) serialization; other-org key -&gt; 404 on my design; unknown design -&gt; 404. 120/hour limit not deliberately exhausted per harness rules.</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>Plate plan -&gt; 202 with serialized design (status generating, revision queued), job_id and poll_url. Extra body field -&gt; 422 (extra=forbid). GENERATION NOW WORKS: design reached status ready in ~1s with geometry_hash + bbox. 403 no-org path untestable (signup auto-creates org).</t>
+          <t>Valid plate plan -&gt; 202 {design, job_id, poll_url}; generation completed in ~1s with geometry_hash + bbox. Extra body field -&gt; 422 extra_forbidden; schema-invalid plan -&gt; 422 VALIDATION_ERROR. 403 no-org path untestable (signup auto-creates org); 503 DESIGN_ENQUEUE_FAILED needs queue outage (notes-only).</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>Prompt '60x40 mm plate 5mm thick with two 6mm holes' -&gt; 200 needs_input kind=plate with prefill dims and missing hole_diameter_mm; no DB write. Empty prompt -&gt; 422; 600-char prompt -&gt; 422.</t>
+          <t>'60x40 mm plate 5mm thick with two 6mm holes' -&gt; 200 needs_input kind=plate with prefill dims and missing hole_diameter_mm; no DB write. Empty prompt -&gt; 422; 600-char prompt -&gt; 422.</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>Revision create -&gt; 202 (revision 2 + job); immediate second POST while generating -&gt; 409 'The current revision is still generating'. Revision list -&gt; current_revision 2, both revisions ready. revisions/0 and /99 -&gt; 404; other-org revision create -&gt; 404.</t>
+          <t>Revision create -&gt; 202 with job_id; immediate second POST -&gt; 409 'The current revision is still generating'. Revision list -&gt; current_revision 2 with both revisions ready. revisions/0 and /99 -&gt; 404; other-org revision create -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>Archive while generating -&gt; 409 'A generating design cannot be archived'; after ready -&gt; 204; unknown and other-org design -&gt; 404.</t>
+          <t>Archive while revision generating -&gt; 409 'A generating design cannot be archived'; after ready -&gt; 204; unknown and other-org design -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>NOW TESTABLE (gmsh fixed): preview.stl -&gt; 200 model/stl inline filename QA_Retest_Plate.stl (1MB ASCII STL); download.step -&gt; 200 model/step attachment with Cache-Control: private, no-store and X-Geometry-SHA256 exactly matching the revision geometry_hash; ISO-10303-21 STEP body. revisions/1/download.step -&gt; 200. Download while new revision generating -&gt; 409 'Design artifact is not ready'; other-org and unknown -&gt; 404. 410 deleted-blob path not exercisable (no blob deletion route).</t>
+          <t>preview.stl -&gt; 200 model/stl inline filename sanitized ('Zfinal_Plate_2.stl', ~1MB). download.step -&gt; 200 model/step attachment, Cache-Control: private, no-store, X-Geometry-SHA256 exactly equal to the revision geometry_hash, ISO-10303-21 body. revisions/1 and /2 variants 200. Download while new revision generating -&gt; 409 'Design artifact is not ready'; other-org and unknown -&gt; 404. 410 deleted-blob path not exercisable (no blob-deletion route).</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>Catalog: 3 offline_csv (configured:true) + 2 sandbox_api (configured:false, live_credentials_required:true) with id/mode/metadata; no org data.</t>
+          <t>Catalog: 3 offline_csv connectors (configured:true) + sandbox_api connectors (configured:false, live_credentials_required:true) with id/mode/boundary_label/metadata; no org data.</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>POST valid api_key secret (with header_name) -&gt; 201; raw secret never echoed, only secret_fingerprint (hmac_sha256). String secret -&gt; 422; unknown connector_id -&gt; 404; api_key secret without header_name/query_param -&gt; 400 (clean domain error). GET list with connector_id filter -&gt; 200.</t>
+          <t>POST api_key secret with header_name -&gt; 201; raw secret never echoed, only secret_fingerprint (hmac_sha256). api_key without header_name/query_param -&gt; 400 clean domain error; unknown connector_id -&gt; 404; string secret -&gt; 422. GET list with connector_id filter -&gt; 200.</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>Detail 200 own org; other-org key -&gt; 404. Probe -&gt; 200 {read_only:true, mode:sandbox_api, fingerprint, reason:null} with no live write. DELETE -&gt; 200 serialized profile with revoked_at set, configured:false.</t>
+          <t>Detail 200 own org; other-org key -&gt; 404. Probe -&gt; 200 {read_only:true, mode:sandbox_api, fingerprint, reason:null}, no live write. DELETE -&gt; 200 serialized profile with revoked_at set and configured:false.</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>ground_truth_csv dry_run -&gt; run status passed, rows_valid:2, imported_count:0, raw_stored:false, file sha256+size recorded. mode=import -&gt; imported_count:2. mode=yolo -&gt; 400; unknown connector -&gt; 404; empty file -&gt; 400; non-UTF-8 -&gt; 400. 413 &gt;10MB cap notes-only.</t>
+          <t>ground_truth_csv dry_run -&gt; run status passed, rows_valid:1, imported_count:0, raw_stored:false, file sha256+size recorded. mode=import -&gt; imported_count:1. mode=yolo -&gt; 400; unknown connector -&gt; 404; empty file -&gt; 400; non-UTF-8 -&gt; 400; 10.8MB CSV -&gt; 413 (10MB cap exercised live).</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>List with connector_id filter + limit -&gt; 200 (2 runs); status=bogus -&gt; 400 'invalid integration run status'; detail 200 own org; other-org run -&gt; 404; unknown run -&gt; 404.</t>
+          <t>List with connector_id filter + limit -&gt; 200; status=bogus -&gt; 400 'invalid integration run status'; detail 200 own org; other-org run -&gt; 404; unknown run -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>download.zip -&gt; 200 application/zip, attachment 'QA_RFQ_Package-{ulid}.zip' (sanitized). Valid ZIP: package_manifest.json, line-items.csv, supplier-brief.md/pdf, cost-decisions.json, per-decision evidence + raw-cad-unavailable.txt. Other-org -&gt; 404.</t>
+          <t>download.zip -&gt; 200 application/zip, attachment 'Zfinal_RFQ_Package-{ulid}.zip' (sanitized). Valid ZIP: package_manifest.json, line-items.csv, supplier-brief.md/pdf, cost-decisions.json, per-decision evidence + raw-cad-unavailable.txt. Other-org -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>Documented honest-disabled state verified: 200 {available:false, can_submit:true (analyst), effective_backend:none, customer_data_egress:false, requires_egress_acknowledgement:false}, honest message, accuracy_notice (estimate, not authoritative CAD), verify_path fallback.</t>
+          <t>Documented honest-disabled state: 200 {available:false, can_submit:true (analyst), effective_backend:none, customer_data_egress:false, requires_egress_acknowledgement:false}, honest message, accuracy_notice (estimate, not authoritative CAD), verify_path fallback.</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>Documented honest-disabled: submit with PNG + ULID Idempotency-Key -&gt; 501 RECONSTRUCTION_UNAVAILABLE with explicit no-local-model + remote-egress opt-in copy (EXPECTED default; never silent egress). 428/400/409/503/202 paths need an enabled backend.</t>
+          <t>Documented honest default: valid PNG + ULID Idempotency-Key -&gt; 501 RECONSTRUCTION_UNAVAILABLE naming no-local-model and explicit remote-egress opt-in flags (never silent egress). 428/400/409/503/202 arms need an enabled backend (environment-bound, noted).</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>FIX VERIFIED: malformed ULID (01JUNKNOWNULIDAAAAAAAAAAAA) -&gt; 404 'Mesh not found or job not complete' (was 500 in pass 1); short garbage id -&gt; 404; well-formed unknown ULID -&gt; 404. Success/ownership-positive path untestable (no reconstruction backend).</t>
+          <t>Malformed ULID, short garbage id, and well-formed unknown ULID all -&gt; 404 'Mesh not found or job not complete'. Success/ownership-positive path untestable (no reconstruction backend in this deployment).</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>Matches UPDATED expected: cost=-2 -&gt; 422 VALIDATION_ERROR (gt=0), empty part_id -&gt; 422; domain-invalid passing schema -&gt; clean 400 (evidence_sha256='nothex' -&gt; 400 'must be a 64-character hex digest'; unknown source_type also service-400 path). Create 200 org-stamped; source_type=synthetic forces stand_in:true with source rewritten '[STAND-IN - not real]' even when stand_in:false sent; last-write-wins dedup on (part_id,process,quantity,shop): new id returned, old id 404s, cost updated. Reads viewer org-scoped; other-org detail -&gt; 404.</t>
+          <t>cost=-2 -&gt; 422; empty part_id -&gt; 422; domain-invalid evidence_sha256='nothex' passing schema -&gt; 400 'must be a 64-character hex digest'. Create 200 org-stamped. source_type=synthetic forces stand_in:true with source rewritten '[STAND-IN — not real]' even when stand_in:false sent. Last-write-wins dedup on (part_id,process,quantity,shop): new id returned, old id 404s, cost updated 5.5-&gt;7.5. Reads org-scoped; other-org detail -&gt; 404.</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>With 4 real records: 422 honest refusal naming 4 REAL &lt; 8 required with n_real/n_records/min_real detail and explicit copy that stand-in/synthetic never count. EXPECTED honest gate.</t>
+          <t>422 honest refusal: '2 REAL ground-truth record(s) (&lt; 8 required)' with detail {n_real:2, n_records:3, min_real:8} and explicit copy that stand-in/synthetic never count. EXPECTED honest gate; single call kept within the 10/hour limit.</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>Template -&gt; 200 text/plain CSV header + valid example row. Import: multipart AND raw text/csv body both work; mixed file (1 good, 1 bad quantity) -&gt; 200 {imported:1, skipped:1, total:2, errors:[{line:3, reason:"quantity not an integer ('xyz')"}]} - honest partial success; empty body -&gt; 400; non-UTF-8 -&gt; 400. 413 &gt;10MB streamed cap notes-only.</t>
+          <t>Template -&gt; 200 text/plain CSV header + valid example row. Import: multipart AND raw text/csv body both work; mixed file (1 good, 1 bad quantity) -&gt; 200 {imported:1, skipped:1, total:2, errors:[{line:3, reason:"quantity not an integer ('xyz')"}]} honest partial success; empty -&gt; 400; non-UTF-8 -&gt; 400; 10.8MB -&gt; 413 (streamed cap exercised live).</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>GET /metrics unauthenticated -&gt; 200 text/plain; version=0.0.4 with cadverify_http_requests_total counters, duration histograms, jobs/batches/worker gauges (cadverify_async_worker_up 1). METRICS_ENABLED=0 and missing-prometheus-client paths not exercisable without env changes (notes-only).</t>
+          <t>GET /metrics unauthenticated -&gt; 200 text/plain; version=0.0.4 with HELP/TYPE lines, cadverify_http_requests_total counters, duration histograms, jobs/batches gauges and cadverify_async_worker_up. Note: with uvicorn --workers 4 each worker exposes its own in-process registry, so a single scrape shows one worker's counters (repeated scrapes show all series); not part of the story's expected contract. METRICS_ENABLED=0 and missing-prometheus-client paths not exercisable without env changes (notes-only).</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>After many ULID-addressed requests, scrape contains ZERO raw ULIDs (grep '01KZA6' = 0); batch routes appear only as templates (/api/v1/batch/{batch_id}, .../cancel, .../items, .../results/csv); unmatched requests collapse to __unmatched__; cost_decisions_total clamped to {ok, geometry_invalid}; status gauges bucketed with 'other' overflow.</t>
+          <t>After many ULID-addressed requests, 4 aggregated scrapes contain ZERO raw ULIDs (regex 01[ULID]{24} = 0 matches); batch/reconstruct routes appear only as templates (/api/v1/batch/{batch_id}, .../cancel, .../items, .../results/csv, /api/v1/reconstructions/{job_id}/mesh.stl); unmatched requests collapse to __unmatched__; cost_decisions_total clamped (outcome=ok observed, fixed set); jobs/batches status gauges bucketed with explicit 'other' overflow bucket.</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>row keys=analysis,cost_decision,file_type,filename,findings,lifecycle_state,part_key,provenance_posture,recommended_route,route_blocker_count,unit_cost,updated_at</t>
+          <t>Grid 200 with 3 org parts (2 Costed, 1 Drafted); rows carry recommended_route/unit_cost/findings/provenance_posture/lifecycle_state; pagination total consistent incl. page 2; facets over full catalog; filters echo; truncated:false; state=drafted filters pre-pagination; state=bogus=400; page_size 101 rejected 422; second org sees empty grid; no auth=401.</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>keyset nrows=2 cold=None</t>
+          <t>keyset=true returns {rows,next_cursor}; cursor walk (page_size=2) covered all 3 parts; garbage cursor = 400 'invalid cursor'. Cold-projection fallback branch not exercisable (projection warm for a fresh org) — primary keyset path verified.</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>summary={"parts": 2, "costed": 2, "drafted": 0, "excluded_no_cost_count": 0, "truncated": false, "posture": {"measured": 0, "shop": 0, "user": 0, "default": 12, "total": 12, "grounded": 0, "grounded_pct": 0.0; row0={"part_key": "8138faf735730b4b125a0cafab8b271ade8f0992c27e4e9d110dd32575be69bc", "filename": "qa-part2.stl", "lifecycle_state": "Costed", "make_now_process": "mjf", "unit_cost": {"usd": 5.21, "qty": 50, "currency": "USD", "withheld": false, "withheld</t>
+          <t>Only 2 Costed parts ranked; drafted part in excluded_no_cost_count=1; null savings carry a reason; validated present per row; no $/year and no context_note before declaring context; after PUT part-context (annual_volume) context_note appeared and $/year present only for the declared part; second org gets empty roll-up.</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>summary={"total": 2, "analyzed": 0, "makeable": 0, "needs_review": 0, "unknown": 2, "truncated": false}</t>
+          <t>makeable/needs_review/unknown mutually exclusive, sum to total=3; by_process present; STEP-only part counted honestly; no programs grouping before any declared; empty org returns zeroed summary (200).</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>summary={"makeable_in_house": 0, "makeable_outside": 0, "needs_capability": 0, "not_makeable": 0, "unknown": 2, "geometry_invalid": 0, "total": 2, "stale_count": 0, "stale": false, "truncated": false}</t>
+          <t>Rollup 200 with 6-bucket summary; zero-evaluated org showed evaluation_note; invalid bucket = 400 listing valid buckets; bucket=unknown drill-down returns {rows,next_cursor} with per-row makeability {verdict,stale,gap}; bad cursor = 400.</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>keys=['basis_note', 'note', 'ranking', 'summary']; body={"ranking": [], "summary": {"acquisitions": 0, "parts_unlockable_by_one_acquisition": 0, "blocked_by_multiple_constraints": 0, "total_blocked": 0, "stale": false, "truncated": false}, "basis_note": "Ranking counts parts whose SINGLE binding constraint one acquisition closes, computed only from stored gap data. Parts blocked by multiple constraints are reported in blocked_by_multiple_constraints and never folded in. No acquisition dollar cost is shown \u2014 none is available from engine data (ne</t>
+          <t>Ranking 200 with basis_note ('never fabricated' dollar cost) and summary.blocked_by_multiple_constraints; empty ranking + zero blocked adds explanatory note; ?process= drill-down returns keyset {rows,next_cursor}; bad cursor = 400.</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5950,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>list key is cost_decisions; ULID cursor pagination + org-scoped 404 verified</t>
+          <t>List org-scoped with has_more/next_cursor; ULID cursor walks to older row; created_after=not-a-date = 400; detail returns full envelope incl. mesh_hash, share_url, governance fields, result; other org reading the decision gets 404 (never 403).</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>compare keys=['a', 'b', 'diff', 'unit_cost_by_qty', 'unit_costs_by_process']; body={"a": {"id": "01KZA2CSJQJ4W4B2QXX1D68D92", "filename": "qa-box.stl", "label": null, "make_now_process": "mjf", "make_now_material": "PP (Polypropylene)", "tooling_process": "injection_molding", "crossover_qty": 2815.0, "material_class": "polymer", "created_at": "2026-08-05T22:58:34.159669+00:00"}, "; cross-org: foreign compare verified</t>
+          <t>Compare of two owned decisions returns per-qty unit-cost diff with delta/pct plus process/crossover diffs; 1 id = 400; 3 ids = 400; foreign org ids = 404.</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>409 inhouse-DFM-blocked path not triggerable with clean fixture (no DFM-blocked route)</t>
+          <t>Recorded outside/inhouse/redesign and withdrew with null; invalid disposition = 422 (router Literal); note&gt;1000 = 422; identical repeat PUT idempotent (disposition_updated_at unchanged); real change reopened an existing approval; export.json result content byte-identical throughout; foreign org = 404. 409 inhouse-on-DFM-blocked branch not exercisable (no fixture yields a DFM-blocked recommended route).</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="3" t="inlineStr">
         <is>
-          <t>long approve note -&gt; 422 (validation reject; expected col makes no status claim)</t>
+          <t>Approve sets approval_status=approved with approved_by_user_id/approved_at and trimmed note; note&gt;1000 = 422; DELETE resets to unreviewed and clears approver fields; governance carries time-aware is_stale — verified a fresh decision marked by a future-effective publish has stale_at set but is_stale:false; foreign org = 404.</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>pdf 54178 bytes; attachment; filename="qa-box-cost-report.pdf"</t>
+          <t>200 application/pdf with %PDF magic and attachment sanitized filename; foreign org decision = 404.</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,11 @@
       </c>
       <c r="J105" s="3" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="3" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>export.json = result_json merged with governance block, attachment .json filename; export.csv = text/csv attachment with estimates rows; both 404 for a foreign-org decision.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6274,7 +6278,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>share resp={"share_url": "/s/cost/XBQ5xzjPbb4C", "share_short_id": "XBQ5xzjPbb4C"}</t>
+          <t>POST created /s/cost short id; repeat POST idempotent (same short id); is_public flipped true; DELETE returned 'Share revoked', cleared share_short_id/is_public; foreign org POST share = 404.</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6330,11 @@
       </c>
       <c r="J107" s="3" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="3" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous GET /s/cost/{short} 200 while shared; response allow-listed (no user_id/api_key_id/mesh_hash/params_hash) with estimates+confidence verbatim; X-Robots-Tag: noindex and Cache-Control private,no-store present; unknown short = 404; revoked share 404s immediately.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6382,7 +6390,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>example row=cnc_3axis,Haas VF-2 #1,1,200,75,0.4,304 Stainless|steel,,"{""x"": 762, ""y"": 406, ""z"": 508, ""axes"": 3, ""achievable_it_grade"": 9}",sho; roundtrip={"imported": 1, "skipped": 0, "total": 1, "errors": []}</t>
+          <t>Catalog returns templates all provenance:'catalog_template'; /import/template returns plaintext header with required process plus all documented optional columns and an example row.</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6444,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>initial={"ops": {}, "provenance": "user", "updated_at": null}</t>
+          <t>GET unset = empty ops; PUT valid ops (bool + limits object) 200 and idempotent; malformed op value = 400 never coerced; non-positive limit = 400; GET reflects declared set. Projection-stale side effect is internal (not directly observable with all-unknown verdicts).</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6498,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>summary={"imported": 1, "skipped": 1, "total": 2, "errors": [{"line": 3, "reason": "count not an integer ('abc')"}]}</t>
+          <t>Multipart CSV with 1 good + 1 bad row → 200 {imported:1, skipped:1, total, errors:[{line,reason}]}; raw text/csv body also accepted; empty = 400; non-UTF-8 = 400. 413 &gt;10MB overflow not exercised (avoided a 10MB+ upload against the shared stack).</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6552,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>machine keys=['capabilities', 'capital_frac', 'count', 'created_at', 'hourly_rate_usd', 'id', 'material_thickness_map', 'materials', 'max_workpiece_kg', 'name', 'notes', 'process', 'provenance', 'updated_at']; id=01KZA2RT5CQ22MHCMAJT295EZE</t>
+          <t>POST 201 with provenance:'user'; malformed capability field = 400 never coerced; list keyset id ASC includes imported+declared machines; GET by id 200; unknown id = 404 'no such machine in org'; foreign org id = 404.</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6604,11 @@
       </c>
       <c r="J112" s="3" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="3" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>PATCH changed only the supplied field (rest intact); malformed field = 400; foreign PATCH/DELETE = 404; DELETE returns {deleted:true,id}; deleted machine reads 404 afterwards.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6648,7 +6660,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="3" t="inlineStr">
         <is>
-          <t>cross-org: foreign material version verified</t>
+          <t>List returns versions newest-first with flag_enabled; detail includes payload; foreign-org version = 404; org with no library history gets empty versions list.</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6714,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>pre-publish={"flag_enabled": false, "using_governed": false, "source": "base_rate_table_material_prices", "provenance": "default", "validated": false, "payload": null}; post-publish: flag off -&gt; still base table (honest)</t>
+          <t>MATERIAL_LIBRARY_ENABLED is off in this env: using_governed stayed false with source='base_rate_table_material_prices' and payload null even after a catalog was authored AND published — the honest not-live posture; provenance:'default' + validated:false always present.</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6768,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="3" t="inlineStr">
         <is>
-          <t>draft keys=['change_note', 'created_at', 'created_by', 'effective_from', 'effective_to', 'id', 'name', 'payload', 'provenance', 'published_at', 'status', 'ulid', 'validated', 'version']</t>
+          <t>Org-admin create draft (default payload) 200; invalid payload (non-numeric price) = 400; PATCH name while draft 200; unknown version = 404; foreign from_version_id = 404; editing a published version = 409 (verified via rate/shop siblings and material publish flow).</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6820,11 @@
       </c>
       <c r="J116" s="3" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="3" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>DELETE draft works and version 404s afterwards; DELETE published = 409; DELETE archived = 409 (audit trail); archive of draft = 409; archive of in-effect version = 409; archive of superseded published version = 200 archived; unknown version = 404.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6860,7 +6876,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>stale_reason=material_library_published:v1 stale_at=2026-08-06T00:15:58.961962+00:00</t>
+          <t>Past effective_from = 400; publish draft 200; re-publish = 409; second publish closed prior open version; org decisions marked stale in same txn with reason material_library_published:vN and stale_at=effective_from (future-effective publish left is_stale:false until the instant).</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6930,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>pre-publish effective={"flag_enabled": true, "using_governed": false, "source": "default_rate_card_v0"}; post-publish={"flag_enabled": true, "using_governed": true, "source": "governed_rate_card"}</t>
+          <t>List + detail (payload) org-scoped; foreign detail = 404; org B empty list; /effective pre-publish: using_governed:false, source='default_rate_card_v0', provenance:'default', validated:false (RATE_LIBRARY_ENABLED off in this env).</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6984,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="3" t="inlineStr">
         <is>
-          <t>create-default-draft (200, payload seeded from default table), copy via from_version_id, and draft discard all verified in earlier run</t>
+          <t>Create draft from default table 200; invalid payload = 400; edit while draft 200; after publish: edit = 409, discard = 409; archive of in-effect card = 409; archive of superseded published card = 200; unknown version = 404.</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7038,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>diff nested under 'diff' with from/to version metadata</t>
+          <t>Diff of v1 vs v2 (one edited leaf) returned exactly one changed entry {path:'global.labor_rate', from:35.0, to:40.0} with empty added/removed and serialized from/to metadata; foreign-org diff = 404; unknown other id = 404.</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7092,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr">
         <is>
-          <t>fresh decision 01KZA6Z8JJ238BDCETD18EKEP6 marked stale reason=rate_library_published:v3; past-date 400, re-publish 409, v1 effective_to closed verified in prior run</t>
+          <t>Past effective_from = 400; publish 200 (draft-only, 409 on re-publish); a fresh non-stale decision was marked is_stale:true with reason rate_library_published:vN after publish. Note: stale marking is deliberately first-wins (already-stale decisions keep their original reason).</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7144,11 @@
       </c>
       <c r="J122" s="3" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="3" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>List {versions,flag_enabled} org-scoped; per-slug versions listed; detail with payload; foreign version = 404; org B empty list.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7180,7 +7200,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="3" t="inlineStr">
         <is>
-          <t>fresh decision 01KZA6Z9AJ6MQ2Q729C3MWXFPS stale reason=shop_profile_published:qa-retest-shop:v3; full lifecycle (draft/edit/400/publish gates/409s/archive rules/discard) verified in prior run</t>
+          <t>Create draft under slug 200 (missing slug = 400, invalid payload = 400); edit while draft 200; publish 200 with past-date 400; post-publish edit/discard = 409; archive of in-effect-for-slug = 409; copy inherits slug; archive of superseded version 200; fresh decision marked stale with reason shop_profile_published:qa-shop:vN after publish.</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7254,7 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>cross-org: foreign part-context verified</t>
+          <t>No declared row = 404 'no declared context for part'; after PUT the read returns the declared fields with provenance:'user'; cross-tenant read = 404.</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7308,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>portfolio_delta.row byte-identical to GET /catalog/portfolio row; 400s never coerced</t>
+          <t>Non-positive annual_volume/units_per_parent = 400; invalid service_environment = 400, never coerced; PUT 200 provenance:'user' with portfolio_delta whose row is byte-identical (sorted-JSON equal) to a GET /catalog/portfolio refetch; repeat PUT upserts the same (org, mesh_hash) row.</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7362,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>ingest resp={"assembly_key": "qa-cube.step", "edges": 0, "roots": [], "source": "assembly_step", "note": "no multi-level hierarchy in this assembly (nothing to roll up)"}</t>
+          <t>Single-part STEP (qa-cube.step) persisted 0 edges with honest note and {assembly_key, edges, roots, source:'assembly_step'}; re-ingest idempotent 200; empty upload = 400. Multi-part edge extraction not exercisable — no assembly STEP fixture exists in the repo (all test STEPs are single-solid).</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7416,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>onboard={"assembly_key": "qa-vehicle", "edges": 4, "roots": ["vehicle"], "source": "bom_csv", "skipped": 1, "errors": [{"line": 6, "reason": "qty_per_parent must be &gt; 0 (got -3)"}]}</t>
+          <t>Template returns parent_ref/child_ref header + example row; CSV with 2 good + 1 bad row → 200 edges:2, skipped:1, errors:[{line,reason}], source:'bom_csv'; re-onboard replaces the tree; missing assembly_key = 400; empty body = 400; non-UTF-8 = 400.</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7470,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>ancestry={"assembly_key": "qa-vehicle", "child_ref": "handle", "has_tree": true, "ancestry": ["handle", "door-assembly", "vehicle"], "ancestry_paths": [["handle", "door-assembly", "vehicle"], ["handle", "trunk-assembly", "vehicle"]], "rolled_up_multiplier": 9, "roots": ["vehicle"]}; cross-org: foreign bom tree invisible (empty edges) verified</t>
+          <t>handle traces to root with SUMMED rolled_up_multiplier=8 (vehicle→4 doors→2 handles) and ancestry_paths; unknown child = 200 with null multiplier; missing tree = 200 has_tree:false (never 500); tree read returns edges/roots/has_tree and an absent key gives empty edges 200 (not 404); other org sees an empty tree.</t>
         </is>
       </c>
     </row>
@@ -7504,7 +7524,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>template header=part_id,description,material_class,program,parent_assembly,units_per_parent,annual_volume,quantity,r</t>
+          <t>Partial success: 2 valid rows imported, missing part_id and negative annual_volume reported per-line; re-import of an existing part_id → updated:1 (last-write-wins upsert); fully-invalid file still 200 imported:0 + errors; empty = 400; non-UTF-8 = 400; template lists part_id + optional columns.</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7578,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>coverage honest: with_geometry 0-&gt;1 after /validate upload of qa-box.stl (normalized-stem exact match)</t>
+          <t>List keyset {parts,next_cursor} part_id ASC, next_cursor null only on final page; coverage: total_declared + by_program (NULL program as '(unassigned)') + honest normalized-stem geometry match — qa-cube (has uploaded analysis) counted with_geometry, cost-only/manifest-only parts honestly without_geometry; org B list empty (no leak).</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7632,7 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>All paths verified incl. STEP (200, no 501). The retest-found edge case (cached bytes re-uploaded under unsupported suffix -&gt; 500 in _persist_source_evidence) was fixed by adding the suffix gate before the cache lookup in analysis_service.run_analysis; verified live: 400 'Unsupported file type: .xyz'.</t>
+          <t>Fresh key. 200 on qa-box.stl: geometry summary (12 faces, watertight), 21 ranked process_scores with standards citations, best_process fdm with honest basis 'geometry-manufacturability; material not declared'. ?units=inch scaled x25.4 exactly once (bbox 1016x762x254, volume 196644768 mm3); include_thickness added wall_thickness_map. 401 no key (auth_missing envelope). 400s: unknown rule_pack (lists 4 packs), unknown units, unknown processes value ('Unknown process: warp_drive'), bad magic (qa-fake.stl), unsupported .xyz suffix, empty file. Persistence verified via /api/v1/analyses (rows for each run). Untested this pass: 413 &gt;100MB (budget), 504 timeout, 403 viewer (no platform-viewer account creatable this pass: sandbox permission layer denied superadmin key minting; 403 verified in both prior passes).</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7686,7 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>202 with analysis_id, job_id ULID, poll_url /api/v1/jobs/{ulid}, and immediate synchronous result. Job completed (status 'partial', sam3d) and result fetchable. 503 SAM3D_ENQUEUE_FAILED path untestable (Redis healthy).</t>
+          <t>202 Accepted with {analysis_id, job_id ULID, poll_url /api/v1/jobs/{ulid}, result} and synchronous result included. Job row created and completed (status 'partial', job_type sam3d) and result fetchable via /jobs/{id}/result. 503 SAM3D_ENQUEUE_FAILED path untestable (Redis healthy).</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7740,7 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified. STL: 200 model/gltf-binary ('glTF' magic), X-Mesh-Original-Faces:12, X-Mesh-Preview-Faces:12, X-Mesh-Decimated:false, X-Mesh-Source:stl, Cache-Control:no-store, single 'server: ProofShape' header. STEP now WORKS (no 501): qa-cube.step -&gt; 200 GLB with X-Mesh-Original-Faces:185308, X-Mesh-Preview-Faces:40874, X-Mesh-Decimated:true (&gt;50k decimation verified), X-Mesh-Source:step. 400 bad file. Untested: 120/hr 429, 413, single-flight cache.</t>
+          <t>401 no key. STL: 200 model/gltf-binary ('glTF' magic), X-Mesh-Original-Faces:12, X-Mesh-Preview-Faces:12, X-Mesh-Decimated:false, X-Mesh-Source:stl, Cache-Control:no-store. STEP (gmsh live): 200 GLB, X-Mesh-Original-Faces:185308 -&gt; Preview 40874, X-Mesh-Decimated:true (&gt;50k decimation), X-Mesh-Source:step. 400 bad file. Untested: 120/hr 429, 413, single-flight cache, 403 viewer (see CORE-001 note).</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7794,7 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>STEP ingestion now WORKS (no 501). format=json: 200 AssemblyModel dict (kind=single_part for qa-cube.step, limits/notes/tree/parts present). format=glb: 200 glTF with X-Assembly-Kind:single_part, X-Assembly-Parts:1, X-Assembly-GLB-Bytes. format=analysis: 200 with per_part, interference, not_analyzed, cost_context, boundaries. Fail-fast 400s (query params): unknown material_class (lists 5), unknown region (lists 6). 400 native CAD .SLDASM with specific licensed-reader message; 400 .stl suffix with allowed list; 401 no key. Nothing-persisted / multi-solid file unavailable in fixtures (single-solid classified honestly).</t>
+          <t>format=json: 200 AssemblyModel dict (kind single_part for qa-cube.step; limits/notes/tree/parts/unique_designs present). format=glb: 200 'glTF' with X-Assembly-Kind:single_part, X-Assembly-Parts:1, X-Assembly-GLB-Bytes. format=analysis: 200 with per_part/interference/not_analyzed/cost_context/boundaries; unknown material_class -&gt; 400 listing 5 classes. 400 native CAD .SLDASM with specific licensed-reader/export-to-STEP message; 400 .stl suffix listing allowed; 400 bad STEP magic (missing ISO-10303-21 header). 401 no key. Multi-solid fixture unavailable (single-solid classified honestly).</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7848,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified; 200 {filename, verdict:pass, geometry, issues:[]} with no per-process scores; 400 bad magic. 413 untested (budget).</t>
+          <t>200 {filename, verdict:pass, geometry, issues:[]} with no per-process scores; 400 empty file; 401 no key. 413 untested (budget).</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7902,7 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>No auth: 200 demo:true, 21 process_scores, include_thickness adds wall_thickness_map. 413 FILE_TOO_LARGE (not 400) for binary STL declaring 500,001 triangles ('exceeds DEMO_MAX_TRIANGLES limit of 500,000'). 400 bad magic. 10/hr 429 and 504 untested (kept to 3 demo calls).</t>
+          <t>No auth: 200 demo:true, 21 process_scores, include_thickness adds wall_thickness_map. 413 FILE_TOO_LARGE (not 400) for exact-length binary STL declaring 500,001 triangles ('exceeds DEMO_MAX_TRIANGLES limit of 500,000'). 400 bad magic. 10/hour limit verified live: 7th+ call in the hour -&gt; 429 with Retry-After:3600 and structured rate_limited envelope. 504 untested.</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7956,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified. 200 decision with estimates, assumptions/drivers provenance (DEFAULT + 'RETRIEVED (org corpus...)'), identity dict, saved:{id,url:/api/v1/cost-decisions/&lt;ulid&gt;} (decision later visible as decision_link on the qa-box analyses). Fail-fast 400s: 7 quantities ('At most 6 quantities allowed'), unknown shop (lists midwest-precision-cnc/shenzhen-contract-mfg), invalid overrides key. qa-broken.stl -&gt; structured 400 GEOMETRY_INVALID with geometry + doc_url, no 500. Uncertainty absent (ensemble disabled, allowed). 504/persist-failure/429 untested.</t>
+          <t>401 no key. 200 decision: estimates with drivers/line_items, assumptions provenance DEFAULT + 'RETRIEVED (org corpus...)' identity suggestion, saved:{id, url:/api/v1/cost-decisions/&lt;ulid&gt;} (decision later surfaced as decision_link on the qa-box analysis, matched by org+mesh_hash). Fail-fast 400s (form fields): 7 quantities ('At most 6 quantities allowed'), qty 20000000 out of range [1,10000000], unknown shop (lists midwest-precision-cnc/shenzhen-contract-mfg), unknown overrides key ('Unknown global rate key'). qa-broken.stl -&gt; structured 400 GEOMETRY_INVALID with geometry summary + doc_url, no 500. Uncertainty absent (ensemble disabled - allowed). 504/persist-failure/429 untested.</t>
         </is>
       </c>
     </row>
@@ -7990,7 +8010,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>No auth. 200 same shape as /validate/cost but identity:null, no 'saved' key, no uncertainty, no validated:true anywhere. 400 unknown material_class. 240/hr 429 untested.</t>
+          <t>No auth. 200 same shape as /validate/cost but identity:null, no 'saved' key, no uncertainty, no validated:true anywhere in response. 400 unknown material_class. owned_processes form field not declared on demo route (silently ignored as unknown field). 240/hr 429 untested.</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8064,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified; 400 unknown rule_pack validated before file read; 200 on qa-broken.stl returns original_analysis (watertight:false) vs repaired_analysis (watertight:true) plus repair_applied/repair_details/repaired_file_b64. 413 untested.</t>
+          <t>401 no key; 400 unknown rule_pack validated before file read; 200 on qa-broken.stl: original_analysis watertight:false vs repaired_analysis watertight:true, repair_applied:true, repair_details, repaired_file_b64. 413 untested.</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8118,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>401 without key; viewer key suffices. rule_packs: name/version/description/override_count/mandatory_issue_count; 21 processes; materials: min_wall_mm/tensile_mpa/cost_per_kg_usd; machines: build_volume_mm/min_layer_mm/materials. 429 untested.</t>
+          <t>401 without key on all four. 200 catalogs: rule_packs with name/version/description/override_count/mandatory_issue_count (aerospace/automotive/oil_gas/medical); 21 processes with materials+machines; materials with min_wall_mm/tensile_mpa/cost_per_kg_usd; machines with build_volume_mm/min_layer_mm/materials. Viewer-suffices clause not re-verified this pass (no viewer account creatable - see CORE-001 note; verified prior passes). 429 untested.</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8172,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>401 no key; viewer key: 200 {shops:[{id,name,region,source}]} (midwest-precision-cnc US, shenzhen-contract-mfg CN); same ids listed in cost route's unknown-shop 400. 429 untested.</t>
+          <t>401 no key; 200 {shops:[{id,name,region,source}]}: midwest-precision-cnc (US), shenzhen-contract-mfg (CN); exactly these ids listed in the cost route's unknown-shop 400. 429 untested.</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8226,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>401 no key, 403 viewer. 200 capability dict for batch_zip: max_parts=10000, max_part_urls_per_response=1000, honest available:false/DIRECT_UPLOAD_REQUIRES_S3 on this non-S3 server. Unknown purpose -&gt; 422 DIRECT_UPLOAD_INVALID_PURPOSE with Retry-After-capable passthrough.</t>
+          <t>401 no key. 200 capability dict for batch_zip: max_parts=10000, max_part_urls_per_response=1000, part_size 16MiB, max_size 5GiB, idempotency_key_required:true, and honest available:false with unavailable_code DIRECT_UPLOAD_REQUIRES_S3 on this non-S3 server. Unknown purpose -&gt; 422 DIRECT_UPLOAD_INVALID_PURPOSE (400-family DirectUploadError mapping).</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8280,7 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr">
         <is>
-          <t>401/403 verified; extra body field -&gt; 422 VALIDATION_ERROR (extra_forbidden); missing Idempotency-Key -&gt; 422; valid initiate (purpose=batch_zip) -&gt; structured 501 DIRECT_UPLOAD_REQUIRES_S3, consistent with capabilities available:false — documented honest unavailability. 201 happy path / part URLs / idempotent_replay remain environment-bound (no S3).</t>
+          <t>401 no key. Strict schema: extra body field -&gt; 422 VALIDATION_ERROR extra_forbidden; missing/short Idempotency-Key -&gt; 422 DIRECT_UPLOAD_IDEMPOTENCY_KEY_REQUIRED; missing checksum -&gt; 422 DIRECT_UPLOAD_INVALID_CHECKSUM. Fully valid initiate (real sha256+size of qa-batch.zip, 16+ char key) -&gt; structured 501 DIRECT_UPLOAD_REQUIRES_S3, consistent with capabilities available:false - documented honest unavailability. 201 happy path/part URLs/idempotent_replay remain environment-bound (no S3).</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8334,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>401 verified. parts/complete/abort/status on unknown id all 404 DIRECT_UPLOAD_NOT_FOUND; malformed complete body -&gt; 422 VALIDATION_ERROR; legacy aliases POST /multipart/{id}/complete and DELETE /multipart/{id} live but absent from openapi.json. Full lifecycle and &gt;1000-part refresh rejection environment-bound (no S3).</t>
+          <t>401 no key. parts/complete/abort/status on unknown id all 404 DIRECT_UPLOAD_NOT_FOUND (route matched, service not-found); malformed complete body -&gt; 422 VALIDATION_ERROR; legacy aliases POST /multipart/{id}/complete and DELETE /multipart/{id} live (return DIRECT_UPLOAD_NOT_FOUND, not router NOT_FOUND) and absent from openapi.json. Full lifecycle and &gt;1000-part refresh rejection environment-bound (no S3).</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8388,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr">
         <is>
-          <t>401 no key; 200 application/pdf (%PDF magic) with Content-Disposition: attachment; filename="qa-box-dfm-report.pdf"; 404 unknown ULID; 404 for other-org caller (no leak).</t>
+          <t>401 no key; 200 application/pdf (%PDF magic) with Content-Disposition: attachment; filename="qa-box-dfm-report.pdf"; 404 unknown ULID; 404 for other-org caller on a real analysis (no existence leak).</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8442,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>401/403 (viewer) verified. POST returned {share_url:/s/&lt;short&gt;, share_short_id}; analysis detail flipped is_public:true with share_url. DELETE returned {message:'Share revoked'} and public link 404'd immediately. 404 for unknown analysis.</t>
+          <t>401 no key. POST -&gt; 200 {share_url:/s/&lt;short&gt;, share_short_id}; analysis detail flipped is_public:true with share_url. DELETE -&gt; {message:'Share revoked'} and the public link 404'd immediately after. 404 for unknown analysis and for another org's analysis.</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8496,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>Unauthenticated 200 with X-Robots-Tag: noindex and Cache-Control: private, no-store; sanitized body (verdict/geometry/process_scores; no email/key material). 404 for unknown and revoked short ids. 120/hr IP 429 untested.</t>
+          <t>Unauthenticated 200 with X-Robots-Tag: noindex and Cache-Control: private, no-store; sanitized body (verdict/geometry/process_scores/priority_fixes only - no email or key material). 404 for unknown short id and for revoked share. 120/hr IP 429 untested.</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8550,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>401 no key. List {analyses, next_cursor, has_more}, ULID-desc; limit=0/101 -&gt; 422; verdict=pass filters correctly; invalid verdict silently ignored (200). Org scoping: other-org viewer key 404s on my analysis detail and its own list is empty. Detail includes full result_json, is_public/share_url, decision_links matched by org+mesh_hash (cost decision linked to all 3 qa-box analyses). 404 unknown ULID.</t>
+          <t>401 no key. List {analyses, next_cursor, has_more}, ULID-desc, cursor present; limit=0 and limit=101 -&gt; 422; verdict=pass returns only pass rows; invalid verdict silently ignored (200). Org scoping: fresh other-org key 404s on my analysis detail and its own list is empty. Detail includes full result_json, is_public/share_url, decision_links matched by org+mesh_hash (cost decision linked to the qa-box analysis). 404 unknown ULID.</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8604,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr">
         <is>
-          <t>401 no key. Status: {job_id, status:partial, job_type:sam3d, timestamps, result_url set, error:null}; /result 200 with {job_id,status,result}. 404 for non-existent job AND for another user's job (no existence leak). Failed-job error shape and queued-state /result 404 untested (job completed instantly).</t>
+          <t>401 no key. Status: {job_id, status:partial, job_type:sam3d, created/started/completed timestamps, result_url set, error:null}; /result 200 {job_id, status, result}. 404 for non-existent job, malformed job id, AND another user's job (no existence leak). Failed-job error shape and queued-state /result 404 untested (job completed instantly).</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8658,7 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>200 {status:ok} with real probes: postgres:true, redis:true, async{redis:true, worker:'ok', expected:true, worker_strict:false}, reconstruction{available:false, backend:'none', egress:false} (honest), version, build_id. Single 'server: ProofShape' header confirmed. 503 degraded path untestable (cannot take deps down).</t>
+          <t>200 {status:ok} with real probes: postgres:true, redis:true, async{redis:true, worker:'ok', expected:true, worker_strict:false}, reconstruction{available:false, backend:'none', egress:false} (honest), version, build_id. Single 'server: ProofShape' header. 503 degraded path untestable (cannot take deps down).</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8712,7 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>DEEP_HEALTH_TOKEN unset -&gt; endpoint open (200 without and with a wrong token, as documented). All fields present: checks.postgres{ok,error}, checks.redis{ok,expected,configured,error}, checks.worker{state:'ok', heartbeat_age_seconds:36, stale_threshold_seconds:90}, checks.queue{depth:3, name:'arq:queue'}, checks.object_store{ok:false, expected:false, backend:'local'} — failing-but-unexpected store correctly does not gate. Token-gated 404 path untestable here.</t>
+          <t>DEEP_HEALTH_TOKEN unset -&gt; endpoint open: 200 without and with a wrong X-CadVerify-Health-Token. All documented fields present: checks.postgres{ok,error}, checks.redis{ok,expected,configured,error}, checks.worker{state:'ok', heartbeat_age_seconds:12, stale_threshold_seconds:90}, checks.queue{depth:3, name:'arq:queue'}, checks.object_store{ok:false, expected:false, backend:'local'} - failing-but-unexpected store correctly does not gate status. Token-gated 404 path untestable here (dev-flag state).</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8766,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>Every HTTPException-based error observed carried {code,message,doc_url}: BAD_REQUEST, NOT_FOUND (unknown route + resources), FILE_TOO_LARGE (demo 413), VALIDATION_ERROR (extra_forbidden, int_parsing), plus passthrough detail codes GEOMETRY_INVALID, DIRECT_UPLOAD_* (422/501/404), auth_missing (401), insufficient_role (403). Caveat: the CORE-001 regression produces a plain-text 500 with NO envelope (unhandled ValueError, not an HTTPException) — tracked as the CORE-001 failure. 429/409/503/504 codes not triggered (stayed under limits).</t>
+          <t>Every error observed carried {code, message, doc_url}: BAD_REQUEST (bad params/files), NOT_FOUND (unknown route + resources), FILE_TOO_LARGE (demo 413), VALIDATION_ERROR (extra_forbidden, missing fields, limit out of range), plus passthrough detail codes preserved unchanged: auth_missing (401), GEOMETRY_INVALID (400 with geometry payload), DIRECT_UPLOAD_INVALID_PURPOSE/INVALID_CHECKSUM/IDEMPOTENCY_KEY_REQUIRED/NOT_FOUND/REQUIRES_S3 (422/404/501), rate_limited (429 with Retry-After:3600). The pass-1 plain-text 500 regression is gone (unsupported-suffix re-upload now clean 400 envelope). 409/503/504 codes not triggered.</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8820,7 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>Browser navigation to /docs lands on /developers (Next.js redirect); curl separately confirms 307 with location /developers.</t>
+          <t>curl: 307 redirect to /developers; browser navigation to /docs lands on /developers with no content rendered at /docs.</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8874,7 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>confirm 200; source=user_confirmed; declared fields upserted; 400 no declared field; 400 blank mesh_hash; 404 unknown mesh; 404 cross-tenant confirm; no cross-tenant write happened; 403 platform viewer (analyst gate); identity.confirm audit event. Rate-limit 120/hour not exhausted (budget). No-org 400 branch untestable: signup always creates an org.</t>
+          <t>Confirm upserts declared fields with source=user_confirmed (200); 400 blank mesh_hash; 400 no declared field; 404 unknown mesh; 404 cross-org write attempt (other org's mesh_hash); 403 for platform-viewer caller. identity.confirm audit event visible in org audit log.</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8928,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="3" t="inlineStr">
         <is>
-          <t>onboard 200; honest summary shape; 2 valid files onboarded; qa-fake.stl skipped with reason, batch not aborted; ZIP onboard works (bare geometry); 400 no files; 400 non-UTF-8 mapping; 403 platform viewer (analyst gate). 413 &gt;512MB / ONBOARD_MAX_FILES cap not exercised (impractical payload size); 20/hour limit not exhausted.</t>
+          <t>Onboarded 2 STLs + mapping CSV: honest summary {onboarded:2, skipped:[qa-fake.stl with reason], mapping_errors:[], library_size:2}; unparseable file skipped without aborting batch; 400 no files; 400 non-UTF-8 mapping; 403 viewer role. 413 &gt;512MB / ONBOARD_MAX_FILES cap not exercised (impractical upload size), all other documented paths verified.</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8982,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>GET /library shape; raw signature vector never emitted; org-scoped: B never sees A rows; viewer role allowed on library read; template text/csv; header starts with filename; optional columns present. No-org 403 branch untestable: every account has an org.</t>
+          <t>GET /library returns {library_size, recent} org-scoped, declared identity only (no raw signature vector in payload); viewer role allowed and sees only own org (empty for fresh org). Template is text/csv with filename + part_id/name/program/material_class columns.</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9036,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="3" t="inlineStr">
         <is>
-          <t>201 {org_id,name,slug,org_role:admin}; active org NOT auto-switched; 400 empty name; 400 name&gt;200; platform-viewer 403 (analyst gate); org.created audit event present (recorded under the NEW org's scope - verified via superadmin audit-log with resource_id = new org).</t>
+          <t>201 {org_id,name,slug,org_role:admin}; active org NOT auto-switched (verified via GET /orgs is_active flags); 400 empty name; 400 name &gt;200 chars; 403 platform-viewer.</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9090,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>caller memberships listed; active org flagged; no cross-user data (M sees only own orgs)</t>
+          <t>Returns caller memberships with active_org_id + is_active flags; second user sees only own orgs (no cross-user data).</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9144,7 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="3" t="inlineStr">
         <is>
-          <t>API key refused 403 api_key_org_bound; dashboard session switch 200; 403 not a member; switch back 200; org.switched audit event</t>
+          <t>API key switch refused 403 {code:api_key_org_bound}; dashboard-session switch succeeds (200 with new org); switch to non-member org 403 'not a member of that organization'.</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9198,7 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>POST 201 serialized mapping; 400 invalid role; list shows own mapping; org B list excludes A rows; cross-org delete 404; own delete ok; saml.group_mapping.* audit events (created)</t>
+          <t>POST 201 with serialized mapping (org roles admin/member/viewer; invalid role 400); list strictly org-scoped (other org sees empty); cross-org DELETE of mapping id returns 404; org-admin required.</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9252,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="3" t="inlineStr">
         <is>
-          <t>201 invite M; one-time accept_link + emailed flag; 400 invalid role; GET lists org invites; no raw tokens in list; non-admin-of-A invite attempt via M personal-org key returned 201 (M is admin of own org, so 201/permitted there). Role-exceeds-inviter 403 branch unreachable (only org admins can invite; admin is top org role). Emailed flag observed (best-effort, no RESEND config). 20/hour limit exercised under ID-036.</t>
+          <t>POST 201 returns accept_link exactly once + emailed:false (no RESEND config, creation unaffected); GET lists invites with statuses and no tokens; non-admin org member gets 403; 21st invite in the hour hit the 20/hour limit (429) per ID-036 test. Inviter is always org-admin (top org role) so 'role exceeds inviter' 403 is not reachable via this route.</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9306,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>400 empty token; 404 unknown token; 403 different account redeems; correct account joins {org_id,org_role,created}; 409 re-accept (single-use); member.joined audit event. Expired-invite 409 branch not exercisable (cannot age a token). Never-escalate branch implied by created-only membership.</t>
+          <t>Accept 200 {org_id, org_role, created:true}; 400 empty token; 404 unknown token; 409 replay (already used); 409 revoked token; 403 token issued to a different account; re-invite of existing member at admin role returned created:false and did NOT escalate (member kept).</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9360,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="3" t="inlineStr">
         <is>
-          <t>cross-org revoke 404; revoke returns invite in revoked state; accepting revoked token 409; revoking accepted invite 409; unknown id 404</t>
+          <t>Revoke returns serialized invite status=revoked; revoked link then 409 on accept; 404 unknown id and 404 for another org's invite id; 409 revoking an accepted invite.</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9414,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>org viewer sees active-org members; no cross-org leakage; org B list only B members</t>
+          <t>Org viewer can list; returns only caller's active org members (org A: admin/member/viewer; other org key sees only its own single member) - no cross-org leakage.</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9468,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="3" t="inlineStr">
         <is>
-          <t>non-admin PATCH 403; 404 target not a member; 409 demoting last admin; returns {user_id,org_role}; member.role_changed audit event</t>
+          <t>Admin promoted viewer-&gt;member (200 {user_id, org_role}); 404 target not a member; 409 demoting the last admin; 403 non-admin caller.</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9522,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>non-admin removing other 403 insufficient_org_role; 404 target not a member; 409 removing last admin; self-leave by non-admin 200; membership gone immediately; account still active after leave (org-scoped removal); member.left/removed audit event; departed member's org-A key loses org access (membership re-validation)</t>
+          <t>Non-admin removing another member: 403 {code:insufficient_org_role}; self-leave 200 and the leaver's org-bound API key was rejected 401 immediately after; 404 non-member target; 409 last-admin removal; leaver's account still active in other org (org-scoped removal, not deactivation).</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9576,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>org-admin list has own-org users; org-admin list bounded to own org; cross-org detail 404 (no existence leak); detail fields present; superadmin cursor pagination limit=2; cursor page 2 follows; superadmin sees any user detail; limit bounds 422; org member (non-admin) 403</t>
+          <t>Org-admin list bounded to own org (only org members returned); detail of out-of-org user 404 (no existence leak); superadmin paginated platform-wide (limit=2 -&gt; next_cursor + has_more:true); detail includes org_role, auth_provider, analysis_count, batch_count; 403 for org member.</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9630,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>org-admin 403 platform_superadmin_required; 400 role=superadmin not assignable; 404 unknown user; 400 changing own role; demotion effective: V (analyst-&gt;viewer) got 403 on analyst-gated routes in ID-001/002/004 while reads still worked (ID-003); user.role_changed audit with old/new roles</t>
+          <t>Org-admin 403 {code:platform_superadmin_required}; 400 changing own role; 400 role 'superadmin' not assignable; 404 unknown user; valid change 200 and reversible.</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9684,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>C session works pre-deactivation; org-admin refused 403 (superadmin only); 400 self-deactivate; 404 unknown user; deactivate 200; API key blocked after deactivation; existing dashboard session dead; password login refused; idempotent (session_version unchanged on repeat); reactivate 200; API key restored after reactivate; deactivate/reactivate audited. SAML/Google/magic re-provision paths not exercisable locally (no IdP); password/session/key paths all blocked as specified.</t>
+          <t>Org-admin 403; 400 self-deactivate; 404 unknown user. Deactivate blocked API key (403 account_deactivated), killed existing dashboard session (403), and blocked login (403). Idempotent re-deactivate did not bump session_version; reactivate restored key + login (session_version bumped on real state change only).</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9738,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>org-admin 403; 404 unknown user; returns new session_version; existing dashboard session invalidated; API key still works, account active; user.sessions_revoked audit event</t>
+          <t>Superadmin only (org-admin 403); 404 unknown user; returns new session_version; existing dashboard session became 401 immediately while the user's org-bound API key kept working (initial 403 seen was api_key_org_mismatch from an active-org switch, unrelated to revocation) and account stayed active.</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9792,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>separate honest counts under counts{}; per-event-type breakdown present; webhook-status breakdown present; org-admin filtered to own org; real analysis count &gt;=1; superadmin unfiltered org_id null; superadmin counts &gt;= org counts; days bounds rejected 422; org member (non-admin) 403</t>
+          <t>Org-admin gets org-filtered honest zero counts (analyses/cost_decisions/usage_events/webhook_deliveries) + breakdown maps; days 0 and 91 rejected (422); superadmin unfiltered with org_id:null; 403 for org member.</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9846,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>200 with deliveries list; no payload body fields; non-admin 403; limit bound 422. No webhook endpoints configured in env, so deliveries list is honestly empty; per-row fields not observable on real rows.</t>
+          <t>Org-scoped (fresh org sees []); superadmin sees platform deliveries joined to batch_ulid with status/attempts/response_code/retry timestamps and NO payload body field; limit=101 rejected (422).</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9900,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t>org-admin 200; PII-free summary; non-admin 403; superadmin platform-wide 200</t>
+          <t>Org-admin gets PII-free async/jobs/batches/batch_items/webhooks summary scoped to own org_id; 403 for org member.</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9954,7 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>missing start/end rejected 422; invalid datetime 400; &gt;90-day range 400; org-admin sees only own-org entries; superadmin sees all orgs; action filter works; JSON cursor-paginated; format=csv text/csv attachment; limit 201 rejected; non-admin 403</t>
+          <t>start/end mandatory (422 missing, 400 invalid datetime); 400 range &gt;90 days; org-admin sees only own-org-relevant entries (verified no other tenants' events; superadmin same window saw 33 users' events platform-wide); action filter works; cursor pagination works; format=csv returns text/csv attachment with header row; 403 for org member.</t>
         </is>
       </c>
     </row>
@@ -9988,7 +10008,7 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="inlineStr">
         <is>
-          <t>200 /scim/v2/ServiceProviderConfig; SCIM 2.0 schema doc; 200 /scim/v2/Schemas; 200 /scim/v2/ResourceTypes; no auth 401; org-member-bound key 403 (org-admin required). 403 {code:scim_org_required} for an org-less token untestable: every mintable key is org-bound.</t>
+          <t>Org-admin API key returns static ServiceProviderConfig/Schemas/ResourceTypes (200); non-admin org key 403 insufficient_org_role; unauthenticated 401. No-org key state not constructible in this stack (every account has a personal org); scim_org_required guard is present in code for that case.</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10062,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>POST 201 create; list startIndex/count; SCIM filter userName eq; GET by id; cross-org GET 404; PUT preserves userName; PATCH wrong schema 400; PatchOp applies active=false</t>
+          <t>POST 201 creates SCIM user in key's org; re-POST same userName upserts to same id; list supports startIndex/count (count max 100, 101 rejected 422) and userName eq filter; GET of user outside org 404 SCIM error; PUT without userName preserves existing userName (documented setdefault behavior); PATCH with non-PatchOp schema 400; proper PatchOp toggles active.</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10116,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>cross-org DELETE 404; 204 no body; soft deactivation - still readable active:false</t>
+          <t>DELETE returns 204 no body; user soft-deactivated (GET shows active:false, still retrievable - no hard delete; membership removed); cross-org delete 404.</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10170,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>groups listed; GET group path segment 'role:member'; PATCH membership applied; member visible after PATCH; unknown group 404 SCIM error; PATCH unknown group surfaces service error (no tenant crossing)</t>
+          <t>Groups are org-scoped role groups (role:admin/member/viewer) with members; colon path segment works; unknown group 404 SCIM error; PATCH add member moved user viewer-&gt;member (confirmed via /orgs/members).</t>
         </is>
       </c>
     </row>
@@ -10204,7 +10224,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t>unauthenticated caller passes admission fail-open, clean 401 (no 429/500); 401 body is an auth error. Load-dependent sub-assertions NOT exercised (per harness rules on not exhausting capacity/limits): global server_busy 429 beyond 8 in-flight, per-org org_at_capacity 429 beyond 3, finally-release, RELEASE-mode ADMISSION_DISABLED lockout. Code inspection confirms admit_analysis dependency on /validate siblings.</t>
+          <t>16 concurrent STEP /validate from one org: 11x 200, 5x 429 {code:org_at_capacity} with Retry-After: 5; slots released (subsequent requests succeeded, no 500s). Counters are per-worker (4 uvicorn workers), so moderate cross-org bursts pass; global server_busy ceiling not separately triggered (would need 8+ in flight on one worker across 3+ orgs) - same gate, org path verified.</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10278,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>org member proposes -&gt; 'proposed'; second proposal created; 400 unknown asset_type; 404 target version not found; cross-org target 404; 400 target not in draft status (published); governance.change_requested notification emitted to admin inbox. 60/hour limit not exhausted (budget).</t>
+          <t>Org member proposed draft -&gt; 'proposed' request serialized; 400 unknown asset_type; 404 target version not found; 400 target not in draft status (after publish); admin notification governance.change_requested emitted (seen in admin inbox).</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10332,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>list shows org requests; newest-first; ?status filter honored; org member (viewer+) reads detail; missing 404; cross-org detail 404; B list excludes A requests. No-org honest-empty branch untestable.</t>
+          <t>List org-scoped newest-first with ?status filter; other org's list honestly empty; detail 404 for missing id and for another org's request id.</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10386,7 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>org member (non-admin) 403; cross-org admin 404; unknown request 404; approve 200 request approved; returns published version; re-approve 409 (not proposed); governance.approved audit event; library.version_published audit event; pending review notification resolved. Publish-failure fail-closed branch not exercisable without breaking the library.</t>
+          <t>Non-admin 403; cross-org 404; approve published the target draft via the library path and returned {change_request approved, published_version status:published}; re-approve 409; unknown id 404; pending review notification resolved (status resolved in inbox).</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10440,7 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t>cross-org reject 404; unknown 404; reject 200 status rejected; note persisted; target draft remained draft (nothing published); re-reject 409; governance.rejected audit event</t>
+          <t>Non-admin 403; reject returned status rejected with note; target draft remained status draft (verified via rate-library GET); re-reject 409; cross-org 404.</t>
         </is>
       </c>
     </row>
@@ -10474,7 +10494,7 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>default list shows unread non-dismissed; invalid status rejected; 400 dismissed=true + unread=true contradictory; cursor-paginated limit=1; cursor follows to next page; org-scoped: B never sees A ids; limit bound 422. No-org honest-empty branch untestable (every account has an org).</t>
+          <t>Org-scoped list with per-user read/dismiss state; default = open + unread non-dismissed; status must match open|resolved|all (bogus 422); dismissed=true&amp;unread=true 400; limit 101 rejected; cursor fields present.</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10548,7 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>read returns updated serialized notification; per-user state: MA still sees it unread after A read; dismiss sets dismissed_at; dismissed item left default inbox; restore 200; restored item back in inbox; org B notification created for cross-org probe; another org's notification id 404; unknown id 404. No-org dismiss/restore-404 and read-noop branches untestable (every account has an org).</t>
+          <t>read/dismiss/restore each return {ok, notification} with updated per-user read_at/dismissed_at; dismissed item leaves default view and appears under dismissed=true; restore clears dismissed_at; another org's notification id 404; state is per-user (admin's read-all left other member's copy unread).</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10602,7 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>{ok,count,read_at}; counted MA unread items; MA inbox cleared; A's unread state unaffected (per-user only). No-org count-0 branch untestable.</t>
+          <t>Marks caller's open org notifications read: returned {ok:true, count:1, read_at} with an open unread present, honest {ok:true, count:0, read_at:null} otherwise (only open-status notifications counted, matching implementation); other user's unread state untouched.</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10660,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="3" t="inlineStr">
         <is>
-          <t>FIX VERIFIED: uvicorn banner gone - exactly ONE 'server: ProofShape' header (checked via raw http.client preserving duplicates) on normal responses (/health, authed JSON /api/v1/orgs), error responses (404 unknown route, 405 method mismatch, unauth 401), and the streamed CSV audit-log export. All hardening headers present on every case: HSTS max-age=63072000; includeSubDomains, X-Content-Type-Options nosniff, X-Frame-Options DENY, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy camera/microphone/geolocation disabled. SECURITY_HEADERS_ENABLED=0 disable path not testable without restarting the app (default-on confirmed live).</t>
+          <t>HSTS max-age=63072000; includeSubDomains, nosniff, X-Frame-Options DENY, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy camera/mic/geo disabled, single 'server: ProofShape' header - present on normal responses, 404 errors, and the streamed audit-log CSV export.</t>
         </is>
       </c>
     </row>
@@ -10694,7 +10714,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>inbound X-Request-ID echoed; absent header -&gt; distinct UUID4 per request. structlog contextvar binding + Sentry tagging not externally observable via API.</t>
+          <t>Inbound X-Request-ID echoed verbatim on the response; absent one, a fresh UUID4 is generated per request (distinct across calls). Log/Sentry binding not externally observable; header contract fully verified.</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10768,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="3" t="inlineStr">
         <is>
-          <t>slowapi 429 hit on invite creation; exactly 20/hour allowed before 429; Retry-After header on 429; reads still available (invite list 200); org list read unaffected; kill-switch dependency present on org/identity mutation routes (code). Kill-switch open state allows all mutations (verified throughout the run); the CLOSED state is driven by the running process's env and cannot be flipped without restarting/modifying the app (forbidden) - dependency presence confirmed in code on all mutating org/identity routes.</t>
+          <t>Invite route 20/hour limit enforced: 20 creations passed, 21st returned 429 {code:rate_limited} with Retry-After: 3600 and x-ratelimit-limit:20/remaining:0. Identity confirm/library reads carried their own x-ratelimit headers (120/hour). Kill-switch is open (ACCEPTING_NEW_ANALYSES=true baked into the running process env): all gated mutations succeed and reads work; the closed-switch 503 service_paused path cannot be exercised without restarting the stack (env-flag state) - code path verified in src/auth/kill_switch.py.</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10822,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>Fresh share /s/xUS262U4hyfI (qa-box.stl) viewed logged-out. filename=true, read-only header=true, geometry cards=true, process ranking=true, noindex=true; bogus id: not-available+revoked copy=true, home link=true</t>
+          <t>Fresh share /s/EyGuAe1T3lSN (qa-box.stl) viewed logged out: filename + verdict, 'Shared analysis · read-only' header, geometry cards (faces/volume/dimensions/watertight), process-ranking table with scores, OG title 'qa-box.stl - DFM Analysis', noindex,nofollow. Bogus id -&gt; 'not available... may have been revoked' with a home link.</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10876,7 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="3" t="inlineStr">
         <is>
-          <t>Fresh cost share /s/cost/QUnXUyrBZ1CQ viewed logged-out. Make-by=true, badge=true, crossover sentence=true, confidence band=true, footer=true, noindex=true; bogus id message=true</t>
+          <t>Fresh cost share /s/cost/ASvRTHGyIf4d logged out: 'Make by MJF (HP)' with DFM-ready badge, crossover sentence ('Make below ~2,815 units with MJF (HP); tool up with Injection Molding above it.'), honesty note, verbatim confidence band ($3.12–$7.29/unit ±40%, assumption-band basis), geometry cards, recommendation-by-quantity table, footer 'assumption-based... not a validated quote', noindex. Bogus id -&gt; 'not available'.</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10930,7 @@
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>title fallback OK; 1 canvas; rail 6 stops (PART|ROUTED|OPENED|SEATED|THE NUMBER|PROOF); dot click scrolled 0-&gt;5130px; pill -&gt; /company#pilot; /platform + /method links OK; no console errors</t>
+          <t>Tab title = layout default 'ProofShape — verification, made of glass'; WebGL canvas renders; nav[aria-label='Story progress'] rail has exactly 6 stops labeled PART...PROOF; clicking the last dot scrolled 0 -&gt; ~5900px to the PROOF act; 'See it on your part' pill -&gt; /company#pilot; 'The full platform -&gt;' -&gt; /platform; 'or read the method first -&gt;' -&gt; /method; zero console errors on full scroll.</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10984,7 @@
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>default 500 units MJF make; ~1900 units MAKE, ~2100 units 'Tool up: injection molding' with 'if redesigned' — flips at documented 1,962 crossover; SVG curves render; /company#pilot link present</t>
+          <t>input[type=range][aria-label='Quantity'] default 500 units with 'Make by MJF (PP)'; dragged to 1,959 units (&lt;=1962) -&gt; still MJF make branch; 2,089 units (&gt;1962) -&gt; 'Tool up: injection molding' with 'if redesigned' conditional line; unit-cost readout and highlighted curve updated ($10.43 -&gt; $10.18); underline link below -&gt; /company#pilot. Log-scale slider quantization means the flip lands between achievable values 1,960 and ~1,978, consistent with the &lt;=1962 expectation.</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11038,7 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>email input not inside any form; typed value, clicked Request a pilot -&gt; plain Link nav to /company#pilot; zero non-GET requests fired</t>
+          <t>Close-act email input (aria-label 'Work email') has no enclosing form; typed an email and clicked 'Request a pilot' — plain Link navigation to /company#pilot, zero POST requests fired, input value not carried anywhere.</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11092,7 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>wordmark -&gt; /; six nav links present; data-active on current section incl /teams/* subtree; Log in -&gt; /login; Request a pilot -&gt; /company#pilot; mobile menu: opens, 8 links, Escape closes, link click navigates</t>
+          <t>Wordmark 'ProofShape' -&gt; /; all six nav links + 'Log in' (/login) + 'Request a pilot' (/company#pilot) correct; data-active=true on current section and on /teams for /teams/sourcing subtree; home uses st-nav-cinematic, /method uses st-nav-document; mobile &lt;details&gt; menu mirrors all 8 links, closes on link click and on Escape.</t>
         </is>
       </c>
     </row>
@@ -11126,7 +11146,7 @@
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>document footer: tagline + Home + six nav + Log in + legal row (2026, Privacy/Terms/DPA/Status) all correct, Privacy click routed; home closes with inline tagline (Method/Platform/Security/Developers), footer count on home=0</t>
+          <t>Document-page footer: tagline 'ProofShape — verification, made of glass', links Home + six nav items + Log in, legal row '© 2026 ProofShape' with Privacy /privacy, Terms /terms, DPA /dpa, Status /status. Cinematic home has no full footer; closes with inline p.st-footer-tagline containing exactly 4 links (Method/Platform/Security/Developers).</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11200,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title falls back to layout default as documented; full-page scroll reveals the record-assembly drivers reconciling to $14.14; 'Cost a part' -&gt; /signup, 'Explore the platform' -&gt; /platform; no console errors.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11254,7 @@
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'Platform — ProofShape'; 'Cost a part' -&gt; /signup, 'How the number is built' -&gt; /method; SiteShell nav+footer chrome; no console errors.</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11308,7 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'Teams — ProofShape'; all five persona journey links present (/teams/in-house-manufacturing, /teams/cost-engineering, /teams/sourcing, /teams/design-engineering, /teams/shop-owners); 'Request a pilot' -&gt; /company#pilot, 'Explore the platform' -&gt; /platform.</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11362,7 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'For Cost Engineering — ProofShape'; hero link back to /teams; WebGL canvas renders; full scroll clean (no console errors); closing CTAs -&gt; /company#pilot and /teams.</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11416,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Client page title falls back to layout default 'ProofShape — verification, made of glass' as documented; zero form/slider inputs on the page; hero /teams link; closing CTAs -&gt; /company#pilot and /teams; no console errors.</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11470,7 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'ProofShape — For In-house manufacturing &amp; MRO'; /teams link near top; closing CTAs -&gt; /company#pilot and /teams; SiteShell chrome; no console errors.</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11524,7 @@
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'For shop owners — ProofShape'; hero /teams link; closing CTAs -&gt; /company#pilot and /teams; full scroll with no console errors.</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11578,7 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'For Sourcing — ProofShape'; WebGL stage canvas renders; hero /teams link; closing CTAs -&gt; /company#pilot and /teams; no console errors.</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11632,7 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'Developers — ProofShape'; 'Get an API key' -&gt; /signup, 'Full API reference' -&gt; /docs; page renders with no console errors (record reveal is CSS-only, no client JS needed).</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11686,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'API Reference - ProofShape'; 'Open API console' -&gt; /scalar (route responds 307 to the console), 'Developer overview' -&gt; /developers; static &lt;pre&gt; lists all four endpoints (POST /api/v1/validate, POST /api/v1/validate/cost, GET /api/v1/cost-decisions, GET /api/v1/catalog) with Bearer auth note.</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11740,7 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>Title 'Company — ProofShape'; section#pilot has non-zero scroll-margin-top and /company#pilot lands the section in view below the sticky nav; four WeekCell columns present (rendered uppercase 'WEEK 1'..'WEEK 4' — initial automated case-sensitive match was a false positive, verified in page text); no email address published in body; SiteShell chrome; no console errors.</t>
+          <t>Title 'Company — ProofShape'; section#pilot exists with computed scroll-margin-top 84px; navigating /company#pilot lands the section in view below the sticky nav; four 'Week N' pilot columns; contact section points to the form, no mailto:/email published; SiteShell chrome; no console errors.</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11794,7 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>GET /api/pilot/request cfg={"turnstileSiteKey":null}; empty submit blocked by native required validation (email,company,what); deployment opts undecided,cloud,vpc,air-gapped; real POST -&gt; 200; role=status 'Request received' with receipt CV-bd3d4ef9-e4c1-4712-9173-dc90ce9f856b</t>
+          <t>On mount form GET /api/pilot/request -&gt; 200 {turnstileSiteKey:null} (dev release, no Turnstile gate) and submit enabled; empty submit blocked by native required validation (no POST fired); deployment select offers exactly [undecided, cloud, vpc, air-gapped]; filled submit POSTed JSON with UUID requestId + website honeypot -&gt; 200 {status:'received', receipt:...}; form replaced by 'Request received' status showing durable receipt CV-80e28993-bcf1-4173-962e-7a5c053aff51; no console errors.</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11848,7 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'Security — ProofShape'; cloud/self-hosted/air-gapped deployment models rendered; no compliance badges (SOC 2 honestly stated as 'in progress', explicitly no badge printed early); 'Talk to us' -&gt; /company#pilot, 'Self-host it today' -&gt; /developers; SiteShell chrome.</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11902,7 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'Pilot Report - ProofShape'; numbered cards cover held-out accuracy, floor declaration, decision ledger, next actions; single CTA 'Request a pilot' -&gt; /company#pilot; SiteShell chrome.</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11956,7 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'Privacy - ProofShape'; 'What we collect' / usage / 'Retention and deletion' sections present; 'Talk to ProofShape' pill -&gt; /company#pilot.</t>
         </is>
       </c>
     </row>
@@ -11990,7 +12010,7 @@
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'Terms - ProofShape'; static article with zero links/CTAs in the body beyond shared nav/footer; reachable from footer legal row (verified in SITE-005).</t>
         </is>
       </c>
     </row>
@@ -12044,7 +12064,7 @@
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>title OK; CTAs/links verified; no console errors</t>
+          <t>Title 'Data Processing Addendum - ProofShape'; static article (0 links, 0 forms in body) stating DPA travels with the pilot, subprocessors, and security-questionnaire process via pilot intake.</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12118,7 @@
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>Title 'Status - ProofShape'; exactly three rows (Hosted app, API, Workers) each 'No public metric feed yet'; no fake green indicators — the only 'uptime' mention is the honest disclaimer 'ProofShape does not show synthetic uptime' (initial regex hit was a false positive); no console errors.</t>
+          <t>Title 'Status - ProofShape'; exactly three rows (Hosted app, API, Workers), each reading 'No public metric feed yet' (3 occurrences); no fake green indicators.</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12172,7 @@
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>bogus route -&gt; HTTP 404, branded 'That record is not here.' in SiteShell, Back pill -&gt; /, nav+footer present, Method click routed; only console entry is the expected resource-404</t>
+          <t>GET /qa-zfinal-bogus-route -&gt; HTTP 404 with branded page inside SiteShell: heading 'That record is not here.', 'Back to ProofShape' pill href=/; clicked Method in the nav from the 404 page and it navigated correctly; footer present.</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12226,7 @@
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>injected toLocaleString crash -&gt; root error boundary 'Something went wrong' with 'Try again' button (client error carries no digest so no Error ID line, as documented 'when present'); cleared fault + Try again re-rendered the working page</t>
+          <t>Verified with the sweep agent's repro: injected a render-time fault on / (Number.prototype.toLocaleString patched to throw while a flag is set) -&gt; root error boundary rendered 'Something went wrong' + 'Try again' (no Error ID line, as expected for a digest-less client error). Cleared the fault and clicked 'Try again': zero pageerror/console errors (previously 'TypeError: l is not a function'), boundary dismissed, and the working home page re-rendered. Fix confirmed: error.tsx/global-error.tsx/(app)/error.tsx now destructure `retry`, which Next 16.3.0 passes (per node_modules/next/dist/docs error.md). Screenshot: qa/results/screenshots/zzverify-site-025.png (recovered page after retry). NOTE: the port-3000 process is `next start` serving the pre-fix 12:50 production build (not `next dev`; no hot reload) and still reproduced the old TypeError; killing/restarting it was permission-denied, so verification ran against a fresh `next build` of the working tree served identically via `next start -p 3001`. Port 3000 needs a rebuild+restart to pick up the fix.</t>
         </is>
       </c>
     </row>
@@ -12260,7 +12280,7 @@
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>robots.txt: 18 Allow (exact public set), 13 Disallow app/auth routes, Sitemap pointer -&gt; http://localhost:3000/sitemap.xml; sitemap.xml: same 18 routes, priority 1 home / 0.7 others; /opengraph-image -&gt; 200 image/png 53631 bytes; layout default title verified on home</t>
+          <t>robots.txt allows exactly the 18 public marketing routes and disallows the app/auth routes (/analyze,/batch,/cost,/cost-decisions,/history,/label,/reconstruct,/settings,/verify,/login,/signup,/magic,/orgs), pointing at ${NEXT_PUBLIC_SITE_URL}/sitemap.xml; sitemap.xml lists the same 18 routes with priority 1 for / and 0.7 elsewhere; /opengraph-image serves image/png (53,631 bytes); (site) layout supplies the default title 'ProofShape — verification, made of glass'.</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12334,7 @@
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>Unauth /verify 307s to /login?next=%2Fverify. Membership-less user (fresh account, membership removed in DB): verify-organization-gate renders 'ORGANIZATION REQUIRED / You haven't joined an organization yet…' with invitation guidance, the 'No organization data has been loaded or treated as empty.' honesty line and 2 links to /settings/organization (screenshot RETEST-VER-001-gate.png). Memberships-but-none-active and access-unavailable branches remain defensive-only (backend always resolves the oldest live membership), as in pass 1. VERIFY_UI-off 404 not toggled (shared dev server).</t>
+          <t>Unauth /verify 307s to /login?next=%2Fverify; with an active org the workspace renders and verify-organization-gate is absent. The membership-less gate branch could not be re-created this pass: the app's own APIs refuse removing the last org admin (CONFLICT) and direct DB setup was denied by the sandbox permission layer; that branch was UI-verified in the prior retest pass. VERIFY_UI-off 404 not toggled (shared dev server flag state).</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12388,7 @@
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>First-run dialog opened with all four actions; 'Set up my shop' lands on Machines screen; closing records proofshape_welcome_v2=1; no reopen once set; ?welcome=1 reopens and the param is stripped from the URL; 'Start here' button reopens the guide; 'Check my CAD file' opens the native file picker (filechooser event).</t>
+          <t>Fresh account: dialog opens with all four actions; 'Check my CAD file' fires the native filechooser; 'Set up my shop' lands on the Machines screen; closing writes proofshape_welcome_v2=1 and no reopen on reload; ?welcome=1 reopens and the param is stripped to /verify; 'Start here' reopens anytime.</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12442,7 @@
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>'Run a guided example' drives the real pipeline (POST /validate 200 + POST /validate/cost 200); guided-example-status walks running→ready; GuidedResultSummary shows recommended route, measured geometry, resource cost and shop fit; 'Show full technical result' closes into the walk; leaving via rail navigation cancels the guided lifecycle (status bar gone).</t>
+          <t>'Run a guided example' drives the real pipeline (POST /api/proxy/validate + /validate/cost observed); guided-example-status bar walks running ('Guided example: analyzing a real routing bracket') -&gt; ready ('Example complete'); GuidedResultSummary shows recommended route, measured geometry, resource cost and shop fit; 'Show full technical result' closes into the walk; leaving the screen cancels the guided lifecycle (status bar gone).</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12496,7 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>.sldprt upload → role=alert verify-upload-rejection with SolidWorks-specific 'needs a STEP export' copy, 'was not uploaded… No analysis was started' honesty line, dismiss works; zero network requests fired for the rejected file; input accept='.stl,.step,.stp,.iges,.igs,model/stl,application/step'.</t>
+          <t>.sldprt upload -&gt; role=alert verify-upload-rejection with SolidWorks 'needs a STEP export' copy, 'was not uploaded... No analysis was started' honesty line, 'Choose a STEP export' offer, dismiss works; zero /validate requests fired; input accept='.stl,.step,.stp,.iges,.igs,model/stl,application/step'.</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12550,7 @@
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>With validate delayed 1.5s and cost 5s: /validate returned before /validate/cost started (sequential, never parallel); verify-first-insight visible with MEASURED chips while cost still in flight; GET /machine-inventory and PUT /part-context/{sha256} ran alongside; cost completed 200. Run-token supersedence verified in VER-011 rapid material switch.</t>
+          <t>Request log: POST /validate returned (200) before POST /validate/cost started (strictly sequential); GET /machine-inventory and PUT /part-context/{sha256-of-bytes} ran alongside; first-insight ('ROUTING + DFM READY · COST CALCULATING' with MEASURED chips) visible while cost was in flight. Run-token supersedence verified via VER-011 rapid material switch.</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12604,7 @@
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>Overlay COMPUTING header 'GATES CHECKING IN' observed; five-milestone rail (received/measured/routed/gates walked/record assembled) narrated; partial state 'ROUTING + DFM READY · COST CALCULATING' observed; dismiss ('Skip to the walk') present in overlay markup on longer runs; geometry-blocked stop and interrupted headers exercised in VER-007/VER-008 (walk stops at failed gate, INTERRUPTED · NO VERDICT PRODUCED).</t>
+          <t>Overlay rail observed with all five milestones (received/measured/routed/gates walked/record assembled), 'COMPUTING — GATES CHECKING IN' header, and the dismiss button titled 'Skip to the walk' which closes it. Partial-while-running header observed; interrupted header ('INTERRUPTED · NO VERDICT PRODUCED') observed in the VER-008 outage. Settled complete/partial headers are ephemeral by design (overlay hands off within ~200-400ms once validation lands so unfinished cost is never narrated as complete); blocked-gate stop verified in VER-007 (downstream steps not rendered).</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12658,7 @@
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>qa-broken.stl → /validate/cost 400 GEOMETRY_INVALID; fail banner 'Geometry invalid — the engine won't guess' + 'THE WALK STOPS AT THE FAILED GATE' block quoting the backend message with measured facts (faces/watertight/volume) and 'Repair &amp; re-upload' CTA; downstream materials/cost/decide steps not rendered.</t>
+          <t>qa-broken.stl -&gt; /validate/cost 400 GEOMETRY_INVALID; 'Geometry invalid — the engine won't guess' banner + 'THE WALK STOPS AT THE FAILED GATE' block quoting the backend message with measured facts (faces/watertight/volume) and 'Repair &amp; re-upload' CTA; downstream materials/cost/decide steps absent.</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12712,7 @@
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>Outages induced by client request interception. Total: 'ANALYSIS INTERRUPTED · NO VERDICT PRODUCED' with the exact error and 'Retry verification'. Cost-only: 'RESOURCE COST INTERRUPTED' with exact copy 'Routing and DFM are ready. Cost needs another try.', names the costError and why machine fit is absent, offers both 'Retry cost only' and 'Rerun full verification'. Retry cost only re-POSTed only /validate/cost (validate count unchanged) and merged onto the preserved DFM into a completed walk.</t>
+          <t>Both requests aborted -&gt; 'ANALYSIS INTERRUPTED · NO VERDICT PRODUCED' with the error and 'Retry verification'. Cost-only abort -&gt; 'RESOURCE COST INTERRUPTED' with exact copy 'Routing and DFM are ready. Cost needs another try.', both 'Retry cost only' and 'Rerun full verification' offered; 'Retry cost only' re-POSTed only /validate/cost (validate count unchanged) and merged onto the preserved DFM into a completed verdict.</t>
         </is>
       </c>
     </row>
@@ -12746,7 +12766,7 @@
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>Fresh org, no machines/env: banner 'VERDICT · DFM … · SHOULD-COST COMPUTED' with explicit 'not evaluated here because no machines and no service conditions are declared' copy. With machines declared (VER-012 run) the verification block drove 'Makeable — outsource only' banner with should-cost line and per-route marks.</t>
+          <t>Fresh org, no machines/env: 'VERDICT · DFM PASS · SHOULD-COST COMPUTED' banner with explicit 'not evaluated here because no machines and no service conditions are declared' copy. With machines declared, the verification block drove 'VERDICT · OUTSOURCE ONLY' (makeable-outsource-only) with should-cost line and per-route fit marks.</t>
         </is>
       </c>
     </row>
@@ -12800,7 +12820,7 @@
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>120°C chip toggle re-ran verification: PUT /part-context/{sha256} carrying "max_temp_c":120 landed before POST /validate/cost; door chip walked capturing… → '● USER · on the record' after successful persistence; induced PUT abort on the 35 MPa toggle → honest 'drives this preview only' chip. Material-exclusion citations (HDT/NACE) present in step-2 copy; ambient state verified pre-toggle.</t>
+          <t>120°C chip toggle: PUT /part-context/{sha256} with {"service_environment":{"max_temp_c":120}} landed before POST /validate/cost; door walked 'capturing...' -&gt; '● USER · on the record'. Induced PUT abort on the 35 MPa toggle -&gt; honest 'drives this preview only' chip. With conditions applied and nothing excluded, the walk states 'no candidate material on the shortlisted routes is excluded by them' and that struck materials would cite their standard — the honest no-strikes state.</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12874,7 @@
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>DEFAULT copy 'uses a default material and ambient service until you declare otherwise' before declaration; selecting Steel re-ran cost and the walk shows 'material class steel' with USER provenance; rapid Aluminum→Titanium leaves Titanium displayed (monotonic run token, no stale result).</t>
+          <t>DEFAULT copy 'uses a default material and ambient service until you declare otherwise' before declaration; selecting Steel re-ran cost and shows 'material class steel' with ● USER provenance; rapid Aluminum-&gt;Titanium leaves 'material class titanium' displayed (monotonic run token, no stale result).</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12928,7 @@
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>Empty floor: step 1 shows 'No machines declared' with 'Declare your floor →' CTA that opens the Machines screen. Declared cnc_3axis 'QA VF-2' (762×406×508, $85/hr) + sla 'QA Mars 4' via authed proxy (unknown 'thermoforming' now rejected 400 at declaration — engine catalog enforced server-side, so unknown ids can never reach owned_processes; cost stayed 200). Re-run lists machines with USER provenance and envelope summaries '762 × 406 × 508 mm'; verification block returned 'Makeable — outsource only' with per-route ✓/✗ marks and acquisition-gap language; rail rate dot fills once the $85/hr rate exists ('Your shop rates are bound · ● SHOP').</t>
+          <t>Empty floor: step 1 shows 'No machines declared' with 'Declare your floor →' CTA that opens the Machines screen. Declared cnc_3axis 'QA VF-2' (x/y/z 762/406/508, $85/hr) + sla 'QA Mars 4' via authed proxy (unknown capability key rejected 400 server-side — catalog enforced); re-run lists both machines with USER provenance and envelope figures, per-route fit marks and acquisition language render from the verification block, and the rail rate dot fills ('Your shop rates are bound · ● SHOP').</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12982,7 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>Default readout 'engine-exact — a computed point'; scrubbed to qty 74 → 'interpolated between computed 1 and 100'; qty 1 edge is engine-exact (a real ladder point, no clamp needed); crossover from decision.crossover_qty marked on the axis ('crossover ≈ 529'); band labelled 'not shop-validated'. Ladder [1,100,1000,2000,5000,10000]; annual_volume replacement verified in pass 1.</t>
+          <t>Default readout 'engine-exact — a computed point' at qty 100; scrubbed interior position -&gt; 'interpolated between computed 1 and 100'; min edge stays engine-exact (real ladder point 1); 'crossover ≈ 529' marked from decision.crossover_qty; band 'assumption-based, not yet validated' with n=0. Ladder endpoints 1..10,000 rendered; annual_volume point replacement not re-exercised this pass (no program declared on the fresh org; mechanics verified in pass 1).</t>
         </is>
       </c>
     </row>
@@ -13016,7 +13036,7 @@
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>Choosing 'Make outside' saved via PUT /api/proxy/cost-decisions/{id}/disposition (story says PATCH; PUT is the implemented method, unchanged from pass 1) with toast 'Make outside — saved to cost-decision #01KZA7RR' and status '✓ … saved and auditable'; hydrate GET /cost-decisions/{id} 200; note save toasts 'Outcome note saved…'; induced save outage → 'Decision controls paused — Failed to fetch. Nothing was changed.' with Retry which clears the pause leaving state intact; 'Open the record →' navigates to Records.</t>
+          <t>'Make outside' saved via PUT /api/proxy/cost-decisions/{id}/disposition with status '✓ Make outside — recorded ... saved and auditable on cost-decision #...' (PUT is the implemented method vs the story's PATCH wording — unchanged from both prior passes, same semantics); hydration GET /cost-decisions/{id} observed; note save works. Induced save outage (with the client's 2 retries exhausted) -&gt; 'Decision controls paused — Failed to fetch. Nothing was changed.' with Retry; Retry clears the pause and controls become usable again. 'Open the record →' present.</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13090,7 @@
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>Opened from the tooling card ('Open acquisition consideration →'); modal charts only engine per-quantity unit costs with crossover economics; 'standalone vendor tool price is not an engine output, so no purchase price is printed' honesty kept; org ranking fetched from /api/proxy/catalog/capability-investment (200); Esc closes back to the walk.</t>
+          <t>Opened from the tooling card 'Open acquisition consideration →'; modal charts only engine per-quantity unit costs with crossover/amortization economics; vendor purchase price explicitly withheld (not an engine output); org ranking fetched live from /api/proxy/catalog/capability-investment (1 request observed on open); Esc closes back to the walk.</t>
         </is>
       </c>
     </row>
@@ -13124,7 +13144,7 @@
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>Dock disabled placeholder 'Load a part above — the engine answers only about a computed part.' without a result; with a result 'cost drivers at qty 500' renders the drivers artifact; 'compare routes' renders the comparison; 'compare saved decisions' does a live GET /cost-decisions/compare (3 calls observed); natural-language ask ('will this survive a drop test?') renders a refusal artifact — no fabricated numbers.</t>
+          <t>Before any result the dock input is disabled with 'Load a part above — the engine answers only about a computed part.' After a run: 'cost drivers at qty 500' renders the drivers artifact; 'compare routes' renders the comparison; 'Compare saved decisions' with one record renders the honest refusal ('Compare needs a second saved decision — this org has just this one on record'), and with 2+ records performs a live GET /cost-decisions/compare (observed); natural-language ask and the 'An uncomputable ask' chip render refusal artifacts — no fabricated numbers.</t>
         </is>
       </c>
     </row>
@@ -13178,7 +13198,7 @@
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>STEP now works (gmsh installed). as1-tu-203.stp (5-solid AS1 assembly, 18 tree occurrences) → POST /validate/assembly?format=json 200 + ?format=glb 200, single-part /validate/cost skipped (no spurious 400). 'ANALYSING PER-PART' status shown honestly; 18 assembly-part-rows populated with tree paths, tree-counted quantities (×1/×2/×6) and unit costs (plate $235.4, l-bracket $178.9, rod $141.3; bolts ≈M12 COTS rows). Row click highlights the part on stage ('◆ selected plate as1/PLATE/plate'). Single-solid qa-cube.step stayed on the single-part path (no assembly calls) and verified normally.</t>
+          <t>as1-tu-203.stp (AS1 assembly): POST /validate/assembly?format=json + ?format=glb + ?format=analysis ran; no single-part /validate/cost fired at upload (no spurious 400). 'ANALYSING PER-PART — running DFM + should-cost on every solid' shown honestly in flight; 18 product-tree rows with full tree paths and tree-counted quantities (·2/·3) populated with per-part DFM verdicts and unit costs ($) when analysis completed. Row click highlights on stage ('◆ selected plate · as1/PLATE/plate'). Single-solid qa-cube.step is probed (format=json classifies single_part by design) then stays on the single-part path — no assembly panel, normal verdict walk completes.</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13252,7 @@
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>After the run, GET /part-context/{sha256} hydrates verify-stage-context; with no declared parent the card shows 'CONTEXT · not declared · no parent assembly declared · orphan until declared' (200 with empty context — same honest orphan state as the 404 path; the run's own PUT creates the row). No false error pill. annual_volume ladder reshaping verified in pass 1 and the ladder mechanics re-verified in VER-013.</t>
+          <t>GET /part-context/{sha256} hydrates verify-stage-context after the run; undeclared parent renders 'CONTEXT · not declared · no parent assembly declared · orphan until declared' — the honest orphan state, no false error pill. Ladder mechanics re-verified in VER-013.</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13306,7 @@
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>Corpus is seeded (2 QA parts in data/corpus/manifest.jsonl) and retrieval demonstrably runs: the VER-020 imported-plate run rendered the explicit honest line 'No confident match in your part library yet — geometry retrieved 4 prior parts, none confident enough to suggest.' — retrieval executed, below-bar match → NO identity card fabricated (per story: non-grounded/low corpus renders nothing or soft copy, never an assertion). No grounded suggestion reached the confident bar for this org's uploads, so the confirm POST path was not reachable live; confirm/dismiss flows remain code-verified.</t>
+          <t>Corpus retrieval demonstrably runs: uploading qa-part2.stl in an org with prior parts rendered the honest line 'No confident match in your part library yet — geometry retrieved 1 prior part, none confident enough to suggest.' — retrieval executed and no identity card was fabricated below the confidence bar; a truly empty fresh org renders nothing at all, per the story. No upload reached the grounded-confident bar live, so the /identity/confirm POST path was not reachable this pass (same as prior retest).</t>
         </is>
       </c>
     </row>
@@ -13340,7 +13360,7 @@
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>Design generation now works: POST /api/proxy/designs (plate 80×60×5, 2 holes) → 202, revision reached status=ready with geometry_hash. /verify?design=&lt;id&gt; fetched download.step (200), banner walked 'Imported QA_Retest_Plate.step. Verification is running.' → 'Verification finished.' (dismissible); normal untrusted pipeline ran (validate 200, cost 200) and produced the full verdict walk; on-page Evidence hash equals the revision geometry_hash (51c7179c…48ed) — integrity check passed. Tampered x-geometry-sha256 (route-injected) → role=alert 'The generated STEP artifact failed its integrity check.' with Return to Design Studio. Invalid id → 'That Design Studio link is invalid.'; invalid revision → 'That design revision is invalid.'; nonexistent id → 'The design artifact is not ready (404).' — all with Return links.</t>
+          <t>Fresh design (plate 80x60x5, 2 holes) generated to ready; /verify?design=&lt;id&gt; fetched download.step, banner walked importing -&gt; 'Verification finished', the normal pipeline ran, and the on-page Evidence hash equals the revision geometry_hash (47c2ea1b...9613) — integrity verified. Tampered x-geometry-sha256 (route-injected) -&gt; 'The generated STEP artifact failed its integrity check.'; invalid id -&gt; 'That Design Studio link is invalid.' (role=alert + Return to Design Studio); invalid revision -&gt; 'That design revision is invalid.'; nonexistent id -&gt; 'The design artifact is not ready (404).'</t>
         </is>
       </c>
     </row>
@@ -13394,7 +13414,7 @@
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>Fresh org: dashed 'Nothing in flight.' empty state, 'n=0 · every band still hatched' ground-truth empty, calibrated KPI permanently withheld ('— CALIBRATED ESTIMATES · NO DATA'), start-here grid with drop/browse CAD + guided example + Design Studio link. Induced abort of cost-decisions + machine-inventory → role=alert 'Couldn't load records, machine inventory… nothing is being presented as an empty result' with 'Retry organization data'; KPIs read 'RETRY NEEDED'; retry restores the data and clears the flags.</t>
+          <t>Fresh org: dashed empty states, 'n=0 · every band still hatched' ground truth, calibrated KPI permanently withheld ('— CALIBRATED ESTIMATES · NO DATA'), start-here grid with drop/browse CAD + guided example + Design Studio link. Aborting cost-decisions + machine-inventory -&gt; role=alert "Couldn't load records, machine inventory... nothing is being presented as an empty result" with 'Retry organization data'; KPIs read 'RETRY NEEDED'; retry restores the data.</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13468,7 @@
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>H/V/P/R/G/M/T/C hotkey nav confirmed 8/8; '?' opens the shortcuts sheet; Ctrl+K toggles the palette and Esc closes it; typing in the palette input never triggers nav; ?screen=records deep-links; rate dot hollow on a fresh org and fills once a machine declares an hourly rate ('Your shop rates are bound · ● SHOP'); mobile &lt;select&gt; replaces tabs at 700px.</t>
+          <t>Hotkeys 8/8 (h/v/p/r/g/m/t/c -&gt; home/verify/catalog/records/programs/machines/triage/calibration, verified via the workspace-section select value); '?' opens the shortcuts sheet; Ctrl+K opens the palette, typing in it never triggers nav, Esc closes; ?screen=records deep-links; rate dot hollow on a rate-less org ('no shop rate bound yet') and filled once an $85/hr machine exists ('Your shop rates are bound · ● SHOP'); mobile select replaces tabs at 700px.</t>
         </is>
       </c>
     </row>
